--- a/pipeline/credit_rating/output/xhtn_tong_hop_20260918.xlsx
+++ b/pipeline/credit_rating/output/xhtn_tong_hop_20260918.xlsx
@@ -685,7 +685,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1011,7 +1011,7 @@
       <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -1099,7 +1099,7 @@
       <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -1219,7 +1219,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -1555,7 +1555,7 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:38</t>
+          <t>2026-09-18 08:13:51</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -1665,7 +1665,7 @@
       <c r="AD11" t="inlineStr"/>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:38</t>
+          <t>2026-09-18 08:13:51</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:38</t>
+          <t>2026-09-18 08:13:51</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -1891,7 +1891,7 @@
       <c r="AD13" t="inlineStr"/>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:38</t>
+          <t>2026-09-18 08:13:51</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -2019,7 +2019,7 @@
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -2133,7 +2133,7 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -2247,7 +2247,7 @@
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -2367,7 +2367,7 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -2595,7 +2595,7 @@
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -2709,7 +2709,7 @@
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -2825,7 +2825,7 @@
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:38</t>
+          <t>2026-09-18 08:13:51</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -2939,7 +2939,7 @@
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -3049,7 +3049,7 @@
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -3177,7 +3177,7 @@
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
@@ -3291,7 +3291,7 @@
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
@@ -3411,7 +3411,7 @@
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
@@ -3525,7 +3525,7 @@
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
@@ -3635,7 +3635,7 @@
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:38</t>
+          <t>2026-09-18 08:13:51</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
@@ -3861,7 +3861,7 @@
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
@@ -3971,7 +3971,7 @@
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF31" t="inlineStr">
@@ -4095,7 +4095,7 @@
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
@@ -4205,7 +4205,7 @@
       </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF33" t="inlineStr">
@@ -4315,7 +4315,7 @@
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF34" t="inlineStr">
@@ -4425,7 +4425,7 @@
       </c>
       <c r="AE35" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF35" t="inlineStr">
@@ -4525,7 +4525,7 @@
       </c>
       <c r="AE36" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF36" t="inlineStr">
@@ -4635,7 +4635,7 @@
       </c>
       <c r="AE37" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF37" t="inlineStr">
@@ -4745,7 +4745,7 @@
       </c>
       <c r="AE38" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF38" t="inlineStr">
@@ -4855,7 +4855,7 @@
       </c>
       <c r="AE39" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF39" t="inlineStr">
@@ -4987,7 +4987,7 @@
       </c>
       <c r="AE40" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="AF40" t="inlineStr">
@@ -5115,7 +5115,7 @@
       </c>
       <c r="AE41" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="AF41" t="inlineStr">
@@ -5247,7 +5247,7 @@
       </c>
       <c r="AE42" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="AF42" t="inlineStr">
@@ -5375,7 +5375,7 @@
       </c>
       <c r="AE43" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="AF43" t="inlineStr">
@@ -5485,7 +5485,7 @@
       </c>
       <c r="AE44" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF44" t="inlineStr">
@@ -5597,7 +5597,7 @@
       </c>
       <c r="AE45" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF45" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="AE46" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF46" t="inlineStr">
@@ -5827,7 +5827,7 @@
       </c>
       <c r="AE47" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF47" t="inlineStr">
@@ -5943,7 +5943,7 @@
       </c>
       <c r="AE48" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF48" t="inlineStr">
@@ -6043,7 +6043,7 @@
       </c>
       <c r="AE49" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF49" t="inlineStr">
@@ -6157,7 +6157,7 @@
       </c>
       <c r="AE50" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF50" t="inlineStr">
@@ -6273,7 +6273,7 @@
       </c>
       <c r="AE51" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:38</t>
+          <t>2026-09-18 08:13:51</t>
         </is>
       </c>
       <c r="AF51" t="inlineStr">
@@ -6383,7 +6383,7 @@
       </c>
       <c r="AE52" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF52" t="inlineStr">
@@ -6497,7 +6497,7 @@
       </c>
       <c r="AE53" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF53" t="inlineStr">
@@ -6611,7 +6611,7 @@
       </c>
       <c r="AE54" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF54" t="inlineStr">
@@ -6739,7 +6739,7 @@
       </c>
       <c r="AE55" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="AF55" t="inlineStr">
@@ -6855,7 +6855,7 @@
       </c>
       <c r="AE56" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF56" t="inlineStr">
@@ -6951,7 +6951,7 @@
       </c>
       <c r="AE57" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF57" t="inlineStr">
@@ -7061,7 +7061,7 @@
       </c>
       <c r="AE58" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF58" t="inlineStr">
@@ -7161,7 +7161,7 @@
       </c>
       <c r="AE59" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF59" t="inlineStr">
@@ -7275,7 +7275,7 @@
       </c>
       <c r="AE60" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF60" t="inlineStr">
@@ -7389,7 +7389,7 @@
       </c>
       <c r="AE61" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF61" t="inlineStr">
@@ -7489,7 +7489,7 @@
       </c>
       <c r="AE62" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF62" t="inlineStr">
@@ -7603,7 +7603,7 @@
       </c>
       <c r="AE63" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:22</t>
+          <t>2026-09-18 08:13:36</t>
         </is>
       </c>
       <c r="AF63" t="inlineStr">
@@ -7713,7 +7713,7 @@
       </c>
       <c r="AE64" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF64" t="inlineStr">
@@ -7827,7 +7827,7 @@
       </c>
       <c r="AE65" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF65" t="inlineStr">
@@ -7941,7 +7941,7 @@
       </c>
       <c r="AE66" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF66" t="inlineStr">
@@ -8051,7 +8051,7 @@
       </c>
       <c r="AE67" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF67" t="inlineStr">
@@ -8165,7 +8165,7 @@
       </c>
       <c r="AE68" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF68" t="inlineStr">
@@ -8279,7 +8279,7 @@
       </c>
       <c r="AE69" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:22</t>
+          <t>2026-09-18 08:13:36</t>
         </is>
       </c>
       <c r="AF69" t="inlineStr">
@@ -8393,7 +8393,7 @@
       </c>
       <c r="AE70" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:22</t>
+          <t>2026-09-18 08:13:36</t>
         </is>
       </c>
       <c r="AF70" t="inlineStr">
@@ -8517,7 +8517,7 @@
       </c>
       <c r="AE71" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:24</t>
+          <t>2026-09-18 08:13:38</t>
         </is>
       </c>
       <c r="AF71" t="inlineStr">
@@ -8627,7 +8627,7 @@
       </c>
       <c r="AE72" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF72" t="inlineStr">
@@ -8741,7 +8741,7 @@
       </c>
       <c r="AE73" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF73" t="inlineStr">
@@ -8855,7 +8855,7 @@
       </c>
       <c r="AE74" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF74" t="inlineStr">
@@ -8969,7 +8969,7 @@
       </c>
       <c r="AE75" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF75" t="inlineStr">
@@ -9081,7 +9081,7 @@
       </c>
       <c r="AE76" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF76" t="inlineStr">
@@ -9197,7 +9197,7 @@
       </c>
       <c r="AE77" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:38</t>
+          <t>2026-09-18 08:13:51</t>
         </is>
       </c>
       <c r="AF77" t="inlineStr">
@@ -9307,7 +9307,7 @@
       </c>
       <c r="AE78" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF78" t="inlineStr">
@@ -9417,7 +9417,7 @@
       </c>
       <c r="AE79" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF79" t="inlineStr">
@@ -9535,7 +9535,7 @@
       </c>
       <c r="AE80" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:22</t>
+          <t>2026-09-18 08:13:36</t>
         </is>
       </c>
       <c r="AF80" t="inlineStr">
@@ -9659,7 +9659,7 @@
       </c>
       <c r="AE81" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="AF81" t="inlineStr">
@@ -9779,7 +9779,7 @@
       </c>
       <c r="AE82" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="AF82" t="inlineStr">
@@ -9899,7 +9899,7 @@
       </c>
       <c r="AE83" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="AF83" t="inlineStr">
@@ -10031,7 +10031,7 @@
       </c>
       <c r="AE84" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="AF84" t="inlineStr">
@@ -10155,7 +10155,7 @@
       </c>
       <c r="AE85" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF85" t="inlineStr">
@@ -10279,7 +10279,7 @@
       </c>
       <c r="AE86" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF86" t="inlineStr">
@@ -10379,7 +10379,7 @@
       </c>
       <c r="AE87" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF87" t="inlineStr">
@@ -10499,7 +10499,7 @@
       </c>
       <c r="AE88" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="AF88" t="inlineStr">
@@ -10627,7 +10627,7 @@
       </c>
       <c r="AE89" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="AF89" t="inlineStr">
@@ -10741,7 +10741,7 @@
       </c>
       <c r="AE90" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF90" t="inlineStr">
@@ -10855,7 +10855,7 @@
       </c>
       <c r="AE91" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF91" t="inlineStr">
@@ -10969,7 +10969,7 @@
       </c>
       <c r="AE92" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF92" t="inlineStr">
@@ -11079,7 +11079,7 @@
       </c>
       <c r="AE93" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF93" t="inlineStr">
@@ -11193,7 +11193,7 @@
       </c>
       <c r="AE94" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF94" t="inlineStr">
@@ -11307,7 +11307,7 @@
       </c>
       <c r="AE95" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF95" t="inlineStr">
@@ -11421,7 +11421,7 @@
       </c>
       <c r="AE96" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF96" t="inlineStr">
@@ -11535,7 +11535,7 @@
       </c>
       <c r="AE97" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF97" t="inlineStr">
@@ -11655,7 +11655,7 @@
       </c>
       <c r="AE98" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="AF98" t="inlineStr">
@@ -11771,7 +11771,7 @@
       </c>
       <c r="AE99" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:38</t>
+          <t>2026-09-18 08:13:51</t>
         </is>
       </c>
       <c r="AF99" t="inlineStr">
@@ -11881,7 +11881,7 @@
       </c>
       <c r="AE100" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF100" t="inlineStr">
@@ -12001,7 +12001,7 @@
       </c>
       <c r="AE101" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="AF101" t="inlineStr">
@@ -12133,7 +12133,7 @@
       </c>
       <c r="AE102" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="AF102" t="inlineStr">
@@ -12261,7 +12261,7 @@
       </c>
       <c r="AE103" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="AF103" t="inlineStr">
@@ -12373,7 +12373,7 @@
       </c>
       <c r="AE104" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF104" t="inlineStr">
@@ -12483,7 +12483,7 @@
       </c>
       <c r="AE105" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF105" t="inlineStr">
@@ -12593,7 +12593,7 @@
       </c>
       <c r="AE106" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF106" t="inlineStr">
@@ -12703,7 +12703,7 @@
       </c>
       <c r="AE107" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF107" t="inlineStr">
@@ -12817,7 +12817,7 @@
       </c>
       <c r="AE108" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:22</t>
+          <t>2026-09-18 08:13:36</t>
         </is>
       </c>
       <c r="AF108" t="inlineStr">
@@ -12929,7 +12929,7 @@
       </c>
       <c r="AE109" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF109" t="inlineStr">
@@ -13045,7 +13045,7 @@
       </c>
       <c r="AE110" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF110" t="inlineStr">
@@ -13167,7 +13167,7 @@
       <c r="AD111" t="inlineStr"/>
       <c r="AE111" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="AF111" t="inlineStr">
@@ -13279,7 +13279,7 @@
       </c>
       <c r="AE112" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:24</t>
+          <t>2026-09-18 08:13:38</t>
         </is>
       </c>
       <c r="AF112" t="inlineStr">
@@ -13407,7 +13407,7 @@
       </c>
       <c r="AE113" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="AF113" t="inlineStr">
@@ -13527,7 +13527,7 @@
       </c>
       <c r="AE114" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF114" t="inlineStr">
@@ -13647,7 +13647,7 @@
       </c>
       <c r="AE115" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF115" t="inlineStr">
@@ -13757,7 +13757,7 @@
       </c>
       <c r="AE116" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF116" t="inlineStr">
@@ -13873,7 +13873,7 @@
       </c>
       <c r="AE117" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF117" t="inlineStr">
@@ -13985,7 +13985,7 @@
       </c>
       <c r="AE118" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF118" t="inlineStr">
@@ -14095,7 +14095,7 @@
       </c>
       <c r="AE119" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF119" t="inlineStr">
@@ -14205,7 +14205,7 @@
       </c>
       <c r="AE120" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF120" t="inlineStr">
@@ -14329,7 +14329,7 @@
       </c>
       <c r="AE121" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF121" t="inlineStr">
@@ -14445,7 +14445,7 @@
       </c>
       <c r="AE122" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF122" t="inlineStr">
@@ -14565,7 +14565,7 @@
       </c>
       <c r="AE123" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="AF123" t="inlineStr">
@@ -14677,7 +14677,7 @@
       </c>
       <c r="AE124" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF124" t="inlineStr">
@@ -14797,7 +14797,7 @@
       </c>
       <c r="AE125" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF125" t="inlineStr">
@@ -14907,7 +14907,7 @@
       </c>
       <c r="AE126" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF126" t="inlineStr">
@@ -15017,7 +15017,7 @@
       </c>
       <c r="AE127" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF127" t="inlineStr">
@@ -15137,7 +15137,7 @@
       </c>
       <c r="AE128" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="AF128" t="inlineStr">
@@ -15251,7 +15251,7 @@
       </c>
       <c r="AE129" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF129" t="inlineStr">
@@ -15365,7 +15365,7 @@
       </c>
       <c r="AE130" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF130" t="inlineStr">
@@ -15485,7 +15485,7 @@
       </c>
       <c r="AE131" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="AF131" t="inlineStr">
@@ -15595,7 +15595,7 @@
       </c>
       <c r="AE132" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF132" t="inlineStr">
@@ -15711,7 +15711,7 @@
       </c>
       <c r="AE133" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF133" t="inlineStr">
@@ -15823,7 +15823,7 @@
       </c>
       <c r="AE134" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:24</t>
+          <t>2026-09-18 08:13:38</t>
         </is>
       </c>
       <c r="AF134" t="inlineStr">
@@ -15935,7 +15935,7 @@
       </c>
       <c r="AE135" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF135" t="inlineStr">
@@ -16049,7 +16049,7 @@
       </c>
       <c r="AE136" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF136" t="inlineStr">
@@ -16163,7 +16163,7 @@
       </c>
       <c r="AE137" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF137" t="inlineStr">
@@ -16277,7 +16277,7 @@
       </c>
       <c r="AE138" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:22</t>
+          <t>2026-09-18 08:13:36</t>
         </is>
       </c>
       <c r="AF138" t="inlineStr">
@@ -16387,7 +16387,7 @@
       </c>
       <c r="AE139" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF139" t="inlineStr">
@@ -16497,7 +16497,7 @@
       </c>
       <c r="AE140" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF140" t="inlineStr">
@@ -16607,7 +16607,7 @@
       </c>
       <c r="AE141" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF141" t="inlineStr">
@@ -16721,7 +16721,7 @@
       </c>
       <c r="AE142" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF142" t="inlineStr">
@@ -16835,7 +16835,7 @@
       </c>
       <c r="AE143" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF143" t="inlineStr">
@@ -16963,7 +16963,7 @@
       </c>
       <c r="AE144" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="AF144" t="inlineStr">
@@ -17091,7 +17091,7 @@
       </c>
       <c r="AE145" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="AF145" t="inlineStr">
@@ -17201,7 +17201,7 @@
       </c>
       <c r="AE146" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF146" t="inlineStr">
@@ -17311,7 +17311,7 @@
       </c>
       <c r="AE147" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF147" t="inlineStr">
@@ -17431,7 +17431,7 @@
       </c>
       <c r="AE148" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="AF148" t="inlineStr">
@@ -17545,7 +17545,7 @@
       </c>
       <c r="AE149" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF149" t="inlineStr">
@@ -17655,7 +17655,7 @@
       </c>
       <c r="AE150" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF150" t="inlineStr">
@@ -17783,7 +17783,7 @@
       </c>
       <c r="AE151" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="AF151" t="inlineStr">
@@ -17905,7 +17905,7 @@
       <c r="AD152" t="inlineStr"/>
       <c r="AE152" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="AF152" t="inlineStr">
@@ -18033,7 +18033,7 @@
       </c>
       <c r="AE153" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="AF153" t="inlineStr">
@@ -18149,7 +18149,7 @@
       </c>
       <c r="AE154" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:38</t>
+          <t>2026-09-18 08:13:51</t>
         </is>
       </c>
       <c r="AF154" t="inlineStr">
@@ -18277,7 +18277,7 @@
       </c>
       <c r="AE155" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="AF155" t="inlineStr">
@@ -18409,7 +18409,7 @@
       </c>
       <c r="AE156" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="AF156" t="inlineStr">
@@ -18523,7 +18523,7 @@
       </c>
       <c r="AE157" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF157" t="inlineStr">
@@ -18645,7 +18645,7 @@
       <c r="AD158" t="inlineStr"/>
       <c r="AE158" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="AF158" t="inlineStr">
@@ -18757,7 +18757,7 @@
       </c>
       <c r="AE159" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF159" t="inlineStr">
@@ -18857,7 +18857,7 @@
       </c>
       <c r="AE160" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF160" t="inlineStr">
@@ -18967,7 +18967,7 @@
       </c>
       <c r="AE161" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF161" t="inlineStr">
@@ -19083,7 +19083,7 @@
       </c>
       <c r="AE162" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF162" t="inlineStr">
@@ -19199,7 +19199,7 @@
       </c>
       <c r="AE163" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF163" t="inlineStr">
@@ -19327,7 +19327,7 @@
       </c>
       <c r="AE164" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="AF164" t="inlineStr">
@@ -19437,7 +19437,7 @@
       </c>
       <c r="AE165" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF165" t="inlineStr">
@@ -19551,7 +19551,7 @@
       </c>
       <c r="AE166" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF166" t="inlineStr">
@@ -19665,7 +19665,7 @@
       </c>
       <c r="AE167" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF167" t="inlineStr">
@@ -19779,7 +19779,7 @@
       </c>
       <c r="AE168" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF168" t="inlineStr">
@@ -19889,7 +19889,7 @@
       </c>
       <c r="AE169" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF169" t="inlineStr">
@@ -20003,7 +20003,7 @@
       </c>
       <c r="AE170" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF170" t="inlineStr">
@@ -20113,7 +20113,7 @@
       </c>
       <c r="AE171" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF171" t="inlineStr">
@@ -20225,7 +20225,7 @@
       </c>
       <c r="AE172" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF172" t="inlineStr">
@@ -20341,7 +20341,7 @@
       </c>
       <c r="AE173" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:38</t>
+          <t>2026-09-18 08:13:51</t>
         </is>
       </c>
       <c r="AF173" t="inlineStr">
@@ -20457,7 +20457,7 @@
       </c>
       <c r="AE174" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF174" t="inlineStr">
@@ -20569,7 +20569,7 @@
       </c>
       <c r="AE175" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF175" t="inlineStr">
@@ -20681,7 +20681,7 @@
       </c>
       <c r="AE176" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF176" t="inlineStr">
@@ -20809,7 +20809,7 @@
       </c>
       <c r="AE177" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:24</t>
+          <t>2026-09-18 08:13:38</t>
         </is>
       </c>
       <c r="AF177" t="inlineStr">
@@ -20919,7 +20919,7 @@
       </c>
       <c r="AE178" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF178" t="inlineStr">
@@ -21039,7 +21039,7 @@
       </c>
       <c r="AE179" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="AF179" t="inlineStr">
@@ -21161,7 +21161,7 @@
       <c r="AD180" t="inlineStr"/>
       <c r="AE180" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="AF180" t="inlineStr">
@@ -21287,7 +21287,7 @@
       <c r="AD181" t="inlineStr"/>
       <c r="AE181" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="AF181" t="inlineStr">
@@ -21413,7 +21413,7 @@
       <c r="AD182" t="inlineStr"/>
       <c r="AE182" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="AF182" t="inlineStr">
@@ -21529,7 +21529,7 @@
       </c>
       <c r="AE183" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:38</t>
+          <t>2026-09-18 08:13:51</t>
         </is>
       </c>
       <c r="AF183" t="inlineStr">
@@ -21643,7 +21643,7 @@
       </c>
       <c r="AE184" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF184" t="inlineStr">
@@ -21757,7 +21757,7 @@
       </c>
       <c r="AE185" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF185" t="inlineStr">
@@ -21871,7 +21871,7 @@
       </c>
       <c r="AE186" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF186" t="inlineStr">
@@ -21991,7 +21991,7 @@
       </c>
       <c r="AE187" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="AF187" t="inlineStr">
@@ -22111,7 +22111,7 @@
       </c>
       <c r="AE188" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="AF188" t="inlineStr">
@@ -22221,7 +22221,7 @@
       </c>
       <c r="AE189" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF189" t="inlineStr">
@@ -22331,7 +22331,7 @@
       </c>
       <c r="AE190" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF190" t="inlineStr">
@@ -22441,7 +22441,7 @@
       </c>
       <c r="AE191" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF191" t="inlineStr">
@@ -22557,7 +22557,7 @@
       </c>
       <c r="AE192" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF192" t="inlineStr">
@@ -22685,7 +22685,7 @@
       </c>
       <c r="AE193" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="AF193" t="inlineStr">
@@ -22797,7 +22797,7 @@
       </c>
       <c r="AE194" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF194" t="inlineStr">
@@ -22909,7 +22909,7 @@
       </c>
       <c r="AE195" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF195" t="inlineStr">
@@ -23027,7 +23027,7 @@
       </c>
       <c r="AE196" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:22</t>
+          <t>2026-09-18 08:13:36</t>
         </is>
       </c>
       <c r="AF196" t="inlineStr">
@@ -23137,7 +23137,7 @@
       </c>
       <c r="AE197" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF197" t="inlineStr">
@@ -23247,7 +23247,7 @@
       </c>
       <c r="AE198" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF198" t="inlineStr">
@@ -23359,7 +23359,7 @@
       </c>
       <c r="AE199" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF199" t="inlineStr">
@@ -23469,7 +23469,7 @@
       </c>
       <c r="AE200" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF200" t="inlineStr">
@@ -23589,7 +23589,7 @@
       </c>
       <c r="AE201" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="AF201" t="inlineStr">
@@ -23705,7 +23705,7 @@
       </c>
       <c r="AE202" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF202" t="inlineStr">
@@ -23821,7 +23821,7 @@
       </c>
       <c r="AE203" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF203" t="inlineStr">
@@ -23949,7 +23949,7 @@
       </c>
       <c r="AE204" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="AF204" t="inlineStr">
@@ -24061,7 +24061,7 @@
       </c>
       <c r="AE205" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF205" t="inlineStr">
@@ -24173,7 +24173,7 @@
       </c>
       <c r="AE206" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF206" t="inlineStr">
@@ -24285,7 +24285,7 @@
       </c>
       <c r="AE207" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF207" t="inlineStr">
@@ -24401,7 +24401,7 @@
       </c>
       <c r="AE208" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF208" t="inlineStr">
@@ -24511,7 +24511,7 @@
       </c>
       <c r="AE209" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF209" t="inlineStr">
@@ -24631,7 +24631,7 @@
       </c>
       <c r="AE210" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="AF210" t="inlineStr">
@@ -24741,7 +24741,7 @@
       </c>
       <c r="AE211" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF211" t="inlineStr">
@@ -24861,7 +24861,7 @@
       </c>
       <c r="AE212" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="AF212" t="inlineStr">
@@ -24971,7 +24971,7 @@
       </c>
       <c r="AE213" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF213" t="inlineStr">
@@ -25085,7 +25085,7 @@
       </c>
       <c r="AE214" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:22</t>
+          <t>2026-09-18 08:13:36</t>
         </is>
       </c>
       <c r="AF214" t="inlineStr">
@@ -25195,7 +25195,7 @@
       </c>
       <c r="AE215" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF215" t="inlineStr">
@@ -25305,7 +25305,7 @@
       </c>
       <c r="AE216" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF216" t="inlineStr">
@@ -25419,7 +25419,7 @@
       </c>
       <c r="AE217" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF217" t="inlineStr">
@@ -25529,7 +25529,7 @@
       </c>
       <c r="AE218" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF218" t="inlineStr">
@@ -25641,7 +25641,7 @@
       </c>
       <c r="AE219" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF219" t="inlineStr">
@@ -25751,7 +25751,7 @@
       </c>
       <c r="AE220" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF220" t="inlineStr">
@@ -25871,7 +25871,7 @@
       </c>
       <c r="AE221" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="AF221" t="inlineStr">
@@ -25983,7 +25983,7 @@
       </c>
       <c r="AE222" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF222" t="inlineStr">
@@ -26093,7 +26093,7 @@
       </c>
       <c r="AE223" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF223" t="inlineStr">
@@ -26217,7 +26217,7 @@
       </c>
       <c r="AE224" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:24</t>
+          <t>2026-09-18 08:13:38</t>
         </is>
       </c>
       <c r="AF224" t="inlineStr">
@@ -26341,7 +26341,7 @@
       </c>
       <c r="AE225" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:24</t>
+          <t>2026-09-18 08:13:38</t>
         </is>
       </c>
       <c r="AF225" t="inlineStr">
@@ -26451,7 +26451,7 @@
       </c>
       <c r="AE226" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF226" t="inlineStr">
@@ -26561,7 +26561,7 @@
       </c>
       <c r="AE227" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF227" t="inlineStr">
@@ -26671,7 +26671,7 @@
       </c>
       <c r="AE228" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF228" t="inlineStr">
@@ -26783,7 +26783,7 @@
       </c>
       <c r="AE229" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF229" t="inlineStr">
@@ -26893,7 +26893,7 @@
       </c>
       <c r="AE230" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF230" t="inlineStr">
@@ -27003,7 +27003,7 @@
       </c>
       <c r="AE231" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF231" t="inlineStr">
@@ -27131,7 +27131,7 @@
       </c>
       <c r="AE232" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="AF232" t="inlineStr">
@@ -27237,7 +27237,7 @@
       </c>
       <c r="AE233" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF233" t="inlineStr">
@@ -27349,7 +27349,7 @@
       </c>
       <c r="AE234" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF234" t="inlineStr">
@@ -27465,7 +27465,7 @@
       </c>
       <c r="AE235" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:38</t>
+          <t>2026-09-18 08:13:51</t>
         </is>
       </c>
       <c r="AF235" t="inlineStr">
@@ -27581,7 +27581,7 @@
       </c>
       <c r="AE236" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:38</t>
+          <t>2026-09-18 08:13:51</t>
         </is>
       </c>
       <c r="AF236" t="inlineStr">
@@ -27691,7 +27691,7 @@
       </c>
       <c r="AE237" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF237" t="inlineStr">
@@ -27801,7 +27801,7 @@
       </c>
       <c r="AE238" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF238" t="inlineStr">
@@ -27917,7 +27917,7 @@
       </c>
       <c r="AE239" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:38</t>
+          <t>2026-09-18 08:13:51</t>
         </is>
       </c>
       <c r="AF239" t="inlineStr">
@@ -28033,7 +28033,7 @@
       </c>
       <c r="AE240" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:38</t>
+          <t>2026-09-18 08:13:51</t>
         </is>
       </c>
       <c r="AF240" t="inlineStr">
@@ -28143,7 +28143,7 @@
       </c>
       <c r="AE241" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF241" t="inlineStr">
@@ -28259,7 +28259,7 @@
       </c>
       <c r="AE242" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:38</t>
+          <t>2026-09-18 08:13:51</t>
         </is>
       </c>
       <c r="AF242" t="inlineStr">
@@ -28375,7 +28375,7 @@
       </c>
       <c r="AE243" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:38</t>
+          <t>2026-09-18 08:13:51</t>
         </is>
       </c>
       <c r="AF243" t="inlineStr">
@@ -28485,7 +28485,7 @@
       </c>
       <c r="AE244" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF244" t="inlineStr">
@@ -28595,7 +28595,7 @@
       </c>
       <c r="AE245" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF245" t="inlineStr">
@@ -28705,7 +28705,7 @@
       </c>
       <c r="AE246" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF246" t="inlineStr">
@@ -28805,7 +28805,7 @@
       </c>
       <c r="AE247" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF247" t="inlineStr">
@@ -28921,7 +28921,7 @@
       </c>
       <c r="AE248" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:38</t>
+          <t>2026-09-18 08:13:51</t>
         </is>
       </c>
       <c r="AF248" t="inlineStr">
@@ -29031,7 +29031,7 @@
       </c>
       <c r="AE249" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF249" t="inlineStr">
@@ -29143,7 +29143,7 @@
       </c>
       <c r="AE250" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF250" t="inlineStr">
@@ -29253,7 +29253,7 @@
       </c>
       <c r="AE251" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF251" t="inlineStr">
@@ -29373,7 +29373,7 @@
       </c>
       <c r="AE252" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="AF252" t="inlineStr">
@@ -29485,7 +29485,7 @@
       </c>
       <c r="AE253" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF253" t="inlineStr">
@@ -29595,7 +29595,7 @@
       </c>
       <c r="AE254" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF254" t="inlineStr">
@@ -29707,7 +29707,7 @@
       </c>
       <c r="AE255" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF255" t="inlineStr">
@@ -29823,7 +29823,7 @@
       </c>
       <c r="AE256" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF256" t="inlineStr">
@@ -29935,7 +29935,7 @@
       </c>
       <c r="AE257" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF257" t="inlineStr">
@@ -30045,7 +30045,7 @@
       </c>
       <c r="AE258" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF258" t="inlineStr">
@@ -30161,7 +30161,7 @@
       </c>
       <c r="AE259" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF259" t="inlineStr">
@@ -30271,7 +30271,7 @@
       </c>
       <c r="AE260" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF260" t="inlineStr">
@@ -30397,7 +30397,7 @@
       <c r="AD261" t="inlineStr"/>
       <c r="AE261" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="AF261" t="inlineStr">
@@ -30525,7 +30525,7 @@
       </c>
       <c r="AE262" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="AF262" t="inlineStr">
@@ -30637,7 +30637,7 @@
       </c>
       <c r="AE263" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF263" t="inlineStr">
@@ -30737,7 +30737,7 @@
       </c>
       <c r="AE264" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF264" t="inlineStr">
@@ -30837,7 +30837,7 @@
       </c>
       <c r="AE265" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF265" t="inlineStr">
@@ -30951,7 +30951,7 @@
       </c>
       <c r="AE266" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF266" t="inlineStr">
@@ -31065,7 +31065,7 @@
       </c>
       <c r="AE267" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF267" t="inlineStr">
@@ -31165,7 +31165,7 @@
       </c>
       <c r="AE268" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF268" t="inlineStr">
@@ -31285,7 +31285,7 @@
       </c>
       <c r="AE269" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="AF269" t="inlineStr">
@@ -31397,7 +31397,7 @@
       </c>
       <c r="AE270" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF270" t="inlineStr">
@@ -31509,7 +31509,7 @@
       </c>
       <c r="AE271" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF271" t="inlineStr">
@@ -31623,7 +31623,7 @@
       </c>
       <c r="AE272" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF272" t="inlineStr">
@@ -31737,7 +31737,7 @@
       </c>
       <c r="AE273" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:22</t>
+          <t>2026-09-18 08:13:36</t>
         </is>
       </c>
       <c r="AF273" t="inlineStr">
@@ -31851,7 +31851,7 @@
       </c>
       <c r="AE274" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:22</t>
+          <t>2026-09-18 08:13:36</t>
         </is>
       </c>
       <c r="AF274" t="inlineStr">
@@ -31983,7 +31983,7 @@
       </c>
       <c r="AE275" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="AF275" t="inlineStr">
@@ -32111,7 +32111,7 @@
       </c>
       <c r="AE276" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="AF276" t="inlineStr">
@@ -32239,7 +32239,7 @@
       </c>
       <c r="AE277" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="AF277" t="inlineStr">
@@ -32367,7 +32367,7 @@
       </c>
       <c r="AE278" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="AF278" t="inlineStr">
@@ -32479,7 +32479,7 @@
       </c>
       <c r="AE279" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF279" t="inlineStr">
@@ -32591,7 +32591,7 @@
       </c>
       <c r="AE280" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF280" t="inlineStr">
@@ -32701,7 +32701,7 @@
       </c>
       <c r="AE281" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF281" t="inlineStr">
@@ -32811,7 +32811,7 @@
       </c>
       <c r="AE282" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF282" t="inlineStr">
@@ -32939,7 +32939,7 @@
       </c>
       <c r="AE283" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="AF283" t="inlineStr">
@@ -33049,7 +33049,7 @@
       </c>
       <c r="AE284" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF284" t="inlineStr">
@@ -33177,7 +33177,7 @@
       </c>
       <c r="AE285" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="AF285" t="inlineStr">
@@ -33289,7 +33289,7 @@
       </c>
       <c r="AE286" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF286" t="inlineStr">
@@ -33401,7 +33401,7 @@
       </c>
       <c r="AE287" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF287" t="inlineStr">
@@ -33511,7 +33511,7 @@
       </c>
       <c r="AE288" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF288" t="inlineStr">
@@ -33631,7 +33631,7 @@
       </c>
       <c r="AE289" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="AF289" t="inlineStr">
@@ -33755,7 +33755,7 @@
       </c>
       <c r="AE290" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="AF290" t="inlineStr">
@@ -33879,7 +33879,7 @@
       </c>
       <c r="AE291" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="AF291" t="inlineStr">
@@ -34003,7 +34003,7 @@
       </c>
       <c r="AE292" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="AF292" t="inlineStr">
@@ -34115,7 +34115,7 @@
       </c>
       <c r="AE293" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF293" t="inlineStr">
@@ -34231,7 +34231,7 @@
       </c>
       <c r="AE294" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF294" t="inlineStr">
@@ -34343,7 +34343,7 @@
       </c>
       <c r="AE295" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:24</t>
+          <t>2026-09-18 08:13:38</t>
         </is>
       </c>
       <c r="AF295" t="inlineStr">
@@ -34471,7 +34471,7 @@
       </c>
       <c r="AE296" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:24</t>
+          <t>2026-09-18 08:13:38</t>
         </is>
       </c>
       <c r="AF296" t="inlineStr">
@@ -34599,7 +34599,7 @@
       </c>
       <c r="AE297" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="AF297" t="inlineStr">
@@ -34711,7 +34711,7 @@
       </c>
       <c r="AE298" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF298" t="inlineStr">
@@ -34823,7 +34823,7 @@
       </c>
       <c r="AE299" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF299" t="inlineStr">
@@ -34933,7 +34933,7 @@
       </c>
       <c r="AE300" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF300" t="inlineStr">
@@ -35043,7 +35043,7 @@
       </c>
       <c r="AE301" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF301" t="inlineStr">
@@ -35159,7 +35159,7 @@
       </c>
       <c r="AE302" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF302" t="inlineStr">
@@ -35271,7 +35271,7 @@
       </c>
       <c r="AE303" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF303" t="inlineStr">
@@ -35391,7 +35391,7 @@
       </c>
       <c r="AE304" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="AF304" t="inlineStr">
@@ -35519,7 +35519,7 @@
       </c>
       <c r="AE305" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="AF305" t="inlineStr">
@@ -35635,7 +35635,7 @@
       </c>
       <c r="AE306" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF306" t="inlineStr">
@@ -35735,7 +35735,7 @@
       </c>
       <c r="AE307" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF307" t="inlineStr">
@@ -35847,7 +35847,7 @@
       </c>
       <c r="AE308" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF308" t="inlineStr">
@@ -35975,7 +35975,7 @@
       </c>
       <c r="AE309" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="AF309" t="inlineStr">
@@ -36099,7 +36099,7 @@
       </c>
       <c r="AE310" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:24</t>
+          <t>2026-09-18 08:13:38</t>
         </is>
       </c>
       <c r="AF310" t="inlineStr">
@@ -36211,7 +36211,7 @@
       </c>
       <c r="AE311" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF311" t="inlineStr">
@@ -36321,7 +36321,7 @@
       </c>
       <c r="AE312" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF312" t="inlineStr">
@@ -36431,7 +36431,7 @@
       </c>
       <c r="AE313" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF313" t="inlineStr">
@@ -36541,7 +36541,7 @@
       </c>
       <c r="AE314" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF314" t="inlineStr">
@@ -36651,7 +36651,7 @@
       </c>
       <c r="AE315" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF315" t="inlineStr">
@@ -36771,7 +36771,7 @@
       </c>
       <c r="AE316" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="AF316" t="inlineStr">
@@ -36881,7 +36881,7 @@
       </c>
       <c r="AE317" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF317" t="inlineStr">
@@ -36991,7 +36991,7 @@
       </c>
       <c r="AE318" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF318" t="inlineStr">
@@ -37101,7 +37101,7 @@
       </c>
       <c r="AE319" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF319" t="inlineStr">
@@ -37221,7 +37221,7 @@
       </c>
       <c r="AE320" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="AF320" t="inlineStr">
@@ -37341,7 +37341,7 @@
       </c>
       <c r="AE321" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="AF321" t="inlineStr">
@@ -37461,7 +37461,7 @@
       </c>
       <c r="AE322" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="AF322" t="inlineStr">
@@ -37581,7 +37581,7 @@
       </c>
       <c r="AE323" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="AF323" t="inlineStr">
@@ -37697,7 +37697,7 @@
       </c>
       <c r="AE324" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:38</t>
+          <t>2026-09-18 08:13:51</t>
         </is>
       </c>
       <c r="AF324" t="inlineStr">
@@ -37813,7 +37813,7 @@
       </c>
       <c r="AE325" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:38</t>
+          <t>2026-09-18 08:13:51</t>
         </is>
       </c>
       <c r="AF325" t="inlineStr">
@@ -37929,7 +37929,7 @@
       </c>
       <c r="AE326" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:38</t>
+          <t>2026-09-18 08:13:51</t>
         </is>
       </c>
       <c r="AF326" t="inlineStr">
@@ -38041,7 +38041,7 @@
       </c>
       <c r="AE327" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF327" t="inlineStr">
@@ -38157,7 +38157,7 @@
       </c>
       <c r="AE328" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:38</t>
+          <t>2026-09-18 08:13:51</t>
         </is>
       </c>
       <c r="AF328" t="inlineStr">
@@ -38277,7 +38277,7 @@
       </c>
       <c r="AE329" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="AF329" t="inlineStr">
@@ -38389,7 +38389,7 @@
       </c>
       <c r="AE330" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF330" t="inlineStr">
@@ -38505,7 +38505,7 @@
       </c>
       <c r="AE331" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:38</t>
+          <t>2026-09-18 08:13:51</t>
         </is>
       </c>
       <c r="AF331" t="inlineStr">
@@ -38621,7 +38621,7 @@
       </c>
       <c r="AE332" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:38</t>
+          <t>2026-09-18 08:13:51</t>
         </is>
       </c>
       <c r="AF332" t="inlineStr">
@@ -38737,7 +38737,7 @@
       </c>
       <c r="AE333" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:38</t>
+          <t>2026-09-18 08:13:51</t>
         </is>
       </c>
       <c r="AF333" t="inlineStr">
@@ -38853,7 +38853,7 @@
       </c>
       <c r="AE334" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:38</t>
+          <t>2026-09-18 08:13:51</t>
         </is>
       </c>
       <c r="AF334" t="inlineStr">
@@ -38967,7 +38967,7 @@
       </c>
       <c r="AE335" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:22</t>
+          <t>2026-09-18 08:13:36</t>
         </is>
       </c>
       <c r="AF335" t="inlineStr">
@@ -39083,7 +39083,7 @@
       </c>
       <c r="AE336" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:38</t>
+          <t>2026-09-18 08:13:51</t>
         </is>
       </c>
       <c r="AF336" t="inlineStr">
@@ -39199,7 +39199,7 @@
       </c>
       <c r="AE337" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:38</t>
+          <t>2026-09-18 08:13:51</t>
         </is>
       </c>
       <c r="AF337" t="inlineStr">
@@ -39315,7 +39315,7 @@
       </c>
       <c r="AE338" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:38</t>
+          <t>2026-09-18 08:13:51</t>
         </is>
       </c>
       <c r="AF338" t="inlineStr">
@@ -39425,7 +39425,7 @@
       </c>
       <c r="AE339" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF339" t="inlineStr">
@@ -39541,7 +39541,7 @@
       </c>
       <c r="AE340" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF340" t="inlineStr">
@@ -39653,7 +39653,7 @@
       </c>
       <c r="AE341" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF341" t="inlineStr">
@@ -39763,7 +39763,7 @@
       </c>
       <c r="AE342" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF342" t="inlineStr">
@@ -39875,7 +39875,7 @@
       </c>
       <c r="AE343" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF343" t="inlineStr">
@@ -39987,7 +39987,7 @@
       </c>
       <c r="AE344" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF344" t="inlineStr">
@@ -40099,7 +40099,7 @@
       </c>
       <c r="AE345" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF345" t="inlineStr">
@@ -40219,7 +40219,7 @@
       </c>
       <c r="AE346" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="AF346" t="inlineStr">
@@ -40347,7 +40347,7 @@
       </c>
       <c r="AE347" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="AF347" t="inlineStr">
@@ -40467,7 +40467,7 @@
       </c>
       <c r="AE348" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="AF348" t="inlineStr">
@@ -40595,7 +40595,7 @@
       </c>
       <c r="AE349" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="AF349" t="inlineStr">
@@ -40707,7 +40707,7 @@
       </c>
       <c r="AE350" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF350" t="inlineStr">
@@ -40817,7 +40817,7 @@
       </c>
       <c r="AE351" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF351" t="inlineStr">
@@ -40927,7 +40927,7 @@
       </c>
       <c r="AE352" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF352" t="inlineStr">
@@ -41039,7 +41039,7 @@
       </c>
       <c r="AE353" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF353" t="inlineStr">
@@ -41151,7 +41151,7 @@
       </c>
       <c r="AE354" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF354" t="inlineStr">
@@ -41261,7 +41261,7 @@
       </c>
       <c r="AE355" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF355" t="inlineStr">
@@ -41377,7 +41377,7 @@
       </c>
       <c r="AE356" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF356" t="inlineStr">
@@ -41487,7 +41487,7 @@
       </c>
       <c r="AE357" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF357" t="inlineStr">
@@ -41599,7 +41599,7 @@
       </c>
       <c r="AE358" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF358" t="inlineStr">
@@ -41709,7 +41709,7 @@
       </c>
       <c r="AE359" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF359" t="inlineStr">
@@ -41819,7 +41819,7 @@
       </c>
       <c r="AE360" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF360" t="inlineStr">
@@ -41947,7 +41947,7 @@
       </c>
       <c r="AE361" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="AF361" t="inlineStr">
@@ -42059,7 +42059,7 @@
       </c>
       <c r="AE362" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF362" t="inlineStr">
@@ -42187,7 +42187,7 @@
       </c>
       <c r="AE363" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="AF363" t="inlineStr">
@@ -42299,7 +42299,7 @@
       </c>
       <c r="AE364" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF364" t="inlineStr">
@@ -42409,7 +42409,7 @@
       </c>
       <c r="AE365" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF365" t="inlineStr">
@@ -42519,7 +42519,7 @@
       </c>
       <c r="AE366" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF366" t="inlineStr">
@@ -42629,7 +42629,7 @@
       </c>
       <c r="AE367" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF367" t="inlineStr">
@@ -42741,7 +42741,7 @@
       </c>
       <c r="AE368" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF368" t="inlineStr">
@@ -42851,7 +42851,7 @@
       </c>
       <c r="AE369" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF369" t="inlineStr">
@@ -42979,7 +42979,7 @@
       </c>
       <c r="AE370" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="AF370" t="inlineStr">
@@ -43091,7 +43091,7 @@
       </c>
       <c r="AE371" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF371" t="inlineStr">
@@ -43201,7 +43201,7 @@
       </c>
       <c r="AE372" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF372" t="inlineStr">
@@ -43311,7 +43311,7 @@
       </c>
       <c r="AE373" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF373" t="inlineStr">
@@ -43421,7 +43421,7 @@
       </c>
       <c r="AE374" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF374" t="inlineStr">
@@ -43531,7 +43531,7 @@
       </c>
       <c r="AE375" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF375" t="inlineStr">
@@ -43641,7 +43641,7 @@
       </c>
       <c r="AE376" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF376" t="inlineStr">
@@ -43753,7 +43753,7 @@
       </c>
       <c r="AE377" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF377" t="inlineStr">
@@ -43881,7 +43881,7 @@
       </c>
       <c r="AE378" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="AF378" t="inlineStr">
@@ -43991,7 +43991,7 @@
       </c>
       <c r="AE379" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF379" t="inlineStr">
@@ -44101,7 +44101,7 @@
       </c>
       <c r="AE380" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF380" t="inlineStr">
@@ -44213,7 +44213,7 @@
       </c>
       <c r="AE381" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:24</t>
+          <t>2026-09-18 08:13:38</t>
         </is>
       </c>
       <c r="AF381" t="inlineStr">
@@ -44323,7 +44323,7 @@
       </c>
       <c r="AE382" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF382" t="inlineStr">
@@ -44435,7 +44435,7 @@
       </c>
       <c r="AE383" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF383" t="inlineStr">
@@ -44563,7 +44563,7 @@
       </c>
       <c r="AE384" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="AF384" t="inlineStr">
@@ -44673,7 +44673,7 @@
       </c>
       <c r="AE385" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF385" t="inlineStr">
@@ -44785,7 +44785,7 @@
       </c>
       <c r="AE386" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF386" t="inlineStr">
@@ -44895,7 +44895,7 @@
       </c>
       <c r="AE387" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF387" t="inlineStr">
@@ -45005,7 +45005,7 @@
       </c>
       <c r="AE388" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF388" t="inlineStr">
@@ -45115,7 +45115,7 @@
       </c>
       <c r="AE389" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF389" t="inlineStr">
@@ -45215,7 +45215,7 @@
       </c>
       <c r="AE390" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF390" t="inlineStr">
@@ -45325,7 +45325,7 @@
       </c>
       <c r="AE391" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF391" t="inlineStr">
@@ -45425,7 +45425,7 @@
       </c>
       <c r="AE392" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF392" t="inlineStr">
@@ -45535,7 +45535,7 @@
       </c>
       <c r="AE393" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF393" t="inlineStr">
@@ -45663,7 +45663,7 @@
       </c>
       <c r="AE394" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="AF394" t="inlineStr">
@@ -45773,7 +45773,7 @@
       </c>
       <c r="AE395" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF395" t="inlineStr">
@@ -45883,7 +45883,7 @@
       </c>
       <c r="AE396" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF396" t="inlineStr">
@@ -45993,7 +45993,7 @@
       </c>
       <c r="AE397" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF397" t="inlineStr">
@@ -46103,7 +46103,7 @@
       </c>
       <c r="AE398" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF398" t="inlineStr">
@@ -46213,7 +46213,7 @@
       </c>
       <c r="AE399" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF399" t="inlineStr">
@@ -46323,7 +46323,7 @@
       </c>
       <c r="AE400" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF400" t="inlineStr">
@@ -46433,7 +46433,7 @@
       </c>
       <c r="AE401" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF401" t="inlineStr">
@@ -46543,7 +46543,7 @@
       </c>
       <c r="AE402" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF402" t="inlineStr">
@@ -46671,7 +46671,7 @@
       </c>
       <c r="AE403" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="AF403" t="inlineStr">
@@ -46783,7 +46783,7 @@
       </c>
       <c r="AE404" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF404" t="inlineStr">
@@ -46883,7 +46883,7 @@
       </c>
       <c r="AE405" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF405" t="inlineStr">
@@ -46993,7 +46993,7 @@
       </c>
       <c r="AE406" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF406" t="inlineStr">
@@ -47107,7 +47107,7 @@
       </c>
       <c r="AE407" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF407" t="inlineStr">
@@ -47217,7 +47217,7 @@
       </c>
       <c r="AE408" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF408" t="inlineStr">
@@ -47317,7 +47317,7 @@
       </c>
       <c r="AE409" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF409" t="inlineStr">
@@ -47429,7 +47429,7 @@
       </c>
       <c r="AE410" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF410" t="inlineStr">
@@ -47541,7 +47541,7 @@
       </c>
       <c r="AE411" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF411" t="inlineStr">
@@ -47651,7 +47651,7 @@
       </c>
       <c r="AE412" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF412" t="inlineStr">
@@ -47763,7 +47763,7 @@
       </c>
       <c r="AE413" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF413" t="inlineStr">
@@ -47875,7 +47875,7 @@
       </c>
       <c r="AE414" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF414" t="inlineStr">
@@ -47985,7 +47985,7 @@
       </c>
       <c r="AE415" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF415" t="inlineStr">
@@ -48113,7 +48113,7 @@
       </c>
       <c r="AE416" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="AF416" t="inlineStr">
@@ -48245,7 +48245,7 @@
       </c>
       <c r="AE417" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="AF417" t="inlineStr">
@@ -48377,7 +48377,7 @@
       </c>
       <c r="AE418" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="AF418" t="inlineStr">
@@ -48509,7 +48509,7 @@
       </c>
       <c r="AE419" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="AF419" t="inlineStr">
@@ -48633,7 +48633,7 @@
       </c>
       <c r="AE420" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:24</t>
+          <t>2026-09-18 08:13:38</t>
         </is>
       </c>
       <c r="AF420" t="inlineStr">
@@ -48745,7 +48745,7 @@
       </c>
       <c r="AE421" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF421" t="inlineStr">
@@ -48845,7 +48845,7 @@
       </c>
       <c r="AE422" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF422" t="inlineStr">
@@ -48965,7 +48965,7 @@
       </c>
       <c r="AE423" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="AF423" t="inlineStr">
@@ -49081,7 +49081,7 @@
       </c>
       <c r="AE424" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF424" t="inlineStr">
@@ -49193,7 +49193,7 @@
       </c>
       <c r="AE425" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF425" t="inlineStr">
@@ -49315,7 +49315,7 @@
       <c r="AD426" t="inlineStr"/>
       <c r="AE426" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="AF426" t="inlineStr">
@@ -49427,7 +49427,7 @@
       </c>
       <c r="AE427" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF427" t="inlineStr">
@@ -49537,7 +49537,7 @@
       </c>
       <c r="AE428" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF428" t="inlineStr">
@@ -49647,7 +49647,7 @@
       </c>
       <c r="AE429" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF429" t="inlineStr">
@@ -49757,7 +49757,7 @@
       </c>
       <c r="AE430" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF430" t="inlineStr">
@@ -49867,7 +49867,7 @@
       </c>
       <c r="AE431" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF431" t="inlineStr">
@@ -49995,7 +49995,7 @@
       </c>
       <c r="AE432" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="AF432" t="inlineStr">
@@ -50111,7 +50111,7 @@
       </c>
       <c r="AE433" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF433" t="inlineStr">
@@ -50221,7 +50221,7 @@
       </c>
       <c r="AE434" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF434" t="inlineStr">
@@ -50349,7 +50349,7 @@
       </c>
       <c r="AE435" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="AF435" t="inlineStr">
@@ -50477,7 +50477,7 @@
       </c>
       <c r="AE436" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="AF436" t="inlineStr">
@@ -50605,7 +50605,7 @@
       </c>
       <c r="AE437" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="AF437" t="inlineStr">
@@ -50733,7 +50733,7 @@
       </c>
       <c r="AE438" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="AF438" t="inlineStr">
@@ -50845,7 +50845,7 @@
       </c>
       <c r="AE439" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF439" t="inlineStr">
@@ -50955,7 +50955,7 @@
       </c>
       <c r="AE440" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF440" t="inlineStr">
@@ -51083,7 +51083,7 @@
       </c>
       <c r="AE441" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="AF441" t="inlineStr">
@@ -51195,7 +51195,7 @@
       </c>
       <c r="AE442" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF442" t="inlineStr">
@@ -51307,7 +51307,7 @@
       </c>
       <c r="AE443" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF443" t="inlineStr">
@@ -51423,7 +51423,7 @@
       </c>
       <c r="AE444" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF444" t="inlineStr">
@@ -51535,7 +51535,7 @@
       </c>
       <c r="AE445" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF445" t="inlineStr">
@@ -51647,7 +51647,7 @@
       </c>
       <c r="AE446" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF446" t="inlineStr">
@@ -51759,7 +51759,7 @@
       </c>
       <c r="AE447" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF447" t="inlineStr">
@@ -51871,7 +51871,7 @@
       </c>
       <c r="AE448" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF448" t="inlineStr">
@@ -51991,7 +51991,7 @@
       </c>
       <c r="AE449" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="AF449" t="inlineStr">
@@ -52101,7 +52101,7 @@
       </c>
       <c r="AE450" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF450" t="inlineStr">
@@ -52229,7 +52229,7 @@
       </c>
       <c r="AE451" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="AF451" t="inlineStr">
@@ -52349,7 +52349,7 @@
       </c>
       <c r="AE452" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="AF452" t="inlineStr">
@@ -52461,7 +52461,7 @@
       </c>
       <c r="AE453" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF453" t="inlineStr">
@@ -52573,7 +52573,7 @@
       </c>
       <c r="AE454" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF454" t="inlineStr">
@@ -52673,7 +52673,7 @@
       </c>
       <c r="AE455" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF455" t="inlineStr">
@@ -52789,7 +52789,7 @@
       </c>
       <c r="AE456" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF456" t="inlineStr">
@@ -52899,7 +52899,7 @@
       </c>
       <c r="AE457" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF457" t="inlineStr">
@@ -53011,7 +53011,7 @@
       </c>
       <c r="AE458" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF458" t="inlineStr">
@@ -53121,7 +53121,7 @@
       </c>
       <c r="AE459" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF459" t="inlineStr">
@@ -53233,7 +53233,7 @@
       </c>
       <c r="AE460" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF460" t="inlineStr">
@@ -53345,7 +53345,7 @@
       </c>
       <c r="AE461" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF461" t="inlineStr">
@@ -53445,7 +53445,7 @@
       </c>
       <c r="AE462" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF462" t="inlineStr">
@@ -53555,7 +53555,7 @@
       </c>
       <c r="AE463" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF463" t="inlineStr">
@@ -53667,7 +53667,7 @@
       </c>
       <c r="AE464" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF464" t="inlineStr">
@@ -53777,7 +53777,7 @@
       </c>
       <c r="AE465" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF465" t="inlineStr">
@@ -53887,7 +53887,7 @@
       </c>
       <c r="AE466" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF466" t="inlineStr">
@@ -53999,7 +53999,7 @@
       </c>
       <c r="AE467" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF467" t="inlineStr">
@@ -54109,7 +54109,7 @@
       </c>
       <c r="AE468" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF468" t="inlineStr">
@@ -54219,7 +54219,7 @@
       </c>
       <c r="AE469" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF469" t="inlineStr">
@@ -54329,7 +54329,7 @@
       </c>
       <c r="AE470" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF470" t="inlineStr">
@@ -54449,7 +54449,7 @@
       </c>
       <c r="AE471" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="AF471" t="inlineStr">
@@ -54573,7 +54573,7 @@
       </c>
       <c r="AE472" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:24</t>
+          <t>2026-09-18 08:13:38</t>
         </is>
       </c>
       <c r="AF472" t="inlineStr">
@@ -54683,7 +54683,7 @@
       </c>
       <c r="AE473" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF473" t="inlineStr">
@@ -54795,7 +54795,7 @@
       </c>
       <c r="AE474" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF474" t="inlineStr">
@@ -54905,7 +54905,7 @@
       </c>
       <c r="AE475" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF475" t="inlineStr">
@@ -55017,7 +55017,7 @@
       </c>
       <c r="AE476" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF476" t="inlineStr">
@@ -55129,7 +55129,7 @@
       </c>
       <c r="AE477" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF477" t="inlineStr">
@@ -55239,7 +55239,7 @@
       </c>
       <c r="AE478" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF478" t="inlineStr">
@@ -55349,7 +55349,7 @@
       </c>
       <c r="AE479" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF479" t="inlineStr">
@@ -55459,7 +55459,7 @@
       </c>
       <c r="AE480" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF480" t="inlineStr">
@@ -55569,7 +55569,7 @@
       </c>
       <c r="AE481" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF481" t="inlineStr">
@@ -55679,7 +55679,7 @@
       </c>
       <c r="AE482" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF482" t="inlineStr">
@@ -55789,7 +55789,7 @@
       </c>
       <c r="AE483" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF483" t="inlineStr">
@@ -55901,7 +55901,7 @@
       </c>
       <c r="AE484" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF484" t="inlineStr">
@@ -56013,7 +56013,7 @@
       </c>
       <c r="AE485" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF485" t="inlineStr">
@@ -56125,7 +56125,7 @@
       </c>
       <c r="AE486" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF486" t="inlineStr">
@@ -56235,7 +56235,7 @@
       </c>
       <c r="AE487" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF487" t="inlineStr">
@@ -56347,7 +56347,7 @@
       </c>
       <c r="AE488" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF488" t="inlineStr">
@@ -56447,7 +56447,7 @@
       </c>
       <c r="AE489" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF489" t="inlineStr">
@@ -56557,7 +56557,7 @@
       </c>
       <c r="AE490" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF490" t="inlineStr">
@@ -56657,7 +56657,7 @@
       </c>
       <c r="AE491" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF491" t="inlineStr">
@@ -56757,7 +56757,7 @@
       </c>
       <c r="AE492" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF492" t="inlineStr">
@@ -56869,7 +56869,7 @@
       </c>
       <c r="AE493" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF493" t="inlineStr">
@@ -56981,7 +56981,7 @@
       </c>
       <c r="AE494" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF494" t="inlineStr">
@@ -57093,7 +57093,7 @@
       </c>
       <c r="AE495" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF495" t="inlineStr">
@@ -57203,7 +57203,7 @@
       </c>
       <c r="AE496" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF496" t="inlineStr">
@@ -57313,7 +57313,7 @@
       </c>
       <c r="AE497" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF497" t="inlineStr">
@@ -57423,7 +57423,7 @@
       </c>
       <c r="AE498" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF498" t="inlineStr">
@@ -57535,7 +57535,7 @@
       </c>
       <c r="AE499" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF499" t="inlineStr">
@@ -57645,7 +57645,7 @@
       </c>
       <c r="AE500" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF500" t="inlineStr">
@@ -57755,7 +57755,7 @@
       </c>
       <c r="AE501" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF501" t="inlineStr">
@@ -57865,7 +57865,7 @@
       </c>
       <c r="AE502" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF502" t="inlineStr">
@@ -57975,7 +57975,7 @@
       </c>
       <c r="AE503" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF503" t="inlineStr">
@@ -58087,7 +58087,7 @@
       </c>
       <c r="AE504" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF504" t="inlineStr">
@@ -58199,7 +58199,7 @@
       </c>
       <c r="AE505" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF505" t="inlineStr">
@@ -58315,7 +58315,7 @@
       </c>
       <c r="AE506" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF506" t="inlineStr">
@@ -58443,7 +58443,7 @@
       </c>
       <c r="AE507" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="AF507" t="inlineStr">
@@ -58555,7 +58555,7 @@
       </c>
       <c r="AE508" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF508" t="inlineStr">
@@ -58665,7 +58665,7 @@
       </c>
       <c r="AE509" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF509" t="inlineStr">
@@ -58785,7 +58785,7 @@
       </c>
       <c r="AE510" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="AF510" t="inlineStr">
@@ -58895,7 +58895,7 @@
       </c>
       <c r="AE511" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF511" t="inlineStr">
@@ -59005,7 +59005,7 @@
       </c>
       <c r="AE512" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF512" t="inlineStr">
@@ -59115,7 +59115,7 @@
       </c>
       <c r="AE513" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF513" t="inlineStr">
@@ -59235,7 +59235,7 @@
       </c>
       <c r="AE514" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="AF514" t="inlineStr">
@@ -59351,7 +59351,7 @@
       </c>
       <c r="AE515" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF515" t="inlineStr">
@@ -59463,7 +59463,7 @@
       </c>
       <c r="AE516" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF516" t="inlineStr">
@@ -59583,7 +59583,7 @@
       </c>
       <c r="AE517" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="AF517" t="inlineStr">
@@ -59695,7 +59695,7 @@
       </c>
       <c r="AE518" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF518" t="inlineStr">
@@ -59795,7 +59795,7 @@
       </c>
       <c r="AE519" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF519" t="inlineStr">
@@ -59915,7 +59915,7 @@
       </c>
       <c r="AE520" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="AF520" t="inlineStr">
@@ -60025,7 +60025,7 @@
       </c>
       <c r="AE521" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF521" t="inlineStr">
@@ -60137,7 +60137,7 @@
       </c>
       <c r="AE522" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF522" t="inlineStr">
@@ -60253,7 +60253,7 @@
       </c>
       <c r="AE523" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF523" t="inlineStr">
@@ -60365,7 +60365,7 @@
       </c>
       <c r="AE524" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF524" t="inlineStr">
@@ -60477,7 +60477,7 @@
       </c>
       <c r="AE525" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF525" t="inlineStr">
@@ -60605,7 +60605,7 @@
       </c>
       <c r="AE526" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="AF526" t="inlineStr">
@@ -60715,7 +60715,7 @@
       </c>
       <c r="AE527" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF527" t="inlineStr">
@@ -60825,7 +60825,7 @@
       </c>
       <c r="AE528" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF528" t="inlineStr">
@@ -60935,7 +60935,7 @@
       </c>
       <c r="AE529" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF529" t="inlineStr">
@@ -61047,7 +61047,7 @@
       </c>
       <c r="AE530" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF530" t="inlineStr">
@@ -61175,7 +61175,7 @@
       </c>
       <c r="AE531" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="AF531" t="inlineStr">
@@ -61287,7 +61287,7 @@
       </c>
       <c r="AE532" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF532" t="inlineStr">
@@ -61399,7 +61399,7 @@
       </c>
       <c r="AE533" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF533" t="inlineStr">
@@ -61511,7 +61511,7 @@
       </c>
       <c r="AE534" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF534" t="inlineStr">
@@ -61611,7 +61611,7 @@
       </c>
       <c r="AE535" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF535" t="inlineStr">
@@ -61721,7 +61721,7 @@
       </c>
       <c r="AE536" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF536" t="inlineStr">
@@ -61831,7 +61831,7 @@
       </c>
       <c r="AE537" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF537" t="inlineStr">
@@ -61931,7 +61931,7 @@
       </c>
       <c r="AE538" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF538" t="inlineStr">
@@ -62041,7 +62041,7 @@
       </c>
       <c r="AE539" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF539" t="inlineStr">
@@ -62169,7 +62169,7 @@
       </c>
       <c r="AE540" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="AF540" t="inlineStr">
@@ -62279,7 +62279,7 @@
       </c>
       <c r="AE541" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF541" t="inlineStr">
@@ -62391,7 +62391,7 @@
       </c>
       <c r="AE542" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF542" t="inlineStr">
@@ -62501,7 +62501,7 @@
       </c>
       <c r="AE543" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF543" t="inlineStr">
@@ -62613,7 +62613,7 @@
       </c>
       <c r="AE544" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF544" t="inlineStr">
@@ -62723,7 +62723,7 @@
       </c>
       <c r="AE545" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF545" t="inlineStr">
@@ -62833,7 +62833,7 @@
       </c>
       <c r="AE546" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF546" t="inlineStr">
@@ -62933,7 +62933,7 @@
       </c>
       <c r="AE547" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF547" t="inlineStr">
@@ -63043,7 +63043,7 @@
       </c>
       <c r="AE548" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF548" t="inlineStr">
@@ -63155,7 +63155,7 @@
       </c>
       <c r="AE549" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF549" t="inlineStr">
@@ -63265,7 +63265,7 @@
       </c>
       <c r="AE550" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF550" t="inlineStr">
@@ -63375,7 +63375,7 @@
       </c>
       <c r="AE551" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF551" t="inlineStr">
@@ -63485,7 +63485,7 @@
       </c>
       <c r="AE552" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF552" t="inlineStr">
@@ -63595,7 +63595,7 @@
       </c>
       <c r="AE553" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF553" t="inlineStr">
@@ -63705,7 +63705,7 @@
       </c>
       <c r="AE554" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF554" t="inlineStr">
@@ -63815,7 +63815,7 @@
       </c>
       <c r="AE555" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF555" t="inlineStr">
@@ -63915,7 +63915,7 @@
       </c>
       <c r="AE556" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF556" t="inlineStr">
@@ -64025,7 +64025,7 @@
       </c>
       <c r="AE557" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF557" t="inlineStr">
@@ -64135,7 +64135,7 @@
       </c>
       <c r="AE558" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF558" t="inlineStr">
@@ -64247,7 +64247,7 @@
       </c>
       <c r="AE559" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF559" t="inlineStr">
@@ -64357,7 +64357,7 @@
       </c>
       <c r="AE560" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF560" t="inlineStr">
@@ -64469,7 +64469,7 @@
       </c>
       <c r="AE561" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF561" t="inlineStr">
@@ -64579,7 +64579,7 @@
       </c>
       <c r="AE562" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF562" t="inlineStr">
@@ -64689,7 +64689,7 @@
       </c>
       <c r="AE563" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF563" t="inlineStr">
@@ -64799,7 +64799,7 @@
       </c>
       <c r="AE564" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF564" t="inlineStr">
@@ -64909,7 +64909,7 @@
       </c>
       <c r="AE565" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF565" t="inlineStr">
@@ -65019,7 +65019,7 @@
       </c>
       <c r="AE566" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF566" t="inlineStr">
@@ -65131,7 +65131,7 @@
       </c>
       <c r="AE567" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF567" t="inlineStr">
@@ -65241,7 +65241,7 @@
       </c>
       <c r="AE568" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF568" t="inlineStr">
@@ -65353,7 +65353,7 @@
       </c>
       <c r="AE569" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF569" t="inlineStr">
@@ -65465,7 +65465,7 @@
       </c>
       <c r="AE570" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF570" t="inlineStr">
@@ -65575,7 +65575,7 @@
       </c>
       <c r="AE571" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF571" t="inlineStr">
@@ -65687,7 +65687,7 @@
       </c>
       <c r="AE572" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF572" t="inlineStr">
@@ -65799,7 +65799,7 @@
       </c>
       <c r="AE573" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF573" t="inlineStr">
@@ -65909,7 +65909,7 @@
       </c>
       <c r="AE574" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF574" t="inlineStr">
@@ -66019,7 +66019,7 @@
       </c>
       <c r="AE575" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF575" t="inlineStr">
@@ -66129,7 +66129,7 @@
       </c>
       <c r="AE576" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF576" t="inlineStr">
@@ -66239,7 +66239,7 @@
       </c>
       <c r="AE577" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF577" t="inlineStr">
@@ -66339,7 +66339,7 @@
       </c>
       <c r="AE578" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF578" t="inlineStr">
@@ -66451,7 +66451,7 @@
       </c>
       <c r="AE579" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF579" t="inlineStr">
@@ -66561,7 +66561,7 @@
       </c>
       <c r="AE580" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF580" t="inlineStr">
@@ -66671,7 +66671,7 @@
       </c>
       <c r="AE581" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF581" t="inlineStr">
@@ -66799,7 +66799,7 @@
       </c>
       <c r="AE582" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="AF582" t="inlineStr">
@@ -66911,7 +66911,7 @@
       </c>
       <c r="AE583" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF583" t="inlineStr">
@@ -67023,7 +67023,7 @@
       </c>
       <c r="AE584" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF584" t="inlineStr">
@@ -67151,7 +67151,7 @@
       </c>
       <c r="AE585" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="AF585" t="inlineStr">
@@ -67263,7 +67263,7 @@
       </c>
       <c r="AE586" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF586" t="inlineStr">
@@ -67391,7 +67391,7 @@
       </c>
       <c r="AE587" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="AF587" t="inlineStr">
@@ -67519,7 +67519,7 @@
       </c>
       <c r="AE588" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="AF588" t="inlineStr">
@@ -67631,7 +67631,7 @@
       </c>
       <c r="AE589" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF589" t="inlineStr">
@@ -67743,7 +67743,7 @@
       </c>
       <c r="AE590" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF590" t="inlineStr">
@@ -67853,7 +67853,7 @@
       </c>
       <c r="AE591" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF591" t="inlineStr">
@@ -67965,7 +67965,7 @@
       </c>
       <c r="AE592" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF592" t="inlineStr">
@@ -68075,7 +68075,7 @@
       </c>
       <c r="AE593" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF593" t="inlineStr">
@@ -68185,7 +68185,7 @@
       </c>
       <c r="AE594" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF594" t="inlineStr">
@@ -68297,7 +68297,7 @@
       </c>
       <c r="AE595" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF595" t="inlineStr">
@@ -68409,7 +68409,7 @@
       </c>
       <c r="AE596" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF596" t="inlineStr">
@@ -68521,7 +68521,7 @@
       </c>
       <c r="AE597" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF597" t="inlineStr">
@@ -68631,7 +68631,7 @@
       </c>
       <c r="AE598" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF598" t="inlineStr">
@@ -68741,7 +68741,7 @@
       </c>
       <c r="AE599" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF599" t="inlineStr">
@@ -68853,7 +68853,7 @@
       </c>
       <c r="AE600" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF600" t="inlineStr">
@@ -68965,7 +68965,7 @@
       </c>
       <c r="AE601" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF601" t="inlineStr">
@@ -69075,7 +69075,7 @@
       </c>
       <c r="AE602" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF602" t="inlineStr">
@@ -69187,7 +69187,7 @@
       </c>
       <c r="AE603" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF603" t="inlineStr">
@@ -69297,7 +69297,7 @@
       </c>
       <c r="AE604" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF604" t="inlineStr">
@@ -69397,7 +69397,7 @@
       </c>
       <c r="AE605" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF605" t="inlineStr">
@@ -69507,7 +69507,7 @@
       </c>
       <c r="AE606" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF606" t="inlineStr">
@@ -69619,7 +69619,7 @@
       </c>
       <c r="AE607" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF607" t="inlineStr">
@@ -69729,7 +69729,7 @@
       </c>
       <c r="AE608" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF608" t="inlineStr">
@@ -69841,7 +69841,7 @@
       </c>
       <c r="AE609" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF609" t="inlineStr">
@@ -69951,7 +69951,7 @@
       </c>
       <c r="AE610" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF610" t="inlineStr">
@@ -70061,7 +70061,7 @@
       </c>
       <c r="AE611" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF611" t="inlineStr">
@@ -70171,7 +70171,7 @@
       </c>
       <c r="AE612" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF612" t="inlineStr">
@@ -70281,7 +70281,7 @@
       </c>
       <c r="AE613" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF613" t="inlineStr">
@@ -70391,7 +70391,7 @@
       </c>
       <c r="AE614" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF614" t="inlineStr">
@@ -70503,7 +70503,7 @@
       </c>
       <c r="AE615" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF615" t="inlineStr">
@@ -70613,7 +70613,7 @@
       </c>
       <c r="AE616" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF616" t="inlineStr">
@@ -70723,7 +70723,7 @@
       </c>
       <c r="AE617" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF617" t="inlineStr">
@@ -70833,7 +70833,7 @@
       </c>
       <c r="AE618" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF618" t="inlineStr">
@@ -70945,7 +70945,7 @@
       </c>
       <c r="AE619" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF619" t="inlineStr">
@@ -71055,7 +71055,7 @@
       </c>
       <c r="AE620" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF620" t="inlineStr">
@@ -71167,7 +71167,7 @@
       </c>
       <c r="AE621" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF621" t="inlineStr">
@@ -71279,7 +71279,7 @@
       </c>
       <c r="AE622" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF622" t="inlineStr">
@@ -71379,7 +71379,7 @@
       </c>
       <c r="AE623" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF623" t="inlineStr">
@@ -71489,7 +71489,7 @@
       </c>
       <c r="AE624" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF624" t="inlineStr">
@@ -71601,7 +71601,7 @@
       </c>
       <c r="AE625" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF625" t="inlineStr">
@@ -71713,7 +71713,7 @@
       </c>
       <c r="AE626" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF626" t="inlineStr">
@@ -71825,7 +71825,7 @@
       </c>
       <c r="AE627" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF627" t="inlineStr">
@@ -71937,7 +71937,7 @@
       </c>
       <c r="AE628" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF628" t="inlineStr">
@@ -72047,7 +72047,7 @@
       </c>
       <c r="AE629" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF629" t="inlineStr">
@@ -72157,7 +72157,7 @@
       </c>
       <c r="AE630" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF630" t="inlineStr">
@@ -72269,7 +72269,7 @@
       </c>
       <c r="AE631" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF631" t="inlineStr">
@@ -72379,7 +72379,7 @@
       </c>
       <c r="AE632" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF632" t="inlineStr">
@@ -72491,7 +72491,7 @@
       </c>
       <c r="AE633" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF633" t="inlineStr">
@@ -72591,7 +72591,7 @@
       </c>
       <c r="AE634" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF634" t="inlineStr">
@@ -72701,7 +72701,7 @@
       </c>
       <c r="AE635" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF635" t="inlineStr">
@@ -72813,7 +72813,7 @@
       </c>
       <c r="AE636" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF636" t="inlineStr">
@@ -72923,7 +72923,7 @@
       <c r="AD637" t="inlineStr"/>
       <c r="AE637" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:38</t>
+          <t>2026-09-18 08:13:51</t>
         </is>
       </c>
       <c r="AF637" t="inlineStr">
@@ -73035,7 +73035,7 @@
       </c>
       <c r="AE638" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF638" t="inlineStr">
@@ -73147,7 +73147,7 @@
       </c>
       <c r="AE639" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF639" t="inlineStr">
@@ -73257,7 +73257,7 @@
       </c>
       <c r="AE640" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF640" t="inlineStr">
@@ -73369,7 +73369,7 @@
       </c>
       <c r="AE641" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF641" t="inlineStr">
@@ -73469,7 +73469,7 @@
       </c>
       <c r="AE642" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF642" t="inlineStr">
@@ -73569,7 +73569,7 @@
       </c>
       <c r="AE643" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF643" t="inlineStr">
@@ -73669,7 +73669,7 @@
       </c>
       <c r="AE644" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF644" t="inlineStr">
@@ -73781,7 +73781,7 @@
       </c>
       <c r="AE645" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF645" t="inlineStr">
@@ -73881,7 +73881,7 @@
       </c>
       <c r="AE646" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF646" t="inlineStr">
@@ -73991,7 +73991,7 @@
       </c>
       <c r="AE647" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF647" t="inlineStr">
@@ -74091,7 +74091,7 @@
       </c>
       <c r="AE648" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF648" t="inlineStr">
@@ -74203,7 +74203,7 @@
       </c>
       <c r="AE649" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF649" t="inlineStr">
@@ -74315,7 +74315,7 @@
       </c>
       <c r="AE650" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF650" t="inlineStr">
@@ -74427,7 +74427,7 @@
       </c>
       <c r="AE651" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF651" t="inlineStr">
@@ -74539,7 +74539,7 @@
       </c>
       <c r="AE652" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF652" t="inlineStr">
@@ -74639,7 +74639,7 @@
       </c>
       <c r="AE653" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF653" t="inlineStr">
@@ -74751,7 +74751,7 @@
       </c>
       <c r="AE654" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF654" t="inlineStr">
@@ -74861,7 +74861,7 @@
       </c>
       <c r="AE655" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF655" t="inlineStr">
@@ -74973,7 +74973,7 @@
       </c>
       <c r="AE656" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF656" t="inlineStr">
@@ -75073,7 +75073,7 @@
       </c>
       <c r="AE657" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF657" t="inlineStr">
@@ -75173,7 +75173,7 @@
       </c>
       <c r="AE658" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF658" t="inlineStr">
@@ -75273,7 +75273,7 @@
       </c>
       <c r="AE659" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF659" t="inlineStr">
@@ -75373,7 +75373,7 @@
       </c>
       <c r="AE660" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF660" t="inlineStr">
@@ -75485,7 +75485,7 @@
       </c>
       <c r="AE661" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF661" t="inlineStr">
@@ -75597,7 +75597,7 @@
       </c>
       <c r="AE662" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF662" t="inlineStr">
@@ -75697,7 +75697,7 @@
       </c>
       <c r="AE663" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF663" t="inlineStr">
@@ -75807,7 +75807,7 @@
       </c>
       <c r="AE664" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF664" t="inlineStr">
@@ -75919,7 +75919,7 @@
       </c>
       <c r="AE665" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF665" t="inlineStr">
@@ -76031,7 +76031,7 @@
       </c>
       <c r="AE666" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF666" t="inlineStr">
@@ -76143,7 +76143,7 @@
       </c>
       <c r="AE667" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF667" t="inlineStr">
@@ -76255,7 +76255,7 @@
       </c>
       <c r="AE668" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF668" t="inlineStr">
@@ -76367,7 +76367,7 @@
       </c>
       <c r="AE669" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF669" t="inlineStr">
@@ -76479,7 +76479,7 @@
       </c>
       <c r="AE670" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF670" t="inlineStr">
@@ -76591,7 +76591,7 @@
       </c>
       <c r="AE671" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF671" t="inlineStr">
@@ -76691,7 +76691,7 @@
       </c>
       <c r="AE672" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF672" t="inlineStr">
@@ -76791,7 +76791,7 @@
       </c>
       <c r="AE673" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF673" t="inlineStr">
@@ -76903,7 +76903,7 @@
       </c>
       <c r="AE674" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:06</t>
+          <t>2026-09-18 08:13:21</t>
         </is>
       </c>
       <c r="AF674" t="inlineStr">
@@ -77003,7 +77003,7 @@
       </c>
       <c r="AE675" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF675" t="inlineStr">
@@ -77103,7 +77103,7 @@
       </c>
       <c r="AE676" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF676" t="inlineStr">
@@ -77203,7 +77203,7 @@
       </c>
       <c r="AE677" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF677" t="inlineStr">
@@ -77313,7 +77313,7 @@
       </c>
       <c r="AE678" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF678" t="inlineStr">
@@ -77413,7 +77413,7 @@
       </c>
       <c r="AE679" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF679" t="inlineStr">
@@ -77523,7 +77523,7 @@
       </c>
       <c r="AE680" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF680" t="inlineStr">
@@ -77605,7 +77605,7 @@
       <c r="AD681" t="inlineStr"/>
       <c r="AE681" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF681" t="inlineStr">
@@ -77687,7 +77687,7 @@
       <c r="AD682" t="inlineStr"/>
       <c r="AE682" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF682" t="inlineStr">
@@ -77769,7 +77769,7 @@
       <c r="AD683" t="inlineStr"/>
       <c r="AE683" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF683" t="inlineStr">
@@ -77851,7 +77851,7 @@
       <c r="AD684" t="inlineStr"/>
       <c r="AE684" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="AF684" t="inlineStr">

--- a/pipeline/credit_rating/output/xhtn_tong_hop_20260918.xlsx
+++ b/pipeline/credit_rating/output/xhtn_tong_hop_20260918.xlsx
@@ -685,7 +685,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1011,7 +1011,7 @@
       <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -1099,7 +1099,7 @@
       <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -1219,7 +1219,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -1555,7 +1555,7 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:51</t>
+          <t>2026-09-18 08:21:44</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -1665,7 +1665,7 @@
       <c r="AD11" t="inlineStr"/>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:51</t>
+          <t>2026-09-18 08:21:44</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:51</t>
+          <t>2026-09-18 08:21:44</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -1891,7 +1891,7 @@
       <c r="AD13" t="inlineStr"/>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:51</t>
+          <t>2026-09-18 08:21:44</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -2019,7 +2019,7 @@
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -2133,7 +2133,7 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -2247,7 +2247,7 @@
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -2367,7 +2367,7 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -2595,7 +2595,7 @@
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -2709,7 +2709,7 @@
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -2825,7 +2825,7 @@
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:51</t>
+          <t>2026-09-18 08:21:44</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -2939,7 +2939,7 @@
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -3049,7 +3049,7 @@
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -3177,7 +3177,7 @@
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
@@ -3291,7 +3291,7 @@
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
@@ -3411,7 +3411,7 @@
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
@@ -3525,7 +3525,7 @@
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
@@ -3635,7 +3635,7 @@
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:51</t>
+          <t>2026-09-18 08:21:44</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
@@ -3861,7 +3861,7 @@
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
@@ -3971,7 +3971,7 @@
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF31" t="inlineStr">
@@ -4095,7 +4095,7 @@
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
@@ -4205,7 +4205,7 @@
       </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF33" t="inlineStr">
@@ -4315,7 +4315,7 @@
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF34" t="inlineStr">
@@ -4425,7 +4425,7 @@
       </c>
       <c r="AE35" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF35" t="inlineStr">
@@ -4525,7 +4525,7 @@
       </c>
       <c r="AE36" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF36" t="inlineStr">
@@ -4635,7 +4635,7 @@
       </c>
       <c r="AE37" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF37" t="inlineStr">
@@ -4745,7 +4745,7 @@
       </c>
       <c r="AE38" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF38" t="inlineStr">
@@ -4855,7 +4855,7 @@
       </c>
       <c r="AE39" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF39" t="inlineStr">
@@ -4987,7 +4987,7 @@
       </c>
       <c r="AE40" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="AF40" t="inlineStr">
@@ -5115,7 +5115,7 @@
       </c>
       <c r="AE41" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="AF41" t="inlineStr">
@@ -5247,7 +5247,7 @@
       </c>
       <c r="AE42" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="AF42" t="inlineStr">
@@ -5375,7 +5375,7 @@
       </c>
       <c r="AE43" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="AF43" t="inlineStr">
@@ -5485,7 +5485,7 @@
       </c>
       <c r="AE44" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF44" t="inlineStr">
@@ -5597,7 +5597,7 @@
       </c>
       <c r="AE45" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF45" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="AE46" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF46" t="inlineStr">
@@ -5827,7 +5827,7 @@
       </c>
       <c r="AE47" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF47" t="inlineStr">
@@ -5943,7 +5943,7 @@
       </c>
       <c r="AE48" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF48" t="inlineStr">
@@ -6043,7 +6043,7 @@
       </c>
       <c r="AE49" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF49" t="inlineStr">
@@ -6157,7 +6157,7 @@
       </c>
       <c r="AE50" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF50" t="inlineStr">
@@ -6273,7 +6273,7 @@
       </c>
       <c r="AE51" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:51</t>
+          <t>2026-09-18 08:21:44</t>
         </is>
       </c>
       <c r="AF51" t="inlineStr">
@@ -6383,7 +6383,7 @@
       </c>
       <c r="AE52" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF52" t="inlineStr">
@@ -6497,7 +6497,7 @@
       </c>
       <c r="AE53" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF53" t="inlineStr">
@@ -6611,7 +6611,7 @@
       </c>
       <c r="AE54" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF54" t="inlineStr">
@@ -6739,7 +6739,7 @@
       </c>
       <c r="AE55" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="AF55" t="inlineStr">
@@ -6855,7 +6855,7 @@
       </c>
       <c r="AE56" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF56" t="inlineStr">
@@ -6951,7 +6951,7 @@
       </c>
       <c r="AE57" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF57" t="inlineStr">
@@ -7061,7 +7061,7 @@
       </c>
       <c r="AE58" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF58" t="inlineStr">
@@ -7161,7 +7161,7 @@
       </c>
       <c r="AE59" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF59" t="inlineStr">
@@ -7275,7 +7275,7 @@
       </c>
       <c r="AE60" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF60" t="inlineStr">
@@ -7389,7 +7389,7 @@
       </c>
       <c r="AE61" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF61" t="inlineStr">
@@ -7489,7 +7489,7 @@
       </c>
       <c r="AE62" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF62" t="inlineStr">
@@ -7603,7 +7603,7 @@
       </c>
       <c r="AE63" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:36</t>
+          <t>2026-09-18 08:21:26</t>
         </is>
       </c>
       <c r="AF63" t="inlineStr">
@@ -7713,7 +7713,7 @@
       </c>
       <c r="AE64" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF64" t="inlineStr">
@@ -7827,7 +7827,7 @@
       </c>
       <c r="AE65" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF65" t="inlineStr">
@@ -7941,7 +7941,7 @@
       </c>
       <c r="AE66" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF66" t="inlineStr">
@@ -8051,7 +8051,7 @@
       </c>
       <c r="AE67" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF67" t="inlineStr">
@@ -8165,7 +8165,7 @@
       </c>
       <c r="AE68" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF68" t="inlineStr">
@@ -8279,7 +8279,7 @@
       </c>
       <c r="AE69" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:36</t>
+          <t>2026-09-18 08:21:26</t>
         </is>
       </c>
       <c r="AF69" t="inlineStr">
@@ -8393,7 +8393,7 @@
       </c>
       <c r="AE70" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:36</t>
+          <t>2026-09-18 08:21:26</t>
         </is>
       </c>
       <c r="AF70" t="inlineStr">
@@ -8517,7 +8517,7 @@
       </c>
       <c r="AE71" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:38</t>
+          <t>2026-09-18 08:21:28</t>
         </is>
       </c>
       <c r="AF71" t="inlineStr">
@@ -8627,7 +8627,7 @@
       </c>
       <c r="AE72" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF72" t="inlineStr">
@@ -8741,7 +8741,7 @@
       </c>
       <c r="AE73" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF73" t="inlineStr">
@@ -8855,7 +8855,7 @@
       </c>
       <c r="AE74" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF74" t="inlineStr">
@@ -8969,7 +8969,7 @@
       </c>
       <c r="AE75" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF75" t="inlineStr">
@@ -9081,7 +9081,7 @@
       </c>
       <c r="AE76" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF76" t="inlineStr">
@@ -9197,7 +9197,7 @@
       </c>
       <c r="AE77" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:51</t>
+          <t>2026-09-18 08:21:44</t>
         </is>
       </c>
       <c r="AF77" t="inlineStr">
@@ -9307,7 +9307,7 @@
       </c>
       <c r="AE78" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF78" t="inlineStr">
@@ -9417,7 +9417,7 @@
       </c>
       <c r="AE79" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF79" t="inlineStr">
@@ -9535,7 +9535,7 @@
       </c>
       <c r="AE80" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:36</t>
+          <t>2026-09-18 08:21:26</t>
         </is>
       </c>
       <c r="AF80" t="inlineStr">
@@ -9659,7 +9659,7 @@
       </c>
       <c r="AE81" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="AF81" t="inlineStr">
@@ -9779,7 +9779,7 @@
       </c>
       <c r="AE82" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="AF82" t="inlineStr">
@@ -9899,7 +9899,7 @@
       </c>
       <c r="AE83" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="AF83" t="inlineStr">
@@ -10031,7 +10031,7 @@
       </c>
       <c r="AE84" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="AF84" t="inlineStr">
@@ -10155,7 +10155,7 @@
       </c>
       <c r="AE85" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF85" t="inlineStr">
@@ -10279,7 +10279,7 @@
       </c>
       <c r="AE86" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF86" t="inlineStr">
@@ -10379,7 +10379,7 @@
       </c>
       <c r="AE87" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF87" t="inlineStr">
@@ -10499,7 +10499,7 @@
       </c>
       <c r="AE88" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="AF88" t="inlineStr">
@@ -10627,7 +10627,7 @@
       </c>
       <c r="AE89" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="AF89" t="inlineStr">
@@ -10741,7 +10741,7 @@
       </c>
       <c r="AE90" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF90" t="inlineStr">
@@ -10855,7 +10855,7 @@
       </c>
       <c r="AE91" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF91" t="inlineStr">
@@ -10969,7 +10969,7 @@
       </c>
       <c r="AE92" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF92" t="inlineStr">
@@ -11079,7 +11079,7 @@
       </c>
       <c r="AE93" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF93" t="inlineStr">
@@ -11193,7 +11193,7 @@
       </c>
       <c r="AE94" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF94" t="inlineStr">
@@ -11307,7 +11307,7 @@
       </c>
       <c r="AE95" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF95" t="inlineStr">
@@ -11421,7 +11421,7 @@
       </c>
       <c r="AE96" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF96" t="inlineStr">
@@ -11535,7 +11535,7 @@
       </c>
       <c r="AE97" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF97" t="inlineStr">
@@ -11655,7 +11655,7 @@
       </c>
       <c r="AE98" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="AF98" t="inlineStr">
@@ -11771,7 +11771,7 @@
       </c>
       <c r="AE99" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:51</t>
+          <t>2026-09-18 08:21:44</t>
         </is>
       </c>
       <c r="AF99" t="inlineStr">
@@ -11881,7 +11881,7 @@
       </c>
       <c r="AE100" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF100" t="inlineStr">
@@ -12001,7 +12001,7 @@
       </c>
       <c r="AE101" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="AF101" t="inlineStr">
@@ -12133,7 +12133,7 @@
       </c>
       <c r="AE102" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="AF102" t="inlineStr">
@@ -12261,7 +12261,7 @@
       </c>
       <c r="AE103" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="AF103" t="inlineStr">
@@ -12373,7 +12373,7 @@
       </c>
       <c r="AE104" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF104" t="inlineStr">
@@ -12483,7 +12483,7 @@
       </c>
       <c r="AE105" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF105" t="inlineStr">
@@ -12593,7 +12593,7 @@
       </c>
       <c r="AE106" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF106" t="inlineStr">
@@ -12703,7 +12703,7 @@
       </c>
       <c r="AE107" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF107" t="inlineStr">
@@ -12817,7 +12817,7 @@
       </c>
       <c r="AE108" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:36</t>
+          <t>2026-09-18 08:21:26</t>
         </is>
       </c>
       <c r="AF108" t="inlineStr">
@@ -12929,7 +12929,7 @@
       </c>
       <c r="AE109" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF109" t="inlineStr">
@@ -13045,7 +13045,7 @@
       </c>
       <c r="AE110" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF110" t="inlineStr">
@@ -13167,7 +13167,7 @@
       <c r="AD111" t="inlineStr"/>
       <c r="AE111" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="AF111" t="inlineStr">
@@ -13279,7 +13279,7 @@
       </c>
       <c r="AE112" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:38</t>
+          <t>2026-09-18 08:21:28</t>
         </is>
       </c>
       <c r="AF112" t="inlineStr">
@@ -13407,7 +13407,7 @@
       </c>
       <c r="AE113" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="AF113" t="inlineStr">
@@ -13527,7 +13527,7 @@
       </c>
       <c r="AE114" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF114" t="inlineStr">
@@ -13647,7 +13647,7 @@
       </c>
       <c r="AE115" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF115" t="inlineStr">
@@ -13757,7 +13757,7 @@
       </c>
       <c r="AE116" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF116" t="inlineStr">
@@ -13873,7 +13873,7 @@
       </c>
       <c r="AE117" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF117" t="inlineStr">
@@ -13985,7 +13985,7 @@
       </c>
       <c r="AE118" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF118" t="inlineStr">
@@ -14095,7 +14095,7 @@
       </c>
       <c r="AE119" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF119" t="inlineStr">
@@ -14205,7 +14205,7 @@
       </c>
       <c r="AE120" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF120" t="inlineStr">
@@ -14329,7 +14329,7 @@
       </c>
       <c r="AE121" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF121" t="inlineStr">
@@ -14445,7 +14445,7 @@
       </c>
       <c r="AE122" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF122" t="inlineStr">
@@ -14565,7 +14565,7 @@
       </c>
       <c r="AE123" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="AF123" t="inlineStr">
@@ -14677,7 +14677,7 @@
       </c>
       <c r="AE124" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF124" t="inlineStr">
@@ -14797,7 +14797,7 @@
       </c>
       <c r="AE125" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF125" t="inlineStr">
@@ -14907,7 +14907,7 @@
       </c>
       <c r="AE126" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF126" t="inlineStr">
@@ -15017,7 +15017,7 @@
       </c>
       <c r="AE127" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF127" t="inlineStr">
@@ -15137,7 +15137,7 @@
       </c>
       <c r="AE128" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="AF128" t="inlineStr">
@@ -15251,7 +15251,7 @@
       </c>
       <c r="AE129" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF129" t="inlineStr">
@@ -15365,7 +15365,7 @@
       </c>
       <c r="AE130" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF130" t="inlineStr">
@@ -15485,7 +15485,7 @@
       </c>
       <c r="AE131" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="AF131" t="inlineStr">
@@ -15595,7 +15595,7 @@
       </c>
       <c r="AE132" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF132" t="inlineStr">
@@ -15711,7 +15711,7 @@
       </c>
       <c r="AE133" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF133" t="inlineStr">
@@ -15823,7 +15823,7 @@
       </c>
       <c r="AE134" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:38</t>
+          <t>2026-09-18 08:21:28</t>
         </is>
       </c>
       <c r="AF134" t="inlineStr">
@@ -15935,7 +15935,7 @@
       </c>
       <c r="AE135" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF135" t="inlineStr">
@@ -16049,7 +16049,7 @@
       </c>
       <c r="AE136" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF136" t="inlineStr">
@@ -16163,7 +16163,7 @@
       </c>
       <c r="AE137" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF137" t="inlineStr">
@@ -16277,7 +16277,7 @@
       </c>
       <c r="AE138" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:36</t>
+          <t>2026-09-18 08:21:26</t>
         </is>
       </c>
       <c r="AF138" t="inlineStr">
@@ -16387,7 +16387,7 @@
       </c>
       <c r="AE139" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF139" t="inlineStr">
@@ -16497,7 +16497,7 @@
       </c>
       <c r="AE140" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF140" t="inlineStr">
@@ -16607,7 +16607,7 @@
       </c>
       <c r="AE141" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF141" t="inlineStr">
@@ -16721,7 +16721,7 @@
       </c>
       <c r="AE142" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF142" t="inlineStr">
@@ -16835,7 +16835,7 @@
       </c>
       <c r="AE143" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF143" t="inlineStr">
@@ -16963,7 +16963,7 @@
       </c>
       <c r="AE144" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="AF144" t="inlineStr">
@@ -17091,7 +17091,7 @@
       </c>
       <c r="AE145" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="AF145" t="inlineStr">
@@ -17201,7 +17201,7 @@
       </c>
       <c r="AE146" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF146" t="inlineStr">
@@ -17311,7 +17311,7 @@
       </c>
       <c r="AE147" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF147" t="inlineStr">
@@ -17431,7 +17431,7 @@
       </c>
       <c r="AE148" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="AF148" t="inlineStr">
@@ -17545,7 +17545,7 @@
       </c>
       <c r="AE149" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF149" t="inlineStr">
@@ -17655,7 +17655,7 @@
       </c>
       <c r="AE150" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF150" t="inlineStr">
@@ -17783,7 +17783,7 @@
       </c>
       <c r="AE151" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="AF151" t="inlineStr">
@@ -17905,7 +17905,7 @@
       <c r="AD152" t="inlineStr"/>
       <c r="AE152" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="AF152" t="inlineStr">
@@ -18033,7 +18033,7 @@
       </c>
       <c r="AE153" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="AF153" t="inlineStr">
@@ -18149,7 +18149,7 @@
       </c>
       <c r="AE154" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:51</t>
+          <t>2026-09-18 08:21:44</t>
         </is>
       </c>
       <c r="AF154" t="inlineStr">
@@ -18277,7 +18277,7 @@
       </c>
       <c r="AE155" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="AF155" t="inlineStr">
@@ -18409,7 +18409,7 @@
       </c>
       <c r="AE156" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="AF156" t="inlineStr">
@@ -18523,7 +18523,7 @@
       </c>
       <c r="AE157" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF157" t="inlineStr">
@@ -18645,7 +18645,7 @@
       <c r="AD158" t="inlineStr"/>
       <c r="AE158" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="AF158" t="inlineStr">
@@ -18757,7 +18757,7 @@
       </c>
       <c r="AE159" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF159" t="inlineStr">
@@ -18857,7 +18857,7 @@
       </c>
       <c r="AE160" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF160" t="inlineStr">
@@ -18967,7 +18967,7 @@
       </c>
       <c r="AE161" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF161" t="inlineStr">
@@ -19083,7 +19083,7 @@
       </c>
       <c r="AE162" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF162" t="inlineStr">
@@ -19199,7 +19199,7 @@
       </c>
       <c r="AE163" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF163" t="inlineStr">
@@ -19327,7 +19327,7 @@
       </c>
       <c r="AE164" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="AF164" t="inlineStr">
@@ -19437,7 +19437,7 @@
       </c>
       <c r="AE165" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF165" t="inlineStr">
@@ -19551,7 +19551,7 @@
       </c>
       <c r="AE166" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF166" t="inlineStr">
@@ -19665,7 +19665,7 @@
       </c>
       <c r="AE167" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF167" t="inlineStr">
@@ -19779,7 +19779,7 @@
       </c>
       <c r="AE168" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF168" t="inlineStr">
@@ -19889,7 +19889,7 @@
       </c>
       <c r="AE169" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF169" t="inlineStr">
@@ -20003,7 +20003,7 @@
       </c>
       <c r="AE170" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF170" t="inlineStr">
@@ -20113,7 +20113,7 @@
       </c>
       <c r="AE171" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF171" t="inlineStr">
@@ -20225,7 +20225,7 @@
       </c>
       <c r="AE172" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF172" t="inlineStr">
@@ -20341,7 +20341,7 @@
       </c>
       <c r="AE173" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:51</t>
+          <t>2026-09-18 08:21:44</t>
         </is>
       </c>
       <c r="AF173" t="inlineStr">
@@ -20457,7 +20457,7 @@
       </c>
       <c r="AE174" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF174" t="inlineStr">
@@ -20569,7 +20569,7 @@
       </c>
       <c r="AE175" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF175" t="inlineStr">
@@ -20681,7 +20681,7 @@
       </c>
       <c r="AE176" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF176" t="inlineStr">
@@ -20809,7 +20809,7 @@
       </c>
       <c r="AE177" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:38</t>
+          <t>2026-09-18 08:21:28</t>
         </is>
       </c>
       <c r="AF177" t="inlineStr">
@@ -20919,7 +20919,7 @@
       </c>
       <c r="AE178" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF178" t="inlineStr">
@@ -21039,7 +21039,7 @@
       </c>
       <c r="AE179" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="AF179" t="inlineStr">
@@ -21161,7 +21161,7 @@
       <c r="AD180" t="inlineStr"/>
       <c r="AE180" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="AF180" t="inlineStr">
@@ -21287,7 +21287,7 @@
       <c r="AD181" t="inlineStr"/>
       <c r="AE181" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="AF181" t="inlineStr">
@@ -21413,7 +21413,7 @@
       <c r="AD182" t="inlineStr"/>
       <c r="AE182" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="AF182" t="inlineStr">
@@ -21529,7 +21529,7 @@
       </c>
       <c r="AE183" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:51</t>
+          <t>2026-09-18 08:21:44</t>
         </is>
       </c>
       <c r="AF183" t="inlineStr">
@@ -21643,7 +21643,7 @@
       </c>
       <c r="AE184" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF184" t="inlineStr">
@@ -21757,7 +21757,7 @@
       </c>
       <c r="AE185" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF185" t="inlineStr">
@@ -21871,7 +21871,7 @@
       </c>
       <c r="AE186" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF186" t="inlineStr">
@@ -21991,7 +21991,7 @@
       </c>
       <c r="AE187" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="AF187" t="inlineStr">
@@ -22111,7 +22111,7 @@
       </c>
       <c r="AE188" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="AF188" t="inlineStr">
@@ -22221,7 +22221,7 @@
       </c>
       <c r="AE189" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF189" t="inlineStr">
@@ -22331,7 +22331,7 @@
       </c>
       <c r="AE190" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF190" t="inlineStr">
@@ -22441,7 +22441,7 @@
       </c>
       <c r="AE191" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF191" t="inlineStr">
@@ -22557,7 +22557,7 @@
       </c>
       <c r="AE192" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF192" t="inlineStr">
@@ -22685,7 +22685,7 @@
       </c>
       <c r="AE193" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="AF193" t="inlineStr">
@@ -22797,7 +22797,7 @@
       </c>
       <c r="AE194" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF194" t="inlineStr">
@@ -22909,7 +22909,7 @@
       </c>
       <c r="AE195" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF195" t="inlineStr">
@@ -23027,7 +23027,7 @@
       </c>
       <c r="AE196" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:36</t>
+          <t>2026-09-18 08:21:26</t>
         </is>
       </c>
       <c r="AF196" t="inlineStr">
@@ -23137,7 +23137,7 @@
       </c>
       <c r="AE197" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF197" t="inlineStr">
@@ -23247,7 +23247,7 @@
       </c>
       <c r="AE198" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF198" t="inlineStr">
@@ -23359,7 +23359,7 @@
       </c>
       <c r="AE199" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF199" t="inlineStr">
@@ -23469,7 +23469,7 @@
       </c>
       <c r="AE200" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF200" t="inlineStr">
@@ -23589,7 +23589,7 @@
       </c>
       <c r="AE201" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="AF201" t="inlineStr">
@@ -23705,7 +23705,7 @@
       </c>
       <c r="AE202" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF202" t="inlineStr">
@@ -23821,7 +23821,7 @@
       </c>
       <c r="AE203" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF203" t="inlineStr">
@@ -23949,7 +23949,7 @@
       </c>
       <c r="AE204" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="AF204" t="inlineStr">
@@ -24061,7 +24061,7 @@
       </c>
       <c r="AE205" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF205" t="inlineStr">
@@ -24173,7 +24173,7 @@
       </c>
       <c r="AE206" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF206" t="inlineStr">
@@ -24285,7 +24285,7 @@
       </c>
       <c r="AE207" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF207" t="inlineStr">
@@ -24401,7 +24401,7 @@
       </c>
       <c r="AE208" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF208" t="inlineStr">
@@ -24511,7 +24511,7 @@
       </c>
       <c r="AE209" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF209" t="inlineStr">
@@ -24631,7 +24631,7 @@
       </c>
       <c r="AE210" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="AF210" t="inlineStr">
@@ -24741,7 +24741,7 @@
       </c>
       <c r="AE211" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF211" t="inlineStr">
@@ -24861,7 +24861,7 @@
       </c>
       <c r="AE212" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="AF212" t="inlineStr">
@@ -24971,7 +24971,7 @@
       </c>
       <c r="AE213" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF213" t="inlineStr">
@@ -25085,7 +25085,7 @@
       </c>
       <c r="AE214" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:36</t>
+          <t>2026-09-18 08:21:26</t>
         </is>
       </c>
       <c r="AF214" t="inlineStr">
@@ -25195,7 +25195,7 @@
       </c>
       <c r="AE215" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF215" t="inlineStr">
@@ -25305,7 +25305,7 @@
       </c>
       <c r="AE216" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF216" t="inlineStr">
@@ -25419,7 +25419,7 @@
       </c>
       <c r="AE217" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF217" t="inlineStr">
@@ -25529,7 +25529,7 @@
       </c>
       <c r="AE218" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF218" t="inlineStr">
@@ -25641,7 +25641,7 @@
       </c>
       <c r="AE219" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF219" t="inlineStr">
@@ -25751,7 +25751,7 @@
       </c>
       <c r="AE220" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF220" t="inlineStr">
@@ -25871,7 +25871,7 @@
       </c>
       <c r="AE221" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="AF221" t="inlineStr">
@@ -25983,7 +25983,7 @@
       </c>
       <c r="AE222" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF222" t="inlineStr">
@@ -26093,7 +26093,7 @@
       </c>
       <c r="AE223" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF223" t="inlineStr">
@@ -26217,7 +26217,7 @@
       </c>
       <c r="AE224" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:38</t>
+          <t>2026-09-18 08:21:28</t>
         </is>
       </c>
       <c r="AF224" t="inlineStr">
@@ -26341,7 +26341,7 @@
       </c>
       <c r="AE225" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:38</t>
+          <t>2026-09-18 08:21:28</t>
         </is>
       </c>
       <c r="AF225" t="inlineStr">
@@ -26451,7 +26451,7 @@
       </c>
       <c r="AE226" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF226" t="inlineStr">
@@ -26561,7 +26561,7 @@
       </c>
       <c r="AE227" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF227" t="inlineStr">
@@ -26671,7 +26671,7 @@
       </c>
       <c r="AE228" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF228" t="inlineStr">
@@ -26783,7 +26783,7 @@
       </c>
       <c r="AE229" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF229" t="inlineStr">
@@ -26893,7 +26893,7 @@
       </c>
       <c r="AE230" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF230" t="inlineStr">
@@ -27003,7 +27003,7 @@
       </c>
       <c r="AE231" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF231" t="inlineStr">
@@ -27131,7 +27131,7 @@
       </c>
       <c r="AE232" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="AF232" t="inlineStr">
@@ -27237,7 +27237,7 @@
       </c>
       <c r="AE233" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF233" t="inlineStr">
@@ -27349,7 +27349,7 @@
       </c>
       <c r="AE234" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF234" t="inlineStr">
@@ -27465,7 +27465,7 @@
       </c>
       <c r="AE235" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:51</t>
+          <t>2026-09-18 08:21:44</t>
         </is>
       </c>
       <c r="AF235" t="inlineStr">
@@ -27581,7 +27581,7 @@
       </c>
       <c r="AE236" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:51</t>
+          <t>2026-09-18 08:21:44</t>
         </is>
       </c>
       <c r="AF236" t="inlineStr">
@@ -27691,7 +27691,7 @@
       </c>
       <c r="AE237" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF237" t="inlineStr">
@@ -27801,7 +27801,7 @@
       </c>
       <c r="AE238" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF238" t="inlineStr">
@@ -27917,7 +27917,7 @@
       </c>
       <c r="AE239" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:51</t>
+          <t>2026-09-18 08:21:44</t>
         </is>
       </c>
       <c r="AF239" t="inlineStr">
@@ -28033,7 +28033,7 @@
       </c>
       <c r="AE240" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:51</t>
+          <t>2026-09-18 08:21:44</t>
         </is>
       </c>
       <c r="AF240" t="inlineStr">
@@ -28143,7 +28143,7 @@
       </c>
       <c r="AE241" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF241" t="inlineStr">
@@ -28259,7 +28259,7 @@
       </c>
       <c r="AE242" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:51</t>
+          <t>2026-09-18 08:21:44</t>
         </is>
       </c>
       <c r="AF242" t="inlineStr">
@@ -28375,7 +28375,7 @@
       </c>
       <c r="AE243" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:51</t>
+          <t>2026-09-18 08:21:44</t>
         </is>
       </c>
       <c r="AF243" t="inlineStr">
@@ -28485,7 +28485,7 @@
       </c>
       <c r="AE244" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF244" t="inlineStr">
@@ -28595,7 +28595,7 @@
       </c>
       <c r="AE245" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF245" t="inlineStr">
@@ -28705,7 +28705,7 @@
       </c>
       <c r="AE246" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF246" t="inlineStr">
@@ -28805,7 +28805,7 @@
       </c>
       <c r="AE247" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF247" t="inlineStr">
@@ -28921,7 +28921,7 @@
       </c>
       <c r="AE248" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:51</t>
+          <t>2026-09-18 08:21:44</t>
         </is>
       </c>
       <c r="AF248" t="inlineStr">
@@ -29031,7 +29031,7 @@
       </c>
       <c r="AE249" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF249" t="inlineStr">
@@ -29143,7 +29143,7 @@
       </c>
       <c r="AE250" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF250" t="inlineStr">
@@ -29253,7 +29253,7 @@
       </c>
       <c r="AE251" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF251" t="inlineStr">
@@ -29373,7 +29373,7 @@
       </c>
       <c r="AE252" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="AF252" t="inlineStr">
@@ -29485,7 +29485,7 @@
       </c>
       <c r="AE253" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF253" t="inlineStr">
@@ -29595,7 +29595,7 @@
       </c>
       <c r="AE254" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF254" t="inlineStr">
@@ -29707,7 +29707,7 @@
       </c>
       <c r="AE255" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF255" t="inlineStr">
@@ -29823,7 +29823,7 @@
       </c>
       <c r="AE256" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF256" t="inlineStr">
@@ -29935,7 +29935,7 @@
       </c>
       <c r="AE257" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF257" t="inlineStr">
@@ -30045,7 +30045,7 @@
       </c>
       <c r="AE258" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF258" t="inlineStr">
@@ -30161,7 +30161,7 @@
       </c>
       <c r="AE259" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF259" t="inlineStr">
@@ -30271,7 +30271,7 @@
       </c>
       <c r="AE260" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF260" t="inlineStr">
@@ -30397,7 +30397,7 @@
       <c r="AD261" t="inlineStr"/>
       <c r="AE261" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="AF261" t="inlineStr">
@@ -30525,7 +30525,7 @@
       </c>
       <c r="AE262" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="AF262" t="inlineStr">
@@ -30637,7 +30637,7 @@
       </c>
       <c r="AE263" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF263" t="inlineStr">
@@ -30737,7 +30737,7 @@
       </c>
       <c r="AE264" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF264" t="inlineStr">
@@ -30837,7 +30837,7 @@
       </c>
       <c r="AE265" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF265" t="inlineStr">
@@ -30951,7 +30951,7 @@
       </c>
       <c r="AE266" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF266" t="inlineStr">
@@ -31065,7 +31065,7 @@
       </c>
       <c r="AE267" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF267" t="inlineStr">
@@ -31165,7 +31165,7 @@
       </c>
       <c r="AE268" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF268" t="inlineStr">
@@ -31285,7 +31285,7 @@
       </c>
       <c r="AE269" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="AF269" t="inlineStr">
@@ -31397,7 +31397,7 @@
       </c>
       <c r="AE270" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF270" t="inlineStr">
@@ -31509,7 +31509,7 @@
       </c>
       <c r="AE271" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF271" t="inlineStr">
@@ -31623,7 +31623,7 @@
       </c>
       <c r="AE272" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF272" t="inlineStr">
@@ -31737,7 +31737,7 @@
       </c>
       <c r="AE273" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:36</t>
+          <t>2026-09-18 08:21:26</t>
         </is>
       </c>
       <c r="AF273" t="inlineStr">
@@ -31851,7 +31851,7 @@
       </c>
       <c r="AE274" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:36</t>
+          <t>2026-09-18 08:21:26</t>
         </is>
       </c>
       <c r="AF274" t="inlineStr">
@@ -31983,7 +31983,7 @@
       </c>
       <c r="AE275" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="AF275" t="inlineStr">
@@ -32111,7 +32111,7 @@
       </c>
       <c r="AE276" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="AF276" t="inlineStr">
@@ -32239,7 +32239,7 @@
       </c>
       <c r="AE277" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="AF277" t="inlineStr">
@@ -32367,7 +32367,7 @@
       </c>
       <c r="AE278" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="AF278" t="inlineStr">
@@ -32479,7 +32479,7 @@
       </c>
       <c r="AE279" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF279" t="inlineStr">
@@ -32591,7 +32591,7 @@
       </c>
       <c r="AE280" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF280" t="inlineStr">
@@ -32701,7 +32701,7 @@
       </c>
       <c r="AE281" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF281" t="inlineStr">
@@ -32811,7 +32811,7 @@
       </c>
       <c r="AE282" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF282" t="inlineStr">
@@ -32939,7 +32939,7 @@
       </c>
       <c r="AE283" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="AF283" t="inlineStr">
@@ -33049,7 +33049,7 @@
       </c>
       <c r="AE284" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF284" t="inlineStr">
@@ -33177,7 +33177,7 @@
       </c>
       <c r="AE285" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="AF285" t="inlineStr">
@@ -33289,7 +33289,7 @@
       </c>
       <c r="AE286" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF286" t="inlineStr">
@@ -33401,7 +33401,7 @@
       </c>
       <c r="AE287" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF287" t="inlineStr">
@@ -33511,7 +33511,7 @@
       </c>
       <c r="AE288" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF288" t="inlineStr">
@@ -33631,7 +33631,7 @@
       </c>
       <c r="AE289" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="AF289" t="inlineStr">
@@ -33755,7 +33755,7 @@
       </c>
       <c r="AE290" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="AF290" t="inlineStr">
@@ -33879,7 +33879,7 @@
       </c>
       <c r="AE291" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="AF291" t="inlineStr">
@@ -34003,7 +34003,7 @@
       </c>
       <c r="AE292" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="AF292" t="inlineStr">
@@ -34115,7 +34115,7 @@
       </c>
       <c r="AE293" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF293" t="inlineStr">
@@ -34231,7 +34231,7 @@
       </c>
       <c r="AE294" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF294" t="inlineStr">
@@ -34343,7 +34343,7 @@
       </c>
       <c r="AE295" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:38</t>
+          <t>2026-09-18 08:21:28</t>
         </is>
       </c>
       <c r="AF295" t="inlineStr">
@@ -34471,7 +34471,7 @@
       </c>
       <c r="AE296" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:38</t>
+          <t>2026-09-18 08:21:28</t>
         </is>
       </c>
       <c r="AF296" t="inlineStr">
@@ -34599,7 +34599,7 @@
       </c>
       <c r="AE297" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="AF297" t="inlineStr">
@@ -34711,7 +34711,7 @@
       </c>
       <c r="AE298" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF298" t="inlineStr">
@@ -34823,7 +34823,7 @@
       </c>
       <c r="AE299" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF299" t="inlineStr">
@@ -34933,7 +34933,7 @@
       </c>
       <c r="AE300" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF300" t="inlineStr">
@@ -35043,7 +35043,7 @@
       </c>
       <c r="AE301" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF301" t="inlineStr">
@@ -35159,7 +35159,7 @@
       </c>
       <c r="AE302" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF302" t="inlineStr">
@@ -35271,7 +35271,7 @@
       </c>
       <c r="AE303" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF303" t="inlineStr">
@@ -35391,7 +35391,7 @@
       </c>
       <c r="AE304" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="AF304" t="inlineStr">
@@ -35519,7 +35519,7 @@
       </c>
       <c r="AE305" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="AF305" t="inlineStr">
@@ -35635,7 +35635,7 @@
       </c>
       <c r="AE306" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF306" t="inlineStr">
@@ -35735,7 +35735,7 @@
       </c>
       <c r="AE307" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF307" t="inlineStr">
@@ -35847,7 +35847,7 @@
       </c>
       <c r="AE308" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF308" t="inlineStr">
@@ -35975,7 +35975,7 @@
       </c>
       <c r="AE309" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="AF309" t="inlineStr">
@@ -36099,7 +36099,7 @@
       </c>
       <c r="AE310" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:38</t>
+          <t>2026-09-18 08:21:28</t>
         </is>
       </c>
       <c r="AF310" t="inlineStr">
@@ -36211,7 +36211,7 @@
       </c>
       <c r="AE311" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF311" t="inlineStr">
@@ -36321,7 +36321,7 @@
       </c>
       <c r="AE312" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF312" t="inlineStr">
@@ -36431,7 +36431,7 @@
       </c>
       <c r="AE313" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF313" t="inlineStr">
@@ -36541,7 +36541,7 @@
       </c>
       <c r="AE314" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF314" t="inlineStr">
@@ -36651,7 +36651,7 @@
       </c>
       <c r="AE315" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF315" t="inlineStr">
@@ -36771,7 +36771,7 @@
       </c>
       <c r="AE316" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="AF316" t="inlineStr">
@@ -36881,7 +36881,7 @@
       </c>
       <c r="AE317" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF317" t="inlineStr">
@@ -36991,7 +36991,7 @@
       </c>
       <c r="AE318" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF318" t="inlineStr">
@@ -37101,7 +37101,7 @@
       </c>
       <c r="AE319" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF319" t="inlineStr">
@@ -37221,7 +37221,7 @@
       </c>
       <c r="AE320" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="AF320" t="inlineStr">
@@ -37341,7 +37341,7 @@
       </c>
       <c r="AE321" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="AF321" t="inlineStr">
@@ -37461,7 +37461,7 @@
       </c>
       <c r="AE322" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="AF322" t="inlineStr">
@@ -37581,7 +37581,7 @@
       </c>
       <c r="AE323" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="AF323" t="inlineStr">
@@ -37697,7 +37697,7 @@
       </c>
       <c r="AE324" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:51</t>
+          <t>2026-09-18 08:21:44</t>
         </is>
       </c>
       <c r="AF324" t="inlineStr">
@@ -37813,7 +37813,7 @@
       </c>
       <c r="AE325" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:51</t>
+          <t>2026-09-18 08:21:44</t>
         </is>
       </c>
       <c r="AF325" t="inlineStr">
@@ -37929,7 +37929,7 @@
       </c>
       <c r="AE326" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:51</t>
+          <t>2026-09-18 08:21:44</t>
         </is>
       </c>
       <c r="AF326" t="inlineStr">
@@ -38041,7 +38041,7 @@
       </c>
       <c r="AE327" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF327" t="inlineStr">
@@ -38157,7 +38157,7 @@
       </c>
       <c r="AE328" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:51</t>
+          <t>2026-09-18 08:21:44</t>
         </is>
       </c>
       <c r="AF328" t="inlineStr">
@@ -38277,7 +38277,7 @@
       </c>
       <c r="AE329" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="AF329" t="inlineStr">
@@ -38389,7 +38389,7 @@
       </c>
       <c r="AE330" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF330" t="inlineStr">
@@ -38505,7 +38505,7 @@
       </c>
       <c r="AE331" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:51</t>
+          <t>2026-09-18 08:21:44</t>
         </is>
       </c>
       <c r="AF331" t="inlineStr">
@@ -38621,7 +38621,7 @@
       </c>
       <c r="AE332" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:51</t>
+          <t>2026-09-18 08:21:44</t>
         </is>
       </c>
       <c r="AF332" t="inlineStr">
@@ -38737,7 +38737,7 @@
       </c>
       <c r="AE333" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:51</t>
+          <t>2026-09-18 08:21:44</t>
         </is>
       </c>
       <c r="AF333" t="inlineStr">
@@ -38853,7 +38853,7 @@
       </c>
       <c r="AE334" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:51</t>
+          <t>2026-09-18 08:21:44</t>
         </is>
       </c>
       <c r="AF334" t="inlineStr">
@@ -38967,7 +38967,7 @@
       </c>
       <c r="AE335" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:36</t>
+          <t>2026-09-18 08:21:26</t>
         </is>
       </c>
       <c r="AF335" t="inlineStr">
@@ -39083,7 +39083,7 @@
       </c>
       <c r="AE336" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:51</t>
+          <t>2026-09-18 08:21:44</t>
         </is>
       </c>
       <c r="AF336" t="inlineStr">
@@ -39199,7 +39199,7 @@
       </c>
       <c r="AE337" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:51</t>
+          <t>2026-09-18 08:21:44</t>
         </is>
       </c>
       <c r="AF337" t="inlineStr">
@@ -39315,7 +39315,7 @@
       </c>
       <c r="AE338" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:51</t>
+          <t>2026-09-18 08:21:44</t>
         </is>
       </c>
       <c r="AF338" t="inlineStr">
@@ -39425,7 +39425,7 @@
       </c>
       <c r="AE339" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF339" t="inlineStr">
@@ -39541,7 +39541,7 @@
       </c>
       <c r="AE340" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF340" t="inlineStr">
@@ -39653,7 +39653,7 @@
       </c>
       <c r="AE341" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF341" t="inlineStr">
@@ -39763,7 +39763,7 @@
       </c>
       <c r="AE342" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF342" t="inlineStr">
@@ -39875,7 +39875,7 @@
       </c>
       <c r="AE343" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF343" t="inlineStr">
@@ -39987,7 +39987,7 @@
       </c>
       <c r="AE344" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF344" t="inlineStr">
@@ -40099,7 +40099,7 @@
       </c>
       <c r="AE345" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF345" t="inlineStr">
@@ -40219,7 +40219,7 @@
       </c>
       <c r="AE346" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="AF346" t="inlineStr">
@@ -40347,7 +40347,7 @@
       </c>
       <c r="AE347" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="AF347" t="inlineStr">
@@ -40467,7 +40467,7 @@
       </c>
       <c r="AE348" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="AF348" t="inlineStr">
@@ -40595,7 +40595,7 @@
       </c>
       <c r="AE349" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="AF349" t="inlineStr">
@@ -40707,7 +40707,7 @@
       </c>
       <c r="AE350" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF350" t="inlineStr">
@@ -40817,7 +40817,7 @@
       </c>
       <c r="AE351" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF351" t="inlineStr">
@@ -40927,7 +40927,7 @@
       </c>
       <c r="AE352" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF352" t="inlineStr">
@@ -41039,7 +41039,7 @@
       </c>
       <c r="AE353" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF353" t="inlineStr">
@@ -41151,7 +41151,7 @@
       </c>
       <c r="AE354" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF354" t="inlineStr">
@@ -41261,7 +41261,7 @@
       </c>
       <c r="AE355" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF355" t="inlineStr">
@@ -41377,7 +41377,7 @@
       </c>
       <c r="AE356" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF356" t="inlineStr">
@@ -41487,7 +41487,7 @@
       </c>
       <c r="AE357" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF357" t="inlineStr">
@@ -41599,7 +41599,7 @@
       </c>
       <c r="AE358" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF358" t="inlineStr">
@@ -41709,7 +41709,7 @@
       </c>
       <c r="AE359" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF359" t="inlineStr">
@@ -41819,7 +41819,7 @@
       </c>
       <c r="AE360" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF360" t="inlineStr">
@@ -41947,7 +41947,7 @@
       </c>
       <c r="AE361" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="AF361" t="inlineStr">
@@ -42059,7 +42059,7 @@
       </c>
       <c r="AE362" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF362" t="inlineStr">
@@ -42187,7 +42187,7 @@
       </c>
       <c r="AE363" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="AF363" t="inlineStr">
@@ -42299,7 +42299,7 @@
       </c>
       <c r="AE364" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF364" t="inlineStr">
@@ -42409,7 +42409,7 @@
       </c>
       <c r="AE365" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF365" t="inlineStr">
@@ -42519,7 +42519,7 @@
       </c>
       <c r="AE366" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF366" t="inlineStr">
@@ -42629,7 +42629,7 @@
       </c>
       <c r="AE367" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF367" t="inlineStr">
@@ -42741,7 +42741,7 @@
       </c>
       <c r="AE368" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF368" t="inlineStr">
@@ -42851,7 +42851,7 @@
       </c>
       <c r="AE369" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF369" t="inlineStr">
@@ -42979,7 +42979,7 @@
       </c>
       <c r="AE370" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="AF370" t="inlineStr">
@@ -43091,7 +43091,7 @@
       </c>
       <c r="AE371" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF371" t="inlineStr">
@@ -43201,7 +43201,7 @@
       </c>
       <c r="AE372" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF372" t="inlineStr">
@@ -43311,7 +43311,7 @@
       </c>
       <c r="AE373" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF373" t="inlineStr">
@@ -43421,7 +43421,7 @@
       </c>
       <c r="AE374" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF374" t="inlineStr">
@@ -43531,7 +43531,7 @@
       </c>
       <c r="AE375" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF375" t="inlineStr">
@@ -43641,7 +43641,7 @@
       </c>
       <c r="AE376" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF376" t="inlineStr">
@@ -43753,7 +43753,7 @@
       </c>
       <c r="AE377" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF377" t="inlineStr">
@@ -43881,7 +43881,7 @@
       </c>
       <c r="AE378" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="AF378" t="inlineStr">
@@ -43991,7 +43991,7 @@
       </c>
       <c r="AE379" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF379" t="inlineStr">
@@ -44101,7 +44101,7 @@
       </c>
       <c r="AE380" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF380" t="inlineStr">
@@ -44213,7 +44213,7 @@
       </c>
       <c r="AE381" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:38</t>
+          <t>2026-09-18 08:21:28</t>
         </is>
       </c>
       <c r="AF381" t="inlineStr">
@@ -44323,7 +44323,7 @@
       </c>
       <c r="AE382" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF382" t="inlineStr">
@@ -44435,7 +44435,7 @@
       </c>
       <c r="AE383" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF383" t="inlineStr">
@@ -44563,7 +44563,7 @@
       </c>
       <c r="AE384" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="AF384" t="inlineStr">
@@ -44673,7 +44673,7 @@
       </c>
       <c r="AE385" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF385" t="inlineStr">
@@ -44785,7 +44785,7 @@
       </c>
       <c r="AE386" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF386" t="inlineStr">
@@ -44895,7 +44895,7 @@
       </c>
       <c r="AE387" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF387" t="inlineStr">
@@ -45005,7 +45005,7 @@
       </c>
       <c r="AE388" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF388" t="inlineStr">
@@ -45115,7 +45115,7 @@
       </c>
       <c r="AE389" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF389" t="inlineStr">
@@ -45215,7 +45215,7 @@
       </c>
       <c r="AE390" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF390" t="inlineStr">
@@ -45325,7 +45325,7 @@
       </c>
       <c r="AE391" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF391" t="inlineStr">
@@ -45425,7 +45425,7 @@
       </c>
       <c r="AE392" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF392" t="inlineStr">
@@ -45535,7 +45535,7 @@
       </c>
       <c r="AE393" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF393" t="inlineStr">
@@ -45663,7 +45663,7 @@
       </c>
       <c r="AE394" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="AF394" t="inlineStr">
@@ -45773,7 +45773,7 @@
       </c>
       <c r="AE395" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF395" t="inlineStr">
@@ -45883,7 +45883,7 @@
       </c>
       <c r="AE396" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF396" t="inlineStr">
@@ -45993,7 +45993,7 @@
       </c>
       <c r="AE397" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF397" t="inlineStr">
@@ -46103,7 +46103,7 @@
       </c>
       <c r="AE398" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF398" t="inlineStr">
@@ -46213,7 +46213,7 @@
       </c>
       <c r="AE399" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF399" t="inlineStr">
@@ -46323,7 +46323,7 @@
       </c>
       <c r="AE400" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF400" t="inlineStr">
@@ -46433,7 +46433,7 @@
       </c>
       <c r="AE401" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF401" t="inlineStr">
@@ -46543,7 +46543,7 @@
       </c>
       <c r="AE402" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF402" t="inlineStr">
@@ -46671,7 +46671,7 @@
       </c>
       <c r="AE403" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="AF403" t="inlineStr">
@@ -46783,7 +46783,7 @@
       </c>
       <c r="AE404" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF404" t="inlineStr">
@@ -46883,7 +46883,7 @@
       </c>
       <c r="AE405" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF405" t="inlineStr">
@@ -46993,7 +46993,7 @@
       </c>
       <c r="AE406" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF406" t="inlineStr">
@@ -47107,7 +47107,7 @@
       </c>
       <c r="AE407" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF407" t="inlineStr">
@@ -47217,7 +47217,7 @@
       </c>
       <c r="AE408" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF408" t="inlineStr">
@@ -47317,7 +47317,7 @@
       </c>
       <c r="AE409" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF409" t="inlineStr">
@@ -47429,7 +47429,7 @@
       </c>
       <c r="AE410" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF410" t="inlineStr">
@@ -47541,7 +47541,7 @@
       </c>
       <c r="AE411" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF411" t="inlineStr">
@@ -47651,7 +47651,7 @@
       </c>
       <c r="AE412" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF412" t="inlineStr">
@@ -47763,7 +47763,7 @@
       </c>
       <c r="AE413" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF413" t="inlineStr">
@@ -47875,7 +47875,7 @@
       </c>
       <c r="AE414" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF414" t="inlineStr">
@@ -47985,7 +47985,7 @@
       </c>
       <c r="AE415" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF415" t="inlineStr">
@@ -48113,7 +48113,7 @@
       </c>
       <c r="AE416" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="AF416" t="inlineStr">
@@ -48245,7 +48245,7 @@
       </c>
       <c r="AE417" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="AF417" t="inlineStr">
@@ -48377,7 +48377,7 @@
       </c>
       <c r="AE418" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="AF418" t="inlineStr">
@@ -48509,7 +48509,7 @@
       </c>
       <c r="AE419" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="AF419" t="inlineStr">
@@ -48633,7 +48633,7 @@
       </c>
       <c r="AE420" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:38</t>
+          <t>2026-09-18 08:21:28</t>
         </is>
       </c>
       <c r="AF420" t="inlineStr">
@@ -48745,7 +48745,7 @@
       </c>
       <c r="AE421" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF421" t="inlineStr">
@@ -48845,7 +48845,7 @@
       </c>
       <c r="AE422" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF422" t="inlineStr">
@@ -48965,7 +48965,7 @@
       </c>
       <c r="AE423" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="AF423" t="inlineStr">
@@ -49081,7 +49081,7 @@
       </c>
       <c r="AE424" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF424" t="inlineStr">
@@ -49193,7 +49193,7 @@
       </c>
       <c r="AE425" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF425" t="inlineStr">
@@ -49315,7 +49315,7 @@
       <c r="AD426" t="inlineStr"/>
       <c r="AE426" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="AF426" t="inlineStr">
@@ -49427,7 +49427,7 @@
       </c>
       <c r="AE427" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF427" t="inlineStr">
@@ -49537,7 +49537,7 @@
       </c>
       <c r="AE428" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF428" t="inlineStr">
@@ -49647,7 +49647,7 @@
       </c>
       <c r="AE429" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF429" t="inlineStr">
@@ -49757,7 +49757,7 @@
       </c>
       <c r="AE430" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF430" t="inlineStr">
@@ -49867,7 +49867,7 @@
       </c>
       <c r="AE431" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF431" t="inlineStr">
@@ -49995,7 +49995,7 @@
       </c>
       <c r="AE432" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="AF432" t="inlineStr">
@@ -50111,7 +50111,7 @@
       </c>
       <c r="AE433" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF433" t="inlineStr">
@@ -50221,7 +50221,7 @@
       </c>
       <c r="AE434" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF434" t="inlineStr">
@@ -50349,7 +50349,7 @@
       </c>
       <c r="AE435" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="AF435" t="inlineStr">
@@ -50477,7 +50477,7 @@
       </c>
       <c r="AE436" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="AF436" t="inlineStr">
@@ -50605,7 +50605,7 @@
       </c>
       <c r="AE437" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="AF437" t="inlineStr">
@@ -50733,7 +50733,7 @@
       </c>
       <c r="AE438" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="AF438" t="inlineStr">
@@ -50845,7 +50845,7 @@
       </c>
       <c r="AE439" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF439" t="inlineStr">
@@ -50955,7 +50955,7 @@
       </c>
       <c r="AE440" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF440" t="inlineStr">
@@ -51083,7 +51083,7 @@
       </c>
       <c r="AE441" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="AF441" t="inlineStr">
@@ -51195,7 +51195,7 @@
       </c>
       <c r="AE442" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF442" t="inlineStr">
@@ -51307,7 +51307,7 @@
       </c>
       <c r="AE443" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF443" t="inlineStr">
@@ -51423,7 +51423,7 @@
       </c>
       <c r="AE444" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF444" t="inlineStr">
@@ -51535,7 +51535,7 @@
       </c>
       <c r="AE445" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF445" t="inlineStr">
@@ -51647,7 +51647,7 @@
       </c>
       <c r="AE446" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF446" t="inlineStr">
@@ -51759,7 +51759,7 @@
       </c>
       <c r="AE447" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF447" t="inlineStr">
@@ -51871,7 +51871,7 @@
       </c>
       <c r="AE448" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF448" t="inlineStr">
@@ -51991,7 +51991,7 @@
       </c>
       <c r="AE449" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="AF449" t="inlineStr">
@@ -52101,7 +52101,7 @@
       </c>
       <c r="AE450" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF450" t="inlineStr">
@@ -52229,7 +52229,7 @@
       </c>
       <c r="AE451" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="AF451" t="inlineStr">
@@ -52349,7 +52349,7 @@
       </c>
       <c r="AE452" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="AF452" t="inlineStr">
@@ -52461,7 +52461,7 @@
       </c>
       <c r="AE453" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF453" t="inlineStr">
@@ -52573,7 +52573,7 @@
       </c>
       <c r="AE454" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF454" t="inlineStr">
@@ -52673,7 +52673,7 @@
       </c>
       <c r="AE455" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF455" t="inlineStr">
@@ -52789,7 +52789,7 @@
       </c>
       <c r="AE456" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF456" t="inlineStr">
@@ -52899,7 +52899,7 @@
       </c>
       <c r="AE457" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF457" t="inlineStr">
@@ -53011,7 +53011,7 @@
       </c>
       <c r="AE458" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF458" t="inlineStr">
@@ -53121,7 +53121,7 @@
       </c>
       <c r="AE459" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF459" t="inlineStr">
@@ -53233,7 +53233,7 @@
       </c>
       <c r="AE460" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF460" t="inlineStr">
@@ -53345,7 +53345,7 @@
       </c>
       <c r="AE461" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF461" t="inlineStr">
@@ -53445,7 +53445,7 @@
       </c>
       <c r="AE462" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF462" t="inlineStr">
@@ -53555,7 +53555,7 @@
       </c>
       <c r="AE463" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF463" t="inlineStr">
@@ -53667,7 +53667,7 @@
       </c>
       <c r="AE464" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF464" t="inlineStr">
@@ -53777,7 +53777,7 @@
       </c>
       <c r="AE465" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF465" t="inlineStr">
@@ -53887,7 +53887,7 @@
       </c>
       <c r="AE466" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF466" t="inlineStr">
@@ -53999,7 +53999,7 @@
       </c>
       <c r="AE467" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF467" t="inlineStr">
@@ -54109,7 +54109,7 @@
       </c>
       <c r="AE468" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF468" t="inlineStr">
@@ -54219,7 +54219,7 @@
       </c>
       <c r="AE469" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF469" t="inlineStr">
@@ -54329,7 +54329,7 @@
       </c>
       <c r="AE470" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF470" t="inlineStr">
@@ -54449,7 +54449,7 @@
       </c>
       <c r="AE471" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="AF471" t="inlineStr">
@@ -54573,7 +54573,7 @@
       </c>
       <c r="AE472" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:38</t>
+          <t>2026-09-18 08:21:28</t>
         </is>
       </c>
       <c r="AF472" t="inlineStr">
@@ -54683,7 +54683,7 @@
       </c>
       <c r="AE473" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF473" t="inlineStr">
@@ -54795,7 +54795,7 @@
       </c>
       <c r="AE474" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF474" t="inlineStr">
@@ -54905,7 +54905,7 @@
       </c>
       <c r="AE475" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF475" t="inlineStr">
@@ -55017,7 +55017,7 @@
       </c>
       <c r="AE476" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF476" t="inlineStr">
@@ -55129,7 +55129,7 @@
       </c>
       <c r="AE477" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF477" t="inlineStr">
@@ -55239,7 +55239,7 @@
       </c>
       <c r="AE478" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF478" t="inlineStr">
@@ -55349,7 +55349,7 @@
       </c>
       <c r="AE479" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF479" t="inlineStr">
@@ -55459,7 +55459,7 @@
       </c>
       <c r="AE480" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF480" t="inlineStr">
@@ -55569,7 +55569,7 @@
       </c>
       <c r="AE481" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF481" t="inlineStr">
@@ -55679,7 +55679,7 @@
       </c>
       <c r="AE482" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF482" t="inlineStr">
@@ -55789,7 +55789,7 @@
       </c>
       <c r="AE483" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF483" t="inlineStr">
@@ -55901,7 +55901,7 @@
       </c>
       <c r="AE484" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF484" t="inlineStr">
@@ -56013,7 +56013,7 @@
       </c>
       <c r="AE485" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF485" t="inlineStr">
@@ -56125,7 +56125,7 @@
       </c>
       <c r="AE486" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF486" t="inlineStr">
@@ -56235,7 +56235,7 @@
       </c>
       <c r="AE487" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF487" t="inlineStr">
@@ -56347,7 +56347,7 @@
       </c>
       <c r="AE488" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF488" t="inlineStr">
@@ -56447,7 +56447,7 @@
       </c>
       <c r="AE489" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF489" t="inlineStr">
@@ -56557,7 +56557,7 @@
       </c>
       <c r="AE490" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF490" t="inlineStr">
@@ -56657,7 +56657,7 @@
       </c>
       <c r="AE491" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF491" t="inlineStr">
@@ -56757,7 +56757,7 @@
       </c>
       <c r="AE492" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF492" t="inlineStr">
@@ -56869,7 +56869,7 @@
       </c>
       <c r="AE493" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF493" t="inlineStr">
@@ -56981,7 +56981,7 @@
       </c>
       <c r="AE494" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF494" t="inlineStr">
@@ -57093,7 +57093,7 @@
       </c>
       <c r="AE495" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF495" t="inlineStr">
@@ -57203,7 +57203,7 @@
       </c>
       <c r="AE496" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF496" t="inlineStr">
@@ -57313,7 +57313,7 @@
       </c>
       <c r="AE497" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF497" t="inlineStr">
@@ -57423,7 +57423,7 @@
       </c>
       <c r="AE498" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF498" t="inlineStr">
@@ -57535,7 +57535,7 @@
       </c>
       <c r="AE499" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF499" t="inlineStr">
@@ -57645,7 +57645,7 @@
       </c>
       <c r="AE500" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF500" t="inlineStr">
@@ -57755,7 +57755,7 @@
       </c>
       <c r="AE501" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF501" t="inlineStr">
@@ -57865,7 +57865,7 @@
       </c>
       <c r="AE502" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF502" t="inlineStr">
@@ -57975,7 +57975,7 @@
       </c>
       <c r="AE503" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF503" t="inlineStr">
@@ -58087,7 +58087,7 @@
       </c>
       <c r="AE504" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF504" t="inlineStr">
@@ -58199,7 +58199,7 @@
       </c>
       <c r="AE505" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF505" t="inlineStr">
@@ -58315,7 +58315,7 @@
       </c>
       <c r="AE506" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF506" t="inlineStr">
@@ -58443,7 +58443,7 @@
       </c>
       <c r="AE507" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="AF507" t="inlineStr">
@@ -58555,7 +58555,7 @@
       </c>
       <c r="AE508" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF508" t="inlineStr">
@@ -58665,7 +58665,7 @@
       </c>
       <c r="AE509" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF509" t="inlineStr">
@@ -58785,7 +58785,7 @@
       </c>
       <c r="AE510" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="AF510" t="inlineStr">
@@ -58895,7 +58895,7 @@
       </c>
       <c r="AE511" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF511" t="inlineStr">
@@ -59005,7 +59005,7 @@
       </c>
       <c r="AE512" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF512" t="inlineStr">
@@ -59115,7 +59115,7 @@
       </c>
       <c r="AE513" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF513" t="inlineStr">
@@ -59235,7 +59235,7 @@
       </c>
       <c r="AE514" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="AF514" t="inlineStr">
@@ -59351,7 +59351,7 @@
       </c>
       <c r="AE515" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF515" t="inlineStr">
@@ -59463,7 +59463,7 @@
       </c>
       <c r="AE516" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF516" t="inlineStr">
@@ -59583,7 +59583,7 @@
       </c>
       <c r="AE517" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="AF517" t="inlineStr">
@@ -59695,7 +59695,7 @@
       </c>
       <c r="AE518" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF518" t="inlineStr">
@@ -59795,7 +59795,7 @@
       </c>
       <c r="AE519" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF519" t="inlineStr">
@@ -59915,7 +59915,7 @@
       </c>
       <c r="AE520" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="AF520" t="inlineStr">
@@ -60025,7 +60025,7 @@
       </c>
       <c r="AE521" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF521" t="inlineStr">
@@ -60137,7 +60137,7 @@
       </c>
       <c r="AE522" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF522" t="inlineStr">
@@ -60253,7 +60253,7 @@
       </c>
       <c r="AE523" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF523" t="inlineStr">
@@ -60365,7 +60365,7 @@
       </c>
       <c r="AE524" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF524" t="inlineStr">
@@ -60477,7 +60477,7 @@
       </c>
       <c r="AE525" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF525" t="inlineStr">
@@ -60605,7 +60605,7 @@
       </c>
       <c r="AE526" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="AF526" t="inlineStr">
@@ -60715,7 +60715,7 @@
       </c>
       <c r="AE527" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF527" t="inlineStr">
@@ -60825,7 +60825,7 @@
       </c>
       <c r="AE528" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF528" t="inlineStr">
@@ -60935,7 +60935,7 @@
       </c>
       <c r="AE529" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF529" t="inlineStr">
@@ -61047,7 +61047,7 @@
       </c>
       <c r="AE530" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF530" t="inlineStr">
@@ -61175,7 +61175,7 @@
       </c>
       <c r="AE531" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="AF531" t="inlineStr">
@@ -61287,7 +61287,7 @@
       </c>
       <c r="AE532" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF532" t="inlineStr">
@@ -61399,7 +61399,7 @@
       </c>
       <c r="AE533" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF533" t="inlineStr">
@@ -61511,7 +61511,7 @@
       </c>
       <c r="AE534" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF534" t="inlineStr">
@@ -61611,7 +61611,7 @@
       </c>
       <c r="AE535" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF535" t="inlineStr">
@@ -61721,7 +61721,7 @@
       </c>
       <c r="AE536" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF536" t="inlineStr">
@@ -61831,7 +61831,7 @@
       </c>
       <c r="AE537" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF537" t="inlineStr">
@@ -61931,7 +61931,7 @@
       </c>
       <c r="AE538" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF538" t="inlineStr">
@@ -62041,7 +62041,7 @@
       </c>
       <c r="AE539" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF539" t="inlineStr">
@@ -62169,7 +62169,7 @@
       </c>
       <c r="AE540" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="AF540" t="inlineStr">
@@ -62279,7 +62279,7 @@
       </c>
       <c r="AE541" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF541" t="inlineStr">
@@ -62391,7 +62391,7 @@
       </c>
       <c r="AE542" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF542" t="inlineStr">
@@ -62501,7 +62501,7 @@
       </c>
       <c r="AE543" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF543" t="inlineStr">
@@ -62613,7 +62613,7 @@
       </c>
       <c r="AE544" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF544" t="inlineStr">
@@ -62723,7 +62723,7 @@
       </c>
       <c r="AE545" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF545" t="inlineStr">
@@ -62833,7 +62833,7 @@
       </c>
       <c r="AE546" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF546" t="inlineStr">
@@ -62933,7 +62933,7 @@
       </c>
       <c r="AE547" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF547" t="inlineStr">
@@ -63043,7 +63043,7 @@
       </c>
       <c r="AE548" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF548" t="inlineStr">
@@ -63155,7 +63155,7 @@
       </c>
       <c r="AE549" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF549" t="inlineStr">
@@ -63265,7 +63265,7 @@
       </c>
       <c r="AE550" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF550" t="inlineStr">
@@ -63375,7 +63375,7 @@
       </c>
       <c r="AE551" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF551" t="inlineStr">
@@ -63485,7 +63485,7 @@
       </c>
       <c r="AE552" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF552" t="inlineStr">
@@ -63595,7 +63595,7 @@
       </c>
       <c r="AE553" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF553" t="inlineStr">
@@ -63705,7 +63705,7 @@
       </c>
       <c r="AE554" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF554" t="inlineStr">
@@ -63815,7 +63815,7 @@
       </c>
       <c r="AE555" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF555" t="inlineStr">
@@ -63915,7 +63915,7 @@
       </c>
       <c r="AE556" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF556" t="inlineStr">
@@ -64025,7 +64025,7 @@
       </c>
       <c r="AE557" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF557" t="inlineStr">
@@ -64135,7 +64135,7 @@
       </c>
       <c r="AE558" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF558" t="inlineStr">
@@ -64247,7 +64247,7 @@
       </c>
       <c r="AE559" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF559" t="inlineStr">
@@ -64357,7 +64357,7 @@
       </c>
       <c r="AE560" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF560" t="inlineStr">
@@ -64469,7 +64469,7 @@
       </c>
       <c r="AE561" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF561" t="inlineStr">
@@ -64579,7 +64579,7 @@
       </c>
       <c r="AE562" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF562" t="inlineStr">
@@ -64689,7 +64689,7 @@
       </c>
       <c r="AE563" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF563" t="inlineStr">
@@ -64799,7 +64799,7 @@
       </c>
       <c r="AE564" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF564" t="inlineStr">
@@ -64909,7 +64909,7 @@
       </c>
       <c r="AE565" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF565" t="inlineStr">
@@ -65019,7 +65019,7 @@
       </c>
       <c r="AE566" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF566" t="inlineStr">
@@ -65131,7 +65131,7 @@
       </c>
       <c r="AE567" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF567" t="inlineStr">
@@ -65241,7 +65241,7 @@
       </c>
       <c r="AE568" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF568" t="inlineStr">
@@ -65353,7 +65353,7 @@
       </c>
       <c r="AE569" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF569" t="inlineStr">
@@ -65465,7 +65465,7 @@
       </c>
       <c r="AE570" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF570" t="inlineStr">
@@ -65575,7 +65575,7 @@
       </c>
       <c r="AE571" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF571" t="inlineStr">
@@ -65687,7 +65687,7 @@
       </c>
       <c r="AE572" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF572" t="inlineStr">
@@ -65799,7 +65799,7 @@
       </c>
       <c r="AE573" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF573" t="inlineStr">
@@ -65909,7 +65909,7 @@
       </c>
       <c r="AE574" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF574" t="inlineStr">
@@ -66019,7 +66019,7 @@
       </c>
       <c r="AE575" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF575" t="inlineStr">
@@ -66129,7 +66129,7 @@
       </c>
       <c r="AE576" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF576" t="inlineStr">
@@ -66239,7 +66239,7 @@
       </c>
       <c r="AE577" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF577" t="inlineStr">
@@ -66339,7 +66339,7 @@
       </c>
       <c r="AE578" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF578" t="inlineStr">
@@ -66451,7 +66451,7 @@
       </c>
       <c r="AE579" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF579" t="inlineStr">
@@ -66561,7 +66561,7 @@
       </c>
       <c r="AE580" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF580" t="inlineStr">
@@ -66671,7 +66671,7 @@
       </c>
       <c r="AE581" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF581" t="inlineStr">
@@ -66799,7 +66799,7 @@
       </c>
       <c r="AE582" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="AF582" t="inlineStr">
@@ -66911,7 +66911,7 @@
       </c>
       <c r="AE583" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF583" t="inlineStr">
@@ -67023,7 +67023,7 @@
       </c>
       <c r="AE584" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF584" t="inlineStr">
@@ -67151,7 +67151,7 @@
       </c>
       <c r="AE585" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="AF585" t="inlineStr">
@@ -67263,7 +67263,7 @@
       </c>
       <c r="AE586" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF586" t="inlineStr">
@@ -67391,7 +67391,7 @@
       </c>
       <c r="AE587" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="AF587" t="inlineStr">
@@ -67519,7 +67519,7 @@
       </c>
       <c r="AE588" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="AF588" t="inlineStr">
@@ -67631,7 +67631,7 @@
       </c>
       <c r="AE589" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF589" t="inlineStr">
@@ -67743,7 +67743,7 @@
       </c>
       <c r="AE590" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF590" t="inlineStr">
@@ -67853,7 +67853,7 @@
       </c>
       <c r="AE591" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF591" t="inlineStr">
@@ -67965,7 +67965,7 @@
       </c>
       <c r="AE592" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF592" t="inlineStr">
@@ -68075,7 +68075,7 @@
       </c>
       <c r="AE593" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF593" t="inlineStr">
@@ -68185,7 +68185,7 @@
       </c>
       <c r="AE594" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF594" t="inlineStr">
@@ -68297,7 +68297,7 @@
       </c>
       <c r="AE595" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF595" t="inlineStr">
@@ -68409,7 +68409,7 @@
       </c>
       <c r="AE596" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF596" t="inlineStr">
@@ -68521,7 +68521,7 @@
       </c>
       <c r="AE597" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF597" t="inlineStr">
@@ -68631,7 +68631,7 @@
       </c>
       <c r="AE598" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF598" t="inlineStr">
@@ -68741,7 +68741,7 @@
       </c>
       <c r="AE599" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF599" t="inlineStr">
@@ -68853,7 +68853,7 @@
       </c>
       <c r="AE600" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF600" t="inlineStr">
@@ -68965,7 +68965,7 @@
       </c>
       <c r="AE601" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF601" t="inlineStr">
@@ -69075,7 +69075,7 @@
       </c>
       <c r="AE602" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF602" t="inlineStr">
@@ -69187,7 +69187,7 @@
       </c>
       <c r="AE603" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF603" t="inlineStr">
@@ -69297,7 +69297,7 @@
       </c>
       <c r="AE604" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF604" t="inlineStr">
@@ -69397,7 +69397,7 @@
       </c>
       <c r="AE605" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF605" t="inlineStr">
@@ -69507,7 +69507,7 @@
       </c>
       <c r="AE606" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF606" t="inlineStr">
@@ -69619,7 +69619,7 @@
       </c>
       <c r="AE607" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF607" t="inlineStr">
@@ -69729,7 +69729,7 @@
       </c>
       <c r="AE608" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF608" t="inlineStr">
@@ -69841,7 +69841,7 @@
       </c>
       <c r="AE609" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF609" t="inlineStr">
@@ -69951,7 +69951,7 @@
       </c>
       <c r="AE610" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF610" t="inlineStr">
@@ -70061,7 +70061,7 @@
       </c>
       <c r="AE611" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF611" t="inlineStr">
@@ -70171,7 +70171,7 @@
       </c>
       <c r="AE612" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF612" t="inlineStr">
@@ -70281,7 +70281,7 @@
       </c>
       <c r="AE613" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF613" t="inlineStr">
@@ -70391,7 +70391,7 @@
       </c>
       <c r="AE614" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF614" t="inlineStr">
@@ -70503,7 +70503,7 @@
       </c>
       <c r="AE615" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF615" t="inlineStr">
@@ -70613,7 +70613,7 @@
       </c>
       <c r="AE616" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF616" t="inlineStr">
@@ -70723,7 +70723,7 @@
       </c>
       <c r="AE617" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF617" t="inlineStr">
@@ -70833,7 +70833,7 @@
       </c>
       <c r="AE618" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF618" t="inlineStr">
@@ -70945,7 +70945,7 @@
       </c>
       <c r="AE619" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF619" t="inlineStr">
@@ -71055,7 +71055,7 @@
       </c>
       <c r="AE620" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF620" t="inlineStr">
@@ -71167,7 +71167,7 @@
       </c>
       <c r="AE621" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF621" t="inlineStr">
@@ -71279,7 +71279,7 @@
       </c>
       <c r="AE622" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF622" t="inlineStr">
@@ -71379,7 +71379,7 @@
       </c>
       <c r="AE623" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF623" t="inlineStr">
@@ -71489,7 +71489,7 @@
       </c>
       <c r="AE624" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF624" t="inlineStr">
@@ -71601,7 +71601,7 @@
       </c>
       <c r="AE625" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF625" t="inlineStr">
@@ -71713,7 +71713,7 @@
       </c>
       <c r="AE626" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF626" t="inlineStr">
@@ -71825,7 +71825,7 @@
       </c>
       <c r="AE627" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF627" t="inlineStr">
@@ -71937,7 +71937,7 @@
       </c>
       <c r="AE628" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF628" t="inlineStr">
@@ -72047,7 +72047,7 @@
       </c>
       <c r="AE629" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF629" t="inlineStr">
@@ -72157,7 +72157,7 @@
       </c>
       <c r="AE630" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF630" t="inlineStr">
@@ -72269,7 +72269,7 @@
       </c>
       <c r="AE631" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF631" t="inlineStr">
@@ -72379,7 +72379,7 @@
       </c>
       <c r="AE632" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF632" t="inlineStr">
@@ -72491,7 +72491,7 @@
       </c>
       <c r="AE633" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF633" t="inlineStr">
@@ -72591,7 +72591,7 @@
       </c>
       <c r="AE634" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF634" t="inlineStr">
@@ -72701,7 +72701,7 @@
       </c>
       <c r="AE635" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF635" t="inlineStr">
@@ -72813,7 +72813,7 @@
       </c>
       <c r="AE636" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF636" t="inlineStr">
@@ -72923,7 +72923,7 @@
       <c r="AD637" t="inlineStr"/>
       <c r="AE637" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:51</t>
+          <t>2026-09-18 08:21:44</t>
         </is>
       </c>
       <c r="AF637" t="inlineStr">
@@ -73035,7 +73035,7 @@
       </c>
       <c r="AE638" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF638" t="inlineStr">
@@ -73147,7 +73147,7 @@
       </c>
       <c r="AE639" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF639" t="inlineStr">
@@ -73257,7 +73257,7 @@
       </c>
       <c r="AE640" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF640" t="inlineStr">
@@ -73369,7 +73369,7 @@
       </c>
       <c r="AE641" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF641" t="inlineStr">
@@ -73469,7 +73469,7 @@
       </c>
       <c r="AE642" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF642" t="inlineStr">
@@ -73569,7 +73569,7 @@
       </c>
       <c r="AE643" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF643" t="inlineStr">
@@ -73669,7 +73669,7 @@
       </c>
       <c r="AE644" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF644" t="inlineStr">
@@ -73781,7 +73781,7 @@
       </c>
       <c r="AE645" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF645" t="inlineStr">
@@ -73881,7 +73881,7 @@
       </c>
       <c r="AE646" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF646" t="inlineStr">
@@ -73991,7 +73991,7 @@
       </c>
       <c r="AE647" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF647" t="inlineStr">
@@ -74091,7 +74091,7 @@
       </c>
       <c r="AE648" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF648" t="inlineStr">
@@ -74203,7 +74203,7 @@
       </c>
       <c r="AE649" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF649" t="inlineStr">
@@ -74315,7 +74315,7 @@
       </c>
       <c r="AE650" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF650" t="inlineStr">
@@ -74427,7 +74427,7 @@
       </c>
       <c r="AE651" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF651" t="inlineStr">
@@ -74539,7 +74539,7 @@
       </c>
       <c r="AE652" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF652" t="inlineStr">
@@ -74639,7 +74639,7 @@
       </c>
       <c r="AE653" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF653" t="inlineStr">
@@ -74751,7 +74751,7 @@
       </c>
       <c r="AE654" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF654" t="inlineStr">
@@ -74861,7 +74861,7 @@
       </c>
       <c r="AE655" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF655" t="inlineStr">
@@ -74973,7 +74973,7 @@
       </c>
       <c r="AE656" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF656" t="inlineStr">
@@ -75073,7 +75073,7 @@
       </c>
       <c r="AE657" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF657" t="inlineStr">
@@ -75173,7 +75173,7 @@
       </c>
       <c r="AE658" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF658" t="inlineStr">
@@ -75273,7 +75273,7 @@
       </c>
       <c r="AE659" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF659" t="inlineStr">
@@ -75373,7 +75373,7 @@
       </c>
       <c r="AE660" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF660" t="inlineStr">
@@ -75485,7 +75485,7 @@
       </c>
       <c r="AE661" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF661" t="inlineStr">
@@ -75597,7 +75597,7 @@
       </c>
       <c r="AE662" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF662" t="inlineStr">
@@ -75697,7 +75697,7 @@
       </c>
       <c r="AE663" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF663" t="inlineStr">
@@ -75807,7 +75807,7 @@
       </c>
       <c r="AE664" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF664" t="inlineStr">
@@ -75919,7 +75919,7 @@
       </c>
       <c r="AE665" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF665" t="inlineStr">
@@ -76031,7 +76031,7 @@
       </c>
       <c r="AE666" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF666" t="inlineStr">
@@ -76143,7 +76143,7 @@
       </c>
       <c r="AE667" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF667" t="inlineStr">
@@ -76255,7 +76255,7 @@
       </c>
       <c r="AE668" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF668" t="inlineStr">
@@ -76367,7 +76367,7 @@
       </c>
       <c r="AE669" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF669" t="inlineStr">
@@ -76479,7 +76479,7 @@
       </c>
       <c r="AE670" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF670" t="inlineStr">
@@ -76591,7 +76591,7 @@
       </c>
       <c r="AE671" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF671" t="inlineStr">
@@ -76691,7 +76691,7 @@
       </c>
       <c r="AE672" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF672" t="inlineStr">
@@ -76791,7 +76791,7 @@
       </c>
       <c r="AE673" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF673" t="inlineStr">
@@ -76903,7 +76903,7 @@
       </c>
       <c r="AE674" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:21</t>
+          <t>2026-09-18 08:21:12</t>
         </is>
       </c>
       <c r="AF674" t="inlineStr">
@@ -77003,7 +77003,7 @@
       </c>
       <c r="AE675" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF675" t="inlineStr">
@@ -77103,7 +77103,7 @@
       </c>
       <c r="AE676" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF676" t="inlineStr">
@@ -77203,7 +77203,7 @@
       </c>
       <c r="AE677" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF677" t="inlineStr">
@@ -77313,7 +77313,7 @@
       </c>
       <c r="AE678" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF678" t="inlineStr">
@@ -77413,7 +77413,7 @@
       </c>
       <c r="AE679" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF679" t="inlineStr">
@@ -77523,7 +77523,7 @@
       </c>
       <c r="AE680" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF680" t="inlineStr">
@@ -77605,7 +77605,7 @@
       <c r="AD681" t="inlineStr"/>
       <c r="AE681" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF681" t="inlineStr">
@@ -77687,7 +77687,7 @@
       <c r="AD682" t="inlineStr"/>
       <c r="AE682" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF682" t="inlineStr">
@@ -77769,7 +77769,7 @@
       <c r="AD683" t="inlineStr"/>
       <c r="AE683" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF683" t="inlineStr">
@@ -77851,7 +77851,7 @@
       <c r="AD684" t="inlineStr"/>
       <c r="AE684" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="AF684" t="inlineStr">

--- a/pipeline/credit_rating/output/xhtn_tong_hop_20260918.xlsx
+++ b/pipeline/credit_rating/output/xhtn_tong_hop_20260918.xlsx
@@ -685,7 +685,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1011,7 +1011,7 @@
       <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -1099,7 +1099,7 @@
       <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -1219,7 +1219,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -1555,7 +1555,7 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:44</t>
+          <t>2026-09-18 08:50:17</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -1665,7 +1665,7 @@
       <c r="AD11" t="inlineStr"/>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:44</t>
+          <t>2026-09-18 08:50:17</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:44</t>
+          <t>2026-09-18 08:50:17</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -1891,7 +1891,7 @@
       <c r="AD13" t="inlineStr"/>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:44</t>
+          <t>2026-09-18 08:50:17</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -2019,7 +2019,7 @@
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -2133,7 +2133,7 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -2247,7 +2247,7 @@
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -2367,7 +2367,7 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -2595,7 +2595,7 @@
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -2709,7 +2709,7 @@
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -2825,7 +2825,7 @@
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:44</t>
+          <t>2026-09-18 08:50:17</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -2939,7 +2939,7 @@
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -3049,7 +3049,7 @@
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -3177,7 +3177,7 @@
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
@@ -3291,7 +3291,7 @@
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
@@ -3411,7 +3411,7 @@
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
@@ -3525,7 +3525,7 @@
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
@@ -3635,7 +3635,7 @@
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:44</t>
+          <t>2026-09-18 08:50:17</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
@@ -3861,7 +3861,7 @@
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
@@ -3971,7 +3971,7 @@
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF31" t="inlineStr">
@@ -4095,7 +4095,7 @@
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
@@ -4205,7 +4205,7 @@
       </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF33" t="inlineStr">
@@ -4315,7 +4315,7 @@
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF34" t="inlineStr">
@@ -4425,7 +4425,7 @@
       </c>
       <c r="AE35" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF35" t="inlineStr">
@@ -4525,7 +4525,7 @@
       </c>
       <c r="AE36" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF36" t="inlineStr">
@@ -4635,7 +4635,7 @@
       </c>
       <c r="AE37" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF37" t="inlineStr">
@@ -4745,7 +4745,7 @@
       </c>
       <c r="AE38" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF38" t="inlineStr">
@@ -4855,7 +4855,7 @@
       </c>
       <c r="AE39" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF39" t="inlineStr">
@@ -4987,7 +4987,7 @@
       </c>
       <c r="AE40" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="AF40" t="inlineStr">
@@ -5115,7 +5115,7 @@
       </c>
       <c r="AE41" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="AF41" t="inlineStr">
@@ -5247,7 +5247,7 @@
       </c>
       <c r="AE42" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="AF42" t="inlineStr">
@@ -5375,7 +5375,7 @@
       </c>
       <c r="AE43" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="AF43" t="inlineStr">
@@ -5485,7 +5485,7 @@
       </c>
       <c r="AE44" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF44" t="inlineStr">
@@ -5597,7 +5597,7 @@
       </c>
       <c r="AE45" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF45" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="AE46" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF46" t="inlineStr">
@@ -5827,7 +5827,7 @@
       </c>
       <c r="AE47" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF47" t="inlineStr">
@@ -5943,7 +5943,7 @@
       </c>
       <c r="AE48" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF48" t="inlineStr">
@@ -6043,7 +6043,7 @@
       </c>
       <c r="AE49" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF49" t="inlineStr">
@@ -6157,7 +6157,7 @@
       </c>
       <c r="AE50" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF50" t="inlineStr">
@@ -6273,7 +6273,7 @@
       </c>
       <c r="AE51" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:44</t>
+          <t>2026-09-18 08:50:17</t>
         </is>
       </c>
       <c r="AF51" t="inlineStr">
@@ -6383,7 +6383,7 @@
       </c>
       <c r="AE52" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF52" t="inlineStr">
@@ -6497,7 +6497,7 @@
       </c>
       <c r="AE53" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF53" t="inlineStr">
@@ -6611,7 +6611,7 @@
       </c>
       <c r="AE54" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF54" t="inlineStr">
@@ -6739,7 +6739,7 @@
       </c>
       <c r="AE55" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="AF55" t="inlineStr">
@@ -6855,7 +6855,7 @@
       </c>
       <c r="AE56" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF56" t="inlineStr">
@@ -6951,7 +6951,7 @@
       </c>
       <c r="AE57" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF57" t="inlineStr">
@@ -7061,7 +7061,7 @@
       </c>
       <c r="AE58" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF58" t="inlineStr">
@@ -7161,7 +7161,7 @@
       </c>
       <c r="AE59" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF59" t="inlineStr">
@@ -7275,7 +7275,7 @@
       </c>
       <c r="AE60" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF60" t="inlineStr">
@@ -7389,7 +7389,7 @@
       </c>
       <c r="AE61" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF61" t="inlineStr">
@@ -7489,7 +7489,7 @@
       </c>
       <c r="AE62" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF62" t="inlineStr">
@@ -7603,7 +7603,7 @@
       </c>
       <c r="AE63" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:26</t>
+          <t>2026-09-18 08:50:00</t>
         </is>
       </c>
       <c r="AF63" t="inlineStr">
@@ -7713,7 +7713,7 @@
       </c>
       <c r="AE64" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF64" t="inlineStr">
@@ -7827,7 +7827,7 @@
       </c>
       <c r="AE65" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF65" t="inlineStr">
@@ -7941,7 +7941,7 @@
       </c>
       <c r="AE66" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF66" t="inlineStr">
@@ -8051,7 +8051,7 @@
       </c>
       <c r="AE67" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF67" t="inlineStr">
@@ -8165,7 +8165,7 @@
       </c>
       <c r="AE68" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF68" t="inlineStr">
@@ -8279,7 +8279,7 @@
       </c>
       <c r="AE69" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:26</t>
+          <t>2026-09-18 08:50:00</t>
         </is>
       </c>
       <c r="AF69" t="inlineStr">
@@ -8393,7 +8393,7 @@
       </c>
       <c r="AE70" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:26</t>
+          <t>2026-09-18 08:50:00</t>
         </is>
       </c>
       <c r="AF70" t="inlineStr">
@@ -8517,7 +8517,7 @@
       </c>
       <c r="AE71" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:28</t>
+          <t>2026-09-18 08:50:02</t>
         </is>
       </c>
       <c r="AF71" t="inlineStr">
@@ -8627,7 +8627,7 @@
       </c>
       <c r="AE72" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF72" t="inlineStr">
@@ -8741,7 +8741,7 @@
       </c>
       <c r="AE73" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF73" t="inlineStr">
@@ -8855,7 +8855,7 @@
       </c>
       <c r="AE74" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF74" t="inlineStr">
@@ -8969,7 +8969,7 @@
       </c>
       <c r="AE75" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF75" t="inlineStr">
@@ -9081,7 +9081,7 @@
       </c>
       <c r="AE76" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF76" t="inlineStr">
@@ -9197,7 +9197,7 @@
       </c>
       <c r="AE77" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:44</t>
+          <t>2026-09-18 08:50:17</t>
         </is>
       </c>
       <c r="AF77" t="inlineStr">
@@ -9307,7 +9307,7 @@
       </c>
       <c r="AE78" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF78" t="inlineStr">
@@ -9417,7 +9417,7 @@
       </c>
       <c r="AE79" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF79" t="inlineStr">
@@ -9535,7 +9535,7 @@
       </c>
       <c r="AE80" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:26</t>
+          <t>2026-09-18 08:50:00</t>
         </is>
       </c>
       <c r="AF80" t="inlineStr">
@@ -9659,7 +9659,7 @@
       </c>
       <c r="AE81" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="AF81" t="inlineStr">
@@ -9779,7 +9779,7 @@
       </c>
       <c r="AE82" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="AF82" t="inlineStr">
@@ -9899,7 +9899,7 @@
       </c>
       <c r="AE83" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="AF83" t="inlineStr">
@@ -10031,7 +10031,7 @@
       </c>
       <c r="AE84" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="AF84" t="inlineStr">
@@ -10155,7 +10155,7 @@
       </c>
       <c r="AE85" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF85" t="inlineStr">
@@ -10279,7 +10279,7 @@
       </c>
       <c r="AE86" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF86" t="inlineStr">
@@ -10379,7 +10379,7 @@
       </c>
       <c r="AE87" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF87" t="inlineStr">
@@ -10499,7 +10499,7 @@
       </c>
       <c r="AE88" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="AF88" t="inlineStr">
@@ -10627,7 +10627,7 @@
       </c>
       <c r="AE89" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="AF89" t="inlineStr">
@@ -10741,7 +10741,7 @@
       </c>
       <c r="AE90" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF90" t="inlineStr">
@@ -10855,7 +10855,7 @@
       </c>
       <c r="AE91" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF91" t="inlineStr">
@@ -10969,7 +10969,7 @@
       </c>
       <c r="AE92" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF92" t="inlineStr">
@@ -11079,7 +11079,7 @@
       </c>
       <c r="AE93" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF93" t="inlineStr">
@@ -11193,7 +11193,7 @@
       </c>
       <c r="AE94" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF94" t="inlineStr">
@@ -11307,7 +11307,7 @@
       </c>
       <c r="AE95" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF95" t="inlineStr">
@@ -11421,7 +11421,7 @@
       </c>
       <c r="AE96" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF96" t="inlineStr">
@@ -11535,7 +11535,7 @@
       </c>
       <c r="AE97" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF97" t="inlineStr">
@@ -11655,7 +11655,7 @@
       </c>
       <c r="AE98" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="AF98" t="inlineStr">
@@ -11771,7 +11771,7 @@
       </c>
       <c r="AE99" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:44</t>
+          <t>2026-09-18 08:50:17</t>
         </is>
       </c>
       <c r="AF99" t="inlineStr">
@@ -11881,7 +11881,7 @@
       </c>
       <c r="AE100" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF100" t="inlineStr">
@@ -12001,7 +12001,7 @@
       </c>
       <c r="AE101" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="AF101" t="inlineStr">
@@ -12133,7 +12133,7 @@
       </c>
       <c r="AE102" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="AF102" t="inlineStr">
@@ -12261,7 +12261,7 @@
       </c>
       <c r="AE103" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="AF103" t="inlineStr">
@@ -12373,7 +12373,7 @@
       </c>
       <c r="AE104" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF104" t="inlineStr">
@@ -12483,7 +12483,7 @@
       </c>
       <c r="AE105" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF105" t="inlineStr">
@@ -12593,7 +12593,7 @@
       </c>
       <c r="AE106" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF106" t="inlineStr">
@@ -12703,7 +12703,7 @@
       </c>
       <c r="AE107" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF107" t="inlineStr">
@@ -12817,7 +12817,7 @@
       </c>
       <c r="AE108" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:26</t>
+          <t>2026-09-18 08:50:00</t>
         </is>
       </c>
       <c r="AF108" t="inlineStr">
@@ -12929,7 +12929,7 @@
       </c>
       <c r="AE109" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF109" t="inlineStr">
@@ -13045,7 +13045,7 @@
       </c>
       <c r="AE110" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF110" t="inlineStr">
@@ -13167,7 +13167,7 @@
       <c r="AD111" t="inlineStr"/>
       <c r="AE111" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="AF111" t="inlineStr">
@@ -13279,7 +13279,7 @@
       </c>
       <c r="AE112" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:28</t>
+          <t>2026-09-18 08:50:02</t>
         </is>
       </c>
       <c r="AF112" t="inlineStr">
@@ -13407,7 +13407,7 @@
       </c>
       <c r="AE113" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="AF113" t="inlineStr">
@@ -13527,7 +13527,7 @@
       </c>
       <c r="AE114" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF114" t="inlineStr">
@@ -13647,7 +13647,7 @@
       </c>
       <c r="AE115" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF115" t="inlineStr">
@@ -13757,7 +13757,7 @@
       </c>
       <c r="AE116" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF116" t="inlineStr">
@@ -13873,7 +13873,7 @@
       </c>
       <c r="AE117" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF117" t="inlineStr">
@@ -13985,7 +13985,7 @@
       </c>
       <c r="AE118" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF118" t="inlineStr">
@@ -14095,7 +14095,7 @@
       </c>
       <c r="AE119" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF119" t="inlineStr">
@@ -14205,7 +14205,7 @@
       </c>
       <c r="AE120" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF120" t="inlineStr">
@@ -14329,7 +14329,7 @@
       </c>
       <c r="AE121" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF121" t="inlineStr">
@@ -14445,7 +14445,7 @@
       </c>
       <c r="AE122" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF122" t="inlineStr">
@@ -14565,7 +14565,7 @@
       </c>
       <c r="AE123" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="AF123" t="inlineStr">
@@ -14677,7 +14677,7 @@
       </c>
       <c r="AE124" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF124" t="inlineStr">
@@ -14797,7 +14797,7 @@
       </c>
       <c r="AE125" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF125" t="inlineStr">
@@ -14907,7 +14907,7 @@
       </c>
       <c r="AE126" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF126" t="inlineStr">
@@ -15017,7 +15017,7 @@
       </c>
       <c r="AE127" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF127" t="inlineStr">
@@ -15137,7 +15137,7 @@
       </c>
       <c r="AE128" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="AF128" t="inlineStr">
@@ -15251,7 +15251,7 @@
       </c>
       <c r="AE129" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF129" t="inlineStr">
@@ -15365,7 +15365,7 @@
       </c>
       <c r="AE130" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF130" t="inlineStr">
@@ -15485,7 +15485,7 @@
       </c>
       <c r="AE131" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="AF131" t="inlineStr">
@@ -15595,7 +15595,7 @@
       </c>
       <c r="AE132" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF132" t="inlineStr">
@@ -15711,7 +15711,7 @@
       </c>
       <c r="AE133" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF133" t="inlineStr">
@@ -15823,7 +15823,7 @@
       </c>
       <c r="AE134" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:28</t>
+          <t>2026-09-18 08:50:02</t>
         </is>
       </c>
       <c r="AF134" t="inlineStr">
@@ -15935,7 +15935,7 @@
       </c>
       <c r="AE135" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF135" t="inlineStr">
@@ -16049,7 +16049,7 @@
       </c>
       <c r="AE136" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF136" t="inlineStr">
@@ -16163,7 +16163,7 @@
       </c>
       <c r="AE137" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF137" t="inlineStr">
@@ -16277,7 +16277,7 @@
       </c>
       <c r="AE138" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:26</t>
+          <t>2026-09-18 08:50:00</t>
         </is>
       </c>
       <c r="AF138" t="inlineStr">
@@ -16387,7 +16387,7 @@
       </c>
       <c r="AE139" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF139" t="inlineStr">
@@ -16497,7 +16497,7 @@
       </c>
       <c r="AE140" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF140" t="inlineStr">
@@ -16607,7 +16607,7 @@
       </c>
       <c r="AE141" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF141" t="inlineStr">
@@ -16721,7 +16721,7 @@
       </c>
       <c r="AE142" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF142" t="inlineStr">
@@ -16835,7 +16835,7 @@
       </c>
       <c r="AE143" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF143" t="inlineStr">
@@ -16963,7 +16963,7 @@
       </c>
       <c r="AE144" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="AF144" t="inlineStr">
@@ -17091,7 +17091,7 @@
       </c>
       <c r="AE145" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="AF145" t="inlineStr">
@@ -17201,7 +17201,7 @@
       </c>
       <c r="AE146" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF146" t="inlineStr">
@@ -17311,7 +17311,7 @@
       </c>
       <c r="AE147" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF147" t="inlineStr">
@@ -17431,7 +17431,7 @@
       </c>
       <c r="AE148" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="AF148" t="inlineStr">
@@ -17545,7 +17545,7 @@
       </c>
       <c r="AE149" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF149" t="inlineStr">
@@ -17655,7 +17655,7 @@
       </c>
       <c r="AE150" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF150" t="inlineStr">
@@ -17783,7 +17783,7 @@
       </c>
       <c r="AE151" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="AF151" t="inlineStr">
@@ -17905,7 +17905,7 @@
       <c r="AD152" t="inlineStr"/>
       <c r="AE152" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="AF152" t="inlineStr">
@@ -18033,7 +18033,7 @@
       </c>
       <c r="AE153" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="AF153" t="inlineStr">
@@ -18149,7 +18149,7 @@
       </c>
       <c r="AE154" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:44</t>
+          <t>2026-09-18 08:50:17</t>
         </is>
       </c>
       <c r="AF154" t="inlineStr">
@@ -18277,7 +18277,7 @@
       </c>
       <c r="AE155" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="AF155" t="inlineStr">
@@ -18409,7 +18409,7 @@
       </c>
       <c r="AE156" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="AF156" t="inlineStr">
@@ -18523,7 +18523,7 @@
       </c>
       <c r="AE157" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF157" t="inlineStr">
@@ -18645,7 +18645,7 @@
       <c r="AD158" t="inlineStr"/>
       <c r="AE158" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="AF158" t="inlineStr">
@@ -18757,7 +18757,7 @@
       </c>
       <c r="AE159" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF159" t="inlineStr">
@@ -18857,7 +18857,7 @@
       </c>
       <c r="AE160" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF160" t="inlineStr">
@@ -18967,7 +18967,7 @@
       </c>
       <c r="AE161" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF161" t="inlineStr">
@@ -19083,7 +19083,7 @@
       </c>
       <c r="AE162" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF162" t="inlineStr">
@@ -19199,7 +19199,7 @@
       </c>
       <c r="AE163" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF163" t="inlineStr">
@@ -19327,7 +19327,7 @@
       </c>
       <c r="AE164" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="AF164" t="inlineStr">
@@ -19437,7 +19437,7 @@
       </c>
       <c r="AE165" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF165" t="inlineStr">
@@ -19551,7 +19551,7 @@
       </c>
       <c r="AE166" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF166" t="inlineStr">
@@ -19665,7 +19665,7 @@
       </c>
       <c r="AE167" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF167" t="inlineStr">
@@ -19779,7 +19779,7 @@
       </c>
       <c r="AE168" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF168" t="inlineStr">
@@ -19889,7 +19889,7 @@
       </c>
       <c r="AE169" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF169" t="inlineStr">
@@ -20003,7 +20003,7 @@
       </c>
       <c r="AE170" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF170" t="inlineStr">
@@ -20113,7 +20113,7 @@
       </c>
       <c r="AE171" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF171" t="inlineStr">
@@ -20225,7 +20225,7 @@
       </c>
       <c r="AE172" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF172" t="inlineStr">
@@ -20341,7 +20341,7 @@
       </c>
       <c r="AE173" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:44</t>
+          <t>2026-09-18 08:50:17</t>
         </is>
       </c>
       <c r="AF173" t="inlineStr">
@@ -20457,7 +20457,7 @@
       </c>
       <c r="AE174" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF174" t="inlineStr">
@@ -20569,7 +20569,7 @@
       </c>
       <c r="AE175" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF175" t="inlineStr">
@@ -20681,7 +20681,7 @@
       </c>
       <c r="AE176" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF176" t="inlineStr">
@@ -20809,7 +20809,7 @@
       </c>
       <c r="AE177" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:28</t>
+          <t>2026-09-18 08:50:02</t>
         </is>
       </c>
       <c r="AF177" t="inlineStr">
@@ -20919,7 +20919,7 @@
       </c>
       <c r="AE178" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF178" t="inlineStr">
@@ -21039,7 +21039,7 @@
       </c>
       <c r="AE179" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="AF179" t="inlineStr">
@@ -21161,7 +21161,7 @@
       <c r="AD180" t="inlineStr"/>
       <c r="AE180" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="AF180" t="inlineStr">
@@ -21287,7 +21287,7 @@
       <c r="AD181" t="inlineStr"/>
       <c r="AE181" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="AF181" t="inlineStr">
@@ -21413,7 +21413,7 @@
       <c r="AD182" t="inlineStr"/>
       <c r="AE182" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="AF182" t="inlineStr">
@@ -21529,7 +21529,7 @@
       </c>
       <c r="AE183" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:44</t>
+          <t>2026-09-18 08:50:17</t>
         </is>
       </c>
       <c r="AF183" t="inlineStr">
@@ -21643,7 +21643,7 @@
       </c>
       <c r="AE184" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF184" t="inlineStr">
@@ -21757,7 +21757,7 @@
       </c>
       <c r="AE185" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF185" t="inlineStr">
@@ -21871,7 +21871,7 @@
       </c>
       <c r="AE186" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF186" t="inlineStr">
@@ -21991,7 +21991,7 @@
       </c>
       <c r="AE187" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="AF187" t="inlineStr">
@@ -22111,7 +22111,7 @@
       </c>
       <c r="AE188" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="AF188" t="inlineStr">
@@ -22221,7 +22221,7 @@
       </c>
       <c r="AE189" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF189" t="inlineStr">
@@ -22331,7 +22331,7 @@
       </c>
       <c r="AE190" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF190" t="inlineStr">
@@ -22441,7 +22441,7 @@
       </c>
       <c r="AE191" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF191" t="inlineStr">
@@ -22557,7 +22557,7 @@
       </c>
       <c r="AE192" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF192" t="inlineStr">
@@ -22685,7 +22685,7 @@
       </c>
       <c r="AE193" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="AF193" t="inlineStr">
@@ -22797,7 +22797,7 @@
       </c>
       <c r="AE194" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF194" t="inlineStr">
@@ -22909,7 +22909,7 @@
       </c>
       <c r="AE195" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF195" t="inlineStr">
@@ -23027,7 +23027,7 @@
       </c>
       <c r="AE196" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:26</t>
+          <t>2026-09-18 08:50:00</t>
         </is>
       </c>
       <c r="AF196" t="inlineStr">
@@ -23137,7 +23137,7 @@
       </c>
       <c r="AE197" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF197" t="inlineStr">
@@ -23247,7 +23247,7 @@
       </c>
       <c r="AE198" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF198" t="inlineStr">
@@ -23359,7 +23359,7 @@
       </c>
       <c r="AE199" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF199" t="inlineStr">
@@ -23469,7 +23469,7 @@
       </c>
       <c r="AE200" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF200" t="inlineStr">
@@ -23589,7 +23589,7 @@
       </c>
       <c r="AE201" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="AF201" t="inlineStr">
@@ -23705,7 +23705,7 @@
       </c>
       <c r="AE202" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF202" t="inlineStr">
@@ -23821,7 +23821,7 @@
       </c>
       <c r="AE203" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF203" t="inlineStr">
@@ -23949,7 +23949,7 @@
       </c>
       <c r="AE204" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="AF204" t="inlineStr">
@@ -24061,7 +24061,7 @@
       </c>
       <c r="AE205" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF205" t="inlineStr">
@@ -24173,7 +24173,7 @@
       </c>
       <c r="AE206" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF206" t="inlineStr">
@@ -24285,7 +24285,7 @@
       </c>
       <c r="AE207" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF207" t="inlineStr">
@@ -24401,7 +24401,7 @@
       </c>
       <c r="AE208" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF208" t="inlineStr">
@@ -24511,7 +24511,7 @@
       </c>
       <c r="AE209" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF209" t="inlineStr">
@@ -24631,7 +24631,7 @@
       </c>
       <c r="AE210" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="AF210" t="inlineStr">
@@ -24741,7 +24741,7 @@
       </c>
       <c r="AE211" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF211" t="inlineStr">
@@ -24861,7 +24861,7 @@
       </c>
       <c r="AE212" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="AF212" t="inlineStr">
@@ -24971,7 +24971,7 @@
       </c>
       <c r="AE213" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF213" t="inlineStr">
@@ -25085,7 +25085,7 @@
       </c>
       <c r="AE214" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:26</t>
+          <t>2026-09-18 08:50:00</t>
         </is>
       </c>
       <c r="AF214" t="inlineStr">
@@ -25195,7 +25195,7 @@
       </c>
       <c r="AE215" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF215" t="inlineStr">
@@ -25305,7 +25305,7 @@
       </c>
       <c r="AE216" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF216" t="inlineStr">
@@ -25419,7 +25419,7 @@
       </c>
       <c r="AE217" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF217" t="inlineStr">
@@ -25529,7 +25529,7 @@
       </c>
       <c r="AE218" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF218" t="inlineStr">
@@ -25641,7 +25641,7 @@
       </c>
       <c r="AE219" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF219" t="inlineStr">
@@ -25751,7 +25751,7 @@
       </c>
       <c r="AE220" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF220" t="inlineStr">
@@ -25871,7 +25871,7 @@
       </c>
       <c r="AE221" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="AF221" t="inlineStr">
@@ -25983,7 +25983,7 @@
       </c>
       <c r="AE222" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF222" t="inlineStr">
@@ -26093,7 +26093,7 @@
       </c>
       <c r="AE223" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF223" t="inlineStr">
@@ -26217,7 +26217,7 @@
       </c>
       <c r="AE224" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:28</t>
+          <t>2026-09-18 08:50:02</t>
         </is>
       </c>
       <c r="AF224" t="inlineStr">
@@ -26341,7 +26341,7 @@
       </c>
       <c r="AE225" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:28</t>
+          <t>2026-09-18 08:50:02</t>
         </is>
       </c>
       <c r="AF225" t="inlineStr">
@@ -26451,7 +26451,7 @@
       </c>
       <c r="AE226" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF226" t="inlineStr">
@@ -26561,7 +26561,7 @@
       </c>
       <c r="AE227" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF227" t="inlineStr">
@@ -26671,7 +26671,7 @@
       </c>
       <c r="AE228" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF228" t="inlineStr">
@@ -26783,7 +26783,7 @@
       </c>
       <c r="AE229" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF229" t="inlineStr">
@@ -26893,7 +26893,7 @@
       </c>
       <c r="AE230" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF230" t="inlineStr">
@@ -27003,7 +27003,7 @@
       </c>
       <c r="AE231" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF231" t="inlineStr">
@@ -27131,7 +27131,7 @@
       </c>
       <c r="AE232" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="AF232" t="inlineStr">
@@ -27237,7 +27237,7 @@
       </c>
       <c r="AE233" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF233" t="inlineStr">
@@ -27349,7 +27349,7 @@
       </c>
       <c r="AE234" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF234" t="inlineStr">
@@ -27465,7 +27465,7 @@
       </c>
       <c r="AE235" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:44</t>
+          <t>2026-09-18 08:50:17</t>
         </is>
       </c>
       <c r="AF235" t="inlineStr">
@@ -27581,7 +27581,7 @@
       </c>
       <c r="AE236" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:44</t>
+          <t>2026-09-18 08:50:17</t>
         </is>
       </c>
       <c r="AF236" t="inlineStr">
@@ -27691,7 +27691,7 @@
       </c>
       <c r="AE237" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF237" t="inlineStr">
@@ -27801,7 +27801,7 @@
       </c>
       <c r="AE238" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF238" t="inlineStr">
@@ -27917,7 +27917,7 @@
       </c>
       <c r="AE239" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:44</t>
+          <t>2026-09-18 08:50:17</t>
         </is>
       </c>
       <c r="AF239" t="inlineStr">
@@ -28033,7 +28033,7 @@
       </c>
       <c r="AE240" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:44</t>
+          <t>2026-09-18 08:50:17</t>
         </is>
       </c>
       <c r="AF240" t="inlineStr">
@@ -28143,7 +28143,7 @@
       </c>
       <c r="AE241" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF241" t="inlineStr">
@@ -28259,7 +28259,7 @@
       </c>
       <c r="AE242" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:44</t>
+          <t>2026-09-18 08:50:17</t>
         </is>
       </c>
       <c r="AF242" t="inlineStr">
@@ -28375,7 +28375,7 @@
       </c>
       <c r="AE243" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:44</t>
+          <t>2026-09-18 08:50:17</t>
         </is>
       </c>
       <c r="AF243" t="inlineStr">
@@ -28485,7 +28485,7 @@
       </c>
       <c r="AE244" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF244" t="inlineStr">
@@ -28595,7 +28595,7 @@
       </c>
       <c r="AE245" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF245" t="inlineStr">
@@ -28705,7 +28705,7 @@
       </c>
       <c r="AE246" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF246" t="inlineStr">
@@ -28805,7 +28805,7 @@
       </c>
       <c r="AE247" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF247" t="inlineStr">
@@ -28921,7 +28921,7 @@
       </c>
       <c r="AE248" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:44</t>
+          <t>2026-09-18 08:50:17</t>
         </is>
       </c>
       <c r="AF248" t="inlineStr">
@@ -29031,7 +29031,7 @@
       </c>
       <c r="AE249" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF249" t="inlineStr">
@@ -29143,7 +29143,7 @@
       </c>
       <c r="AE250" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF250" t="inlineStr">
@@ -29253,7 +29253,7 @@
       </c>
       <c r="AE251" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF251" t="inlineStr">
@@ -29373,7 +29373,7 @@
       </c>
       <c r="AE252" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="AF252" t="inlineStr">
@@ -29485,7 +29485,7 @@
       </c>
       <c r="AE253" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF253" t="inlineStr">
@@ -29595,7 +29595,7 @@
       </c>
       <c r="AE254" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF254" t="inlineStr">
@@ -29707,7 +29707,7 @@
       </c>
       <c r="AE255" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF255" t="inlineStr">
@@ -29823,7 +29823,7 @@
       </c>
       <c r="AE256" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF256" t="inlineStr">
@@ -29935,7 +29935,7 @@
       </c>
       <c r="AE257" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF257" t="inlineStr">
@@ -30045,7 +30045,7 @@
       </c>
       <c r="AE258" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF258" t="inlineStr">
@@ -30161,7 +30161,7 @@
       </c>
       <c r="AE259" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF259" t="inlineStr">
@@ -30271,7 +30271,7 @@
       </c>
       <c r="AE260" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF260" t="inlineStr">
@@ -30397,7 +30397,7 @@
       <c r="AD261" t="inlineStr"/>
       <c r="AE261" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="AF261" t="inlineStr">
@@ -30525,7 +30525,7 @@
       </c>
       <c r="AE262" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="AF262" t="inlineStr">
@@ -30637,7 +30637,7 @@
       </c>
       <c r="AE263" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF263" t="inlineStr">
@@ -30737,7 +30737,7 @@
       </c>
       <c r="AE264" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF264" t="inlineStr">
@@ -30837,7 +30837,7 @@
       </c>
       <c r="AE265" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF265" t="inlineStr">
@@ -30951,7 +30951,7 @@
       </c>
       <c r="AE266" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF266" t="inlineStr">
@@ -31065,7 +31065,7 @@
       </c>
       <c r="AE267" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF267" t="inlineStr">
@@ -31165,7 +31165,7 @@
       </c>
       <c r="AE268" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF268" t="inlineStr">
@@ -31285,7 +31285,7 @@
       </c>
       <c r="AE269" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="AF269" t="inlineStr">
@@ -31397,7 +31397,7 @@
       </c>
       <c r="AE270" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF270" t="inlineStr">
@@ -31509,7 +31509,7 @@
       </c>
       <c r="AE271" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF271" t="inlineStr">
@@ -31623,7 +31623,7 @@
       </c>
       <c r="AE272" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF272" t="inlineStr">
@@ -31737,7 +31737,7 @@
       </c>
       <c r="AE273" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:26</t>
+          <t>2026-09-18 08:50:00</t>
         </is>
       </c>
       <c r="AF273" t="inlineStr">
@@ -31851,7 +31851,7 @@
       </c>
       <c r="AE274" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:26</t>
+          <t>2026-09-18 08:50:00</t>
         </is>
       </c>
       <c r="AF274" t="inlineStr">
@@ -31983,7 +31983,7 @@
       </c>
       <c r="AE275" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="AF275" t="inlineStr">
@@ -32111,7 +32111,7 @@
       </c>
       <c r="AE276" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="AF276" t="inlineStr">
@@ -32239,7 +32239,7 @@
       </c>
       <c r="AE277" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="AF277" t="inlineStr">
@@ -32367,7 +32367,7 @@
       </c>
       <c r="AE278" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="AF278" t="inlineStr">
@@ -32479,7 +32479,7 @@
       </c>
       <c r="AE279" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF279" t="inlineStr">
@@ -32591,7 +32591,7 @@
       </c>
       <c r="AE280" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF280" t="inlineStr">
@@ -32701,7 +32701,7 @@
       </c>
       <c r="AE281" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF281" t="inlineStr">
@@ -32811,7 +32811,7 @@
       </c>
       <c r="AE282" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF282" t="inlineStr">
@@ -32939,7 +32939,7 @@
       </c>
       <c r="AE283" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="AF283" t="inlineStr">
@@ -33049,7 +33049,7 @@
       </c>
       <c r="AE284" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF284" t="inlineStr">
@@ -33177,7 +33177,7 @@
       </c>
       <c r="AE285" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="AF285" t="inlineStr">
@@ -33289,7 +33289,7 @@
       </c>
       <c r="AE286" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF286" t="inlineStr">
@@ -33401,7 +33401,7 @@
       </c>
       <c r="AE287" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF287" t="inlineStr">
@@ -33511,7 +33511,7 @@
       </c>
       <c r="AE288" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF288" t="inlineStr">
@@ -33631,7 +33631,7 @@
       </c>
       <c r="AE289" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="AF289" t="inlineStr">
@@ -33755,7 +33755,7 @@
       </c>
       <c r="AE290" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="AF290" t="inlineStr">
@@ -33879,7 +33879,7 @@
       </c>
       <c r="AE291" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="AF291" t="inlineStr">
@@ -34003,7 +34003,7 @@
       </c>
       <c r="AE292" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="AF292" t="inlineStr">
@@ -34115,7 +34115,7 @@
       </c>
       <c r="AE293" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF293" t="inlineStr">
@@ -34231,7 +34231,7 @@
       </c>
       <c r="AE294" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF294" t="inlineStr">
@@ -34343,7 +34343,7 @@
       </c>
       <c r="AE295" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:28</t>
+          <t>2026-09-18 08:50:02</t>
         </is>
       </c>
       <c r="AF295" t="inlineStr">
@@ -34471,7 +34471,7 @@
       </c>
       <c r="AE296" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:28</t>
+          <t>2026-09-18 08:50:02</t>
         </is>
       </c>
       <c r="AF296" t="inlineStr">
@@ -34599,7 +34599,7 @@
       </c>
       <c r="AE297" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="AF297" t="inlineStr">
@@ -34711,7 +34711,7 @@
       </c>
       <c r="AE298" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF298" t="inlineStr">
@@ -34823,7 +34823,7 @@
       </c>
       <c r="AE299" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF299" t="inlineStr">
@@ -34933,7 +34933,7 @@
       </c>
       <c r="AE300" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF300" t="inlineStr">
@@ -35043,7 +35043,7 @@
       </c>
       <c r="AE301" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF301" t="inlineStr">
@@ -35159,7 +35159,7 @@
       </c>
       <c r="AE302" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF302" t="inlineStr">
@@ -35271,7 +35271,7 @@
       </c>
       <c r="AE303" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF303" t="inlineStr">
@@ -35391,7 +35391,7 @@
       </c>
       <c r="AE304" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="AF304" t="inlineStr">
@@ -35519,7 +35519,7 @@
       </c>
       <c r="AE305" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="AF305" t="inlineStr">
@@ -35635,7 +35635,7 @@
       </c>
       <c r="AE306" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF306" t="inlineStr">
@@ -35735,7 +35735,7 @@
       </c>
       <c r="AE307" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF307" t="inlineStr">
@@ -35847,7 +35847,7 @@
       </c>
       <c r="AE308" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF308" t="inlineStr">
@@ -35975,7 +35975,7 @@
       </c>
       <c r="AE309" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="AF309" t="inlineStr">
@@ -36099,7 +36099,7 @@
       </c>
       <c r="AE310" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:28</t>
+          <t>2026-09-18 08:50:02</t>
         </is>
       </c>
       <c r="AF310" t="inlineStr">
@@ -36211,7 +36211,7 @@
       </c>
       <c r="AE311" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF311" t="inlineStr">
@@ -36321,7 +36321,7 @@
       </c>
       <c r="AE312" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF312" t="inlineStr">
@@ -36431,7 +36431,7 @@
       </c>
       <c r="AE313" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF313" t="inlineStr">
@@ -36541,7 +36541,7 @@
       </c>
       <c r="AE314" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF314" t="inlineStr">
@@ -36651,7 +36651,7 @@
       </c>
       <c r="AE315" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF315" t="inlineStr">
@@ -36771,7 +36771,7 @@
       </c>
       <c r="AE316" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="AF316" t="inlineStr">
@@ -36881,7 +36881,7 @@
       </c>
       <c r="AE317" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF317" t="inlineStr">
@@ -36991,7 +36991,7 @@
       </c>
       <c r="AE318" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF318" t="inlineStr">
@@ -37101,7 +37101,7 @@
       </c>
       <c r="AE319" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF319" t="inlineStr">
@@ -37221,7 +37221,7 @@
       </c>
       <c r="AE320" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="AF320" t="inlineStr">
@@ -37341,7 +37341,7 @@
       </c>
       <c r="AE321" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="AF321" t="inlineStr">
@@ -37461,7 +37461,7 @@
       </c>
       <c r="AE322" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="AF322" t="inlineStr">
@@ -37581,7 +37581,7 @@
       </c>
       <c r="AE323" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="AF323" t="inlineStr">
@@ -37697,7 +37697,7 @@
       </c>
       <c r="AE324" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:44</t>
+          <t>2026-09-18 08:50:17</t>
         </is>
       </c>
       <c r="AF324" t="inlineStr">
@@ -37813,7 +37813,7 @@
       </c>
       <c r="AE325" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:44</t>
+          <t>2026-09-18 08:50:17</t>
         </is>
       </c>
       <c r="AF325" t="inlineStr">
@@ -37929,7 +37929,7 @@
       </c>
       <c r="AE326" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:44</t>
+          <t>2026-09-18 08:50:17</t>
         </is>
       </c>
       <c r="AF326" t="inlineStr">
@@ -38041,7 +38041,7 @@
       </c>
       <c r="AE327" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF327" t="inlineStr">
@@ -38157,7 +38157,7 @@
       </c>
       <c r="AE328" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:44</t>
+          <t>2026-09-18 08:50:17</t>
         </is>
       </c>
       <c r="AF328" t="inlineStr">
@@ -38277,7 +38277,7 @@
       </c>
       <c r="AE329" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="AF329" t="inlineStr">
@@ -38389,7 +38389,7 @@
       </c>
       <c r="AE330" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF330" t="inlineStr">
@@ -38505,7 +38505,7 @@
       </c>
       <c r="AE331" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:44</t>
+          <t>2026-09-18 08:50:17</t>
         </is>
       </c>
       <c r="AF331" t="inlineStr">
@@ -38621,7 +38621,7 @@
       </c>
       <c r="AE332" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:44</t>
+          <t>2026-09-18 08:50:17</t>
         </is>
       </c>
       <c r="AF332" t="inlineStr">
@@ -38737,7 +38737,7 @@
       </c>
       <c r="AE333" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:44</t>
+          <t>2026-09-18 08:50:17</t>
         </is>
       </c>
       <c r="AF333" t="inlineStr">
@@ -38853,7 +38853,7 @@
       </c>
       <c r="AE334" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:44</t>
+          <t>2026-09-18 08:50:17</t>
         </is>
       </c>
       <c r="AF334" t="inlineStr">
@@ -38967,7 +38967,7 @@
       </c>
       <c r="AE335" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:26</t>
+          <t>2026-09-18 08:50:00</t>
         </is>
       </c>
       <c r="AF335" t="inlineStr">
@@ -39083,7 +39083,7 @@
       </c>
       <c r="AE336" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:44</t>
+          <t>2026-09-18 08:50:17</t>
         </is>
       </c>
       <c r="AF336" t="inlineStr">
@@ -39199,7 +39199,7 @@
       </c>
       <c r="AE337" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:44</t>
+          <t>2026-09-18 08:50:17</t>
         </is>
       </c>
       <c r="AF337" t="inlineStr">
@@ -39315,7 +39315,7 @@
       </c>
       <c r="AE338" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:44</t>
+          <t>2026-09-18 08:50:17</t>
         </is>
       </c>
       <c r="AF338" t="inlineStr">
@@ -39425,7 +39425,7 @@
       </c>
       <c r="AE339" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF339" t="inlineStr">
@@ -39541,7 +39541,7 @@
       </c>
       <c r="AE340" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF340" t="inlineStr">
@@ -39653,7 +39653,7 @@
       </c>
       <c r="AE341" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF341" t="inlineStr">
@@ -39763,7 +39763,7 @@
       </c>
       <c r="AE342" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF342" t="inlineStr">
@@ -39875,7 +39875,7 @@
       </c>
       <c r="AE343" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF343" t="inlineStr">
@@ -39987,7 +39987,7 @@
       </c>
       <c r="AE344" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF344" t="inlineStr">
@@ -40099,7 +40099,7 @@
       </c>
       <c r="AE345" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF345" t="inlineStr">
@@ -40219,7 +40219,7 @@
       </c>
       <c r="AE346" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="AF346" t="inlineStr">
@@ -40347,7 +40347,7 @@
       </c>
       <c r="AE347" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="AF347" t="inlineStr">
@@ -40467,7 +40467,7 @@
       </c>
       <c r="AE348" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="AF348" t="inlineStr">
@@ -40595,7 +40595,7 @@
       </c>
       <c r="AE349" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="AF349" t="inlineStr">
@@ -40707,7 +40707,7 @@
       </c>
       <c r="AE350" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF350" t="inlineStr">
@@ -40817,7 +40817,7 @@
       </c>
       <c r="AE351" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF351" t="inlineStr">
@@ -40927,7 +40927,7 @@
       </c>
       <c r="AE352" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF352" t="inlineStr">
@@ -41039,7 +41039,7 @@
       </c>
       <c r="AE353" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF353" t="inlineStr">
@@ -41151,7 +41151,7 @@
       </c>
       <c r="AE354" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF354" t="inlineStr">
@@ -41261,7 +41261,7 @@
       </c>
       <c r="AE355" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF355" t="inlineStr">
@@ -41377,7 +41377,7 @@
       </c>
       <c r="AE356" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF356" t="inlineStr">
@@ -41487,7 +41487,7 @@
       </c>
       <c r="AE357" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF357" t="inlineStr">
@@ -41599,7 +41599,7 @@
       </c>
       <c r="AE358" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF358" t="inlineStr">
@@ -41709,7 +41709,7 @@
       </c>
       <c r="AE359" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF359" t="inlineStr">
@@ -41819,7 +41819,7 @@
       </c>
       <c r="AE360" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF360" t="inlineStr">
@@ -41947,7 +41947,7 @@
       </c>
       <c r="AE361" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="AF361" t="inlineStr">
@@ -42059,7 +42059,7 @@
       </c>
       <c r="AE362" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF362" t="inlineStr">
@@ -42187,7 +42187,7 @@
       </c>
       <c r="AE363" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="AF363" t="inlineStr">
@@ -42299,7 +42299,7 @@
       </c>
       <c r="AE364" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF364" t="inlineStr">
@@ -42409,7 +42409,7 @@
       </c>
       <c r="AE365" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF365" t="inlineStr">
@@ -42519,7 +42519,7 @@
       </c>
       <c r="AE366" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF366" t="inlineStr">
@@ -42629,7 +42629,7 @@
       </c>
       <c r="AE367" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF367" t="inlineStr">
@@ -42741,7 +42741,7 @@
       </c>
       <c r="AE368" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF368" t="inlineStr">
@@ -42851,7 +42851,7 @@
       </c>
       <c r="AE369" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF369" t="inlineStr">
@@ -42979,7 +42979,7 @@
       </c>
       <c r="AE370" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="AF370" t="inlineStr">
@@ -43091,7 +43091,7 @@
       </c>
       <c r="AE371" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF371" t="inlineStr">
@@ -43201,7 +43201,7 @@
       </c>
       <c r="AE372" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF372" t="inlineStr">
@@ -43311,7 +43311,7 @@
       </c>
       <c r="AE373" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF373" t="inlineStr">
@@ -43421,7 +43421,7 @@
       </c>
       <c r="AE374" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF374" t="inlineStr">
@@ -43531,7 +43531,7 @@
       </c>
       <c r="AE375" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF375" t="inlineStr">
@@ -43641,7 +43641,7 @@
       </c>
       <c r="AE376" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF376" t="inlineStr">
@@ -43753,7 +43753,7 @@
       </c>
       <c r="AE377" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF377" t="inlineStr">
@@ -43881,7 +43881,7 @@
       </c>
       <c r="AE378" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="AF378" t="inlineStr">
@@ -43991,7 +43991,7 @@
       </c>
       <c r="AE379" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF379" t="inlineStr">
@@ -44101,7 +44101,7 @@
       </c>
       <c r="AE380" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF380" t="inlineStr">
@@ -44213,7 +44213,7 @@
       </c>
       <c r="AE381" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:28</t>
+          <t>2026-09-18 08:50:02</t>
         </is>
       </c>
       <c r="AF381" t="inlineStr">
@@ -44323,7 +44323,7 @@
       </c>
       <c r="AE382" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF382" t="inlineStr">
@@ -44435,7 +44435,7 @@
       </c>
       <c r="AE383" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF383" t="inlineStr">
@@ -44563,7 +44563,7 @@
       </c>
       <c r="AE384" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="AF384" t="inlineStr">
@@ -44673,7 +44673,7 @@
       </c>
       <c r="AE385" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF385" t="inlineStr">
@@ -44785,7 +44785,7 @@
       </c>
       <c r="AE386" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF386" t="inlineStr">
@@ -44895,7 +44895,7 @@
       </c>
       <c r="AE387" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF387" t="inlineStr">
@@ -45005,7 +45005,7 @@
       </c>
       <c r="AE388" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF388" t="inlineStr">
@@ -45115,7 +45115,7 @@
       </c>
       <c r="AE389" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF389" t="inlineStr">
@@ -45215,7 +45215,7 @@
       </c>
       <c r="AE390" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF390" t="inlineStr">
@@ -45325,7 +45325,7 @@
       </c>
       <c r="AE391" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF391" t="inlineStr">
@@ -45425,7 +45425,7 @@
       </c>
       <c r="AE392" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF392" t="inlineStr">
@@ -45535,7 +45535,7 @@
       </c>
       <c r="AE393" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF393" t="inlineStr">
@@ -45663,7 +45663,7 @@
       </c>
       <c r="AE394" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="AF394" t="inlineStr">
@@ -45773,7 +45773,7 @@
       </c>
       <c r="AE395" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF395" t="inlineStr">
@@ -45883,7 +45883,7 @@
       </c>
       <c r="AE396" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF396" t="inlineStr">
@@ -45993,7 +45993,7 @@
       </c>
       <c r="AE397" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF397" t="inlineStr">
@@ -46103,7 +46103,7 @@
       </c>
       <c r="AE398" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF398" t="inlineStr">
@@ -46213,7 +46213,7 @@
       </c>
       <c r="AE399" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF399" t="inlineStr">
@@ -46323,7 +46323,7 @@
       </c>
       <c r="AE400" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF400" t="inlineStr">
@@ -46433,7 +46433,7 @@
       </c>
       <c r="AE401" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF401" t="inlineStr">
@@ -46543,7 +46543,7 @@
       </c>
       <c r="AE402" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF402" t="inlineStr">
@@ -46671,7 +46671,7 @@
       </c>
       <c r="AE403" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="AF403" t="inlineStr">
@@ -46783,7 +46783,7 @@
       </c>
       <c r="AE404" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF404" t="inlineStr">
@@ -46883,7 +46883,7 @@
       </c>
       <c r="AE405" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF405" t="inlineStr">
@@ -46993,7 +46993,7 @@
       </c>
       <c r="AE406" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF406" t="inlineStr">
@@ -47107,7 +47107,7 @@
       </c>
       <c r="AE407" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF407" t="inlineStr">
@@ -47217,7 +47217,7 @@
       </c>
       <c r="AE408" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF408" t="inlineStr">
@@ -47317,7 +47317,7 @@
       </c>
       <c r="AE409" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF409" t="inlineStr">
@@ -47429,7 +47429,7 @@
       </c>
       <c r="AE410" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF410" t="inlineStr">
@@ -47541,7 +47541,7 @@
       </c>
       <c r="AE411" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF411" t="inlineStr">
@@ -47651,7 +47651,7 @@
       </c>
       <c r="AE412" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF412" t="inlineStr">
@@ -47763,7 +47763,7 @@
       </c>
       <c r="AE413" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF413" t="inlineStr">
@@ -47875,7 +47875,7 @@
       </c>
       <c r="AE414" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF414" t="inlineStr">
@@ -47985,7 +47985,7 @@
       </c>
       <c r="AE415" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF415" t="inlineStr">
@@ -48113,7 +48113,7 @@
       </c>
       <c r="AE416" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="AF416" t="inlineStr">
@@ -48245,7 +48245,7 @@
       </c>
       <c r="AE417" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="AF417" t="inlineStr">
@@ -48377,7 +48377,7 @@
       </c>
       <c r="AE418" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="AF418" t="inlineStr">
@@ -48509,7 +48509,7 @@
       </c>
       <c r="AE419" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="AF419" t="inlineStr">
@@ -48633,7 +48633,7 @@
       </c>
       <c r="AE420" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:28</t>
+          <t>2026-09-18 08:50:02</t>
         </is>
       </c>
       <c r="AF420" t="inlineStr">
@@ -48745,7 +48745,7 @@
       </c>
       <c r="AE421" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF421" t="inlineStr">
@@ -48845,7 +48845,7 @@
       </c>
       <c r="AE422" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF422" t="inlineStr">
@@ -48965,7 +48965,7 @@
       </c>
       <c r="AE423" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="AF423" t="inlineStr">
@@ -49081,7 +49081,7 @@
       </c>
       <c r="AE424" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF424" t="inlineStr">
@@ -49193,7 +49193,7 @@
       </c>
       <c r="AE425" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF425" t="inlineStr">
@@ -49315,7 +49315,7 @@
       <c r="AD426" t="inlineStr"/>
       <c r="AE426" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="AF426" t="inlineStr">
@@ -49427,7 +49427,7 @@
       </c>
       <c r="AE427" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF427" t="inlineStr">
@@ -49537,7 +49537,7 @@
       </c>
       <c r="AE428" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF428" t="inlineStr">
@@ -49647,7 +49647,7 @@
       </c>
       <c r="AE429" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF429" t="inlineStr">
@@ -49757,7 +49757,7 @@
       </c>
       <c r="AE430" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF430" t="inlineStr">
@@ -49867,7 +49867,7 @@
       </c>
       <c r="AE431" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF431" t="inlineStr">
@@ -49995,7 +49995,7 @@
       </c>
       <c r="AE432" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="AF432" t="inlineStr">
@@ -50111,7 +50111,7 @@
       </c>
       <c r="AE433" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF433" t="inlineStr">
@@ -50221,7 +50221,7 @@
       </c>
       <c r="AE434" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF434" t="inlineStr">
@@ -50349,7 +50349,7 @@
       </c>
       <c r="AE435" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="AF435" t="inlineStr">
@@ -50477,7 +50477,7 @@
       </c>
       <c r="AE436" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="AF436" t="inlineStr">
@@ -50605,7 +50605,7 @@
       </c>
       <c r="AE437" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="AF437" t="inlineStr">
@@ -50733,7 +50733,7 @@
       </c>
       <c r="AE438" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="AF438" t="inlineStr">
@@ -50845,7 +50845,7 @@
       </c>
       <c r="AE439" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF439" t="inlineStr">
@@ -50955,7 +50955,7 @@
       </c>
       <c r="AE440" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF440" t="inlineStr">
@@ -51083,7 +51083,7 @@
       </c>
       <c r="AE441" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="AF441" t="inlineStr">
@@ -51195,7 +51195,7 @@
       </c>
       <c r="AE442" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF442" t="inlineStr">
@@ -51307,7 +51307,7 @@
       </c>
       <c r="AE443" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF443" t="inlineStr">
@@ -51423,7 +51423,7 @@
       </c>
       <c r="AE444" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF444" t="inlineStr">
@@ -51535,7 +51535,7 @@
       </c>
       <c r="AE445" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF445" t="inlineStr">
@@ -51647,7 +51647,7 @@
       </c>
       <c r="AE446" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF446" t="inlineStr">
@@ -51759,7 +51759,7 @@
       </c>
       <c r="AE447" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF447" t="inlineStr">
@@ -51871,7 +51871,7 @@
       </c>
       <c r="AE448" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF448" t="inlineStr">
@@ -51991,7 +51991,7 @@
       </c>
       <c r="AE449" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="AF449" t="inlineStr">
@@ -52101,7 +52101,7 @@
       </c>
       <c r="AE450" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF450" t="inlineStr">
@@ -52229,7 +52229,7 @@
       </c>
       <c r="AE451" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="AF451" t="inlineStr">
@@ -52349,7 +52349,7 @@
       </c>
       <c r="AE452" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="AF452" t="inlineStr">
@@ -52461,7 +52461,7 @@
       </c>
       <c r="AE453" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF453" t="inlineStr">
@@ -52573,7 +52573,7 @@
       </c>
       <c r="AE454" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF454" t="inlineStr">
@@ -52673,7 +52673,7 @@
       </c>
       <c r="AE455" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF455" t="inlineStr">
@@ -52789,7 +52789,7 @@
       </c>
       <c r="AE456" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF456" t="inlineStr">
@@ -52899,7 +52899,7 @@
       </c>
       <c r="AE457" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF457" t="inlineStr">
@@ -53011,7 +53011,7 @@
       </c>
       <c r="AE458" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF458" t="inlineStr">
@@ -53121,7 +53121,7 @@
       </c>
       <c r="AE459" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF459" t="inlineStr">
@@ -53233,7 +53233,7 @@
       </c>
       <c r="AE460" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF460" t="inlineStr">
@@ -53345,7 +53345,7 @@
       </c>
       <c r="AE461" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF461" t="inlineStr">
@@ -53445,7 +53445,7 @@
       </c>
       <c r="AE462" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF462" t="inlineStr">
@@ -53555,7 +53555,7 @@
       </c>
       <c r="AE463" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF463" t="inlineStr">
@@ -53667,7 +53667,7 @@
       </c>
       <c r="AE464" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF464" t="inlineStr">
@@ -53777,7 +53777,7 @@
       </c>
       <c r="AE465" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF465" t="inlineStr">
@@ -53887,7 +53887,7 @@
       </c>
       <c r="AE466" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF466" t="inlineStr">
@@ -53999,7 +53999,7 @@
       </c>
       <c r="AE467" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF467" t="inlineStr">
@@ -54109,7 +54109,7 @@
       </c>
       <c r="AE468" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF468" t="inlineStr">
@@ -54219,7 +54219,7 @@
       </c>
       <c r="AE469" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF469" t="inlineStr">
@@ -54329,7 +54329,7 @@
       </c>
       <c r="AE470" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF470" t="inlineStr">
@@ -54449,7 +54449,7 @@
       </c>
       <c r="AE471" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="AF471" t="inlineStr">
@@ -54573,7 +54573,7 @@
       </c>
       <c r="AE472" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:28</t>
+          <t>2026-09-18 08:50:02</t>
         </is>
       </c>
       <c r="AF472" t="inlineStr">
@@ -54683,7 +54683,7 @@
       </c>
       <c r="AE473" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF473" t="inlineStr">
@@ -54795,7 +54795,7 @@
       </c>
       <c r="AE474" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF474" t="inlineStr">
@@ -54905,7 +54905,7 @@
       </c>
       <c r="AE475" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF475" t="inlineStr">
@@ -55017,7 +55017,7 @@
       </c>
       <c r="AE476" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF476" t="inlineStr">
@@ -55129,7 +55129,7 @@
       </c>
       <c r="AE477" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF477" t="inlineStr">
@@ -55239,7 +55239,7 @@
       </c>
       <c r="AE478" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF478" t="inlineStr">
@@ -55349,7 +55349,7 @@
       </c>
       <c r="AE479" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF479" t="inlineStr">
@@ -55459,7 +55459,7 @@
       </c>
       <c r="AE480" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF480" t="inlineStr">
@@ -55569,7 +55569,7 @@
       </c>
       <c r="AE481" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF481" t="inlineStr">
@@ -55679,7 +55679,7 @@
       </c>
       <c r="AE482" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF482" t="inlineStr">
@@ -55789,7 +55789,7 @@
       </c>
       <c r="AE483" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF483" t="inlineStr">
@@ -55901,7 +55901,7 @@
       </c>
       <c r="AE484" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF484" t="inlineStr">
@@ -56013,7 +56013,7 @@
       </c>
       <c r="AE485" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF485" t="inlineStr">
@@ -56125,7 +56125,7 @@
       </c>
       <c r="AE486" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF486" t="inlineStr">
@@ -56235,7 +56235,7 @@
       </c>
       <c r="AE487" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF487" t="inlineStr">
@@ -56347,7 +56347,7 @@
       </c>
       <c r="AE488" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF488" t="inlineStr">
@@ -56447,7 +56447,7 @@
       </c>
       <c r="AE489" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF489" t="inlineStr">
@@ -56557,7 +56557,7 @@
       </c>
       <c r="AE490" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF490" t="inlineStr">
@@ -56657,7 +56657,7 @@
       </c>
       <c r="AE491" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF491" t="inlineStr">
@@ -56757,7 +56757,7 @@
       </c>
       <c r="AE492" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF492" t="inlineStr">
@@ -56869,7 +56869,7 @@
       </c>
       <c r="AE493" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF493" t="inlineStr">
@@ -56981,7 +56981,7 @@
       </c>
       <c r="AE494" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF494" t="inlineStr">
@@ -57093,7 +57093,7 @@
       </c>
       <c r="AE495" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF495" t="inlineStr">
@@ -57203,7 +57203,7 @@
       </c>
       <c r="AE496" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF496" t="inlineStr">
@@ -57313,7 +57313,7 @@
       </c>
       <c r="AE497" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF497" t="inlineStr">
@@ -57423,7 +57423,7 @@
       </c>
       <c r="AE498" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF498" t="inlineStr">
@@ -57535,7 +57535,7 @@
       </c>
       <c r="AE499" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF499" t="inlineStr">
@@ -57645,7 +57645,7 @@
       </c>
       <c r="AE500" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF500" t="inlineStr">
@@ -57755,7 +57755,7 @@
       </c>
       <c r="AE501" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF501" t="inlineStr">
@@ -57865,7 +57865,7 @@
       </c>
       <c r="AE502" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF502" t="inlineStr">
@@ -57975,7 +57975,7 @@
       </c>
       <c r="AE503" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF503" t="inlineStr">
@@ -58087,7 +58087,7 @@
       </c>
       <c r="AE504" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF504" t="inlineStr">
@@ -58199,7 +58199,7 @@
       </c>
       <c r="AE505" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF505" t="inlineStr">
@@ -58315,7 +58315,7 @@
       </c>
       <c r="AE506" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF506" t="inlineStr">
@@ -58443,7 +58443,7 @@
       </c>
       <c r="AE507" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="AF507" t="inlineStr">
@@ -58555,7 +58555,7 @@
       </c>
       <c r="AE508" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF508" t="inlineStr">
@@ -58665,7 +58665,7 @@
       </c>
       <c r="AE509" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF509" t="inlineStr">
@@ -58785,7 +58785,7 @@
       </c>
       <c r="AE510" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="AF510" t="inlineStr">
@@ -58895,7 +58895,7 @@
       </c>
       <c r="AE511" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF511" t="inlineStr">
@@ -59005,7 +59005,7 @@
       </c>
       <c r="AE512" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF512" t="inlineStr">
@@ -59115,7 +59115,7 @@
       </c>
       <c r="AE513" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF513" t="inlineStr">
@@ -59235,7 +59235,7 @@
       </c>
       <c r="AE514" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="AF514" t="inlineStr">
@@ -59351,7 +59351,7 @@
       </c>
       <c r="AE515" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF515" t="inlineStr">
@@ -59463,7 +59463,7 @@
       </c>
       <c r="AE516" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF516" t="inlineStr">
@@ -59583,7 +59583,7 @@
       </c>
       <c r="AE517" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="AF517" t="inlineStr">
@@ -59695,7 +59695,7 @@
       </c>
       <c r="AE518" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF518" t="inlineStr">
@@ -59795,7 +59795,7 @@
       </c>
       <c r="AE519" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF519" t="inlineStr">
@@ -59915,7 +59915,7 @@
       </c>
       <c r="AE520" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="AF520" t="inlineStr">
@@ -60025,7 +60025,7 @@
       </c>
       <c r="AE521" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF521" t="inlineStr">
@@ -60137,7 +60137,7 @@
       </c>
       <c r="AE522" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF522" t="inlineStr">
@@ -60253,7 +60253,7 @@
       </c>
       <c r="AE523" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF523" t="inlineStr">
@@ -60365,7 +60365,7 @@
       </c>
       <c r="AE524" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF524" t="inlineStr">
@@ -60477,7 +60477,7 @@
       </c>
       <c r="AE525" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF525" t="inlineStr">
@@ -60605,7 +60605,7 @@
       </c>
       <c r="AE526" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="AF526" t="inlineStr">
@@ -60715,7 +60715,7 @@
       </c>
       <c r="AE527" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF527" t="inlineStr">
@@ -60825,7 +60825,7 @@
       </c>
       <c r="AE528" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF528" t="inlineStr">
@@ -60935,7 +60935,7 @@
       </c>
       <c r="AE529" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF529" t="inlineStr">
@@ -61047,7 +61047,7 @@
       </c>
       <c r="AE530" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF530" t="inlineStr">
@@ -61175,7 +61175,7 @@
       </c>
       <c r="AE531" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="AF531" t="inlineStr">
@@ -61287,7 +61287,7 @@
       </c>
       <c r="AE532" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF532" t="inlineStr">
@@ -61399,7 +61399,7 @@
       </c>
       <c r="AE533" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF533" t="inlineStr">
@@ -61511,7 +61511,7 @@
       </c>
       <c r="AE534" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF534" t="inlineStr">
@@ -61611,7 +61611,7 @@
       </c>
       <c r="AE535" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF535" t="inlineStr">
@@ -61721,7 +61721,7 @@
       </c>
       <c r="AE536" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF536" t="inlineStr">
@@ -61831,7 +61831,7 @@
       </c>
       <c r="AE537" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF537" t="inlineStr">
@@ -61931,7 +61931,7 @@
       </c>
       <c r="AE538" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF538" t="inlineStr">
@@ -62041,7 +62041,7 @@
       </c>
       <c r="AE539" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF539" t="inlineStr">
@@ -62169,7 +62169,7 @@
       </c>
       <c r="AE540" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="AF540" t="inlineStr">
@@ -62279,7 +62279,7 @@
       </c>
       <c r="AE541" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF541" t="inlineStr">
@@ -62391,7 +62391,7 @@
       </c>
       <c r="AE542" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF542" t="inlineStr">
@@ -62501,7 +62501,7 @@
       </c>
       <c r="AE543" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF543" t="inlineStr">
@@ -62613,7 +62613,7 @@
       </c>
       <c r="AE544" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF544" t="inlineStr">
@@ -62723,7 +62723,7 @@
       </c>
       <c r="AE545" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF545" t="inlineStr">
@@ -62833,7 +62833,7 @@
       </c>
       <c r="AE546" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF546" t="inlineStr">
@@ -62933,7 +62933,7 @@
       </c>
       <c r="AE547" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF547" t="inlineStr">
@@ -63043,7 +63043,7 @@
       </c>
       <c r="AE548" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF548" t="inlineStr">
@@ -63155,7 +63155,7 @@
       </c>
       <c r="AE549" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF549" t="inlineStr">
@@ -63265,7 +63265,7 @@
       </c>
       <c r="AE550" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF550" t="inlineStr">
@@ -63375,7 +63375,7 @@
       </c>
       <c r="AE551" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF551" t="inlineStr">
@@ -63485,7 +63485,7 @@
       </c>
       <c r="AE552" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF552" t="inlineStr">
@@ -63595,7 +63595,7 @@
       </c>
       <c r="AE553" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF553" t="inlineStr">
@@ -63705,7 +63705,7 @@
       </c>
       <c r="AE554" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF554" t="inlineStr">
@@ -63815,7 +63815,7 @@
       </c>
       <c r="AE555" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF555" t="inlineStr">
@@ -63915,7 +63915,7 @@
       </c>
       <c r="AE556" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF556" t="inlineStr">
@@ -64025,7 +64025,7 @@
       </c>
       <c r="AE557" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF557" t="inlineStr">
@@ -64135,7 +64135,7 @@
       </c>
       <c r="AE558" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF558" t="inlineStr">
@@ -64247,7 +64247,7 @@
       </c>
       <c r="AE559" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF559" t="inlineStr">
@@ -64357,7 +64357,7 @@
       </c>
       <c r="AE560" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF560" t="inlineStr">
@@ -64469,7 +64469,7 @@
       </c>
       <c r="AE561" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF561" t="inlineStr">
@@ -64579,7 +64579,7 @@
       </c>
       <c r="AE562" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF562" t="inlineStr">
@@ -64689,7 +64689,7 @@
       </c>
       <c r="AE563" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF563" t="inlineStr">
@@ -64799,7 +64799,7 @@
       </c>
       <c r="AE564" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF564" t="inlineStr">
@@ -64909,7 +64909,7 @@
       </c>
       <c r="AE565" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF565" t="inlineStr">
@@ -65019,7 +65019,7 @@
       </c>
       <c r="AE566" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF566" t="inlineStr">
@@ -65131,7 +65131,7 @@
       </c>
       <c r="AE567" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF567" t="inlineStr">
@@ -65241,7 +65241,7 @@
       </c>
       <c r="AE568" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF568" t="inlineStr">
@@ -65353,7 +65353,7 @@
       </c>
       <c r="AE569" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF569" t="inlineStr">
@@ -65465,7 +65465,7 @@
       </c>
       <c r="AE570" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF570" t="inlineStr">
@@ -65575,7 +65575,7 @@
       </c>
       <c r="AE571" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF571" t="inlineStr">
@@ -65687,7 +65687,7 @@
       </c>
       <c r="AE572" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF572" t="inlineStr">
@@ -65799,7 +65799,7 @@
       </c>
       <c r="AE573" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF573" t="inlineStr">
@@ -65909,7 +65909,7 @@
       </c>
       <c r="AE574" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF574" t="inlineStr">
@@ -66019,7 +66019,7 @@
       </c>
       <c r="AE575" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF575" t="inlineStr">
@@ -66129,7 +66129,7 @@
       </c>
       <c r="AE576" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF576" t="inlineStr">
@@ -66239,7 +66239,7 @@
       </c>
       <c r="AE577" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF577" t="inlineStr">
@@ -66339,7 +66339,7 @@
       </c>
       <c r="AE578" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF578" t="inlineStr">
@@ -66451,7 +66451,7 @@
       </c>
       <c r="AE579" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF579" t="inlineStr">
@@ -66561,7 +66561,7 @@
       </c>
       <c r="AE580" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF580" t="inlineStr">
@@ -66671,7 +66671,7 @@
       </c>
       <c r="AE581" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF581" t="inlineStr">
@@ -66799,7 +66799,7 @@
       </c>
       <c r="AE582" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="AF582" t="inlineStr">
@@ -66911,7 +66911,7 @@
       </c>
       <c r="AE583" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF583" t="inlineStr">
@@ -67023,7 +67023,7 @@
       </c>
       <c r="AE584" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF584" t="inlineStr">
@@ -67151,7 +67151,7 @@
       </c>
       <c r="AE585" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="AF585" t="inlineStr">
@@ -67263,7 +67263,7 @@
       </c>
       <c r="AE586" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF586" t="inlineStr">
@@ -67391,7 +67391,7 @@
       </c>
       <c r="AE587" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="AF587" t="inlineStr">
@@ -67519,7 +67519,7 @@
       </c>
       <c r="AE588" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="AF588" t="inlineStr">
@@ -67631,7 +67631,7 @@
       </c>
       <c r="AE589" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF589" t="inlineStr">
@@ -67743,7 +67743,7 @@
       </c>
       <c r="AE590" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF590" t="inlineStr">
@@ -67853,7 +67853,7 @@
       </c>
       <c r="AE591" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF591" t="inlineStr">
@@ -67965,7 +67965,7 @@
       </c>
       <c r="AE592" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF592" t="inlineStr">
@@ -68075,7 +68075,7 @@
       </c>
       <c r="AE593" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF593" t="inlineStr">
@@ -68185,7 +68185,7 @@
       </c>
       <c r="AE594" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF594" t="inlineStr">
@@ -68297,7 +68297,7 @@
       </c>
       <c r="AE595" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF595" t="inlineStr">
@@ -68409,7 +68409,7 @@
       </c>
       <c r="AE596" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF596" t="inlineStr">
@@ -68521,7 +68521,7 @@
       </c>
       <c r="AE597" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF597" t="inlineStr">
@@ -68631,7 +68631,7 @@
       </c>
       <c r="AE598" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF598" t="inlineStr">
@@ -68741,7 +68741,7 @@
       </c>
       <c r="AE599" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF599" t="inlineStr">
@@ -68853,7 +68853,7 @@
       </c>
       <c r="AE600" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF600" t="inlineStr">
@@ -68965,7 +68965,7 @@
       </c>
       <c r="AE601" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF601" t="inlineStr">
@@ -69075,7 +69075,7 @@
       </c>
       <c r="AE602" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF602" t="inlineStr">
@@ -69187,7 +69187,7 @@
       </c>
       <c r="AE603" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF603" t="inlineStr">
@@ -69297,7 +69297,7 @@
       </c>
       <c r="AE604" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF604" t="inlineStr">
@@ -69397,7 +69397,7 @@
       </c>
       <c r="AE605" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF605" t="inlineStr">
@@ -69507,7 +69507,7 @@
       </c>
       <c r="AE606" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF606" t="inlineStr">
@@ -69619,7 +69619,7 @@
       </c>
       <c r="AE607" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF607" t="inlineStr">
@@ -69729,7 +69729,7 @@
       </c>
       <c r="AE608" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF608" t="inlineStr">
@@ -69841,7 +69841,7 @@
       </c>
       <c r="AE609" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF609" t="inlineStr">
@@ -69951,7 +69951,7 @@
       </c>
       <c r="AE610" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF610" t="inlineStr">
@@ -70061,7 +70061,7 @@
       </c>
       <c r="AE611" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF611" t="inlineStr">
@@ -70171,7 +70171,7 @@
       </c>
       <c r="AE612" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF612" t="inlineStr">
@@ -70281,7 +70281,7 @@
       </c>
       <c r="AE613" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF613" t="inlineStr">
@@ -70391,7 +70391,7 @@
       </c>
       <c r="AE614" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF614" t="inlineStr">
@@ -70503,7 +70503,7 @@
       </c>
       <c r="AE615" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF615" t="inlineStr">
@@ -70613,7 +70613,7 @@
       </c>
       <c r="AE616" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF616" t="inlineStr">
@@ -70723,7 +70723,7 @@
       </c>
       <c r="AE617" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF617" t="inlineStr">
@@ -70833,7 +70833,7 @@
       </c>
       <c r="AE618" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF618" t="inlineStr">
@@ -70945,7 +70945,7 @@
       </c>
       <c r="AE619" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF619" t="inlineStr">
@@ -71055,7 +71055,7 @@
       </c>
       <c r="AE620" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF620" t="inlineStr">
@@ -71167,7 +71167,7 @@
       </c>
       <c r="AE621" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF621" t="inlineStr">
@@ -71279,7 +71279,7 @@
       </c>
       <c r="AE622" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF622" t="inlineStr">
@@ -71379,7 +71379,7 @@
       </c>
       <c r="AE623" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF623" t="inlineStr">
@@ -71489,7 +71489,7 @@
       </c>
       <c r="AE624" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF624" t="inlineStr">
@@ -71601,7 +71601,7 @@
       </c>
       <c r="AE625" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF625" t="inlineStr">
@@ -71713,7 +71713,7 @@
       </c>
       <c r="AE626" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF626" t="inlineStr">
@@ -71825,7 +71825,7 @@
       </c>
       <c r="AE627" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF627" t="inlineStr">
@@ -71937,7 +71937,7 @@
       </c>
       <c r="AE628" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF628" t="inlineStr">
@@ -72047,7 +72047,7 @@
       </c>
       <c r="AE629" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF629" t="inlineStr">
@@ -72157,7 +72157,7 @@
       </c>
       <c r="AE630" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF630" t="inlineStr">
@@ -72269,7 +72269,7 @@
       </c>
       <c r="AE631" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF631" t="inlineStr">
@@ -72379,7 +72379,7 @@
       </c>
       <c r="AE632" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF632" t="inlineStr">
@@ -72491,7 +72491,7 @@
       </c>
       <c r="AE633" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF633" t="inlineStr">
@@ -72591,7 +72591,7 @@
       </c>
       <c r="AE634" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF634" t="inlineStr">
@@ -72701,7 +72701,7 @@
       </c>
       <c r="AE635" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF635" t="inlineStr">
@@ -72813,7 +72813,7 @@
       </c>
       <c r="AE636" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF636" t="inlineStr">
@@ -72923,7 +72923,7 @@
       <c r="AD637" t="inlineStr"/>
       <c r="AE637" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:44</t>
+          <t>2026-09-18 08:50:17</t>
         </is>
       </c>
       <c r="AF637" t="inlineStr">
@@ -73035,7 +73035,7 @@
       </c>
       <c r="AE638" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF638" t="inlineStr">
@@ -73147,7 +73147,7 @@
       </c>
       <c r="AE639" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF639" t="inlineStr">
@@ -73257,7 +73257,7 @@
       </c>
       <c r="AE640" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF640" t="inlineStr">
@@ -73369,7 +73369,7 @@
       </c>
       <c r="AE641" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF641" t="inlineStr">
@@ -73469,7 +73469,7 @@
       </c>
       <c r="AE642" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF642" t="inlineStr">
@@ -73569,7 +73569,7 @@
       </c>
       <c r="AE643" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF643" t="inlineStr">
@@ -73669,7 +73669,7 @@
       </c>
       <c r="AE644" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF644" t="inlineStr">
@@ -73781,7 +73781,7 @@
       </c>
       <c r="AE645" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF645" t="inlineStr">
@@ -73881,7 +73881,7 @@
       </c>
       <c r="AE646" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF646" t="inlineStr">
@@ -73991,7 +73991,7 @@
       </c>
       <c r="AE647" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF647" t="inlineStr">
@@ -74091,7 +74091,7 @@
       </c>
       <c r="AE648" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF648" t="inlineStr">
@@ -74203,7 +74203,7 @@
       </c>
       <c r="AE649" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF649" t="inlineStr">
@@ -74315,7 +74315,7 @@
       </c>
       <c r="AE650" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF650" t="inlineStr">
@@ -74427,7 +74427,7 @@
       </c>
       <c r="AE651" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF651" t="inlineStr">
@@ -74539,7 +74539,7 @@
       </c>
       <c r="AE652" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF652" t="inlineStr">
@@ -74639,7 +74639,7 @@
       </c>
       <c r="AE653" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF653" t="inlineStr">
@@ -74751,7 +74751,7 @@
       </c>
       <c r="AE654" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF654" t="inlineStr">
@@ -74861,7 +74861,7 @@
       </c>
       <c r="AE655" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF655" t="inlineStr">
@@ -74973,7 +74973,7 @@
       </c>
       <c r="AE656" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF656" t="inlineStr">
@@ -75073,7 +75073,7 @@
       </c>
       <c r="AE657" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF657" t="inlineStr">
@@ -75173,7 +75173,7 @@
       </c>
       <c r="AE658" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF658" t="inlineStr">
@@ -75273,7 +75273,7 @@
       </c>
       <c r="AE659" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF659" t="inlineStr">
@@ -75373,7 +75373,7 @@
       </c>
       <c r="AE660" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF660" t="inlineStr">
@@ -75485,7 +75485,7 @@
       </c>
       <c r="AE661" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF661" t="inlineStr">
@@ -75597,7 +75597,7 @@
       </c>
       <c r="AE662" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF662" t="inlineStr">
@@ -75697,7 +75697,7 @@
       </c>
       <c r="AE663" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF663" t="inlineStr">
@@ -75807,7 +75807,7 @@
       </c>
       <c r="AE664" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF664" t="inlineStr">
@@ -75919,7 +75919,7 @@
       </c>
       <c r="AE665" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF665" t="inlineStr">
@@ -76031,7 +76031,7 @@
       </c>
       <c r="AE666" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF666" t="inlineStr">
@@ -76143,7 +76143,7 @@
       </c>
       <c r="AE667" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF667" t="inlineStr">
@@ -76255,7 +76255,7 @@
       </c>
       <c r="AE668" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF668" t="inlineStr">
@@ -76367,7 +76367,7 @@
       </c>
       <c r="AE669" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF669" t="inlineStr">
@@ -76479,7 +76479,7 @@
       </c>
       <c r="AE670" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF670" t="inlineStr">
@@ -76591,7 +76591,7 @@
       </c>
       <c r="AE671" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF671" t="inlineStr">
@@ -76691,7 +76691,7 @@
       </c>
       <c r="AE672" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF672" t="inlineStr">
@@ -76791,7 +76791,7 @@
       </c>
       <c r="AE673" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF673" t="inlineStr">
@@ -76903,7 +76903,7 @@
       </c>
       <c r="AE674" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:12</t>
+          <t>2026-09-18 08:49:46</t>
         </is>
       </c>
       <c r="AF674" t="inlineStr">
@@ -77003,7 +77003,7 @@
       </c>
       <c r="AE675" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF675" t="inlineStr">
@@ -77103,7 +77103,7 @@
       </c>
       <c r="AE676" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF676" t="inlineStr">
@@ -77203,7 +77203,7 @@
       </c>
       <c r="AE677" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF677" t="inlineStr">
@@ -77313,7 +77313,7 @@
       </c>
       <c r="AE678" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF678" t="inlineStr">
@@ -77413,7 +77413,7 @@
       </c>
       <c r="AE679" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF679" t="inlineStr">
@@ -77523,7 +77523,7 @@
       </c>
       <c r="AE680" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF680" t="inlineStr">
@@ -77605,7 +77605,7 @@
       <c r="AD681" t="inlineStr"/>
       <c r="AE681" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF681" t="inlineStr">
@@ -77687,7 +77687,7 @@
       <c r="AD682" t="inlineStr"/>
       <c r="AE682" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF682" t="inlineStr">
@@ -77769,7 +77769,7 @@
       <c r="AD683" t="inlineStr"/>
       <c r="AE683" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF683" t="inlineStr">
@@ -77851,7 +77851,7 @@
       <c r="AD684" t="inlineStr"/>
       <c r="AE684" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="AF684" t="inlineStr">

--- a/pipeline/credit_rating/output/xhtn_tong_hop_20260918.xlsx
+++ b/pipeline/credit_rating/output/xhtn_tong_hop_20260918.xlsx
@@ -685,7 +685,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1011,7 +1011,7 @@
       <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -1099,7 +1099,7 @@
       <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -1219,7 +1219,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -1555,7 +1555,7 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>2026-09-18 08:50:17</t>
+          <t>2026-09-18 09:05:55</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -1665,7 +1665,7 @@
       <c r="AD11" t="inlineStr"/>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>2026-09-18 08:50:17</t>
+          <t>2026-09-18 09:05:55</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>2026-09-18 08:50:17</t>
+          <t>2026-09-18 09:05:55</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -1891,7 +1891,7 @@
       <c r="AD13" t="inlineStr"/>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>2026-09-18 08:50:17</t>
+          <t>2026-09-18 09:05:55</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -2019,7 +2019,7 @@
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -2133,7 +2133,7 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -2247,7 +2247,7 @@
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -2367,7 +2367,7 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -2595,7 +2595,7 @@
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -2709,7 +2709,7 @@
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -2825,7 +2825,7 @@
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>2026-09-18 08:50:17</t>
+          <t>2026-09-18 09:05:55</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -2939,7 +2939,7 @@
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -3049,7 +3049,7 @@
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -3177,7 +3177,7 @@
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
@@ -3291,7 +3291,7 @@
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
@@ -3411,7 +3411,7 @@
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
@@ -3525,7 +3525,7 @@
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
@@ -3635,7 +3635,7 @@
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>2026-09-18 08:50:17</t>
+          <t>2026-09-18 09:05:55</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
@@ -3861,7 +3861,7 @@
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
@@ -3971,7 +3971,7 @@
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF31" t="inlineStr">
@@ -4095,7 +4095,7 @@
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
@@ -4205,7 +4205,7 @@
       </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF33" t="inlineStr">
@@ -4315,7 +4315,7 @@
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF34" t="inlineStr">
@@ -4425,7 +4425,7 @@
       </c>
       <c r="AE35" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF35" t="inlineStr">
@@ -4525,7 +4525,7 @@
       </c>
       <c r="AE36" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF36" t="inlineStr">
@@ -4635,7 +4635,7 @@
       </c>
       <c r="AE37" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF37" t="inlineStr">
@@ -4745,7 +4745,7 @@
       </c>
       <c r="AE38" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF38" t="inlineStr">
@@ -4855,7 +4855,7 @@
       </c>
       <c r="AE39" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF39" t="inlineStr">
@@ -4987,7 +4987,7 @@
       </c>
       <c r="AE40" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="AF40" t="inlineStr">
@@ -5115,7 +5115,7 @@
       </c>
       <c r="AE41" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="AF41" t="inlineStr">
@@ -5247,7 +5247,7 @@
       </c>
       <c r="AE42" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="AF42" t="inlineStr">
@@ -5375,7 +5375,7 @@
       </c>
       <c r="AE43" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="AF43" t="inlineStr">
@@ -5485,7 +5485,7 @@
       </c>
       <c r="AE44" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF44" t="inlineStr">
@@ -5597,7 +5597,7 @@
       </c>
       <c r="AE45" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF45" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="AE46" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF46" t="inlineStr">
@@ -5827,7 +5827,7 @@
       </c>
       <c r="AE47" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF47" t="inlineStr">
@@ -5943,7 +5943,7 @@
       </c>
       <c r="AE48" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF48" t="inlineStr">
@@ -6043,7 +6043,7 @@
       </c>
       <c r="AE49" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF49" t="inlineStr">
@@ -6157,7 +6157,7 @@
       </c>
       <c r="AE50" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF50" t="inlineStr">
@@ -6273,7 +6273,7 @@
       </c>
       <c r="AE51" t="inlineStr">
         <is>
-          <t>2026-09-18 08:50:17</t>
+          <t>2026-09-18 09:05:55</t>
         </is>
       </c>
       <c r="AF51" t="inlineStr">
@@ -6383,7 +6383,7 @@
       </c>
       <c r="AE52" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF52" t="inlineStr">
@@ -6497,7 +6497,7 @@
       </c>
       <c r="AE53" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF53" t="inlineStr">
@@ -6611,7 +6611,7 @@
       </c>
       <c r="AE54" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF54" t="inlineStr">
@@ -6739,7 +6739,7 @@
       </c>
       <c r="AE55" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="AF55" t="inlineStr">
@@ -6855,7 +6855,7 @@
       </c>
       <c r="AE56" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF56" t="inlineStr">
@@ -6951,7 +6951,7 @@
       </c>
       <c r="AE57" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF57" t="inlineStr">
@@ -7061,7 +7061,7 @@
       </c>
       <c r="AE58" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF58" t="inlineStr">
@@ -7161,7 +7161,7 @@
       </c>
       <c r="AE59" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF59" t="inlineStr">
@@ -7275,7 +7275,7 @@
       </c>
       <c r="AE60" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF60" t="inlineStr">
@@ -7389,7 +7389,7 @@
       </c>
       <c r="AE61" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF61" t="inlineStr">
@@ -7489,7 +7489,7 @@
       </c>
       <c r="AE62" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF62" t="inlineStr">
@@ -7603,7 +7603,7 @@
       </c>
       <c r="AE63" t="inlineStr">
         <is>
-          <t>2026-09-18 08:50:00</t>
+          <t>2026-09-18 09:05:40</t>
         </is>
       </c>
       <c r="AF63" t="inlineStr">
@@ -7713,7 +7713,7 @@
       </c>
       <c r="AE64" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF64" t="inlineStr">
@@ -7827,7 +7827,7 @@
       </c>
       <c r="AE65" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF65" t="inlineStr">
@@ -7941,7 +7941,7 @@
       </c>
       <c r="AE66" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF66" t="inlineStr">
@@ -8051,7 +8051,7 @@
       </c>
       <c r="AE67" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF67" t="inlineStr">
@@ -8165,7 +8165,7 @@
       </c>
       <c r="AE68" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF68" t="inlineStr">
@@ -8279,7 +8279,7 @@
       </c>
       <c r="AE69" t="inlineStr">
         <is>
-          <t>2026-09-18 08:50:00</t>
+          <t>2026-09-18 09:05:40</t>
         </is>
       </c>
       <c r="AF69" t="inlineStr">
@@ -8393,7 +8393,7 @@
       </c>
       <c r="AE70" t="inlineStr">
         <is>
-          <t>2026-09-18 08:50:00</t>
+          <t>2026-09-18 09:05:40</t>
         </is>
       </c>
       <c r="AF70" t="inlineStr">
@@ -8517,7 +8517,7 @@
       </c>
       <c r="AE71" t="inlineStr">
         <is>
-          <t>2026-09-18 08:50:02</t>
+          <t>2026-09-18 09:05:42</t>
         </is>
       </c>
       <c r="AF71" t="inlineStr">
@@ -8627,7 +8627,7 @@
       </c>
       <c r="AE72" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF72" t="inlineStr">
@@ -8741,7 +8741,7 @@
       </c>
       <c r="AE73" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF73" t="inlineStr">
@@ -8855,7 +8855,7 @@
       </c>
       <c r="AE74" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF74" t="inlineStr">
@@ -8969,7 +8969,7 @@
       </c>
       <c r="AE75" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF75" t="inlineStr">
@@ -9081,7 +9081,7 @@
       </c>
       <c r="AE76" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF76" t="inlineStr">
@@ -9197,7 +9197,7 @@
       </c>
       <c r="AE77" t="inlineStr">
         <is>
-          <t>2026-09-18 08:50:17</t>
+          <t>2026-09-18 09:05:55</t>
         </is>
       </c>
       <c r="AF77" t="inlineStr">
@@ -9307,7 +9307,7 @@
       </c>
       <c r="AE78" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF78" t="inlineStr">
@@ -9417,7 +9417,7 @@
       </c>
       <c r="AE79" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF79" t="inlineStr">
@@ -9535,7 +9535,7 @@
       </c>
       <c r="AE80" t="inlineStr">
         <is>
-          <t>2026-09-18 08:50:00</t>
+          <t>2026-09-18 09:05:40</t>
         </is>
       </c>
       <c r="AF80" t="inlineStr">
@@ -9659,7 +9659,7 @@
       </c>
       <c r="AE81" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="AF81" t="inlineStr">
@@ -9779,7 +9779,7 @@
       </c>
       <c r="AE82" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="AF82" t="inlineStr">
@@ -9899,7 +9899,7 @@
       </c>
       <c r="AE83" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="AF83" t="inlineStr">
@@ -10031,7 +10031,7 @@
       </c>
       <c r="AE84" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="AF84" t="inlineStr">
@@ -10155,7 +10155,7 @@
       </c>
       <c r="AE85" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF85" t="inlineStr">
@@ -10279,7 +10279,7 @@
       </c>
       <c r="AE86" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF86" t="inlineStr">
@@ -10379,7 +10379,7 @@
       </c>
       <c r="AE87" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF87" t="inlineStr">
@@ -10499,7 +10499,7 @@
       </c>
       <c r="AE88" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="AF88" t="inlineStr">
@@ -10627,7 +10627,7 @@
       </c>
       <c r="AE89" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="AF89" t="inlineStr">
@@ -10741,7 +10741,7 @@
       </c>
       <c r="AE90" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF90" t="inlineStr">
@@ -10855,7 +10855,7 @@
       </c>
       <c r="AE91" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF91" t="inlineStr">
@@ -10969,7 +10969,7 @@
       </c>
       <c r="AE92" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF92" t="inlineStr">
@@ -11079,7 +11079,7 @@
       </c>
       <c r="AE93" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF93" t="inlineStr">
@@ -11193,7 +11193,7 @@
       </c>
       <c r="AE94" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF94" t="inlineStr">
@@ -11307,7 +11307,7 @@
       </c>
       <c r="AE95" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF95" t="inlineStr">
@@ -11421,7 +11421,7 @@
       </c>
       <c r="AE96" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF96" t="inlineStr">
@@ -11535,7 +11535,7 @@
       </c>
       <c r="AE97" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF97" t="inlineStr">
@@ -11655,7 +11655,7 @@
       </c>
       <c r="AE98" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="AF98" t="inlineStr">
@@ -11771,7 +11771,7 @@
       </c>
       <c r="AE99" t="inlineStr">
         <is>
-          <t>2026-09-18 08:50:17</t>
+          <t>2026-09-18 09:05:55</t>
         </is>
       </c>
       <c r="AF99" t="inlineStr">
@@ -11881,7 +11881,7 @@
       </c>
       <c r="AE100" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF100" t="inlineStr">
@@ -12001,7 +12001,7 @@
       </c>
       <c r="AE101" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="AF101" t="inlineStr">
@@ -12133,7 +12133,7 @@
       </c>
       <c r="AE102" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="AF102" t="inlineStr">
@@ -12261,7 +12261,7 @@
       </c>
       <c r="AE103" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="AF103" t="inlineStr">
@@ -12373,7 +12373,7 @@
       </c>
       <c r="AE104" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF104" t="inlineStr">
@@ -12483,7 +12483,7 @@
       </c>
       <c r="AE105" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF105" t="inlineStr">
@@ -12593,7 +12593,7 @@
       </c>
       <c r="AE106" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF106" t="inlineStr">
@@ -12703,7 +12703,7 @@
       </c>
       <c r="AE107" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF107" t="inlineStr">
@@ -12817,7 +12817,7 @@
       </c>
       <c r="AE108" t="inlineStr">
         <is>
-          <t>2026-09-18 08:50:00</t>
+          <t>2026-09-18 09:05:40</t>
         </is>
       </c>
       <c r="AF108" t="inlineStr">
@@ -12929,7 +12929,7 @@
       </c>
       <c r="AE109" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF109" t="inlineStr">
@@ -13045,7 +13045,7 @@
       </c>
       <c r="AE110" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF110" t="inlineStr">
@@ -13167,7 +13167,7 @@
       <c r="AD111" t="inlineStr"/>
       <c r="AE111" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="AF111" t="inlineStr">
@@ -13279,7 +13279,7 @@
       </c>
       <c r="AE112" t="inlineStr">
         <is>
-          <t>2026-09-18 08:50:02</t>
+          <t>2026-09-18 09:05:42</t>
         </is>
       </c>
       <c r="AF112" t="inlineStr">
@@ -13407,7 +13407,7 @@
       </c>
       <c r="AE113" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="AF113" t="inlineStr">
@@ -13527,7 +13527,7 @@
       </c>
       <c r="AE114" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF114" t="inlineStr">
@@ -13647,7 +13647,7 @@
       </c>
       <c r="AE115" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF115" t="inlineStr">
@@ -13757,7 +13757,7 @@
       </c>
       <c r="AE116" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF116" t="inlineStr">
@@ -13873,7 +13873,7 @@
       </c>
       <c r="AE117" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF117" t="inlineStr">
@@ -13985,7 +13985,7 @@
       </c>
       <c r="AE118" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF118" t="inlineStr">
@@ -14095,7 +14095,7 @@
       </c>
       <c r="AE119" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF119" t="inlineStr">
@@ -14205,7 +14205,7 @@
       </c>
       <c r="AE120" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF120" t="inlineStr">
@@ -14329,7 +14329,7 @@
       </c>
       <c r="AE121" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF121" t="inlineStr">
@@ -14445,7 +14445,7 @@
       </c>
       <c r="AE122" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF122" t="inlineStr">
@@ -14565,7 +14565,7 @@
       </c>
       <c r="AE123" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="AF123" t="inlineStr">
@@ -14677,7 +14677,7 @@
       </c>
       <c r="AE124" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF124" t="inlineStr">
@@ -14797,7 +14797,7 @@
       </c>
       <c r="AE125" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF125" t="inlineStr">
@@ -14907,7 +14907,7 @@
       </c>
       <c r="AE126" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF126" t="inlineStr">
@@ -15017,7 +15017,7 @@
       </c>
       <c r="AE127" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF127" t="inlineStr">
@@ -15137,7 +15137,7 @@
       </c>
       <c r="AE128" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="AF128" t="inlineStr">
@@ -15251,7 +15251,7 @@
       </c>
       <c r="AE129" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF129" t="inlineStr">
@@ -15365,7 +15365,7 @@
       </c>
       <c r="AE130" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF130" t="inlineStr">
@@ -15485,7 +15485,7 @@
       </c>
       <c r="AE131" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="AF131" t="inlineStr">
@@ -15595,7 +15595,7 @@
       </c>
       <c r="AE132" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF132" t="inlineStr">
@@ -15711,7 +15711,7 @@
       </c>
       <c r="AE133" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF133" t="inlineStr">
@@ -15823,7 +15823,7 @@
       </c>
       <c r="AE134" t="inlineStr">
         <is>
-          <t>2026-09-18 08:50:02</t>
+          <t>2026-09-18 09:05:42</t>
         </is>
       </c>
       <c r="AF134" t="inlineStr">
@@ -15935,7 +15935,7 @@
       </c>
       <c r="AE135" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF135" t="inlineStr">
@@ -16049,7 +16049,7 @@
       </c>
       <c r="AE136" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF136" t="inlineStr">
@@ -16163,7 +16163,7 @@
       </c>
       <c r="AE137" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF137" t="inlineStr">
@@ -16277,7 +16277,7 @@
       </c>
       <c r="AE138" t="inlineStr">
         <is>
-          <t>2026-09-18 08:50:00</t>
+          <t>2026-09-18 09:05:40</t>
         </is>
       </c>
       <c r="AF138" t="inlineStr">
@@ -16387,7 +16387,7 @@
       </c>
       <c r="AE139" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF139" t="inlineStr">
@@ -16497,7 +16497,7 @@
       </c>
       <c r="AE140" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF140" t="inlineStr">
@@ -16607,7 +16607,7 @@
       </c>
       <c r="AE141" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF141" t="inlineStr">
@@ -16721,7 +16721,7 @@
       </c>
       <c r="AE142" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF142" t="inlineStr">
@@ -16835,7 +16835,7 @@
       </c>
       <c r="AE143" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF143" t="inlineStr">
@@ -16963,7 +16963,7 @@
       </c>
       <c r="AE144" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="AF144" t="inlineStr">
@@ -17091,7 +17091,7 @@
       </c>
       <c r="AE145" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="AF145" t="inlineStr">
@@ -17201,7 +17201,7 @@
       </c>
       <c r="AE146" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF146" t="inlineStr">
@@ -17311,7 +17311,7 @@
       </c>
       <c r="AE147" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF147" t="inlineStr">
@@ -17431,7 +17431,7 @@
       </c>
       <c r="AE148" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="AF148" t="inlineStr">
@@ -17545,7 +17545,7 @@
       </c>
       <c r="AE149" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF149" t="inlineStr">
@@ -17655,7 +17655,7 @@
       </c>
       <c r="AE150" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF150" t="inlineStr">
@@ -17783,7 +17783,7 @@
       </c>
       <c r="AE151" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="AF151" t="inlineStr">
@@ -17905,7 +17905,7 @@
       <c r="AD152" t="inlineStr"/>
       <c r="AE152" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="AF152" t="inlineStr">
@@ -18033,7 +18033,7 @@
       </c>
       <c r="AE153" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="AF153" t="inlineStr">
@@ -18149,7 +18149,7 @@
       </c>
       <c r="AE154" t="inlineStr">
         <is>
-          <t>2026-09-18 08:50:17</t>
+          <t>2026-09-18 09:05:55</t>
         </is>
       </c>
       <c r="AF154" t="inlineStr">
@@ -18277,7 +18277,7 @@
       </c>
       <c r="AE155" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="AF155" t="inlineStr">
@@ -18409,7 +18409,7 @@
       </c>
       <c r="AE156" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="AF156" t="inlineStr">
@@ -18523,7 +18523,7 @@
       </c>
       <c r="AE157" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF157" t="inlineStr">
@@ -18645,7 +18645,7 @@
       <c r="AD158" t="inlineStr"/>
       <c r="AE158" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="AF158" t="inlineStr">
@@ -18757,7 +18757,7 @@
       </c>
       <c r="AE159" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF159" t="inlineStr">
@@ -18857,7 +18857,7 @@
       </c>
       <c r="AE160" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF160" t="inlineStr">
@@ -18967,7 +18967,7 @@
       </c>
       <c r="AE161" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF161" t="inlineStr">
@@ -19083,7 +19083,7 @@
       </c>
       <c r="AE162" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF162" t="inlineStr">
@@ -19199,7 +19199,7 @@
       </c>
       <c r="AE163" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF163" t="inlineStr">
@@ -19327,7 +19327,7 @@
       </c>
       <c r="AE164" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="AF164" t="inlineStr">
@@ -19437,7 +19437,7 @@
       </c>
       <c r="AE165" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF165" t="inlineStr">
@@ -19551,7 +19551,7 @@
       </c>
       <c r="AE166" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF166" t="inlineStr">
@@ -19665,7 +19665,7 @@
       </c>
       <c r="AE167" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF167" t="inlineStr">
@@ -19779,7 +19779,7 @@
       </c>
       <c r="AE168" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF168" t="inlineStr">
@@ -19889,7 +19889,7 @@
       </c>
       <c r="AE169" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF169" t="inlineStr">
@@ -20003,7 +20003,7 @@
       </c>
       <c r="AE170" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF170" t="inlineStr">
@@ -20113,7 +20113,7 @@
       </c>
       <c r="AE171" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF171" t="inlineStr">
@@ -20225,7 +20225,7 @@
       </c>
       <c r="AE172" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF172" t="inlineStr">
@@ -20341,7 +20341,7 @@
       </c>
       <c r="AE173" t="inlineStr">
         <is>
-          <t>2026-09-18 08:50:17</t>
+          <t>2026-09-18 09:05:55</t>
         </is>
       </c>
       <c r="AF173" t="inlineStr">
@@ -20457,7 +20457,7 @@
       </c>
       <c r="AE174" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF174" t="inlineStr">
@@ -20569,7 +20569,7 @@
       </c>
       <c r="AE175" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF175" t="inlineStr">
@@ -20681,7 +20681,7 @@
       </c>
       <c r="AE176" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF176" t="inlineStr">
@@ -20809,7 +20809,7 @@
       </c>
       <c r="AE177" t="inlineStr">
         <is>
-          <t>2026-09-18 08:50:02</t>
+          <t>2026-09-18 09:05:42</t>
         </is>
       </c>
       <c r="AF177" t="inlineStr">
@@ -20919,7 +20919,7 @@
       </c>
       <c r="AE178" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF178" t="inlineStr">
@@ -21039,7 +21039,7 @@
       </c>
       <c r="AE179" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="AF179" t="inlineStr">
@@ -21161,7 +21161,7 @@
       <c r="AD180" t="inlineStr"/>
       <c r="AE180" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="AF180" t="inlineStr">
@@ -21287,7 +21287,7 @@
       <c r="AD181" t="inlineStr"/>
       <c r="AE181" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="AF181" t="inlineStr">
@@ -21413,7 +21413,7 @@
       <c r="AD182" t="inlineStr"/>
       <c r="AE182" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="AF182" t="inlineStr">
@@ -21529,7 +21529,7 @@
       </c>
       <c r="AE183" t="inlineStr">
         <is>
-          <t>2026-09-18 08:50:17</t>
+          <t>2026-09-18 09:05:55</t>
         </is>
       </c>
       <c r="AF183" t="inlineStr">
@@ -21643,7 +21643,7 @@
       </c>
       <c r="AE184" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF184" t="inlineStr">
@@ -21757,7 +21757,7 @@
       </c>
       <c r="AE185" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF185" t="inlineStr">
@@ -21871,7 +21871,7 @@
       </c>
       <c r="AE186" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF186" t="inlineStr">
@@ -21991,7 +21991,7 @@
       </c>
       <c r="AE187" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="AF187" t="inlineStr">
@@ -22111,7 +22111,7 @@
       </c>
       <c r="AE188" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="AF188" t="inlineStr">
@@ -22221,7 +22221,7 @@
       </c>
       <c r="AE189" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF189" t="inlineStr">
@@ -22331,7 +22331,7 @@
       </c>
       <c r="AE190" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF190" t="inlineStr">
@@ -22441,7 +22441,7 @@
       </c>
       <c r="AE191" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF191" t="inlineStr">
@@ -22557,7 +22557,7 @@
       </c>
       <c r="AE192" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF192" t="inlineStr">
@@ -22685,7 +22685,7 @@
       </c>
       <c r="AE193" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="AF193" t="inlineStr">
@@ -22797,7 +22797,7 @@
       </c>
       <c r="AE194" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF194" t="inlineStr">
@@ -22909,7 +22909,7 @@
       </c>
       <c r="AE195" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF195" t="inlineStr">
@@ -23027,7 +23027,7 @@
       </c>
       <c r="AE196" t="inlineStr">
         <is>
-          <t>2026-09-18 08:50:00</t>
+          <t>2026-09-18 09:05:40</t>
         </is>
       </c>
       <c r="AF196" t="inlineStr">
@@ -23137,7 +23137,7 @@
       </c>
       <c r="AE197" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF197" t="inlineStr">
@@ -23247,7 +23247,7 @@
       </c>
       <c r="AE198" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF198" t="inlineStr">
@@ -23359,7 +23359,7 @@
       </c>
       <c r="AE199" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF199" t="inlineStr">
@@ -23469,7 +23469,7 @@
       </c>
       <c r="AE200" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF200" t="inlineStr">
@@ -23589,7 +23589,7 @@
       </c>
       <c r="AE201" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="AF201" t="inlineStr">
@@ -23705,7 +23705,7 @@
       </c>
       <c r="AE202" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF202" t="inlineStr">
@@ -23821,7 +23821,7 @@
       </c>
       <c r="AE203" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF203" t="inlineStr">
@@ -23949,7 +23949,7 @@
       </c>
       <c r="AE204" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="AF204" t="inlineStr">
@@ -24061,7 +24061,7 @@
       </c>
       <c r="AE205" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF205" t="inlineStr">
@@ -24173,7 +24173,7 @@
       </c>
       <c r="AE206" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF206" t="inlineStr">
@@ -24285,7 +24285,7 @@
       </c>
       <c r="AE207" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF207" t="inlineStr">
@@ -24401,7 +24401,7 @@
       </c>
       <c r="AE208" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF208" t="inlineStr">
@@ -24511,7 +24511,7 @@
       </c>
       <c r="AE209" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF209" t="inlineStr">
@@ -24631,7 +24631,7 @@
       </c>
       <c r="AE210" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="AF210" t="inlineStr">
@@ -24741,7 +24741,7 @@
       </c>
       <c r="AE211" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF211" t="inlineStr">
@@ -24861,7 +24861,7 @@
       </c>
       <c r="AE212" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="AF212" t="inlineStr">
@@ -24971,7 +24971,7 @@
       </c>
       <c r="AE213" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF213" t="inlineStr">
@@ -25085,7 +25085,7 @@
       </c>
       <c r="AE214" t="inlineStr">
         <is>
-          <t>2026-09-18 08:50:00</t>
+          <t>2026-09-18 09:05:40</t>
         </is>
       </c>
       <c r="AF214" t="inlineStr">
@@ -25195,7 +25195,7 @@
       </c>
       <c r="AE215" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF215" t="inlineStr">
@@ -25305,7 +25305,7 @@
       </c>
       <c r="AE216" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF216" t="inlineStr">
@@ -25419,7 +25419,7 @@
       </c>
       <c r="AE217" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF217" t="inlineStr">
@@ -25529,7 +25529,7 @@
       </c>
       <c r="AE218" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF218" t="inlineStr">
@@ -25641,7 +25641,7 @@
       </c>
       <c r="AE219" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF219" t="inlineStr">
@@ -25751,7 +25751,7 @@
       </c>
       <c r="AE220" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF220" t="inlineStr">
@@ -25871,7 +25871,7 @@
       </c>
       <c r="AE221" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="AF221" t="inlineStr">
@@ -25983,7 +25983,7 @@
       </c>
       <c r="AE222" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF222" t="inlineStr">
@@ -26093,7 +26093,7 @@
       </c>
       <c r="AE223" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF223" t="inlineStr">
@@ -26217,7 +26217,7 @@
       </c>
       <c r="AE224" t="inlineStr">
         <is>
-          <t>2026-09-18 08:50:02</t>
+          <t>2026-09-18 09:05:42</t>
         </is>
       </c>
       <c r="AF224" t="inlineStr">
@@ -26341,7 +26341,7 @@
       </c>
       <c r="AE225" t="inlineStr">
         <is>
-          <t>2026-09-18 08:50:02</t>
+          <t>2026-09-18 09:05:42</t>
         </is>
       </c>
       <c r="AF225" t="inlineStr">
@@ -26451,7 +26451,7 @@
       </c>
       <c r="AE226" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF226" t="inlineStr">
@@ -26561,7 +26561,7 @@
       </c>
       <c r="AE227" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF227" t="inlineStr">
@@ -26671,7 +26671,7 @@
       </c>
       <c r="AE228" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF228" t="inlineStr">
@@ -26783,7 +26783,7 @@
       </c>
       <c r="AE229" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF229" t="inlineStr">
@@ -26893,7 +26893,7 @@
       </c>
       <c r="AE230" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF230" t="inlineStr">
@@ -27003,7 +27003,7 @@
       </c>
       <c r="AE231" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF231" t="inlineStr">
@@ -27131,7 +27131,7 @@
       </c>
       <c r="AE232" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="AF232" t="inlineStr">
@@ -27237,7 +27237,7 @@
       </c>
       <c r="AE233" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF233" t="inlineStr">
@@ -27349,7 +27349,7 @@
       </c>
       <c r="AE234" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF234" t="inlineStr">
@@ -27465,7 +27465,7 @@
       </c>
       <c r="AE235" t="inlineStr">
         <is>
-          <t>2026-09-18 08:50:17</t>
+          <t>2026-09-18 09:05:55</t>
         </is>
       </c>
       <c r="AF235" t="inlineStr">
@@ -27581,7 +27581,7 @@
       </c>
       <c r="AE236" t="inlineStr">
         <is>
-          <t>2026-09-18 08:50:17</t>
+          <t>2026-09-18 09:05:55</t>
         </is>
       </c>
       <c r="AF236" t="inlineStr">
@@ -27691,7 +27691,7 @@
       </c>
       <c r="AE237" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF237" t="inlineStr">
@@ -27801,7 +27801,7 @@
       </c>
       <c r="AE238" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF238" t="inlineStr">
@@ -27917,7 +27917,7 @@
       </c>
       <c r="AE239" t="inlineStr">
         <is>
-          <t>2026-09-18 08:50:17</t>
+          <t>2026-09-18 09:05:55</t>
         </is>
       </c>
       <c r="AF239" t="inlineStr">
@@ -28033,7 +28033,7 @@
       </c>
       <c r="AE240" t="inlineStr">
         <is>
-          <t>2026-09-18 08:50:17</t>
+          <t>2026-09-18 09:05:55</t>
         </is>
       </c>
       <c r="AF240" t="inlineStr">
@@ -28143,7 +28143,7 @@
       </c>
       <c r="AE241" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF241" t="inlineStr">
@@ -28259,7 +28259,7 @@
       </c>
       <c r="AE242" t="inlineStr">
         <is>
-          <t>2026-09-18 08:50:17</t>
+          <t>2026-09-18 09:05:55</t>
         </is>
       </c>
       <c r="AF242" t="inlineStr">
@@ -28375,7 +28375,7 @@
       </c>
       <c r="AE243" t="inlineStr">
         <is>
-          <t>2026-09-18 08:50:17</t>
+          <t>2026-09-18 09:05:55</t>
         </is>
       </c>
       <c r="AF243" t="inlineStr">
@@ -28485,7 +28485,7 @@
       </c>
       <c r="AE244" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF244" t="inlineStr">
@@ -28595,7 +28595,7 @@
       </c>
       <c r="AE245" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF245" t="inlineStr">
@@ -28705,7 +28705,7 @@
       </c>
       <c r="AE246" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF246" t="inlineStr">
@@ -28805,7 +28805,7 @@
       </c>
       <c r="AE247" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF247" t="inlineStr">
@@ -28921,7 +28921,7 @@
       </c>
       <c r="AE248" t="inlineStr">
         <is>
-          <t>2026-09-18 08:50:17</t>
+          <t>2026-09-18 09:05:55</t>
         </is>
       </c>
       <c r="AF248" t="inlineStr">
@@ -29031,7 +29031,7 @@
       </c>
       <c r="AE249" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF249" t="inlineStr">
@@ -29143,7 +29143,7 @@
       </c>
       <c r="AE250" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF250" t="inlineStr">
@@ -29253,7 +29253,7 @@
       </c>
       <c r="AE251" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF251" t="inlineStr">
@@ -29373,7 +29373,7 @@
       </c>
       <c r="AE252" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="AF252" t="inlineStr">
@@ -29485,7 +29485,7 @@
       </c>
       <c r="AE253" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF253" t="inlineStr">
@@ -29595,7 +29595,7 @@
       </c>
       <c r="AE254" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF254" t="inlineStr">
@@ -29707,7 +29707,7 @@
       </c>
       <c r="AE255" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF255" t="inlineStr">
@@ -29823,7 +29823,7 @@
       </c>
       <c r="AE256" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF256" t="inlineStr">
@@ -29935,7 +29935,7 @@
       </c>
       <c r="AE257" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF257" t="inlineStr">
@@ -30045,7 +30045,7 @@
       </c>
       <c r="AE258" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF258" t="inlineStr">
@@ -30161,7 +30161,7 @@
       </c>
       <c r="AE259" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF259" t="inlineStr">
@@ -30271,7 +30271,7 @@
       </c>
       <c r="AE260" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF260" t="inlineStr">
@@ -30397,7 +30397,7 @@
       <c r="AD261" t="inlineStr"/>
       <c r="AE261" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="AF261" t="inlineStr">
@@ -30525,7 +30525,7 @@
       </c>
       <c r="AE262" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="AF262" t="inlineStr">
@@ -30637,7 +30637,7 @@
       </c>
       <c r="AE263" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF263" t="inlineStr">
@@ -30737,7 +30737,7 @@
       </c>
       <c r="AE264" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF264" t="inlineStr">
@@ -30837,7 +30837,7 @@
       </c>
       <c r="AE265" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF265" t="inlineStr">
@@ -30951,7 +30951,7 @@
       </c>
       <c r="AE266" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF266" t="inlineStr">
@@ -31065,7 +31065,7 @@
       </c>
       <c r="AE267" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF267" t="inlineStr">
@@ -31165,7 +31165,7 @@
       </c>
       <c r="AE268" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF268" t="inlineStr">
@@ -31285,7 +31285,7 @@
       </c>
       <c r="AE269" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="AF269" t="inlineStr">
@@ -31397,7 +31397,7 @@
       </c>
       <c r="AE270" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF270" t="inlineStr">
@@ -31509,7 +31509,7 @@
       </c>
       <c r="AE271" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF271" t="inlineStr">
@@ -31623,7 +31623,7 @@
       </c>
       <c r="AE272" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF272" t="inlineStr">
@@ -31737,7 +31737,7 @@
       </c>
       <c r="AE273" t="inlineStr">
         <is>
-          <t>2026-09-18 08:50:00</t>
+          <t>2026-09-18 09:05:40</t>
         </is>
       </c>
       <c r="AF273" t="inlineStr">
@@ -31851,7 +31851,7 @@
       </c>
       <c r="AE274" t="inlineStr">
         <is>
-          <t>2026-09-18 08:50:00</t>
+          <t>2026-09-18 09:05:40</t>
         </is>
       </c>
       <c r="AF274" t="inlineStr">
@@ -31983,7 +31983,7 @@
       </c>
       <c r="AE275" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="AF275" t="inlineStr">
@@ -32111,7 +32111,7 @@
       </c>
       <c r="AE276" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="AF276" t="inlineStr">
@@ -32239,7 +32239,7 @@
       </c>
       <c r="AE277" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="AF277" t="inlineStr">
@@ -32367,7 +32367,7 @@
       </c>
       <c r="AE278" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="AF278" t="inlineStr">
@@ -32479,7 +32479,7 @@
       </c>
       <c r="AE279" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF279" t="inlineStr">
@@ -32591,7 +32591,7 @@
       </c>
       <c r="AE280" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF280" t="inlineStr">
@@ -32701,7 +32701,7 @@
       </c>
       <c r="AE281" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF281" t="inlineStr">
@@ -32811,7 +32811,7 @@
       </c>
       <c r="AE282" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF282" t="inlineStr">
@@ -32939,7 +32939,7 @@
       </c>
       <c r="AE283" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="AF283" t="inlineStr">
@@ -33049,7 +33049,7 @@
       </c>
       <c r="AE284" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF284" t="inlineStr">
@@ -33177,7 +33177,7 @@
       </c>
       <c r="AE285" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="AF285" t="inlineStr">
@@ -33289,7 +33289,7 @@
       </c>
       <c r="AE286" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF286" t="inlineStr">
@@ -33401,7 +33401,7 @@
       </c>
       <c r="AE287" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF287" t="inlineStr">
@@ -33511,7 +33511,7 @@
       </c>
       <c r="AE288" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF288" t="inlineStr">
@@ -33631,7 +33631,7 @@
       </c>
       <c r="AE289" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="AF289" t="inlineStr">
@@ -33755,7 +33755,7 @@
       </c>
       <c r="AE290" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="AF290" t="inlineStr">
@@ -33879,7 +33879,7 @@
       </c>
       <c r="AE291" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="AF291" t="inlineStr">
@@ -34003,7 +34003,7 @@
       </c>
       <c r="AE292" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="AF292" t="inlineStr">
@@ -34115,7 +34115,7 @@
       </c>
       <c r="AE293" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF293" t="inlineStr">
@@ -34231,7 +34231,7 @@
       </c>
       <c r="AE294" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF294" t="inlineStr">
@@ -34343,7 +34343,7 @@
       </c>
       <c r="AE295" t="inlineStr">
         <is>
-          <t>2026-09-18 08:50:02</t>
+          <t>2026-09-18 09:05:42</t>
         </is>
       </c>
       <c r="AF295" t="inlineStr">
@@ -34471,7 +34471,7 @@
       </c>
       <c r="AE296" t="inlineStr">
         <is>
-          <t>2026-09-18 08:50:02</t>
+          <t>2026-09-18 09:05:42</t>
         </is>
       </c>
       <c r="AF296" t="inlineStr">
@@ -34599,7 +34599,7 @@
       </c>
       <c r="AE297" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="AF297" t="inlineStr">
@@ -34711,7 +34711,7 @@
       </c>
       <c r="AE298" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF298" t="inlineStr">
@@ -34823,7 +34823,7 @@
       </c>
       <c r="AE299" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF299" t="inlineStr">
@@ -34933,7 +34933,7 @@
       </c>
       <c r="AE300" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF300" t="inlineStr">
@@ -35043,7 +35043,7 @@
       </c>
       <c r="AE301" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF301" t="inlineStr">
@@ -35159,7 +35159,7 @@
       </c>
       <c r="AE302" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF302" t="inlineStr">
@@ -35271,7 +35271,7 @@
       </c>
       <c r="AE303" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF303" t="inlineStr">
@@ -35391,7 +35391,7 @@
       </c>
       <c r="AE304" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="AF304" t="inlineStr">
@@ -35519,7 +35519,7 @@
       </c>
       <c r="AE305" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="AF305" t="inlineStr">
@@ -35635,7 +35635,7 @@
       </c>
       <c r="AE306" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF306" t="inlineStr">
@@ -35735,7 +35735,7 @@
       </c>
       <c r="AE307" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF307" t="inlineStr">
@@ -35847,7 +35847,7 @@
       </c>
       <c r="AE308" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF308" t="inlineStr">
@@ -35975,7 +35975,7 @@
       </c>
       <c r="AE309" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="AF309" t="inlineStr">
@@ -36099,7 +36099,7 @@
       </c>
       <c r="AE310" t="inlineStr">
         <is>
-          <t>2026-09-18 08:50:02</t>
+          <t>2026-09-18 09:05:42</t>
         </is>
       </c>
       <c r="AF310" t="inlineStr">
@@ -36211,7 +36211,7 @@
       </c>
       <c r="AE311" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF311" t="inlineStr">
@@ -36321,7 +36321,7 @@
       </c>
       <c r="AE312" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF312" t="inlineStr">
@@ -36431,7 +36431,7 @@
       </c>
       <c r="AE313" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF313" t="inlineStr">
@@ -36541,7 +36541,7 @@
       </c>
       <c r="AE314" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF314" t="inlineStr">
@@ -36651,7 +36651,7 @@
       </c>
       <c r="AE315" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF315" t="inlineStr">
@@ -36771,7 +36771,7 @@
       </c>
       <c r="AE316" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="AF316" t="inlineStr">
@@ -36881,7 +36881,7 @@
       </c>
       <c r="AE317" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF317" t="inlineStr">
@@ -36991,7 +36991,7 @@
       </c>
       <c r="AE318" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF318" t="inlineStr">
@@ -37101,7 +37101,7 @@
       </c>
       <c r="AE319" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF319" t="inlineStr">
@@ -37221,7 +37221,7 @@
       </c>
       <c r="AE320" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="AF320" t="inlineStr">
@@ -37341,7 +37341,7 @@
       </c>
       <c r="AE321" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="AF321" t="inlineStr">
@@ -37461,7 +37461,7 @@
       </c>
       <c r="AE322" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="AF322" t="inlineStr">
@@ -37581,7 +37581,7 @@
       </c>
       <c r="AE323" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="AF323" t="inlineStr">
@@ -37697,7 +37697,7 @@
       </c>
       <c r="AE324" t="inlineStr">
         <is>
-          <t>2026-09-18 08:50:17</t>
+          <t>2026-09-18 09:05:55</t>
         </is>
       </c>
       <c r="AF324" t="inlineStr">
@@ -37813,7 +37813,7 @@
       </c>
       <c r="AE325" t="inlineStr">
         <is>
-          <t>2026-09-18 08:50:17</t>
+          <t>2026-09-18 09:05:55</t>
         </is>
       </c>
       <c r="AF325" t="inlineStr">
@@ -37929,7 +37929,7 @@
       </c>
       <c r="AE326" t="inlineStr">
         <is>
-          <t>2026-09-18 08:50:17</t>
+          <t>2026-09-18 09:05:55</t>
         </is>
       </c>
       <c r="AF326" t="inlineStr">
@@ -38041,7 +38041,7 @@
       </c>
       <c r="AE327" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF327" t="inlineStr">
@@ -38157,7 +38157,7 @@
       </c>
       <c r="AE328" t="inlineStr">
         <is>
-          <t>2026-09-18 08:50:17</t>
+          <t>2026-09-18 09:05:55</t>
         </is>
       </c>
       <c r="AF328" t="inlineStr">
@@ -38277,7 +38277,7 @@
       </c>
       <c r="AE329" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="AF329" t="inlineStr">
@@ -38389,7 +38389,7 @@
       </c>
       <c r="AE330" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF330" t="inlineStr">
@@ -38505,7 +38505,7 @@
       </c>
       <c r="AE331" t="inlineStr">
         <is>
-          <t>2026-09-18 08:50:17</t>
+          <t>2026-09-18 09:05:55</t>
         </is>
       </c>
       <c r="AF331" t="inlineStr">
@@ -38621,7 +38621,7 @@
       </c>
       <c r="AE332" t="inlineStr">
         <is>
-          <t>2026-09-18 08:50:17</t>
+          <t>2026-09-18 09:05:55</t>
         </is>
       </c>
       <c r="AF332" t="inlineStr">
@@ -38737,7 +38737,7 @@
       </c>
       <c r="AE333" t="inlineStr">
         <is>
-          <t>2026-09-18 08:50:17</t>
+          <t>2026-09-18 09:05:55</t>
         </is>
       </c>
       <c r="AF333" t="inlineStr">
@@ -38853,7 +38853,7 @@
       </c>
       <c r="AE334" t="inlineStr">
         <is>
-          <t>2026-09-18 08:50:17</t>
+          <t>2026-09-18 09:05:55</t>
         </is>
       </c>
       <c r="AF334" t="inlineStr">
@@ -38967,7 +38967,7 @@
       </c>
       <c r="AE335" t="inlineStr">
         <is>
-          <t>2026-09-18 08:50:00</t>
+          <t>2026-09-18 09:05:40</t>
         </is>
       </c>
       <c r="AF335" t="inlineStr">
@@ -39083,7 +39083,7 @@
       </c>
       <c r="AE336" t="inlineStr">
         <is>
-          <t>2026-09-18 08:50:17</t>
+          <t>2026-09-18 09:05:55</t>
         </is>
       </c>
       <c r="AF336" t="inlineStr">
@@ -39199,7 +39199,7 @@
       </c>
       <c r="AE337" t="inlineStr">
         <is>
-          <t>2026-09-18 08:50:17</t>
+          <t>2026-09-18 09:05:55</t>
         </is>
       </c>
       <c r="AF337" t="inlineStr">
@@ -39315,7 +39315,7 @@
       </c>
       <c r="AE338" t="inlineStr">
         <is>
-          <t>2026-09-18 08:50:17</t>
+          <t>2026-09-18 09:05:55</t>
         </is>
       </c>
       <c r="AF338" t="inlineStr">
@@ -39425,7 +39425,7 @@
       </c>
       <c r="AE339" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF339" t="inlineStr">
@@ -39541,7 +39541,7 @@
       </c>
       <c r="AE340" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF340" t="inlineStr">
@@ -39653,7 +39653,7 @@
       </c>
       <c r="AE341" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF341" t="inlineStr">
@@ -39763,7 +39763,7 @@
       </c>
       <c r="AE342" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF342" t="inlineStr">
@@ -39875,7 +39875,7 @@
       </c>
       <c r="AE343" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF343" t="inlineStr">
@@ -39987,7 +39987,7 @@
       </c>
       <c r="AE344" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF344" t="inlineStr">
@@ -40099,7 +40099,7 @@
       </c>
       <c r="AE345" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF345" t="inlineStr">
@@ -40219,7 +40219,7 @@
       </c>
       <c r="AE346" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="AF346" t="inlineStr">
@@ -40347,7 +40347,7 @@
       </c>
       <c r="AE347" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="AF347" t="inlineStr">
@@ -40467,7 +40467,7 @@
       </c>
       <c r="AE348" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="AF348" t="inlineStr">
@@ -40595,7 +40595,7 @@
       </c>
       <c r="AE349" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="AF349" t="inlineStr">
@@ -40707,7 +40707,7 @@
       </c>
       <c r="AE350" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF350" t="inlineStr">
@@ -40817,7 +40817,7 @@
       </c>
       <c r="AE351" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF351" t="inlineStr">
@@ -40927,7 +40927,7 @@
       </c>
       <c r="AE352" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF352" t="inlineStr">
@@ -41039,7 +41039,7 @@
       </c>
       <c r="AE353" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF353" t="inlineStr">
@@ -41151,7 +41151,7 @@
       </c>
       <c r="AE354" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF354" t="inlineStr">
@@ -41261,7 +41261,7 @@
       </c>
       <c r="AE355" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF355" t="inlineStr">
@@ -41377,7 +41377,7 @@
       </c>
       <c r="AE356" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF356" t="inlineStr">
@@ -41487,7 +41487,7 @@
       </c>
       <c r="AE357" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF357" t="inlineStr">
@@ -41599,7 +41599,7 @@
       </c>
       <c r="AE358" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF358" t="inlineStr">
@@ -41709,7 +41709,7 @@
       </c>
       <c r="AE359" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF359" t="inlineStr">
@@ -41819,7 +41819,7 @@
       </c>
       <c r="AE360" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF360" t="inlineStr">
@@ -41947,7 +41947,7 @@
       </c>
       <c r="AE361" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="AF361" t="inlineStr">
@@ -42059,7 +42059,7 @@
       </c>
       <c r="AE362" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF362" t="inlineStr">
@@ -42187,7 +42187,7 @@
       </c>
       <c r="AE363" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="AF363" t="inlineStr">
@@ -42299,7 +42299,7 @@
       </c>
       <c r="AE364" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF364" t="inlineStr">
@@ -42409,7 +42409,7 @@
       </c>
       <c r="AE365" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF365" t="inlineStr">
@@ -42519,7 +42519,7 @@
       </c>
       <c r="AE366" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF366" t="inlineStr">
@@ -42629,7 +42629,7 @@
       </c>
       <c r="AE367" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF367" t="inlineStr">
@@ -42741,7 +42741,7 @@
       </c>
       <c r="AE368" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF368" t="inlineStr">
@@ -42851,7 +42851,7 @@
       </c>
       <c r="AE369" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF369" t="inlineStr">
@@ -42979,7 +42979,7 @@
       </c>
       <c r="AE370" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="AF370" t="inlineStr">
@@ -43091,7 +43091,7 @@
       </c>
       <c r="AE371" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF371" t="inlineStr">
@@ -43201,7 +43201,7 @@
       </c>
       <c r="AE372" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF372" t="inlineStr">
@@ -43311,7 +43311,7 @@
       </c>
       <c r="AE373" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF373" t="inlineStr">
@@ -43421,7 +43421,7 @@
       </c>
       <c r="AE374" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF374" t="inlineStr">
@@ -43531,7 +43531,7 @@
       </c>
       <c r="AE375" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF375" t="inlineStr">
@@ -43641,7 +43641,7 @@
       </c>
       <c r="AE376" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF376" t="inlineStr">
@@ -43753,7 +43753,7 @@
       </c>
       <c r="AE377" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF377" t="inlineStr">
@@ -43881,7 +43881,7 @@
       </c>
       <c r="AE378" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="AF378" t="inlineStr">
@@ -43991,7 +43991,7 @@
       </c>
       <c r="AE379" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF379" t="inlineStr">
@@ -44101,7 +44101,7 @@
       </c>
       <c r="AE380" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF380" t="inlineStr">
@@ -44213,7 +44213,7 @@
       </c>
       <c r="AE381" t="inlineStr">
         <is>
-          <t>2026-09-18 08:50:02</t>
+          <t>2026-09-18 09:05:42</t>
         </is>
       </c>
       <c r="AF381" t="inlineStr">
@@ -44323,7 +44323,7 @@
       </c>
       <c r="AE382" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF382" t="inlineStr">
@@ -44435,7 +44435,7 @@
       </c>
       <c r="AE383" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF383" t="inlineStr">
@@ -44563,7 +44563,7 @@
       </c>
       <c r="AE384" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="AF384" t="inlineStr">
@@ -44673,7 +44673,7 @@
       </c>
       <c r="AE385" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF385" t="inlineStr">
@@ -44785,7 +44785,7 @@
       </c>
       <c r="AE386" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF386" t="inlineStr">
@@ -44895,7 +44895,7 @@
       </c>
       <c r="AE387" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF387" t="inlineStr">
@@ -45005,7 +45005,7 @@
       </c>
       <c r="AE388" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF388" t="inlineStr">
@@ -45115,7 +45115,7 @@
       </c>
       <c r="AE389" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF389" t="inlineStr">
@@ -45215,7 +45215,7 @@
       </c>
       <c r="AE390" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF390" t="inlineStr">
@@ -45325,7 +45325,7 @@
       </c>
       <c r="AE391" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF391" t="inlineStr">
@@ -45425,7 +45425,7 @@
       </c>
       <c r="AE392" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF392" t="inlineStr">
@@ -45535,7 +45535,7 @@
       </c>
       <c r="AE393" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF393" t="inlineStr">
@@ -45663,7 +45663,7 @@
       </c>
       <c r="AE394" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="AF394" t="inlineStr">
@@ -45773,7 +45773,7 @@
       </c>
       <c r="AE395" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF395" t="inlineStr">
@@ -45883,7 +45883,7 @@
       </c>
       <c r="AE396" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF396" t="inlineStr">
@@ -45993,7 +45993,7 @@
       </c>
       <c r="AE397" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF397" t="inlineStr">
@@ -46103,7 +46103,7 @@
       </c>
       <c r="AE398" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF398" t="inlineStr">
@@ -46213,7 +46213,7 @@
       </c>
       <c r="AE399" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF399" t="inlineStr">
@@ -46323,7 +46323,7 @@
       </c>
       <c r="AE400" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF400" t="inlineStr">
@@ -46433,7 +46433,7 @@
       </c>
       <c r="AE401" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF401" t="inlineStr">
@@ -46543,7 +46543,7 @@
       </c>
       <c r="AE402" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF402" t="inlineStr">
@@ -46671,7 +46671,7 @@
       </c>
       <c r="AE403" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="AF403" t="inlineStr">
@@ -46783,7 +46783,7 @@
       </c>
       <c r="AE404" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF404" t="inlineStr">
@@ -46883,7 +46883,7 @@
       </c>
       <c r="AE405" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF405" t="inlineStr">
@@ -46993,7 +46993,7 @@
       </c>
       <c r="AE406" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF406" t="inlineStr">
@@ -47107,7 +47107,7 @@
       </c>
       <c r="AE407" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF407" t="inlineStr">
@@ -47217,7 +47217,7 @@
       </c>
       <c r="AE408" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF408" t="inlineStr">
@@ -47317,7 +47317,7 @@
       </c>
       <c r="AE409" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF409" t="inlineStr">
@@ -47429,7 +47429,7 @@
       </c>
       <c r="AE410" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF410" t="inlineStr">
@@ -47541,7 +47541,7 @@
       </c>
       <c r="AE411" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF411" t="inlineStr">
@@ -47651,7 +47651,7 @@
       </c>
       <c r="AE412" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF412" t="inlineStr">
@@ -47763,7 +47763,7 @@
       </c>
       <c r="AE413" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF413" t="inlineStr">
@@ -47875,7 +47875,7 @@
       </c>
       <c r="AE414" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF414" t="inlineStr">
@@ -47985,7 +47985,7 @@
       </c>
       <c r="AE415" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF415" t="inlineStr">
@@ -48113,7 +48113,7 @@
       </c>
       <c r="AE416" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="AF416" t="inlineStr">
@@ -48245,7 +48245,7 @@
       </c>
       <c r="AE417" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="AF417" t="inlineStr">
@@ -48377,7 +48377,7 @@
       </c>
       <c r="AE418" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="AF418" t="inlineStr">
@@ -48509,7 +48509,7 @@
       </c>
       <c r="AE419" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="AF419" t="inlineStr">
@@ -48633,7 +48633,7 @@
       </c>
       <c r="AE420" t="inlineStr">
         <is>
-          <t>2026-09-18 08:50:02</t>
+          <t>2026-09-18 09:05:42</t>
         </is>
       </c>
       <c r="AF420" t="inlineStr">
@@ -48745,7 +48745,7 @@
       </c>
       <c r="AE421" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF421" t="inlineStr">
@@ -48845,7 +48845,7 @@
       </c>
       <c r="AE422" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF422" t="inlineStr">
@@ -48965,7 +48965,7 @@
       </c>
       <c r="AE423" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="AF423" t="inlineStr">
@@ -49081,7 +49081,7 @@
       </c>
       <c r="AE424" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF424" t="inlineStr">
@@ -49193,7 +49193,7 @@
       </c>
       <c r="AE425" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF425" t="inlineStr">
@@ -49315,7 +49315,7 @@
       <c r="AD426" t="inlineStr"/>
       <c r="AE426" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="AF426" t="inlineStr">
@@ -49427,7 +49427,7 @@
       </c>
       <c r="AE427" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF427" t="inlineStr">
@@ -49537,7 +49537,7 @@
       </c>
       <c r="AE428" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF428" t="inlineStr">
@@ -49647,7 +49647,7 @@
       </c>
       <c r="AE429" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF429" t="inlineStr">
@@ -49757,7 +49757,7 @@
       </c>
       <c r="AE430" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF430" t="inlineStr">
@@ -49867,7 +49867,7 @@
       </c>
       <c r="AE431" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF431" t="inlineStr">
@@ -49995,7 +49995,7 @@
       </c>
       <c r="AE432" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="AF432" t="inlineStr">
@@ -50111,7 +50111,7 @@
       </c>
       <c r="AE433" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF433" t="inlineStr">
@@ -50221,7 +50221,7 @@
       </c>
       <c r="AE434" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF434" t="inlineStr">
@@ -50349,7 +50349,7 @@
       </c>
       <c r="AE435" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="AF435" t="inlineStr">
@@ -50477,7 +50477,7 @@
       </c>
       <c r="AE436" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="AF436" t="inlineStr">
@@ -50605,7 +50605,7 @@
       </c>
       <c r="AE437" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="AF437" t="inlineStr">
@@ -50733,7 +50733,7 @@
       </c>
       <c r="AE438" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="AF438" t="inlineStr">
@@ -50845,7 +50845,7 @@
       </c>
       <c r="AE439" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF439" t="inlineStr">
@@ -50955,7 +50955,7 @@
       </c>
       <c r="AE440" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF440" t="inlineStr">
@@ -51083,7 +51083,7 @@
       </c>
       <c r="AE441" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="AF441" t="inlineStr">
@@ -51195,7 +51195,7 @@
       </c>
       <c r="AE442" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF442" t="inlineStr">
@@ -51307,7 +51307,7 @@
       </c>
       <c r="AE443" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF443" t="inlineStr">
@@ -51423,7 +51423,7 @@
       </c>
       <c r="AE444" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF444" t="inlineStr">
@@ -51535,7 +51535,7 @@
       </c>
       <c r="AE445" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF445" t="inlineStr">
@@ -51647,7 +51647,7 @@
       </c>
       <c r="AE446" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF446" t="inlineStr">
@@ -51759,7 +51759,7 @@
       </c>
       <c r="AE447" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF447" t="inlineStr">
@@ -51871,7 +51871,7 @@
       </c>
       <c r="AE448" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF448" t="inlineStr">
@@ -51991,7 +51991,7 @@
       </c>
       <c r="AE449" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="AF449" t="inlineStr">
@@ -52101,7 +52101,7 @@
       </c>
       <c r="AE450" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF450" t="inlineStr">
@@ -52229,7 +52229,7 @@
       </c>
       <c r="AE451" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="AF451" t="inlineStr">
@@ -52349,7 +52349,7 @@
       </c>
       <c r="AE452" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="AF452" t="inlineStr">
@@ -52461,7 +52461,7 @@
       </c>
       <c r="AE453" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF453" t="inlineStr">
@@ -52573,7 +52573,7 @@
       </c>
       <c r="AE454" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF454" t="inlineStr">
@@ -52673,7 +52673,7 @@
       </c>
       <c r="AE455" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF455" t="inlineStr">
@@ -52789,7 +52789,7 @@
       </c>
       <c r="AE456" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF456" t="inlineStr">
@@ -52899,7 +52899,7 @@
       </c>
       <c r="AE457" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF457" t="inlineStr">
@@ -53011,7 +53011,7 @@
       </c>
       <c r="AE458" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF458" t="inlineStr">
@@ -53121,7 +53121,7 @@
       </c>
       <c r="AE459" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF459" t="inlineStr">
@@ -53233,7 +53233,7 @@
       </c>
       <c r="AE460" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF460" t="inlineStr">
@@ -53345,7 +53345,7 @@
       </c>
       <c r="AE461" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF461" t="inlineStr">
@@ -53445,7 +53445,7 @@
       </c>
       <c r="AE462" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF462" t="inlineStr">
@@ -53555,7 +53555,7 @@
       </c>
       <c r="AE463" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF463" t="inlineStr">
@@ -53667,7 +53667,7 @@
       </c>
       <c r="AE464" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF464" t="inlineStr">
@@ -53777,7 +53777,7 @@
       </c>
       <c r="AE465" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF465" t="inlineStr">
@@ -53887,7 +53887,7 @@
       </c>
       <c r="AE466" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF466" t="inlineStr">
@@ -53999,7 +53999,7 @@
       </c>
       <c r="AE467" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF467" t="inlineStr">
@@ -54109,7 +54109,7 @@
       </c>
       <c r="AE468" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF468" t="inlineStr">
@@ -54219,7 +54219,7 @@
       </c>
       <c r="AE469" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF469" t="inlineStr">
@@ -54329,7 +54329,7 @@
       </c>
       <c r="AE470" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF470" t="inlineStr">
@@ -54449,7 +54449,7 @@
       </c>
       <c r="AE471" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="AF471" t="inlineStr">
@@ -54573,7 +54573,7 @@
       </c>
       <c r="AE472" t="inlineStr">
         <is>
-          <t>2026-09-18 08:50:02</t>
+          <t>2026-09-18 09:05:42</t>
         </is>
       </c>
       <c r="AF472" t="inlineStr">
@@ -54683,7 +54683,7 @@
       </c>
       <c r="AE473" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF473" t="inlineStr">
@@ -54795,7 +54795,7 @@
       </c>
       <c r="AE474" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF474" t="inlineStr">
@@ -54905,7 +54905,7 @@
       </c>
       <c r="AE475" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF475" t="inlineStr">
@@ -55017,7 +55017,7 @@
       </c>
       <c r="AE476" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF476" t="inlineStr">
@@ -55129,7 +55129,7 @@
       </c>
       <c r="AE477" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF477" t="inlineStr">
@@ -55239,7 +55239,7 @@
       </c>
       <c r="AE478" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF478" t="inlineStr">
@@ -55349,7 +55349,7 @@
       </c>
       <c r="AE479" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF479" t="inlineStr">
@@ -55459,7 +55459,7 @@
       </c>
       <c r="AE480" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF480" t="inlineStr">
@@ -55569,7 +55569,7 @@
       </c>
       <c r="AE481" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF481" t="inlineStr">
@@ -55679,7 +55679,7 @@
       </c>
       <c r="AE482" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF482" t="inlineStr">
@@ -55789,7 +55789,7 @@
       </c>
       <c r="AE483" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF483" t="inlineStr">
@@ -55901,7 +55901,7 @@
       </c>
       <c r="AE484" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF484" t="inlineStr">
@@ -56013,7 +56013,7 @@
       </c>
       <c r="AE485" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF485" t="inlineStr">
@@ -56125,7 +56125,7 @@
       </c>
       <c r="AE486" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF486" t="inlineStr">
@@ -56235,7 +56235,7 @@
       </c>
       <c r="AE487" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF487" t="inlineStr">
@@ -56347,7 +56347,7 @@
       </c>
       <c r="AE488" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF488" t="inlineStr">
@@ -56447,7 +56447,7 @@
       </c>
       <c r="AE489" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF489" t="inlineStr">
@@ -56557,7 +56557,7 @@
       </c>
       <c r="AE490" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF490" t="inlineStr">
@@ -56657,7 +56657,7 @@
       </c>
       <c r="AE491" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF491" t="inlineStr">
@@ -56757,7 +56757,7 @@
       </c>
       <c r="AE492" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF492" t="inlineStr">
@@ -56869,7 +56869,7 @@
       </c>
       <c r="AE493" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF493" t="inlineStr">
@@ -56981,7 +56981,7 @@
       </c>
       <c r="AE494" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF494" t="inlineStr">
@@ -57093,7 +57093,7 @@
       </c>
       <c r="AE495" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF495" t="inlineStr">
@@ -57203,7 +57203,7 @@
       </c>
       <c r="AE496" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF496" t="inlineStr">
@@ -57313,7 +57313,7 @@
       </c>
       <c r="AE497" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF497" t="inlineStr">
@@ -57423,7 +57423,7 @@
       </c>
       <c r="AE498" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF498" t="inlineStr">
@@ -57535,7 +57535,7 @@
       </c>
       <c r="AE499" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF499" t="inlineStr">
@@ -57645,7 +57645,7 @@
       </c>
       <c r="AE500" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF500" t="inlineStr">
@@ -57755,7 +57755,7 @@
       </c>
       <c r="AE501" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF501" t="inlineStr">
@@ -57865,7 +57865,7 @@
       </c>
       <c r="AE502" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF502" t="inlineStr">
@@ -57975,7 +57975,7 @@
       </c>
       <c r="AE503" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF503" t="inlineStr">
@@ -58087,7 +58087,7 @@
       </c>
       <c r="AE504" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF504" t="inlineStr">
@@ -58199,7 +58199,7 @@
       </c>
       <c r="AE505" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF505" t="inlineStr">
@@ -58315,7 +58315,7 @@
       </c>
       <c r="AE506" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF506" t="inlineStr">
@@ -58443,7 +58443,7 @@
       </c>
       <c r="AE507" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="AF507" t="inlineStr">
@@ -58555,7 +58555,7 @@
       </c>
       <c r="AE508" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF508" t="inlineStr">
@@ -58665,7 +58665,7 @@
       </c>
       <c r="AE509" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF509" t="inlineStr">
@@ -58785,7 +58785,7 @@
       </c>
       <c r="AE510" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="AF510" t="inlineStr">
@@ -58895,7 +58895,7 @@
       </c>
       <c r="AE511" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF511" t="inlineStr">
@@ -59005,7 +59005,7 @@
       </c>
       <c r="AE512" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF512" t="inlineStr">
@@ -59115,7 +59115,7 @@
       </c>
       <c r="AE513" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF513" t="inlineStr">
@@ -59235,7 +59235,7 @@
       </c>
       <c r="AE514" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="AF514" t="inlineStr">
@@ -59351,7 +59351,7 @@
       </c>
       <c r="AE515" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF515" t="inlineStr">
@@ -59463,7 +59463,7 @@
       </c>
       <c r="AE516" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF516" t="inlineStr">
@@ -59583,7 +59583,7 @@
       </c>
       <c r="AE517" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="AF517" t="inlineStr">
@@ -59695,7 +59695,7 @@
       </c>
       <c r="AE518" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF518" t="inlineStr">
@@ -59795,7 +59795,7 @@
       </c>
       <c r="AE519" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF519" t="inlineStr">
@@ -59915,7 +59915,7 @@
       </c>
       <c r="AE520" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="AF520" t="inlineStr">
@@ -60025,7 +60025,7 @@
       </c>
       <c r="AE521" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF521" t="inlineStr">
@@ -60137,7 +60137,7 @@
       </c>
       <c r="AE522" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF522" t="inlineStr">
@@ -60253,7 +60253,7 @@
       </c>
       <c r="AE523" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF523" t="inlineStr">
@@ -60365,7 +60365,7 @@
       </c>
       <c r="AE524" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF524" t="inlineStr">
@@ -60477,7 +60477,7 @@
       </c>
       <c r="AE525" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF525" t="inlineStr">
@@ -60605,7 +60605,7 @@
       </c>
       <c r="AE526" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="AF526" t="inlineStr">
@@ -60715,7 +60715,7 @@
       </c>
       <c r="AE527" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF527" t="inlineStr">
@@ -60825,7 +60825,7 @@
       </c>
       <c r="AE528" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF528" t="inlineStr">
@@ -60935,7 +60935,7 @@
       </c>
       <c r="AE529" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF529" t="inlineStr">
@@ -61047,7 +61047,7 @@
       </c>
       <c r="AE530" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF530" t="inlineStr">
@@ -61175,7 +61175,7 @@
       </c>
       <c r="AE531" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="AF531" t="inlineStr">
@@ -61287,7 +61287,7 @@
       </c>
       <c r="AE532" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF532" t="inlineStr">
@@ -61399,7 +61399,7 @@
       </c>
       <c r="AE533" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF533" t="inlineStr">
@@ -61511,7 +61511,7 @@
       </c>
       <c r="AE534" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF534" t="inlineStr">
@@ -61611,7 +61611,7 @@
       </c>
       <c r="AE535" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF535" t="inlineStr">
@@ -61721,7 +61721,7 @@
       </c>
       <c r="AE536" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF536" t="inlineStr">
@@ -61831,7 +61831,7 @@
       </c>
       <c r="AE537" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF537" t="inlineStr">
@@ -61931,7 +61931,7 @@
       </c>
       <c r="AE538" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF538" t="inlineStr">
@@ -62041,7 +62041,7 @@
       </c>
       <c r="AE539" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF539" t="inlineStr">
@@ -62169,7 +62169,7 @@
       </c>
       <c r="AE540" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="AF540" t="inlineStr">
@@ -62279,7 +62279,7 @@
       </c>
       <c r="AE541" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF541" t="inlineStr">
@@ -62391,7 +62391,7 @@
       </c>
       <c r="AE542" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF542" t="inlineStr">
@@ -62501,7 +62501,7 @@
       </c>
       <c r="AE543" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF543" t="inlineStr">
@@ -62613,7 +62613,7 @@
       </c>
       <c r="AE544" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF544" t="inlineStr">
@@ -62723,7 +62723,7 @@
       </c>
       <c r="AE545" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF545" t="inlineStr">
@@ -62833,7 +62833,7 @@
       </c>
       <c r="AE546" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF546" t="inlineStr">
@@ -62933,7 +62933,7 @@
       </c>
       <c r="AE547" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF547" t="inlineStr">
@@ -63043,7 +63043,7 @@
       </c>
       <c r="AE548" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF548" t="inlineStr">
@@ -63155,7 +63155,7 @@
       </c>
       <c r="AE549" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF549" t="inlineStr">
@@ -63265,7 +63265,7 @@
       </c>
       <c r="AE550" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF550" t="inlineStr">
@@ -63375,7 +63375,7 @@
       </c>
       <c r="AE551" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF551" t="inlineStr">
@@ -63485,7 +63485,7 @@
       </c>
       <c r="AE552" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF552" t="inlineStr">
@@ -63595,7 +63595,7 @@
       </c>
       <c r="AE553" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF553" t="inlineStr">
@@ -63705,7 +63705,7 @@
       </c>
       <c r="AE554" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF554" t="inlineStr">
@@ -63815,7 +63815,7 @@
       </c>
       <c r="AE555" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF555" t="inlineStr">
@@ -63915,7 +63915,7 @@
       </c>
       <c r="AE556" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF556" t="inlineStr">
@@ -64025,7 +64025,7 @@
       </c>
       <c r="AE557" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF557" t="inlineStr">
@@ -64135,7 +64135,7 @@
       </c>
       <c r="AE558" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF558" t="inlineStr">
@@ -64247,7 +64247,7 @@
       </c>
       <c r="AE559" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF559" t="inlineStr">
@@ -64357,7 +64357,7 @@
       </c>
       <c r="AE560" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF560" t="inlineStr">
@@ -64469,7 +64469,7 @@
       </c>
       <c r="AE561" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF561" t="inlineStr">
@@ -64579,7 +64579,7 @@
       </c>
       <c r="AE562" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF562" t="inlineStr">
@@ -64689,7 +64689,7 @@
       </c>
       <c r="AE563" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF563" t="inlineStr">
@@ -64799,7 +64799,7 @@
       </c>
       <c r="AE564" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF564" t="inlineStr">
@@ -64909,7 +64909,7 @@
       </c>
       <c r="AE565" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF565" t="inlineStr">
@@ -65019,7 +65019,7 @@
       </c>
       <c r="AE566" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF566" t="inlineStr">
@@ -65131,7 +65131,7 @@
       </c>
       <c r="AE567" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF567" t="inlineStr">
@@ -65241,7 +65241,7 @@
       </c>
       <c r="AE568" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF568" t="inlineStr">
@@ -65353,7 +65353,7 @@
       </c>
       <c r="AE569" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF569" t="inlineStr">
@@ -65465,7 +65465,7 @@
       </c>
       <c r="AE570" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF570" t="inlineStr">
@@ -65575,7 +65575,7 @@
       </c>
       <c r="AE571" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF571" t="inlineStr">
@@ -65687,7 +65687,7 @@
       </c>
       <c r="AE572" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF572" t="inlineStr">
@@ -65799,7 +65799,7 @@
       </c>
       <c r="AE573" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF573" t="inlineStr">
@@ -65909,7 +65909,7 @@
       </c>
       <c r="AE574" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF574" t="inlineStr">
@@ -66019,7 +66019,7 @@
       </c>
       <c r="AE575" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF575" t="inlineStr">
@@ -66129,7 +66129,7 @@
       </c>
       <c r="AE576" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF576" t="inlineStr">
@@ -66239,7 +66239,7 @@
       </c>
       <c r="AE577" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF577" t="inlineStr">
@@ -66339,7 +66339,7 @@
       </c>
       <c r="AE578" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF578" t="inlineStr">
@@ -66451,7 +66451,7 @@
       </c>
       <c r="AE579" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF579" t="inlineStr">
@@ -66561,7 +66561,7 @@
       </c>
       <c r="AE580" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF580" t="inlineStr">
@@ -66671,7 +66671,7 @@
       </c>
       <c r="AE581" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF581" t="inlineStr">
@@ -66799,7 +66799,7 @@
       </c>
       <c r="AE582" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="AF582" t="inlineStr">
@@ -66911,7 +66911,7 @@
       </c>
       <c r="AE583" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF583" t="inlineStr">
@@ -67023,7 +67023,7 @@
       </c>
       <c r="AE584" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF584" t="inlineStr">
@@ -67151,7 +67151,7 @@
       </c>
       <c r="AE585" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="AF585" t="inlineStr">
@@ -67263,7 +67263,7 @@
       </c>
       <c r="AE586" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF586" t="inlineStr">
@@ -67391,7 +67391,7 @@
       </c>
       <c r="AE587" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="AF587" t="inlineStr">
@@ -67519,7 +67519,7 @@
       </c>
       <c r="AE588" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="AF588" t="inlineStr">
@@ -67631,7 +67631,7 @@
       </c>
       <c r="AE589" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF589" t="inlineStr">
@@ -67743,7 +67743,7 @@
       </c>
       <c r="AE590" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF590" t="inlineStr">
@@ -67853,7 +67853,7 @@
       </c>
       <c r="AE591" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF591" t="inlineStr">
@@ -67965,7 +67965,7 @@
       </c>
       <c r="AE592" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF592" t="inlineStr">
@@ -68075,7 +68075,7 @@
       </c>
       <c r="AE593" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF593" t="inlineStr">
@@ -68185,7 +68185,7 @@
       </c>
       <c r="AE594" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF594" t="inlineStr">
@@ -68297,7 +68297,7 @@
       </c>
       <c r="AE595" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF595" t="inlineStr">
@@ -68409,7 +68409,7 @@
       </c>
       <c r="AE596" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF596" t="inlineStr">
@@ -68521,7 +68521,7 @@
       </c>
       <c r="AE597" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF597" t="inlineStr">
@@ -68631,7 +68631,7 @@
       </c>
       <c r="AE598" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF598" t="inlineStr">
@@ -68741,7 +68741,7 @@
       </c>
       <c r="AE599" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF599" t="inlineStr">
@@ -68853,7 +68853,7 @@
       </c>
       <c r="AE600" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF600" t="inlineStr">
@@ -68965,7 +68965,7 @@
       </c>
       <c r="AE601" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF601" t="inlineStr">
@@ -69075,7 +69075,7 @@
       </c>
       <c r="AE602" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF602" t="inlineStr">
@@ -69187,7 +69187,7 @@
       </c>
       <c r="AE603" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF603" t="inlineStr">
@@ -69297,7 +69297,7 @@
       </c>
       <c r="AE604" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF604" t="inlineStr">
@@ -69397,7 +69397,7 @@
       </c>
       <c r="AE605" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF605" t="inlineStr">
@@ -69507,7 +69507,7 @@
       </c>
       <c r="AE606" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF606" t="inlineStr">
@@ -69619,7 +69619,7 @@
       </c>
       <c r="AE607" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF607" t="inlineStr">
@@ -69729,7 +69729,7 @@
       </c>
       <c r="AE608" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF608" t="inlineStr">
@@ -69841,7 +69841,7 @@
       </c>
       <c r="AE609" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF609" t="inlineStr">
@@ -69951,7 +69951,7 @@
       </c>
       <c r="AE610" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF610" t="inlineStr">
@@ -70061,7 +70061,7 @@
       </c>
       <c r="AE611" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF611" t="inlineStr">
@@ -70171,7 +70171,7 @@
       </c>
       <c r="AE612" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF612" t="inlineStr">
@@ -70281,7 +70281,7 @@
       </c>
       <c r="AE613" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF613" t="inlineStr">
@@ -70391,7 +70391,7 @@
       </c>
       <c r="AE614" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF614" t="inlineStr">
@@ -70503,7 +70503,7 @@
       </c>
       <c r="AE615" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF615" t="inlineStr">
@@ -70613,7 +70613,7 @@
       </c>
       <c r="AE616" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF616" t="inlineStr">
@@ -70723,7 +70723,7 @@
       </c>
       <c r="AE617" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF617" t="inlineStr">
@@ -70833,7 +70833,7 @@
       </c>
       <c r="AE618" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF618" t="inlineStr">
@@ -70945,7 +70945,7 @@
       </c>
       <c r="AE619" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF619" t="inlineStr">
@@ -71055,7 +71055,7 @@
       </c>
       <c r="AE620" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF620" t="inlineStr">
@@ -71167,7 +71167,7 @@
       </c>
       <c r="AE621" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF621" t="inlineStr">
@@ -71279,7 +71279,7 @@
       </c>
       <c r="AE622" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF622" t="inlineStr">
@@ -71379,7 +71379,7 @@
       </c>
       <c r="AE623" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF623" t="inlineStr">
@@ -71489,7 +71489,7 @@
       </c>
       <c r="AE624" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF624" t="inlineStr">
@@ -71601,7 +71601,7 @@
       </c>
       <c r="AE625" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF625" t="inlineStr">
@@ -71713,7 +71713,7 @@
       </c>
       <c r="AE626" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF626" t="inlineStr">
@@ -71825,7 +71825,7 @@
       </c>
       <c r="AE627" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF627" t="inlineStr">
@@ -71937,7 +71937,7 @@
       </c>
       <c r="AE628" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF628" t="inlineStr">
@@ -72047,7 +72047,7 @@
       </c>
       <c r="AE629" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF629" t="inlineStr">
@@ -72157,7 +72157,7 @@
       </c>
       <c r="AE630" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF630" t="inlineStr">
@@ -72269,7 +72269,7 @@
       </c>
       <c r="AE631" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF631" t="inlineStr">
@@ -72379,7 +72379,7 @@
       </c>
       <c r="AE632" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF632" t="inlineStr">
@@ -72491,7 +72491,7 @@
       </c>
       <c r="AE633" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF633" t="inlineStr">
@@ -72591,7 +72591,7 @@
       </c>
       <c r="AE634" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF634" t="inlineStr">
@@ -72701,7 +72701,7 @@
       </c>
       <c r="AE635" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF635" t="inlineStr">
@@ -72813,7 +72813,7 @@
       </c>
       <c r="AE636" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF636" t="inlineStr">
@@ -72923,7 +72923,7 @@
       <c r="AD637" t="inlineStr"/>
       <c r="AE637" t="inlineStr">
         <is>
-          <t>2026-09-18 08:50:17</t>
+          <t>2026-09-18 09:05:55</t>
         </is>
       </c>
       <c r="AF637" t="inlineStr">
@@ -73035,7 +73035,7 @@
       </c>
       <c r="AE638" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF638" t="inlineStr">
@@ -73147,7 +73147,7 @@
       </c>
       <c r="AE639" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF639" t="inlineStr">
@@ -73257,7 +73257,7 @@
       </c>
       <c r="AE640" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF640" t="inlineStr">
@@ -73369,7 +73369,7 @@
       </c>
       <c r="AE641" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF641" t="inlineStr">
@@ -73469,7 +73469,7 @@
       </c>
       <c r="AE642" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF642" t="inlineStr">
@@ -73569,7 +73569,7 @@
       </c>
       <c r="AE643" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF643" t="inlineStr">
@@ -73669,7 +73669,7 @@
       </c>
       <c r="AE644" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF644" t="inlineStr">
@@ -73781,7 +73781,7 @@
       </c>
       <c r="AE645" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF645" t="inlineStr">
@@ -73881,7 +73881,7 @@
       </c>
       <c r="AE646" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF646" t="inlineStr">
@@ -73991,7 +73991,7 @@
       </c>
       <c r="AE647" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF647" t="inlineStr">
@@ -74091,7 +74091,7 @@
       </c>
       <c r="AE648" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF648" t="inlineStr">
@@ -74203,7 +74203,7 @@
       </c>
       <c r="AE649" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF649" t="inlineStr">
@@ -74315,7 +74315,7 @@
       </c>
       <c r="AE650" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF650" t="inlineStr">
@@ -74427,7 +74427,7 @@
       </c>
       <c r="AE651" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF651" t="inlineStr">
@@ -74539,7 +74539,7 @@
       </c>
       <c r="AE652" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF652" t="inlineStr">
@@ -74639,7 +74639,7 @@
       </c>
       <c r="AE653" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF653" t="inlineStr">
@@ -74751,7 +74751,7 @@
       </c>
       <c r="AE654" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF654" t="inlineStr">
@@ -74861,7 +74861,7 @@
       </c>
       <c r="AE655" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF655" t="inlineStr">
@@ -74973,7 +74973,7 @@
       </c>
       <c r="AE656" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF656" t="inlineStr">
@@ -75073,7 +75073,7 @@
       </c>
       <c r="AE657" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF657" t="inlineStr">
@@ -75173,7 +75173,7 @@
       </c>
       <c r="AE658" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF658" t="inlineStr">
@@ -75273,7 +75273,7 @@
       </c>
       <c r="AE659" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF659" t="inlineStr">
@@ -75373,7 +75373,7 @@
       </c>
       <c r="AE660" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF660" t="inlineStr">
@@ -75485,7 +75485,7 @@
       </c>
       <c r="AE661" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF661" t="inlineStr">
@@ -75597,7 +75597,7 @@
       </c>
       <c r="AE662" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF662" t="inlineStr">
@@ -75697,7 +75697,7 @@
       </c>
       <c r="AE663" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF663" t="inlineStr">
@@ -75807,7 +75807,7 @@
       </c>
       <c r="AE664" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF664" t="inlineStr">
@@ -75919,7 +75919,7 @@
       </c>
       <c r="AE665" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF665" t="inlineStr">
@@ -76031,7 +76031,7 @@
       </c>
       <c r="AE666" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF666" t="inlineStr">
@@ -76143,7 +76143,7 @@
       </c>
       <c r="AE667" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF667" t="inlineStr">
@@ -76255,7 +76255,7 @@
       </c>
       <c r="AE668" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF668" t="inlineStr">
@@ -76367,7 +76367,7 @@
       </c>
       <c r="AE669" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF669" t="inlineStr">
@@ -76479,7 +76479,7 @@
       </c>
       <c r="AE670" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF670" t="inlineStr">
@@ -76591,7 +76591,7 @@
       </c>
       <c r="AE671" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF671" t="inlineStr">
@@ -76691,7 +76691,7 @@
       </c>
       <c r="AE672" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF672" t="inlineStr">
@@ -76791,7 +76791,7 @@
       </c>
       <c r="AE673" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF673" t="inlineStr">
@@ -76903,7 +76903,7 @@
       </c>
       <c r="AE674" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:46</t>
+          <t>2026-09-18 09:05:25</t>
         </is>
       </c>
       <c r="AF674" t="inlineStr">
@@ -77003,7 +77003,7 @@
       </c>
       <c r="AE675" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF675" t="inlineStr">
@@ -77103,7 +77103,7 @@
       </c>
       <c r="AE676" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF676" t="inlineStr">
@@ -77203,7 +77203,7 @@
       </c>
       <c r="AE677" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF677" t="inlineStr">
@@ -77313,7 +77313,7 @@
       </c>
       <c r="AE678" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF678" t="inlineStr">
@@ -77413,7 +77413,7 @@
       </c>
       <c r="AE679" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF679" t="inlineStr">
@@ -77523,7 +77523,7 @@
       </c>
       <c r="AE680" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF680" t="inlineStr">
@@ -77605,7 +77605,7 @@
       <c r="AD681" t="inlineStr"/>
       <c r="AE681" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF681" t="inlineStr">
@@ -77687,7 +77687,7 @@
       <c r="AD682" t="inlineStr"/>
       <c r="AE682" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF682" t="inlineStr">
@@ -77769,7 +77769,7 @@
       <c r="AD683" t="inlineStr"/>
       <c r="AE683" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF683" t="inlineStr">
@@ -77851,7 +77851,7 @@
       <c r="AD684" t="inlineStr"/>
       <c r="AE684" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="AF684" t="inlineStr">

--- a/pipeline/credit_rating/output/xhtn_tong_hop_20260918.xlsx
+++ b/pipeline/credit_rating/output/xhtn_tong_hop_20260918.xlsx
@@ -685,7 +685,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1011,7 +1011,7 @@
       <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -1099,7 +1099,7 @@
       <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -1219,7 +1219,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -1555,7 +1555,7 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:55</t>
+          <t>2026-09-18 09:23:05</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -1665,7 +1665,7 @@
       <c r="AD11" t="inlineStr"/>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:55</t>
+          <t>2026-09-18 09:23:05</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:55</t>
+          <t>2026-09-18 09:23:05</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -1891,7 +1891,7 @@
       <c r="AD13" t="inlineStr"/>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:55</t>
+          <t>2026-09-18 09:23:05</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -2019,7 +2019,7 @@
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -2133,7 +2133,7 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -2247,7 +2247,7 @@
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -2367,7 +2367,7 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -2595,7 +2595,7 @@
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -2709,7 +2709,7 @@
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -2825,7 +2825,7 @@
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:55</t>
+          <t>2026-09-18 09:23:05</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -2939,7 +2939,7 @@
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -3049,7 +3049,7 @@
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -3177,7 +3177,7 @@
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
@@ -3291,7 +3291,7 @@
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
@@ -3411,7 +3411,7 @@
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
@@ -3525,7 +3525,7 @@
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
@@ -3635,7 +3635,7 @@
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:55</t>
+          <t>2026-09-18 09:23:05</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
@@ -3861,7 +3861,7 @@
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
@@ -3971,7 +3971,7 @@
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF31" t="inlineStr">
@@ -4095,7 +4095,7 @@
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
@@ -4205,7 +4205,7 @@
       </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF33" t="inlineStr">
@@ -4315,7 +4315,7 @@
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF34" t="inlineStr">
@@ -4425,7 +4425,7 @@
       </c>
       <c r="AE35" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF35" t="inlineStr">
@@ -4525,7 +4525,7 @@
       </c>
       <c r="AE36" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF36" t="inlineStr">
@@ -4635,7 +4635,7 @@
       </c>
       <c r="AE37" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF37" t="inlineStr">
@@ -4745,7 +4745,7 @@
       </c>
       <c r="AE38" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF38" t="inlineStr">
@@ -4855,7 +4855,7 @@
       </c>
       <c r="AE39" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF39" t="inlineStr">
@@ -4987,7 +4987,7 @@
       </c>
       <c r="AE40" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="AF40" t="inlineStr">
@@ -5115,7 +5115,7 @@
       </c>
       <c r="AE41" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="AF41" t="inlineStr">
@@ -5247,7 +5247,7 @@
       </c>
       <c r="AE42" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="AF42" t="inlineStr">
@@ -5375,7 +5375,7 @@
       </c>
       <c r="AE43" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="AF43" t="inlineStr">
@@ -5485,7 +5485,7 @@
       </c>
       <c r="AE44" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF44" t="inlineStr">
@@ -5597,7 +5597,7 @@
       </c>
       <c r="AE45" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF45" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="AE46" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF46" t="inlineStr">
@@ -5827,7 +5827,7 @@
       </c>
       <c r="AE47" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF47" t="inlineStr">
@@ -5943,7 +5943,7 @@
       </c>
       <c r="AE48" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF48" t="inlineStr">
@@ -6043,7 +6043,7 @@
       </c>
       <c r="AE49" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF49" t="inlineStr">
@@ -6157,7 +6157,7 @@
       </c>
       <c r="AE50" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF50" t="inlineStr">
@@ -6273,7 +6273,7 @@
       </c>
       <c r="AE51" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:55</t>
+          <t>2026-09-18 09:23:05</t>
         </is>
       </c>
       <c r="AF51" t="inlineStr">
@@ -6383,7 +6383,7 @@
       </c>
       <c r="AE52" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF52" t="inlineStr">
@@ -6497,7 +6497,7 @@
       </c>
       <c r="AE53" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF53" t="inlineStr">
@@ -6611,7 +6611,7 @@
       </c>
       <c r="AE54" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF54" t="inlineStr">
@@ -6739,7 +6739,7 @@
       </c>
       <c r="AE55" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="AF55" t="inlineStr">
@@ -6855,7 +6855,7 @@
       </c>
       <c r="AE56" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF56" t="inlineStr">
@@ -6951,7 +6951,7 @@
       </c>
       <c r="AE57" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF57" t="inlineStr">
@@ -7061,7 +7061,7 @@
       </c>
       <c r="AE58" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF58" t="inlineStr">
@@ -7161,7 +7161,7 @@
       </c>
       <c r="AE59" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF59" t="inlineStr">
@@ -7275,7 +7275,7 @@
       </c>
       <c r="AE60" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF60" t="inlineStr">
@@ -7389,7 +7389,7 @@
       </c>
       <c r="AE61" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF61" t="inlineStr">
@@ -7489,7 +7489,7 @@
       </c>
       <c r="AE62" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF62" t="inlineStr">
@@ -7603,7 +7603,7 @@
       </c>
       <c r="AE63" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:40</t>
+          <t>2026-09-18 09:22:49</t>
         </is>
       </c>
       <c r="AF63" t="inlineStr">
@@ -7713,7 +7713,7 @@
       </c>
       <c r="AE64" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF64" t="inlineStr">
@@ -7827,7 +7827,7 @@
       </c>
       <c r="AE65" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF65" t="inlineStr">
@@ -7941,7 +7941,7 @@
       </c>
       <c r="AE66" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF66" t="inlineStr">
@@ -8051,7 +8051,7 @@
       </c>
       <c r="AE67" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF67" t="inlineStr">
@@ -8165,7 +8165,7 @@
       </c>
       <c r="AE68" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF68" t="inlineStr">
@@ -8279,7 +8279,7 @@
       </c>
       <c r="AE69" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:40</t>
+          <t>2026-09-18 09:22:49</t>
         </is>
       </c>
       <c r="AF69" t="inlineStr">
@@ -8393,7 +8393,7 @@
       </c>
       <c r="AE70" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:40</t>
+          <t>2026-09-18 09:22:49</t>
         </is>
       </c>
       <c r="AF70" t="inlineStr">
@@ -8517,7 +8517,7 @@
       </c>
       <c r="AE71" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:42</t>
+          <t>2026-09-18 09:22:51</t>
         </is>
       </c>
       <c r="AF71" t="inlineStr">
@@ -8627,7 +8627,7 @@
       </c>
       <c r="AE72" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF72" t="inlineStr">
@@ -8741,7 +8741,7 @@
       </c>
       <c r="AE73" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF73" t="inlineStr">
@@ -8855,7 +8855,7 @@
       </c>
       <c r="AE74" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF74" t="inlineStr">
@@ -8969,7 +8969,7 @@
       </c>
       <c r="AE75" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF75" t="inlineStr">
@@ -9081,7 +9081,7 @@
       </c>
       <c r="AE76" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF76" t="inlineStr">
@@ -9197,7 +9197,7 @@
       </c>
       <c r="AE77" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:55</t>
+          <t>2026-09-18 09:23:05</t>
         </is>
       </c>
       <c r="AF77" t="inlineStr">
@@ -9307,7 +9307,7 @@
       </c>
       <c r="AE78" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF78" t="inlineStr">
@@ -9417,7 +9417,7 @@
       </c>
       <c r="AE79" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF79" t="inlineStr">
@@ -9535,7 +9535,7 @@
       </c>
       <c r="AE80" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:40</t>
+          <t>2026-09-18 09:22:49</t>
         </is>
       </c>
       <c r="AF80" t="inlineStr">
@@ -9659,7 +9659,7 @@
       </c>
       <c r="AE81" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="AF81" t="inlineStr">
@@ -9779,7 +9779,7 @@
       </c>
       <c r="AE82" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="AF82" t="inlineStr">
@@ -9899,7 +9899,7 @@
       </c>
       <c r="AE83" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="AF83" t="inlineStr">
@@ -10031,7 +10031,7 @@
       </c>
       <c r="AE84" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="AF84" t="inlineStr">
@@ -10155,7 +10155,7 @@
       </c>
       <c r="AE85" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF85" t="inlineStr">
@@ -10279,7 +10279,7 @@
       </c>
       <c r="AE86" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF86" t="inlineStr">
@@ -10379,7 +10379,7 @@
       </c>
       <c r="AE87" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF87" t="inlineStr">
@@ -10499,7 +10499,7 @@
       </c>
       <c r="AE88" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="AF88" t="inlineStr">
@@ -10627,7 +10627,7 @@
       </c>
       <c r="AE89" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="AF89" t="inlineStr">
@@ -10741,7 +10741,7 @@
       </c>
       <c r="AE90" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF90" t="inlineStr">
@@ -10855,7 +10855,7 @@
       </c>
       <c r="AE91" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF91" t="inlineStr">
@@ -10969,7 +10969,7 @@
       </c>
       <c r="AE92" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF92" t="inlineStr">
@@ -11079,7 +11079,7 @@
       </c>
       <c r="AE93" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF93" t="inlineStr">
@@ -11193,7 +11193,7 @@
       </c>
       <c r="AE94" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF94" t="inlineStr">
@@ -11307,7 +11307,7 @@
       </c>
       <c r="AE95" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF95" t="inlineStr">
@@ -11421,7 +11421,7 @@
       </c>
       <c r="AE96" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF96" t="inlineStr">
@@ -11535,7 +11535,7 @@
       </c>
       <c r="AE97" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF97" t="inlineStr">
@@ -11655,7 +11655,7 @@
       </c>
       <c r="AE98" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="AF98" t="inlineStr">
@@ -11771,7 +11771,7 @@
       </c>
       <c r="AE99" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:55</t>
+          <t>2026-09-18 09:23:05</t>
         </is>
       </c>
       <c r="AF99" t="inlineStr">
@@ -11881,7 +11881,7 @@
       </c>
       <c r="AE100" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF100" t="inlineStr">
@@ -12001,7 +12001,7 @@
       </c>
       <c r="AE101" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="AF101" t="inlineStr">
@@ -12133,7 +12133,7 @@
       </c>
       <c r="AE102" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="AF102" t="inlineStr">
@@ -12261,7 +12261,7 @@
       </c>
       <c r="AE103" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="AF103" t="inlineStr">
@@ -12373,7 +12373,7 @@
       </c>
       <c r="AE104" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF104" t="inlineStr">
@@ -12483,7 +12483,7 @@
       </c>
       <c r="AE105" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF105" t="inlineStr">
@@ -12593,7 +12593,7 @@
       </c>
       <c r="AE106" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF106" t="inlineStr">
@@ -12703,7 +12703,7 @@
       </c>
       <c r="AE107" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF107" t="inlineStr">
@@ -12817,7 +12817,7 @@
       </c>
       <c r="AE108" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:40</t>
+          <t>2026-09-18 09:22:49</t>
         </is>
       </c>
       <c r="AF108" t="inlineStr">
@@ -12929,7 +12929,7 @@
       </c>
       <c r="AE109" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF109" t="inlineStr">
@@ -13045,7 +13045,7 @@
       </c>
       <c r="AE110" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF110" t="inlineStr">
@@ -13167,7 +13167,7 @@
       <c r="AD111" t="inlineStr"/>
       <c r="AE111" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="AF111" t="inlineStr">
@@ -13279,7 +13279,7 @@
       </c>
       <c r="AE112" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:42</t>
+          <t>2026-09-18 09:22:51</t>
         </is>
       </c>
       <c r="AF112" t="inlineStr">
@@ -13407,7 +13407,7 @@
       </c>
       <c r="AE113" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="AF113" t="inlineStr">
@@ -13527,7 +13527,7 @@
       </c>
       <c r="AE114" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF114" t="inlineStr">
@@ -13647,7 +13647,7 @@
       </c>
       <c r="AE115" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF115" t="inlineStr">
@@ -13757,7 +13757,7 @@
       </c>
       <c r="AE116" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF116" t="inlineStr">
@@ -13873,7 +13873,7 @@
       </c>
       <c r="AE117" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF117" t="inlineStr">
@@ -13985,7 +13985,7 @@
       </c>
       <c r="AE118" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF118" t="inlineStr">
@@ -14095,7 +14095,7 @@
       </c>
       <c r="AE119" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF119" t="inlineStr">
@@ -14205,7 +14205,7 @@
       </c>
       <c r="AE120" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF120" t="inlineStr">
@@ -14329,7 +14329,7 @@
       </c>
       <c r="AE121" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF121" t="inlineStr">
@@ -14445,7 +14445,7 @@
       </c>
       <c r="AE122" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF122" t="inlineStr">
@@ -14565,7 +14565,7 @@
       </c>
       <c r="AE123" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="AF123" t="inlineStr">
@@ -14677,7 +14677,7 @@
       </c>
       <c r="AE124" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF124" t="inlineStr">
@@ -14797,7 +14797,7 @@
       </c>
       <c r="AE125" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF125" t="inlineStr">
@@ -14907,7 +14907,7 @@
       </c>
       <c r="AE126" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF126" t="inlineStr">
@@ -15017,7 +15017,7 @@
       </c>
       <c r="AE127" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF127" t="inlineStr">
@@ -15137,7 +15137,7 @@
       </c>
       <c r="AE128" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="AF128" t="inlineStr">
@@ -15251,7 +15251,7 @@
       </c>
       <c r="AE129" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF129" t="inlineStr">
@@ -15365,7 +15365,7 @@
       </c>
       <c r="AE130" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF130" t="inlineStr">
@@ -15485,7 +15485,7 @@
       </c>
       <c r="AE131" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="AF131" t="inlineStr">
@@ -15595,7 +15595,7 @@
       </c>
       <c r="AE132" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF132" t="inlineStr">
@@ -15711,7 +15711,7 @@
       </c>
       <c r="AE133" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF133" t="inlineStr">
@@ -15823,7 +15823,7 @@
       </c>
       <c r="AE134" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:42</t>
+          <t>2026-09-18 09:22:51</t>
         </is>
       </c>
       <c r="AF134" t="inlineStr">
@@ -15935,7 +15935,7 @@
       </c>
       <c r="AE135" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF135" t="inlineStr">
@@ -16049,7 +16049,7 @@
       </c>
       <c r="AE136" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF136" t="inlineStr">
@@ -16163,7 +16163,7 @@
       </c>
       <c r="AE137" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF137" t="inlineStr">
@@ -16277,7 +16277,7 @@
       </c>
       <c r="AE138" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:40</t>
+          <t>2026-09-18 09:22:49</t>
         </is>
       </c>
       <c r="AF138" t="inlineStr">
@@ -16387,7 +16387,7 @@
       </c>
       <c r="AE139" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF139" t="inlineStr">
@@ -16497,7 +16497,7 @@
       </c>
       <c r="AE140" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF140" t="inlineStr">
@@ -16607,7 +16607,7 @@
       </c>
       <c r="AE141" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF141" t="inlineStr">
@@ -16721,7 +16721,7 @@
       </c>
       <c r="AE142" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF142" t="inlineStr">
@@ -16835,7 +16835,7 @@
       </c>
       <c r="AE143" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF143" t="inlineStr">
@@ -16963,7 +16963,7 @@
       </c>
       <c r="AE144" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="AF144" t="inlineStr">
@@ -17091,7 +17091,7 @@
       </c>
       <c r="AE145" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="AF145" t="inlineStr">
@@ -17201,7 +17201,7 @@
       </c>
       <c r="AE146" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF146" t="inlineStr">
@@ -17311,7 +17311,7 @@
       </c>
       <c r="AE147" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF147" t="inlineStr">
@@ -17431,7 +17431,7 @@
       </c>
       <c r="AE148" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="AF148" t="inlineStr">
@@ -17545,7 +17545,7 @@
       </c>
       <c r="AE149" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF149" t="inlineStr">
@@ -17655,7 +17655,7 @@
       </c>
       <c r="AE150" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF150" t="inlineStr">
@@ -17783,7 +17783,7 @@
       </c>
       <c r="AE151" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="AF151" t="inlineStr">
@@ -17905,7 +17905,7 @@
       <c r="AD152" t="inlineStr"/>
       <c r="AE152" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="AF152" t="inlineStr">
@@ -18033,7 +18033,7 @@
       </c>
       <c r="AE153" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="AF153" t="inlineStr">
@@ -18149,7 +18149,7 @@
       </c>
       <c r="AE154" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:55</t>
+          <t>2026-09-18 09:23:05</t>
         </is>
       </c>
       <c r="AF154" t="inlineStr">
@@ -18277,7 +18277,7 @@
       </c>
       <c r="AE155" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="AF155" t="inlineStr">
@@ -18409,7 +18409,7 @@
       </c>
       <c r="AE156" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="AF156" t="inlineStr">
@@ -18523,7 +18523,7 @@
       </c>
       <c r="AE157" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF157" t="inlineStr">
@@ -18645,7 +18645,7 @@
       <c r="AD158" t="inlineStr"/>
       <c r="AE158" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="AF158" t="inlineStr">
@@ -18757,7 +18757,7 @@
       </c>
       <c r="AE159" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF159" t="inlineStr">
@@ -18857,7 +18857,7 @@
       </c>
       <c r="AE160" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF160" t="inlineStr">
@@ -18967,7 +18967,7 @@
       </c>
       <c r="AE161" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF161" t="inlineStr">
@@ -19083,7 +19083,7 @@
       </c>
       <c r="AE162" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF162" t="inlineStr">
@@ -19199,7 +19199,7 @@
       </c>
       <c r="AE163" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF163" t="inlineStr">
@@ -19327,7 +19327,7 @@
       </c>
       <c r="AE164" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="AF164" t="inlineStr">
@@ -19437,7 +19437,7 @@
       </c>
       <c r="AE165" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF165" t="inlineStr">
@@ -19551,7 +19551,7 @@
       </c>
       <c r="AE166" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF166" t="inlineStr">
@@ -19665,7 +19665,7 @@
       </c>
       <c r="AE167" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF167" t="inlineStr">
@@ -19779,7 +19779,7 @@
       </c>
       <c r="AE168" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF168" t="inlineStr">
@@ -19889,7 +19889,7 @@
       </c>
       <c r="AE169" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF169" t="inlineStr">
@@ -20003,7 +20003,7 @@
       </c>
       <c r="AE170" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF170" t="inlineStr">
@@ -20113,7 +20113,7 @@
       </c>
       <c r="AE171" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF171" t="inlineStr">
@@ -20225,7 +20225,7 @@
       </c>
       <c r="AE172" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF172" t="inlineStr">
@@ -20341,7 +20341,7 @@
       </c>
       <c r="AE173" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:55</t>
+          <t>2026-09-18 09:23:05</t>
         </is>
       </c>
       <c r="AF173" t="inlineStr">
@@ -20457,7 +20457,7 @@
       </c>
       <c r="AE174" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF174" t="inlineStr">
@@ -20569,7 +20569,7 @@
       </c>
       <c r="AE175" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF175" t="inlineStr">
@@ -20681,7 +20681,7 @@
       </c>
       <c r="AE176" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF176" t="inlineStr">
@@ -20809,7 +20809,7 @@
       </c>
       <c r="AE177" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:42</t>
+          <t>2026-09-18 09:22:51</t>
         </is>
       </c>
       <c r="AF177" t="inlineStr">
@@ -20919,7 +20919,7 @@
       </c>
       <c r="AE178" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF178" t="inlineStr">
@@ -21039,7 +21039,7 @@
       </c>
       <c r="AE179" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="AF179" t="inlineStr">
@@ -21161,7 +21161,7 @@
       <c r="AD180" t="inlineStr"/>
       <c r="AE180" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="AF180" t="inlineStr">
@@ -21287,7 +21287,7 @@
       <c r="AD181" t="inlineStr"/>
       <c r="AE181" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="AF181" t="inlineStr">
@@ -21413,7 +21413,7 @@
       <c r="AD182" t="inlineStr"/>
       <c r="AE182" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="AF182" t="inlineStr">
@@ -21529,7 +21529,7 @@
       </c>
       <c r="AE183" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:55</t>
+          <t>2026-09-18 09:23:05</t>
         </is>
       </c>
       <c r="AF183" t="inlineStr">
@@ -21643,7 +21643,7 @@
       </c>
       <c r="AE184" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF184" t="inlineStr">
@@ -21757,7 +21757,7 @@
       </c>
       <c r="AE185" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF185" t="inlineStr">
@@ -21871,7 +21871,7 @@
       </c>
       <c r="AE186" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF186" t="inlineStr">
@@ -21991,7 +21991,7 @@
       </c>
       <c r="AE187" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="AF187" t="inlineStr">
@@ -22111,7 +22111,7 @@
       </c>
       <c r="AE188" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="AF188" t="inlineStr">
@@ -22221,7 +22221,7 @@
       </c>
       <c r="AE189" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF189" t="inlineStr">
@@ -22331,7 +22331,7 @@
       </c>
       <c r="AE190" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF190" t="inlineStr">
@@ -22441,7 +22441,7 @@
       </c>
       <c r="AE191" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF191" t="inlineStr">
@@ -22557,7 +22557,7 @@
       </c>
       <c r="AE192" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF192" t="inlineStr">
@@ -22685,7 +22685,7 @@
       </c>
       <c r="AE193" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="AF193" t="inlineStr">
@@ -22797,7 +22797,7 @@
       </c>
       <c r="AE194" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF194" t="inlineStr">
@@ -22909,7 +22909,7 @@
       </c>
       <c r="AE195" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF195" t="inlineStr">
@@ -23027,7 +23027,7 @@
       </c>
       <c r="AE196" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:40</t>
+          <t>2026-09-18 09:22:49</t>
         </is>
       </c>
       <c r="AF196" t="inlineStr">
@@ -23137,7 +23137,7 @@
       </c>
       <c r="AE197" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF197" t="inlineStr">
@@ -23247,7 +23247,7 @@
       </c>
       <c r="AE198" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF198" t="inlineStr">
@@ -23359,7 +23359,7 @@
       </c>
       <c r="AE199" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF199" t="inlineStr">
@@ -23469,7 +23469,7 @@
       </c>
       <c r="AE200" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF200" t="inlineStr">
@@ -23589,7 +23589,7 @@
       </c>
       <c r="AE201" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="AF201" t="inlineStr">
@@ -23705,7 +23705,7 @@
       </c>
       <c r="AE202" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF202" t="inlineStr">
@@ -23821,7 +23821,7 @@
       </c>
       <c r="AE203" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF203" t="inlineStr">
@@ -23949,7 +23949,7 @@
       </c>
       <c r="AE204" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="AF204" t="inlineStr">
@@ -24061,7 +24061,7 @@
       </c>
       <c r="AE205" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF205" t="inlineStr">
@@ -24173,7 +24173,7 @@
       </c>
       <c r="AE206" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF206" t="inlineStr">
@@ -24285,7 +24285,7 @@
       </c>
       <c r="AE207" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF207" t="inlineStr">
@@ -24401,7 +24401,7 @@
       </c>
       <c r="AE208" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF208" t="inlineStr">
@@ -24511,7 +24511,7 @@
       </c>
       <c r="AE209" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF209" t="inlineStr">
@@ -24631,7 +24631,7 @@
       </c>
       <c r="AE210" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="AF210" t="inlineStr">
@@ -24741,7 +24741,7 @@
       </c>
       <c r="AE211" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF211" t="inlineStr">
@@ -24861,7 +24861,7 @@
       </c>
       <c r="AE212" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="AF212" t="inlineStr">
@@ -24971,7 +24971,7 @@
       </c>
       <c r="AE213" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF213" t="inlineStr">
@@ -25085,7 +25085,7 @@
       </c>
       <c r="AE214" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:40</t>
+          <t>2026-09-18 09:22:49</t>
         </is>
       </c>
       <c r="AF214" t="inlineStr">
@@ -25195,7 +25195,7 @@
       </c>
       <c r="AE215" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF215" t="inlineStr">
@@ -25305,7 +25305,7 @@
       </c>
       <c r="AE216" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF216" t="inlineStr">
@@ -25419,7 +25419,7 @@
       </c>
       <c r="AE217" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF217" t="inlineStr">
@@ -25529,7 +25529,7 @@
       </c>
       <c r="AE218" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF218" t="inlineStr">
@@ -25641,7 +25641,7 @@
       </c>
       <c r="AE219" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF219" t="inlineStr">
@@ -25751,7 +25751,7 @@
       </c>
       <c r="AE220" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF220" t="inlineStr">
@@ -25871,7 +25871,7 @@
       </c>
       <c r="AE221" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="AF221" t="inlineStr">
@@ -25983,7 +25983,7 @@
       </c>
       <c r="AE222" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF222" t="inlineStr">
@@ -26093,7 +26093,7 @@
       </c>
       <c r="AE223" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF223" t="inlineStr">
@@ -26217,7 +26217,7 @@
       </c>
       <c r="AE224" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:42</t>
+          <t>2026-09-18 09:22:51</t>
         </is>
       </c>
       <c r="AF224" t="inlineStr">
@@ -26341,7 +26341,7 @@
       </c>
       <c r="AE225" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:42</t>
+          <t>2026-09-18 09:22:51</t>
         </is>
       </c>
       <c r="AF225" t="inlineStr">
@@ -26451,7 +26451,7 @@
       </c>
       <c r="AE226" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF226" t="inlineStr">
@@ -26561,7 +26561,7 @@
       </c>
       <c r="AE227" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF227" t="inlineStr">
@@ -26671,7 +26671,7 @@
       </c>
       <c r="AE228" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF228" t="inlineStr">
@@ -26783,7 +26783,7 @@
       </c>
       <c r="AE229" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF229" t="inlineStr">
@@ -26893,7 +26893,7 @@
       </c>
       <c r="AE230" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF230" t="inlineStr">
@@ -27003,7 +27003,7 @@
       </c>
       <c r="AE231" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF231" t="inlineStr">
@@ -27131,7 +27131,7 @@
       </c>
       <c r="AE232" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="AF232" t="inlineStr">
@@ -27237,7 +27237,7 @@
       </c>
       <c r="AE233" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF233" t="inlineStr">
@@ -27349,7 +27349,7 @@
       </c>
       <c r="AE234" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF234" t="inlineStr">
@@ -27465,7 +27465,7 @@
       </c>
       <c r="AE235" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:55</t>
+          <t>2026-09-18 09:23:05</t>
         </is>
       </c>
       <c r="AF235" t="inlineStr">
@@ -27581,7 +27581,7 @@
       </c>
       <c r="AE236" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:55</t>
+          <t>2026-09-18 09:23:05</t>
         </is>
       </c>
       <c r="AF236" t="inlineStr">
@@ -27691,7 +27691,7 @@
       </c>
       <c r="AE237" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF237" t="inlineStr">
@@ -27801,7 +27801,7 @@
       </c>
       <c r="AE238" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF238" t="inlineStr">
@@ -27917,7 +27917,7 @@
       </c>
       <c r="AE239" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:55</t>
+          <t>2026-09-18 09:23:05</t>
         </is>
       </c>
       <c r="AF239" t="inlineStr">
@@ -28033,7 +28033,7 @@
       </c>
       <c r="AE240" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:55</t>
+          <t>2026-09-18 09:23:05</t>
         </is>
       </c>
       <c r="AF240" t="inlineStr">
@@ -28143,7 +28143,7 @@
       </c>
       <c r="AE241" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF241" t="inlineStr">
@@ -28259,7 +28259,7 @@
       </c>
       <c r="AE242" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:55</t>
+          <t>2026-09-18 09:23:05</t>
         </is>
       </c>
       <c r="AF242" t="inlineStr">
@@ -28375,7 +28375,7 @@
       </c>
       <c r="AE243" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:55</t>
+          <t>2026-09-18 09:23:05</t>
         </is>
       </c>
       <c r="AF243" t="inlineStr">
@@ -28485,7 +28485,7 @@
       </c>
       <c r="AE244" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF244" t="inlineStr">
@@ -28595,7 +28595,7 @@
       </c>
       <c r="AE245" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF245" t="inlineStr">
@@ -28705,7 +28705,7 @@
       </c>
       <c r="AE246" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF246" t="inlineStr">
@@ -28805,7 +28805,7 @@
       </c>
       <c r="AE247" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF247" t="inlineStr">
@@ -28921,7 +28921,7 @@
       </c>
       <c r="AE248" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:55</t>
+          <t>2026-09-18 09:23:05</t>
         </is>
       </c>
       <c r="AF248" t="inlineStr">
@@ -29031,7 +29031,7 @@
       </c>
       <c r="AE249" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF249" t="inlineStr">
@@ -29143,7 +29143,7 @@
       </c>
       <c r="AE250" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF250" t="inlineStr">
@@ -29253,7 +29253,7 @@
       </c>
       <c r="AE251" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF251" t="inlineStr">
@@ -29373,7 +29373,7 @@
       </c>
       <c r="AE252" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="AF252" t="inlineStr">
@@ -29485,7 +29485,7 @@
       </c>
       <c r="AE253" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF253" t="inlineStr">
@@ -29595,7 +29595,7 @@
       </c>
       <c r="AE254" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF254" t="inlineStr">
@@ -29707,7 +29707,7 @@
       </c>
       <c r="AE255" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF255" t="inlineStr">
@@ -29823,7 +29823,7 @@
       </c>
       <c r="AE256" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF256" t="inlineStr">
@@ -29935,7 +29935,7 @@
       </c>
       <c r="AE257" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF257" t="inlineStr">
@@ -30045,7 +30045,7 @@
       </c>
       <c r="AE258" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF258" t="inlineStr">
@@ -30161,7 +30161,7 @@
       </c>
       <c r="AE259" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF259" t="inlineStr">
@@ -30271,7 +30271,7 @@
       </c>
       <c r="AE260" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF260" t="inlineStr">
@@ -30397,7 +30397,7 @@
       <c r="AD261" t="inlineStr"/>
       <c r="AE261" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="AF261" t="inlineStr">
@@ -30525,7 +30525,7 @@
       </c>
       <c r="AE262" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="AF262" t="inlineStr">
@@ -30637,7 +30637,7 @@
       </c>
       <c r="AE263" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF263" t="inlineStr">
@@ -30737,7 +30737,7 @@
       </c>
       <c r="AE264" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF264" t="inlineStr">
@@ -30837,7 +30837,7 @@
       </c>
       <c r="AE265" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF265" t="inlineStr">
@@ -30951,7 +30951,7 @@
       </c>
       <c r="AE266" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF266" t="inlineStr">
@@ -31065,7 +31065,7 @@
       </c>
       <c r="AE267" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF267" t="inlineStr">
@@ -31165,7 +31165,7 @@
       </c>
       <c r="AE268" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF268" t="inlineStr">
@@ -31285,7 +31285,7 @@
       </c>
       <c r="AE269" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="AF269" t="inlineStr">
@@ -31397,7 +31397,7 @@
       </c>
       <c r="AE270" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF270" t="inlineStr">
@@ -31509,7 +31509,7 @@
       </c>
       <c r="AE271" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF271" t="inlineStr">
@@ -31623,7 +31623,7 @@
       </c>
       <c r="AE272" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF272" t="inlineStr">
@@ -31737,7 +31737,7 @@
       </c>
       <c r="AE273" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:40</t>
+          <t>2026-09-18 09:22:49</t>
         </is>
       </c>
       <c r="AF273" t="inlineStr">
@@ -31851,7 +31851,7 @@
       </c>
       <c r="AE274" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:40</t>
+          <t>2026-09-18 09:22:49</t>
         </is>
       </c>
       <c r="AF274" t="inlineStr">
@@ -31983,7 +31983,7 @@
       </c>
       <c r="AE275" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="AF275" t="inlineStr">
@@ -32111,7 +32111,7 @@
       </c>
       <c r="AE276" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="AF276" t="inlineStr">
@@ -32239,7 +32239,7 @@
       </c>
       <c r="AE277" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="AF277" t="inlineStr">
@@ -32367,7 +32367,7 @@
       </c>
       <c r="AE278" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="AF278" t="inlineStr">
@@ -32479,7 +32479,7 @@
       </c>
       <c r="AE279" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF279" t="inlineStr">
@@ -32591,7 +32591,7 @@
       </c>
       <c r="AE280" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF280" t="inlineStr">
@@ -32701,7 +32701,7 @@
       </c>
       <c r="AE281" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF281" t="inlineStr">
@@ -32811,7 +32811,7 @@
       </c>
       <c r="AE282" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF282" t="inlineStr">
@@ -32939,7 +32939,7 @@
       </c>
       <c r="AE283" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="AF283" t="inlineStr">
@@ -33049,7 +33049,7 @@
       </c>
       <c r="AE284" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF284" t="inlineStr">
@@ -33177,7 +33177,7 @@
       </c>
       <c r="AE285" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="AF285" t="inlineStr">
@@ -33289,7 +33289,7 @@
       </c>
       <c r="AE286" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF286" t="inlineStr">
@@ -33401,7 +33401,7 @@
       </c>
       <c r="AE287" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF287" t="inlineStr">
@@ -33511,7 +33511,7 @@
       </c>
       <c r="AE288" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF288" t="inlineStr">
@@ -33631,7 +33631,7 @@
       </c>
       <c r="AE289" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="AF289" t="inlineStr">
@@ -33755,7 +33755,7 @@
       </c>
       <c r="AE290" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="AF290" t="inlineStr">
@@ -33879,7 +33879,7 @@
       </c>
       <c r="AE291" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="AF291" t="inlineStr">
@@ -34003,7 +34003,7 @@
       </c>
       <c r="AE292" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="AF292" t="inlineStr">
@@ -34115,7 +34115,7 @@
       </c>
       <c r="AE293" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF293" t="inlineStr">
@@ -34231,7 +34231,7 @@
       </c>
       <c r="AE294" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF294" t="inlineStr">
@@ -34343,7 +34343,7 @@
       </c>
       <c r="AE295" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:42</t>
+          <t>2026-09-18 09:22:51</t>
         </is>
       </c>
       <c r="AF295" t="inlineStr">
@@ -34471,7 +34471,7 @@
       </c>
       <c r="AE296" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:42</t>
+          <t>2026-09-18 09:22:51</t>
         </is>
       </c>
       <c r="AF296" t="inlineStr">
@@ -34599,7 +34599,7 @@
       </c>
       <c r="AE297" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="AF297" t="inlineStr">
@@ -34711,7 +34711,7 @@
       </c>
       <c r="AE298" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF298" t="inlineStr">
@@ -34823,7 +34823,7 @@
       </c>
       <c r="AE299" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF299" t="inlineStr">
@@ -34933,7 +34933,7 @@
       </c>
       <c r="AE300" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF300" t="inlineStr">
@@ -35043,7 +35043,7 @@
       </c>
       <c r="AE301" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF301" t="inlineStr">
@@ -35159,7 +35159,7 @@
       </c>
       <c r="AE302" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF302" t="inlineStr">
@@ -35271,7 +35271,7 @@
       </c>
       <c r="AE303" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF303" t="inlineStr">
@@ -35391,7 +35391,7 @@
       </c>
       <c r="AE304" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="AF304" t="inlineStr">
@@ -35519,7 +35519,7 @@
       </c>
       <c r="AE305" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="AF305" t="inlineStr">
@@ -35635,7 +35635,7 @@
       </c>
       <c r="AE306" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF306" t="inlineStr">
@@ -35735,7 +35735,7 @@
       </c>
       <c r="AE307" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF307" t="inlineStr">
@@ -35847,7 +35847,7 @@
       </c>
       <c r="AE308" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF308" t="inlineStr">
@@ -35975,7 +35975,7 @@
       </c>
       <c r="AE309" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="AF309" t="inlineStr">
@@ -36099,7 +36099,7 @@
       </c>
       <c r="AE310" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:42</t>
+          <t>2026-09-18 09:22:51</t>
         </is>
       </c>
       <c r="AF310" t="inlineStr">
@@ -36211,7 +36211,7 @@
       </c>
       <c r="AE311" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF311" t="inlineStr">
@@ -36321,7 +36321,7 @@
       </c>
       <c r="AE312" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF312" t="inlineStr">
@@ -36431,7 +36431,7 @@
       </c>
       <c r="AE313" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF313" t="inlineStr">
@@ -36541,7 +36541,7 @@
       </c>
       <c r="AE314" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF314" t="inlineStr">
@@ -36651,7 +36651,7 @@
       </c>
       <c r="AE315" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF315" t="inlineStr">
@@ -36771,7 +36771,7 @@
       </c>
       <c r="AE316" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="AF316" t="inlineStr">
@@ -36881,7 +36881,7 @@
       </c>
       <c r="AE317" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF317" t="inlineStr">
@@ -36991,7 +36991,7 @@
       </c>
       <c r="AE318" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF318" t="inlineStr">
@@ -37101,7 +37101,7 @@
       </c>
       <c r="AE319" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF319" t="inlineStr">
@@ -37221,7 +37221,7 @@
       </c>
       <c r="AE320" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="AF320" t="inlineStr">
@@ -37341,7 +37341,7 @@
       </c>
       <c r="AE321" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="AF321" t="inlineStr">
@@ -37461,7 +37461,7 @@
       </c>
       <c r="AE322" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="AF322" t="inlineStr">
@@ -37581,7 +37581,7 @@
       </c>
       <c r="AE323" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="AF323" t="inlineStr">
@@ -37697,7 +37697,7 @@
       </c>
       <c r="AE324" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:55</t>
+          <t>2026-09-18 09:23:05</t>
         </is>
       </c>
       <c r="AF324" t="inlineStr">
@@ -37813,7 +37813,7 @@
       </c>
       <c r="AE325" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:55</t>
+          <t>2026-09-18 09:23:05</t>
         </is>
       </c>
       <c r="AF325" t="inlineStr">
@@ -37929,7 +37929,7 @@
       </c>
       <c r="AE326" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:55</t>
+          <t>2026-09-18 09:23:05</t>
         </is>
       </c>
       <c r="AF326" t="inlineStr">
@@ -38041,7 +38041,7 @@
       </c>
       <c r="AE327" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF327" t="inlineStr">
@@ -38157,7 +38157,7 @@
       </c>
       <c r="AE328" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:55</t>
+          <t>2026-09-18 09:23:05</t>
         </is>
       </c>
       <c r="AF328" t="inlineStr">
@@ -38277,7 +38277,7 @@
       </c>
       <c r="AE329" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="AF329" t="inlineStr">
@@ -38389,7 +38389,7 @@
       </c>
       <c r="AE330" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF330" t="inlineStr">
@@ -38505,7 +38505,7 @@
       </c>
       <c r="AE331" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:55</t>
+          <t>2026-09-18 09:23:05</t>
         </is>
       </c>
       <c r="AF331" t="inlineStr">
@@ -38621,7 +38621,7 @@
       </c>
       <c r="AE332" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:55</t>
+          <t>2026-09-18 09:23:05</t>
         </is>
       </c>
       <c r="AF332" t="inlineStr">
@@ -38737,7 +38737,7 @@
       </c>
       <c r="AE333" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:55</t>
+          <t>2026-09-18 09:23:05</t>
         </is>
       </c>
       <c r="AF333" t="inlineStr">
@@ -38853,7 +38853,7 @@
       </c>
       <c r="AE334" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:55</t>
+          <t>2026-09-18 09:23:05</t>
         </is>
       </c>
       <c r="AF334" t="inlineStr">
@@ -38967,7 +38967,7 @@
       </c>
       <c r="AE335" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:40</t>
+          <t>2026-09-18 09:22:49</t>
         </is>
       </c>
       <c r="AF335" t="inlineStr">
@@ -39083,7 +39083,7 @@
       </c>
       <c r="AE336" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:55</t>
+          <t>2026-09-18 09:23:05</t>
         </is>
       </c>
       <c r="AF336" t="inlineStr">
@@ -39199,7 +39199,7 @@
       </c>
       <c r="AE337" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:55</t>
+          <t>2026-09-18 09:23:05</t>
         </is>
       </c>
       <c r="AF337" t="inlineStr">
@@ -39315,7 +39315,7 @@
       </c>
       <c r="AE338" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:55</t>
+          <t>2026-09-18 09:23:05</t>
         </is>
       </c>
       <c r="AF338" t="inlineStr">
@@ -39425,7 +39425,7 @@
       </c>
       <c r="AE339" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF339" t="inlineStr">
@@ -39541,7 +39541,7 @@
       </c>
       <c r="AE340" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF340" t="inlineStr">
@@ -39653,7 +39653,7 @@
       </c>
       <c r="AE341" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF341" t="inlineStr">
@@ -39763,7 +39763,7 @@
       </c>
       <c r="AE342" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF342" t="inlineStr">
@@ -39875,7 +39875,7 @@
       </c>
       <c r="AE343" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF343" t="inlineStr">
@@ -39987,7 +39987,7 @@
       </c>
       <c r="AE344" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF344" t="inlineStr">
@@ -40099,7 +40099,7 @@
       </c>
       <c r="AE345" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF345" t="inlineStr">
@@ -40219,7 +40219,7 @@
       </c>
       <c r="AE346" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="AF346" t="inlineStr">
@@ -40347,7 +40347,7 @@
       </c>
       <c r="AE347" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="AF347" t="inlineStr">
@@ -40467,7 +40467,7 @@
       </c>
       <c r="AE348" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="AF348" t="inlineStr">
@@ -40595,7 +40595,7 @@
       </c>
       <c r="AE349" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="AF349" t="inlineStr">
@@ -40707,7 +40707,7 @@
       </c>
       <c r="AE350" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF350" t="inlineStr">
@@ -40817,7 +40817,7 @@
       </c>
       <c r="AE351" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF351" t="inlineStr">
@@ -40927,7 +40927,7 @@
       </c>
       <c r="AE352" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF352" t="inlineStr">
@@ -41039,7 +41039,7 @@
       </c>
       <c r="AE353" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF353" t="inlineStr">
@@ -41151,7 +41151,7 @@
       </c>
       <c r="AE354" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF354" t="inlineStr">
@@ -41261,7 +41261,7 @@
       </c>
       <c r="AE355" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF355" t="inlineStr">
@@ -41377,7 +41377,7 @@
       </c>
       <c r="AE356" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF356" t="inlineStr">
@@ -41487,7 +41487,7 @@
       </c>
       <c r="AE357" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF357" t="inlineStr">
@@ -41599,7 +41599,7 @@
       </c>
       <c r="AE358" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF358" t="inlineStr">
@@ -41709,7 +41709,7 @@
       </c>
       <c r="AE359" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF359" t="inlineStr">
@@ -41819,7 +41819,7 @@
       </c>
       <c r="AE360" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF360" t="inlineStr">
@@ -41947,7 +41947,7 @@
       </c>
       <c r="AE361" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="AF361" t="inlineStr">
@@ -42059,7 +42059,7 @@
       </c>
       <c r="AE362" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF362" t="inlineStr">
@@ -42187,7 +42187,7 @@
       </c>
       <c r="AE363" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="AF363" t="inlineStr">
@@ -42299,7 +42299,7 @@
       </c>
       <c r="AE364" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF364" t="inlineStr">
@@ -42409,7 +42409,7 @@
       </c>
       <c r="AE365" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF365" t="inlineStr">
@@ -42519,7 +42519,7 @@
       </c>
       <c r="AE366" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF366" t="inlineStr">
@@ -42629,7 +42629,7 @@
       </c>
       <c r="AE367" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF367" t="inlineStr">
@@ -42741,7 +42741,7 @@
       </c>
       <c r="AE368" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF368" t="inlineStr">
@@ -42851,7 +42851,7 @@
       </c>
       <c r="AE369" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF369" t="inlineStr">
@@ -42979,7 +42979,7 @@
       </c>
       <c r="AE370" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="AF370" t="inlineStr">
@@ -43091,7 +43091,7 @@
       </c>
       <c r="AE371" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF371" t="inlineStr">
@@ -43201,7 +43201,7 @@
       </c>
       <c r="AE372" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF372" t="inlineStr">
@@ -43311,7 +43311,7 @@
       </c>
       <c r="AE373" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF373" t="inlineStr">
@@ -43421,7 +43421,7 @@
       </c>
       <c r="AE374" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF374" t="inlineStr">
@@ -43531,7 +43531,7 @@
       </c>
       <c r="AE375" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF375" t="inlineStr">
@@ -43641,7 +43641,7 @@
       </c>
       <c r="AE376" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF376" t="inlineStr">
@@ -43753,7 +43753,7 @@
       </c>
       <c r="AE377" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF377" t="inlineStr">
@@ -43881,7 +43881,7 @@
       </c>
       <c r="AE378" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="AF378" t="inlineStr">
@@ -43991,7 +43991,7 @@
       </c>
       <c r="AE379" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF379" t="inlineStr">
@@ -44101,7 +44101,7 @@
       </c>
       <c r="AE380" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF380" t="inlineStr">
@@ -44213,7 +44213,7 @@
       </c>
       <c r="AE381" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:42</t>
+          <t>2026-09-18 09:22:51</t>
         </is>
       </c>
       <c r="AF381" t="inlineStr">
@@ -44323,7 +44323,7 @@
       </c>
       <c r="AE382" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF382" t="inlineStr">
@@ -44435,7 +44435,7 @@
       </c>
       <c r="AE383" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF383" t="inlineStr">
@@ -44563,7 +44563,7 @@
       </c>
       <c r="AE384" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="AF384" t="inlineStr">
@@ -44673,7 +44673,7 @@
       </c>
       <c r="AE385" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF385" t="inlineStr">
@@ -44785,7 +44785,7 @@
       </c>
       <c r="AE386" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF386" t="inlineStr">
@@ -44895,7 +44895,7 @@
       </c>
       <c r="AE387" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF387" t="inlineStr">
@@ -45005,7 +45005,7 @@
       </c>
       <c r="AE388" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF388" t="inlineStr">
@@ -45115,7 +45115,7 @@
       </c>
       <c r="AE389" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF389" t="inlineStr">
@@ -45215,7 +45215,7 @@
       </c>
       <c r="AE390" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF390" t="inlineStr">
@@ -45325,7 +45325,7 @@
       </c>
       <c r="AE391" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF391" t="inlineStr">
@@ -45425,7 +45425,7 @@
       </c>
       <c r="AE392" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF392" t="inlineStr">
@@ -45535,7 +45535,7 @@
       </c>
       <c r="AE393" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF393" t="inlineStr">
@@ -45663,7 +45663,7 @@
       </c>
       <c r="AE394" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="AF394" t="inlineStr">
@@ -45773,7 +45773,7 @@
       </c>
       <c r="AE395" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF395" t="inlineStr">
@@ -45883,7 +45883,7 @@
       </c>
       <c r="AE396" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF396" t="inlineStr">
@@ -45993,7 +45993,7 @@
       </c>
       <c r="AE397" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF397" t="inlineStr">
@@ -46103,7 +46103,7 @@
       </c>
       <c r="AE398" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF398" t="inlineStr">
@@ -46213,7 +46213,7 @@
       </c>
       <c r="AE399" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF399" t="inlineStr">
@@ -46323,7 +46323,7 @@
       </c>
       <c r="AE400" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF400" t="inlineStr">
@@ -46433,7 +46433,7 @@
       </c>
       <c r="AE401" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF401" t="inlineStr">
@@ -46543,7 +46543,7 @@
       </c>
       <c r="AE402" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF402" t="inlineStr">
@@ -46671,7 +46671,7 @@
       </c>
       <c r="AE403" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="AF403" t="inlineStr">
@@ -46783,7 +46783,7 @@
       </c>
       <c r="AE404" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF404" t="inlineStr">
@@ -46883,7 +46883,7 @@
       </c>
       <c r="AE405" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF405" t="inlineStr">
@@ -46993,7 +46993,7 @@
       </c>
       <c r="AE406" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF406" t="inlineStr">
@@ -47107,7 +47107,7 @@
       </c>
       <c r="AE407" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF407" t="inlineStr">
@@ -47217,7 +47217,7 @@
       </c>
       <c r="AE408" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF408" t="inlineStr">
@@ -47317,7 +47317,7 @@
       </c>
       <c r="AE409" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF409" t="inlineStr">
@@ -47429,7 +47429,7 @@
       </c>
       <c r="AE410" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF410" t="inlineStr">
@@ -47541,7 +47541,7 @@
       </c>
       <c r="AE411" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF411" t="inlineStr">
@@ -47651,7 +47651,7 @@
       </c>
       <c r="AE412" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF412" t="inlineStr">
@@ -47763,7 +47763,7 @@
       </c>
       <c r="AE413" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF413" t="inlineStr">
@@ -47875,7 +47875,7 @@
       </c>
       <c r="AE414" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF414" t="inlineStr">
@@ -47985,7 +47985,7 @@
       </c>
       <c r="AE415" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF415" t="inlineStr">
@@ -48113,7 +48113,7 @@
       </c>
       <c r="AE416" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="AF416" t="inlineStr">
@@ -48245,7 +48245,7 @@
       </c>
       <c r="AE417" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="AF417" t="inlineStr">
@@ -48377,7 +48377,7 @@
       </c>
       <c r="AE418" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="AF418" t="inlineStr">
@@ -48509,7 +48509,7 @@
       </c>
       <c r="AE419" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="AF419" t="inlineStr">
@@ -48633,7 +48633,7 @@
       </c>
       <c r="AE420" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:42</t>
+          <t>2026-09-18 09:22:51</t>
         </is>
       </c>
       <c r="AF420" t="inlineStr">
@@ -48745,7 +48745,7 @@
       </c>
       <c r="AE421" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF421" t="inlineStr">
@@ -48845,7 +48845,7 @@
       </c>
       <c r="AE422" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF422" t="inlineStr">
@@ -48965,7 +48965,7 @@
       </c>
       <c r="AE423" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="AF423" t="inlineStr">
@@ -49081,7 +49081,7 @@
       </c>
       <c r="AE424" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF424" t="inlineStr">
@@ -49193,7 +49193,7 @@
       </c>
       <c r="AE425" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF425" t="inlineStr">
@@ -49315,7 +49315,7 @@
       <c r="AD426" t="inlineStr"/>
       <c r="AE426" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="AF426" t="inlineStr">
@@ -49427,7 +49427,7 @@
       </c>
       <c r="AE427" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF427" t="inlineStr">
@@ -49537,7 +49537,7 @@
       </c>
       <c r="AE428" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF428" t="inlineStr">
@@ -49647,7 +49647,7 @@
       </c>
       <c r="AE429" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF429" t="inlineStr">
@@ -49757,7 +49757,7 @@
       </c>
       <c r="AE430" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF430" t="inlineStr">
@@ -49867,7 +49867,7 @@
       </c>
       <c r="AE431" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF431" t="inlineStr">
@@ -49995,7 +49995,7 @@
       </c>
       <c r="AE432" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="AF432" t="inlineStr">
@@ -50111,7 +50111,7 @@
       </c>
       <c r="AE433" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF433" t="inlineStr">
@@ -50221,7 +50221,7 @@
       </c>
       <c r="AE434" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF434" t="inlineStr">
@@ -50349,7 +50349,7 @@
       </c>
       <c r="AE435" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="AF435" t="inlineStr">
@@ -50477,7 +50477,7 @@
       </c>
       <c r="AE436" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="AF436" t="inlineStr">
@@ -50605,7 +50605,7 @@
       </c>
       <c r="AE437" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="AF437" t="inlineStr">
@@ -50733,7 +50733,7 @@
       </c>
       <c r="AE438" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="AF438" t="inlineStr">
@@ -50845,7 +50845,7 @@
       </c>
       <c r="AE439" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF439" t="inlineStr">
@@ -50955,7 +50955,7 @@
       </c>
       <c r="AE440" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF440" t="inlineStr">
@@ -51083,7 +51083,7 @@
       </c>
       <c r="AE441" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="AF441" t="inlineStr">
@@ -51195,7 +51195,7 @@
       </c>
       <c r="AE442" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF442" t="inlineStr">
@@ -51307,7 +51307,7 @@
       </c>
       <c r="AE443" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF443" t="inlineStr">
@@ -51423,7 +51423,7 @@
       </c>
       <c r="AE444" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF444" t="inlineStr">
@@ -51535,7 +51535,7 @@
       </c>
       <c r="AE445" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF445" t="inlineStr">
@@ -51647,7 +51647,7 @@
       </c>
       <c r="AE446" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF446" t="inlineStr">
@@ -51759,7 +51759,7 @@
       </c>
       <c r="AE447" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF447" t="inlineStr">
@@ -51871,7 +51871,7 @@
       </c>
       <c r="AE448" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF448" t="inlineStr">
@@ -51991,7 +51991,7 @@
       </c>
       <c r="AE449" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="AF449" t="inlineStr">
@@ -52101,7 +52101,7 @@
       </c>
       <c r="AE450" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF450" t="inlineStr">
@@ -52229,7 +52229,7 @@
       </c>
       <c r="AE451" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="AF451" t="inlineStr">
@@ -52349,7 +52349,7 @@
       </c>
       <c r="AE452" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="AF452" t="inlineStr">
@@ -52461,7 +52461,7 @@
       </c>
       <c r="AE453" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF453" t="inlineStr">
@@ -52573,7 +52573,7 @@
       </c>
       <c r="AE454" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF454" t="inlineStr">
@@ -52673,7 +52673,7 @@
       </c>
       <c r="AE455" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF455" t="inlineStr">
@@ -52789,7 +52789,7 @@
       </c>
       <c r="AE456" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF456" t="inlineStr">
@@ -52899,7 +52899,7 @@
       </c>
       <c r="AE457" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF457" t="inlineStr">
@@ -53011,7 +53011,7 @@
       </c>
       <c r="AE458" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF458" t="inlineStr">
@@ -53121,7 +53121,7 @@
       </c>
       <c r="AE459" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF459" t="inlineStr">
@@ -53233,7 +53233,7 @@
       </c>
       <c r="AE460" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF460" t="inlineStr">
@@ -53345,7 +53345,7 @@
       </c>
       <c r="AE461" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF461" t="inlineStr">
@@ -53445,7 +53445,7 @@
       </c>
       <c r="AE462" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF462" t="inlineStr">
@@ -53555,7 +53555,7 @@
       </c>
       <c r="AE463" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF463" t="inlineStr">
@@ -53667,7 +53667,7 @@
       </c>
       <c r="AE464" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF464" t="inlineStr">
@@ -53777,7 +53777,7 @@
       </c>
       <c r="AE465" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF465" t="inlineStr">
@@ -53887,7 +53887,7 @@
       </c>
       <c r="AE466" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF466" t="inlineStr">
@@ -53999,7 +53999,7 @@
       </c>
       <c r="AE467" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF467" t="inlineStr">
@@ -54109,7 +54109,7 @@
       </c>
       <c r="AE468" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF468" t="inlineStr">
@@ -54219,7 +54219,7 @@
       </c>
       <c r="AE469" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF469" t="inlineStr">
@@ -54329,7 +54329,7 @@
       </c>
       <c r="AE470" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF470" t="inlineStr">
@@ -54449,7 +54449,7 @@
       </c>
       <c r="AE471" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="AF471" t="inlineStr">
@@ -54573,7 +54573,7 @@
       </c>
       <c r="AE472" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:42</t>
+          <t>2026-09-18 09:22:51</t>
         </is>
       </c>
       <c r="AF472" t="inlineStr">
@@ -54683,7 +54683,7 @@
       </c>
       <c r="AE473" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF473" t="inlineStr">
@@ -54795,7 +54795,7 @@
       </c>
       <c r="AE474" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF474" t="inlineStr">
@@ -54905,7 +54905,7 @@
       </c>
       <c r="AE475" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF475" t="inlineStr">
@@ -55017,7 +55017,7 @@
       </c>
       <c r="AE476" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF476" t="inlineStr">
@@ -55129,7 +55129,7 @@
       </c>
       <c r="AE477" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF477" t="inlineStr">
@@ -55239,7 +55239,7 @@
       </c>
       <c r="AE478" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF478" t="inlineStr">
@@ -55349,7 +55349,7 @@
       </c>
       <c r="AE479" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF479" t="inlineStr">
@@ -55459,7 +55459,7 @@
       </c>
       <c r="AE480" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF480" t="inlineStr">
@@ -55569,7 +55569,7 @@
       </c>
       <c r="AE481" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF481" t="inlineStr">
@@ -55679,7 +55679,7 @@
       </c>
       <c r="AE482" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF482" t="inlineStr">
@@ -55789,7 +55789,7 @@
       </c>
       <c r="AE483" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF483" t="inlineStr">
@@ -55901,7 +55901,7 @@
       </c>
       <c r="AE484" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF484" t="inlineStr">
@@ -56013,7 +56013,7 @@
       </c>
       <c r="AE485" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF485" t="inlineStr">
@@ -56125,7 +56125,7 @@
       </c>
       <c r="AE486" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF486" t="inlineStr">
@@ -56235,7 +56235,7 @@
       </c>
       <c r="AE487" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF487" t="inlineStr">
@@ -56347,7 +56347,7 @@
       </c>
       <c r="AE488" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF488" t="inlineStr">
@@ -56447,7 +56447,7 @@
       </c>
       <c r="AE489" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF489" t="inlineStr">
@@ -56557,7 +56557,7 @@
       </c>
       <c r="AE490" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF490" t="inlineStr">
@@ -56657,7 +56657,7 @@
       </c>
       <c r="AE491" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF491" t="inlineStr">
@@ -56757,7 +56757,7 @@
       </c>
       <c r="AE492" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF492" t="inlineStr">
@@ -56869,7 +56869,7 @@
       </c>
       <c r="AE493" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF493" t="inlineStr">
@@ -56981,7 +56981,7 @@
       </c>
       <c r="AE494" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF494" t="inlineStr">
@@ -57093,7 +57093,7 @@
       </c>
       <c r="AE495" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF495" t="inlineStr">
@@ -57203,7 +57203,7 @@
       </c>
       <c r="AE496" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF496" t="inlineStr">
@@ -57313,7 +57313,7 @@
       </c>
       <c r="AE497" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF497" t="inlineStr">
@@ -57423,7 +57423,7 @@
       </c>
       <c r="AE498" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF498" t="inlineStr">
@@ -57535,7 +57535,7 @@
       </c>
       <c r="AE499" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF499" t="inlineStr">
@@ -57645,7 +57645,7 @@
       </c>
       <c r="AE500" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF500" t="inlineStr">
@@ -57755,7 +57755,7 @@
       </c>
       <c r="AE501" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF501" t="inlineStr">
@@ -57865,7 +57865,7 @@
       </c>
       <c r="AE502" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF502" t="inlineStr">
@@ -57975,7 +57975,7 @@
       </c>
       <c r="AE503" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF503" t="inlineStr">
@@ -58087,7 +58087,7 @@
       </c>
       <c r="AE504" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF504" t="inlineStr">
@@ -58199,7 +58199,7 @@
       </c>
       <c r="AE505" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF505" t="inlineStr">
@@ -58315,7 +58315,7 @@
       </c>
       <c r="AE506" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF506" t="inlineStr">
@@ -58443,7 +58443,7 @@
       </c>
       <c r="AE507" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="AF507" t="inlineStr">
@@ -58555,7 +58555,7 @@
       </c>
       <c r="AE508" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF508" t="inlineStr">
@@ -58665,7 +58665,7 @@
       </c>
       <c r="AE509" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF509" t="inlineStr">
@@ -58785,7 +58785,7 @@
       </c>
       <c r="AE510" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="AF510" t="inlineStr">
@@ -58895,7 +58895,7 @@
       </c>
       <c r="AE511" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF511" t="inlineStr">
@@ -59005,7 +59005,7 @@
       </c>
       <c r="AE512" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF512" t="inlineStr">
@@ -59115,7 +59115,7 @@
       </c>
       <c r="AE513" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF513" t="inlineStr">
@@ -59235,7 +59235,7 @@
       </c>
       <c r="AE514" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="AF514" t="inlineStr">
@@ -59351,7 +59351,7 @@
       </c>
       <c r="AE515" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF515" t="inlineStr">
@@ -59463,7 +59463,7 @@
       </c>
       <c r="AE516" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF516" t="inlineStr">
@@ -59583,7 +59583,7 @@
       </c>
       <c r="AE517" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="AF517" t="inlineStr">
@@ -59695,7 +59695,7 @@
       </c>
       <c r="AE518" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF518" t="inlineStr">
@@ -59795,7 +59795,7 @@
       </c>
       <c r="AE519" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF519" t="inlineStr">
@@ -59915,7 +59915,7 @@
       </c>
       <c r="AE520" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="AF520" t="inlineStr">
@@ -60025,7 +60025,7 @@
       </c>
       <c r="AE521" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF521" t="inlineStr">
@@ -60137,7 +60137,7 @@
       </c>
       <c r="AE522" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF522" t="inlineStr">
@@ -60253,7 +60253,7 @@
       </c>
       <c r="AE523" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF523" t="inlineStr">
@@ -60365,7 +60365,7 @@
       </c>
       <c r="AE524" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF524" t="inlineStr">
@@ -60477,7 +60477,7 @@
       </c>
       <c r="AE525" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF525" t="inlineStr">
@@ -60605,7 +60605,7 @@
       </c>
       <c r="AE526" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="AF526" t="inlineStr">
@@ -60715,7 +60715,7 @@
       </c>
       <c r="AE527" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF527" t="inlineStr">
@@ -60825,7 +60825,7 @@
       </c>
       <c r="AE528" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF528" t="inlineStr">
@@ -60935,7 +60935,7 @@
       </c>
       <c r="AE529" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF529" t="inlineStr">
@@ -61047,7 +61047,7 @@
       </c>
       <c r="AE530" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF530" t="inlineStr">
@@ -61175,7 +61175,7 @@
       </c>
       <c r="AE531" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="AF531" t="inlineStr">
@@ -61287,7 +61287,7 @@
       </c>
       <c r="AE532" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF532" t="inlineStr">
@@ -61399,7 +61399,7 @@
       </c>
       <c r="AE533" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF533" t="inlineStr">
@@ -61511,7 +61511,7 @@
       </c>
       <c r="AE534" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF534" t="inlineStr">
@@ -61611,7 +61611,7 @@
       </c>
       <c r="AE535" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF535" t="inlineStr">
@@ -61721,7 +61721,7 @@
       </c>
       <c r="AE536" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF536" t="inlineStr">
@@ -61831,7 +61831,7 @@
       </c>
       <c r="AE537" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF537" t="inlineStr">
@@ -61931,7 +61931,7 @@
       </c>
       <c r="AE538" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF538" t="inlineStr">
@@ -62041,7 +62041,7 @@
       </c>
       <c r="AE539" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF539" t="inlineStr">
@@ -62169,7 +62169,7 @@
       </c>
       <c r="AE540" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="AF540" t="inlineStr">
@@ -62279,7 +62279,7 @@
       </c>
       <c r="AE541" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF541" t="inlineStr">
@@ -62391,7 +62391,7 @@
       </c>
       <c r="AE542" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF542" t="inlineStr">
@@ -62501,7 +62501,7 @@
       </c>
       <c r="AE543" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF543" t="inlineStr">
@@ -62613,7 +62613,7 @@
       </c>
       <c r="AE544" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF544" t="inlineStr">
@@ -62723,7 +62723,7 @@
       </c>
       <c r="AE545" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF545" t="inlineStr">
@@ -62833,7 +62833,7 @@
       </c>
       <c r="AE546" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF546" t="inlineStr">
@@ -62933,7 +62933,7 @@
       </c>
       <c r="AE547" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF547" t="inlineStr">
@@ -63043,7 +63043,7 @@
       </c>
       <c r="AE548" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF548" t="inlineStr">
@@ -63155,7 +63155,7 @@
       </c>
       <c r="AE549" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF549" t="inlineStr">
@@ -63265,7 +63265,7 @@
       </c>
       <c r="AE550" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF550" t="inlineStr">
@@ -63375,7 +63375,7 @@
       </c>
       <c r="AE551" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF551" t="inlineStr">
@@ -63485,7 +63485,7 @@
       </c>
       <c r="AE552" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF552" t="inlineStr">
@@ -63595,7 +63595,7 @@
       </c>
       <c r="AE553" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF553" t="inlineStr">
@@ -63705,7 +63705,7 @@
       </c>
       <c r="AE554" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF554" t="inlineStr">
@@ -63815,7 +63815,7 @@
       </c>
       <c r="AE555" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF555" t="inlineStr">
@@ -63915,7 +63915,7 @@
       </c>
       <c r="AE556" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF556" t="inlineStr">
@@ -64025,7 +64025,7 @@
       </c>
       <c r="AE557" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF557" t="inlineStr">
@@ -64135,7 +64135,7 @@
       </c>
       <c r="AE558" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF558" t="inlineStr">
@@ -64247,7 +64247,7 @@
       </c>
       <c r="AE559" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF559" t="inlineStr">
@@ -64357,7 +64357,7 @@
       </c>
       <c r="AE560" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF560" t="inlineStr">
@@ -64469,7 +64469,7 @@
       </c>
       <c r="AE561" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF561" t="inlineStr">
@@ -64579,7 +64579,7 @@
       </c>
       <c r="AE562" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF562" t="inlineStr">
@@ -64689,7 +64689,7 @@
       </c>
       <c r="AE563" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF563" t="inlineStr">
@@ -64799,7 +64799,7 @@
       </c>
       <c r="AE564" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF564" t="inlineStr">
@@ -64909,7 +64909,7 @@
       </c>
       <c r="AE565" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF565" t="inlineStr">
@@ -65019,7 +65019,7 @@
       </c>
       <c r="AE566" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF566" t="inlineStr">
@@ -65131,7 +65131,7 @@
       </c>
       <c r="AE567" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF567" t="inlineStr">
@@ -65241,7 +65241,7 @@
       </c>
       <c r="AE568" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF568" t="inlineStr">
@@ -65353,7 +65353,7 @@
       </c>
       <c r="AE569" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF569" t="inlineStr">
@@ -65465,7 +65465,7 @@
       </c>
       <c r="AE570" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF570" t="inlineStr">
@@ -65575,7 +65575,7 @@
       </c>
       <c r="AE571" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF571" t="inlineStr">
@@ -65687,7 +65687,7 @@
       </c>
       <c r="AE572" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF572" t="inlineStr">
@@ -65799,7 +65799,7 @@
       </c>
       <c r="AE573" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF573" t="inlineStr">
@@ -65909,7 +65909,7 @@
       </c>
       <c r="AE574" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF574" t="inlineStr">
@@ -66019,7 +66019,7 @@
       </c>
       <c r="AE575" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF575" t="inlineStr">
@@ -66129,7 +66129,7 @@
       </c>
       <c r="AE576" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF576" t="inlineStr">
@@ -66239,7 +66239,7 @@
       </c>
       <c r="AE577" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF577" t="inlineStr">
@@ -66339,7 +66339,7 @@
       </c>
       <c r="AE578" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF578" t="inlineStr">
@@ -66451,7 +66451,7 @@
       </c>
       <c r="AE579" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF579" t="inlineStr">
@@ -66561,7 +66561,7 @@
       </c>
       <c r="AE580" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF580" t="inlineStr">
@@ -66671,7 +66671,7 @@
       </c>
       <c r="AE581" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF581" t="inlineStr">
@@ -66799,7 +66799,7 @@
       </c>
       <c r="AE582" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="AF582" t="inlineStr">
@@ -66911,7 +66911,7 @@
       </c>
       <c r="AE583" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF583" t="inlineStr">
@@ -67023,7 +67023,7 @@
       </c>
       <c r="AE584" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF584" t="inlineStr">
@@ -67151,7 +67151,7 @@
       </c>
       <c r="AE585" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="AF585" t="inlineStr">
@@ -67263,7 +67263,7 @@
       </c>
       <c r="AE586" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF586" t="inlineStr">
@@ -67391,7 +67391,7 @@
       </c>
       <c r="AE587" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="AF587" t="inlineStr">
@@ -67519,7 +67519,7 @@
       </c>
       <c r="AE588" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="AF588" t="inlineStr">
@@ -67631,7 +67631,7 @@
       </c>
       <c r="AE589" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF589" t="inlineStr">
@@ -67743,7 +67743,7 @@
       </c>
       <c r="AE590" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF590" t="inlineStr">
@@ -67853,7 +67853,7 @@
       </c>
       <c r="AE591" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF591" t="inlineStr">
@@ -67965,7 +67965,7 @@
       </c>
       <c r="AE592" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF592" t="inlineStr">
@@ -68075,7 +68075,7 @@
       </c>
       <c r="AE593" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF593" t="inlineStr">
@@ -68185,7 +68185,7 @@
       </c>
       <c r="AE594" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF594" t="inlineStr">
@@ -68297,7 +68297,7 @@
       </c>
       <c r="AE595" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF595" t="inlineStr">
@@ -68409,7 +68409,7 @@
       </c>
       <c r="AE596" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF596" t="inlineStr">
@@ -68521,7 +68521,7 @@
       </c>
       <c r="AE597" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF597" t="inlineStr">
@@ -68631,7 +68631,7 @@
       </c>
       <c r="AE598" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF598" t="inlineStr">
@@ -68741,7 +68741,7 @@
       </c>
       <c r="AE599" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF599" t="inlineStr">
@@ -68853,7 +68853,7 @@
       </c>
       <c r="AE600" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF600" t="inlineStr">
@@ -68965,7 +68965,7 @@
       </c>
       <c r="AE601" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF601" t="inlineStr">
@@ -69075,7 +69075,7 @@
       </c>
       <c r="AE602" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF602" t="inlineStr">
@@ -69187,7 +69187,7 @@
       </c>
       <c r="AE603" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF603" t="inlineStr">
@@ -69297,7 +69297,7 @@
       </c>
       <c r="AE604" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF604" t="inlineStr">
@@ -69397,7 +69397,7 @@
       </c>
       <c r="AE605" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF605" t="inlineStr">
@@ -69507,7 +69507,7 @@
       </c>
       <c r="AE606" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF606" t="inlineStr">
@@ -69619,7 +69619,7 @@
       </c>
       <c r="AE607" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF607" t="inlineStr">
@@ -69729,7 +69729,7 @@
       </c>
       <c r="AE608" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF608" t="inlineStr">
@@ -69841,7 +69841,7 @@
       </c>
       <c r="AE609" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF609" t="inlineStr">
@@ -69951,7 +69951,7 @@
       </c>
       <c r="AE610" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF610" t="inlineStr">
@@ -70061,7 +70061,7 @@
       </c>
       <c r="AE611" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF611" t="inlineStr">
@@ -70171,7 +70171,7 @@
       </c>
       <c r="AE612" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF612" t="inlineStr">
@@ -70281,7 +70281,7 @@
       </c>
       <c r="AE613" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF613" t="inlineStr">
@@ -70391,7 +70391,7 @@
       </c>
       <c r="AE614" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF614" t="inlineStr">
@@ -70503,7 +70503,7 @@
       </c>
       <c r="AE615" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF615" t="inlineStr">
@@ -70613,7 +70613,7 @@
       </c>
       <c r="AE616" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF616" t="inlineStr">
@@ -70723,7 +70723,7 @@
       </c>
       <c r="AE617" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF617" t="inlineStr">
@@ -70833,7 +70833,7 @@
       </c>
       <c r="AE618" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF618" t="inlineStr">
@@ -70945,7 +70945,7 @@
       </c>
       <c r="AE619" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF619" t="inlineStr">
@@ -71055,7 +71055,7 @@
       </c>
       <c r="AE620" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF620" t="inlineStr">
@@ -71167,7 +71167,7 @@
       </c>
       <c r="AE621" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF621" t="inlineStr">
@@ -71279,7 +71279,7 @@
       </c>
       <c r="AE622" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF622" t="inlineStr">
@@ -71379,7 +71379,7 @@
       </c>
       <c r="AE623" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF623" t="inlineStr">
@@ -71489,7 +71489,7 @@
       </c>
       <c r="AE624" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF624" t="inlineStr">
@@ -71601,7 +71601,7 @@
       </c>
       <c r="AE625" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF625" t="inlineStr">
@@ -71713,7 +71713,7 @@
       </c>
       <c r="AE626" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF626" t="inlineStr">
@@ -71825,7 +71825,7 @@
       </c>
       <c r="AE627" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF627" t="inlineStr">
@@ -71937,7 +71937,7 @@
       </c>
       <c r="AE628" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF628" t="inlineStr">
@@ -72047,7 +72047,7 @@
       </c>
       <c r="AE629" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF629" t="inlineStr">
@@ -72157,7 +72157,7 @@
       </c>
       <c r="AE630" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF630" t="inlineStr">
@@ -72269,7 +72269,7 @@
       </c>
       <c r="AE631" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF631" t="inlineStr">
@@ -72379,7 +72379,7 @@
       </c>
       <c r="AE632" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF632" t="inlineStr">
@@ -72491,7 +72491,7 @@
       </c>
       <c r="AE633" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF633" t="inlineStr">
@@ -72591,7 +72591,7 @@
       </c>
       <c r="AE634" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF634" t="inlineStr">
@@ -72701,7 +72701,7 @@
       </c>
       <c r="AE635" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF635" t="inlineStr">
@@ -72813,7 +72813,7 @@
       </c>
       <c r="AE636" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF636" t="inlineStr">
@@ -72923,7 +72923,7 @@
       <c r="AD637" t="inlineStr"/>
       <c r="AE637" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:55</t>
+          <t>2026-09-18 09:23:05</t>
         </is>
       </c>
       <c r="AF637" t="inlineStr">
@@ -73035,7 +73035,7 @@
       </c>
       <c r="AE638" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF638" t="inlineStr">
@@ -73147,7 +73147,7 @@
       </c>
       <c r="AE639" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF639" t="inlineStr">
@@ -73257,7 +73257,7 @@
       </c>
       <c r="AE640" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF640" t="inlineStr">
@@ -73369,7 +73369,7 @@
       </c>
       <c r="AE641" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF641" t="inlineStr">
@@ -73469,7 +73469,7 @@
       </c>
       <c r="AE642" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF642" t="inlineStr">
@@ -73569,7 +73569,7 @@
       </c>
       <c r="AE643" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF643" t="inlineStr">
@@ -73669,7 +73669,7 @@
       </c>
       <c r="AE644" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF644" t="inlineStr">
@@ -73781,7 +73781,7 @@
       </c>
       <c r="AE645" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF645" t="inlineStr">
@@ -73881,7 +73881,7 @@
       </c>
       <c r="AE646" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF646" t="inlineStr">
@@ -73991,7 +73991,7 @@
       </c>
       <c r="AE647" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF647" t="inlineStr">
@@ -74091,7 +74091,7 @@
       </c>
       <c r="AE648" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF648" t="inlineStr">
@@ -74203,7 +74203,7 @@
       </c>
       <c r="AE649" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF649" t="inlineStr">
@@ -74315,7 +74315,7 @@
       </c>
       <c r="AE650" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF650" t="inlineStr">
@@ -74427,7 +74427,7 @@
       </c>
       <c r="AE651" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF651" t="inlineStr">
@@ -74539,7 +74539,7 @@
       </c>
       <c r="AE652" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF652" t="inlineStr">
@@ -74639,7 +74639,7 @@
       </c>
       <c r="AE653" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF653" t="inlineStr">
@@ -74751,7 +74751,7 @@
       </c>
       <c r="AE654" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF654" t="inlineStr">
@@ -74861,7 +74861,7 @@
       </c>
       <c r="AE655" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF655" t="inlineStr">
@@ -74973,7 +74973,7 @@
       </c>
       <c r="AE656" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF656" t="inlineStr">
@@ -75073,7 +75073,7 @@
       </c>
       <c r="AE657" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF657" t="inlineStr">
@@ -75173,7 +75173,7 @@
       </c>
       <c r="AE658" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF658" t="inlineStr">
@@ -75273,7 +75273,7 @@
       </c>
       <c r="AE659" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF659" t="inlineStr">
@@ -75373,7 +75373,7 @@
       </c>
       <c r="AE660" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF660" t="inlineStr">
@@ -75485,7 +75485,7 @@
       </c>
       <c r="AE661" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF661" t="inlineStr">
@@ -75597,7 +75597,7 @@
       </c>
       <c r="AE662" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF662" t="inlineStr">
@@ -75697,7 +75697,7 @@
       </c>
       <c r="AE663" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF663" t="inlineStr">
@@ -75807,7 +75807,7 @@
       </c>
       <c r="AE664" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF664" t="inlineStr">
@@ -75919,7 +75919,7 @@
       </c>
       <c r="AE665" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF665" t="inlineStr">
@@ -76031,7 +76031,7 @@
       </c>
       <c r="AE666" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF666" t="inlineStr">
@@ -76143,7 +76143,7 @@
       </c>
       <c r="AE667" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF667" t="inlineStr">
@@ -76255,7 +76255,7 @@
       </c>
       <c r="AE668" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF668" t="inlineStr">
@@ -76367,7 +76367,7 @@
       </c>
       <c r="AE669" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF669" t="inlineStr">
@@ -76479,7 +76479,7 @@
       </c>
       <c r="AE670" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF670" t="inlineStr">
@@ -76591,7 +76591,7 @@
       </c>
       <c r="AE671" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF671" t="inlineStr">
@@ -76691,7 +76691,7 @@
       </c>
       <c r="AE672" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF672" t="inlineStr">
@@ -76791,7 +76791,7 @@
       </c>
       <c r="AE673" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF673" t="inlineStr">
@@ -76903,7 +76903,7 @@
       </c>
       <c r="AE674" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:25</t>
+          <t>2026-09-18 09:22:35</t>
         </is>
       </c>
       <c r="AF674" t="inlineStr">
@@ -77003,7 +77003,7 @@
       </c>
       <c r="AE675" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF675" t="inlineStr">
@@ -77103,7 +77103,7 @@
       </c>
       <c r="AE676" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF676" t="inlineStr">
@@ -77203,7 +77203,7 @@
       </c>
       <c r="AE677" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF677" t="inlineStr">
@@ -77313,7 +77313,7 @@
       </c>
       <c r="AE678" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF678" t="inlineStr">
@@ -77413,7 +77413,7 @@
       </c>
       <c r="AE679" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF679" t="inlineStr">
@@ -77523,7 +77523,7 @@
       </c>
       <c r="AE680" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF680" t="inlineStr">
@@ -77605,7 +77605,7 @@
       <c r="AD681" t="inlineStr"/>
       <c r="AE681" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF681" t="inlineStr">
@@ -77687,7 +77687,7 @@
       <c r="AD682" t="inlineStr"/>
       <c r="AE682" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF682" t="inlineStr">
@@ -77769,7 +77769,7 @@
       <c r="AD683" t="inlineStr"/>
       <c r="AE683" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF683" t="inlineStr">
@@ -77851,7 +77851,7 @@
       <c r="AD684" t="inlineStr"/>
       <c r="AE684" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="AF684" t="inlineStr">

--- a/pipeline/credit_rating/output/xhtn_tong_hop_20260918.xlsx
+++ b/pipeline/credit_rating/output/xhtn_tong_hop_20260918.xlsx
@@ -685,7 +685,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1011,7 +1011,7 @@
       <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -1099,7 +1099,7 @@
       <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -1219,7 +1219,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -1555,7 +1555,7 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>2026-09-18 09:23:05</t>
+          <t>2026-09-18 13:07:17</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -1665,7 +1665,7 @@
       <c r="AD11" t="inlineStr"/>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>2026-09-18 09:23:05</t>
+          <t>2026-09-18 13:07:17</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>2026-09-18 09:23:05</t>
+          <t>2026-09-18 13:07:17</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -1891,7 +1891,7 @@
       <c r="AD13" t="inlineStr"/>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>2026-09-18 09:23:05</t>
+          <t>2026-09-18 13:07:17</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -2019,7 +2019,7 @@
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -2133,7 +2133,7 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -2247,7 +2247,7 @@
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -2367,7 +2367,7 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -2595,7 +2595,7 @@
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -2709,7 +2709,7 @@
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -2825,7 +2825,7 @@
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>2026-09-18 09:23:05</t>
+          <t>2026-09-18 13:07:17</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -2939,7 +2939,7 @@
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -3049,7 +3049,7 @@
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -3177,7 +3177,7 @@
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
@@ -3291,7 +3291,7 @@
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
@@ -3411,7 +3411,7 @@
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
@@ -3525,7 +3525,7 @@
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
@@ -3635,7 +3635,7 @@
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>2026-09-18 09:23:05</t>
+          <t>2026-09-18 13:07:17</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
@@ -3861,7 +3861,7 @@
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
@@ -3971,7 +3971,7 @@
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF31" t="inlineStr">
@@ -4095,7 +4095,7 @@
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
@@ -4205,7 +4205,7 @@
       </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF33" t="inlineStr">
@@ -4315,7 +4315,7 @@
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF34" t="inlineStr">
@@ -4425,7 +4425,7 @@
       </c>
       <c r="AE35" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF35" t="inlineStr">
@@ -4525,7 +4525,7 @@
       </c>
       <c r="AE36" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF36" t="inlineStr">
@@ -4635,7 +4635,7 @@
       </c>
       <c r="AE37" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF37" t="inlineStr">
@@ -4745,7 +4745,7 @@
       </c>
       <c r="AE38" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF38" t="inlineStr">
@@ -4855,7 +4855,7 @@
       </c>
       <c r="AE39" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF39" t="inlineStr">
@@ -4987,7 +4987,7 @@
       </c>
       <c r="AE40" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="AF40" t="inlineStr">
@@ -5115,7 +5115,7 @@
       </c>
       <c r="AE41" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="AF41" t="inlineStr">
@@ -5247,7 +5247,7 @@
       </c>
       <c r="AE42" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="AF42" t="inlineStr">
@@ -5375,7 +5375,7 @@
       </c>
       <c r="AE43" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="AF43" t="inlineStr">
@@ -5485,7 +5485,7 @@
       </c>
       <c r="AE44" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF44" t="inlineStr">
@@ -5597,7 +5597,7 @@
       </c>
       <c r="AE45" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF45" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="AE46" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF46" t="inlineStr">
@@ -5827,7 +5827,7 @@
       </c>
       <c r="AE47" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF47" t="inlineStr">
@@ -5943,7 +5943,7 @@
       </c>
       <c r="AE48" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF48" t="inlineStr">
@@ -6043,7 +6043,7 @@
       </c>
       <c r="AE49" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF49" t="inlineStr">
@@ -6157,7 +6157,7 @@
       </c>
       <c r="AE50" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF50" t="inlineStr">
@@ -6273,7 +6273,7 @@
       </c>
       <c r="AE51" t="inlineStr">
         <is>
-          <t>2026-09-18 09:23:05</t>
+          <t>2026-09-18 13:07:17</t>
         </is>
       </c>
       <c r="AF51" t="inlineStr">
@@ -6383,7 +6383,7 @@
       </c>
       <c r="AE52" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF52" t="inlineStr">
@@ -6497,7 +6497,7 @@
       </c>
       <c r="AE53" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF53" t="inlineStr">
@@ -6611,7 +6611,7 @@
       </c>
       <c r="AE54" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF54" t="inlineStr">
@@ -6739,7 +6739,7 @@
       </c>
       <c r="AE55" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="AF55" t="inlineStr">
@@ -6855,7 +6855,7 @@
       </c>
       <c r="AE56" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF56" t="inlineStr">
@@ -6951,7 +6951,7 @@
       </c>
       <c r="AE57" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF57" t="inlineStr">
@@ -7061,7 +7061,7 @@
       </c>
       <c r="AE58" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF58" t="inlineStr">
@@ -7161,7 +7161,7 @@
       </c>
       <c r="AE59" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF59" t="inlineStr">
@@ -7275,7 +7275,7 @@
       </c>
       <c r="AE60" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF60" t="inlineStr">
@@ -7389,7 +7389,7 @@
       </c>
       <c r="AE61" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF61" t="inlineStr">
@@ -7489,7 +7489,7 @@
       </c>
       <c r="AE62" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF62" t="inlineStr">
@@ -7603,7 +7603,7 @@
       </c>
       <c r="AE63" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:49</t>
+          <t>2026-09-18 13:07:00</t>
         </is>
       </c>
       <c r="AF63" t="inlineStr">
@@ -7713,7 +7713,7 @@
       </c>
       <c r="AE64" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF64" t="inlineStr">
@@ -7827,7 +7827,7 @@
       </c>
       <c r="AE65" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF65" t="inlineStr">
@@ -7941,7 +7941,7 @@
       </c>
       <c r="AE66" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF66" t="inlineStr">
@@ -8051,7 +8051,7 @@
       </c>
       <c r="AE67" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF67" t="inlineStr">
@@ -8165,7 +8165,7 @@
       </c>
       <c r="AE68" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF68" t="inlineStr">
@@ -8279,7 +8279,7 @@
       </c>
       <c r="AE69" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:49</t>
+          <t>2026-09-18 13:07:00</t>
         </is>
       </c>
       <c r="AF69" t="inlineStr">
@@ -8393,7 +8393,7 @@
       </c>
       <c r="AE70" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:49</t>
+          <t>2026-09-18 13:07:00</t>
         </is>
       </c>
       <c r="AF70" t="inlineStr">
@@ -8517,7 +8517,7 @@
       </c>
       <c r="AE71" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:51</t>
+          <t>2026-09-18 13:07:02</t>
         </is>
       </c>
       <c r="AF71" t="inlineStr">
@@ -8627,7 +8627,7 @@
       </c>
       <c r="AE72" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF72" t="inlineStr">
@@ -8741,7 +8741,7 @@
       </c>
       <c r="AE73" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF73" t="inlineStr">
@@ -8855,7 +8855,7 @@
       </c>
       <c r="AE74" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF74" t="inlineStr">
@@ -8969,7 +8969,7 @@
       </c>
       <c r="AE75" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF75" t="inlineStr">
@@ -9081,7 +9081,7 @@
       </c>
       <c r="AE76" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF76" t="inlineStr">
@@ -9197,7 +9197,7 @@
       </c>
       <c r="AE77" t="inlineStr">
         <is>
-          <t>2026-09-18 09:23:05</t>
+          <t>2026-09-18 13:07:17</t>
         </is>
       </c>
       <c r="AF77" t="inlineStr">
@@ -9307,7 +9307,7 @@
       </c>
       <c r="AE78" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF78" t="inlineStr">
@@ -9417,7 +9417,7 @@
       </c>
       <c r="AE79" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF79" t="inlineStr">
@@ -9535,7 +9535,7 @@
       </c>
       <c r="AE80" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:49</t>
+          <t>2026-09-18 13:07:00</t>
         </is>
       </c>
       <c r="AF80" t="inlineStr">
@@ -9659,7 +9659,7 @@
       </c>
       <c r="AE81" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="AF81" t="inlineStr">
@@ -9779,7 +9779,7 @@
       </c>
       <c r="AE82" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="AF82" t="inlineStr">
@@ -9899,7 +9899,7 @@
       </c>
       <c r="AE83" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="AF83" t="inlineStr">
@@ -10031,7 +10031,7 @@
       </c>
       <c r="AE84" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="AF84" t="inlineStr">
@@ -10155,7 +10155,7 @@
       </c>
       <c r="AE85" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF85" t="inlineStr">
@@ -10279,7 +10279,7 @@
       </c>
       <c r="AE86" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF86" t="inlineStr">
@@ -10379,7 +10379,7 @@
       </c>
       <c r="AE87" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF87" t="inlineStr">
@@ -10499,7 +10499,7 @@
       </c>
       <c r="AE88" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="AF88" t="inlineStr">
@@ -10627,7 +10627,7 @@
       </c>
       <c r="AE89" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="AF89" t="inlineStr">
@@ -10741,7 +10741,7 @@
       </c>
       <c r="AE90" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF90" t="inlineStr">
@@ -10855,7 +10855,7 @@
       </c>
       <c r="AE91" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF91" t="inlineStr">
@@ -10969,7 +10969,7 @@
       </c>
       <c r="AE92" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF92" t="inlineStr">
@@ -11079,7 +11079,7 @@
       </c>
       <c r="AE93" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF93" t="inlineStr">
@@ -11193,7 +11193,7 @@
       </c>
       <c r="AE94" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF94" t="inlineStr">
@@ -11307,7 +11307,7 @@
       </c>
       <c r="AE95" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF95" t="inlineStr">
@@ -11421,7 +11421,7 @@
       </c>
       <c r="AE96" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF96" t="inlineStr">
@@ -11535,7 +11535,7 @@
       </c>
       <c r="AE97" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF97" t="inlineStr">
@@ -11655,7 +11655,7 @@
       </c>
       <c r="AE98" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="AF98" t="inlineStr">
@@ -11771,7 +11771,7 @@
       </c>
       <c r="AE99" t="inlineStr">
         <is>
-          <t>2026-09-18 09:23:05</t>
+          <t>2026-09-18 13:07:17</t>
         </is>
       </c>
       <c r="AF99" t="inlineStr">
@@ -11881,7 +11881,7 @@
       </c>
       <c r="AE100" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF100" t="inlineStr">
@@ -12001,7 +12001,7 @@
       </c>
       <c r="AE101" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="AF101" t="inlineStr">
@@ -12133,7 +12133,7 @@
       </c>
       <c r="AE102" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="AF102" t="inlineStr">
@@ -12261,7 +12261,7 @@
       </c>
       <c r="AE103" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="AF103" t="inlineStr">
@@ -12373,7 +12373,7 @@
       </c>
       <c r="AE104" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF104" t="inlineStr">
@@ -12483,7 +12483,7 @@
       </c>
       <c r="AE105" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF105" t="inlineStr">
@@ -12593,7 +12593,7 @@
       </c>
       <c r="AE106" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF106" t="inlineStr">
@@ -12703,7 +12703,7 @@
       </c>
       <c r="AE107" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF107" t="inlineStr">
@@ -12817,7 +12817,7 @@
       </c>
       <c r="AE108" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:49</t>
+          <t>2026-09-18 13:07:00</t>
         </is>
       </c>
       <c r="AF108" t="inlineStr">
@@ -12929,7 +12929,7 @@
       </c>
       <c r="AE109" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF109" t="inlineStr">
@@ -13045,7 +13045,7 @@
       </c>
       <c r="AE110" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF110" t="inlineStr">
@@ -13167,7 +13167,7 @@
       <c r="AD111" t="inlineStr"/>
       <c r="AE111" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="AF111" t="inlineStr">
@@ -13279,7 +13279,7 @@
       </c>
       <c r="AE112" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:51</t>
+          <t>2026-09-18 13:07:02</t>
         </is>
       </c>
       <c r="AF112" t="inlineStr">
@@ -13407,7 +13407,7 @@
       </c>
       <c r="AE113" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="AF113" t="inlineStr">
@@ -13527,7 +13527,7 @@
       </c>
       <c r="AE114" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF114" t="inlineStr">
@@ -13647,7 +13647,7 @@
       </c>
       <c r="AE115" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF115" t="inlineStr">
@@ -13757,7 +13757,7 @@
       </c>
       <c r="AE116" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF116" t="inlineStr">
@@ -13873,7 +13873,7 @@
       </c>
       <c r="AE117" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF117" t="inlineStr">
@@ -13985,7 +13985,7 @@
       </c>
       <c r="AE118" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF118" t="inlineStr">
@@ -14095,7 +14095,7 @@
       </c>
       <c r="AE119" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF119" t="inlineStr">
@@ -14205,7 +14205,7 @@
       </c>
       <c r="AE120" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF120" t="inlineStr">
@@ -14329,7 +14329,7 @@
       </c>
       <c r="AE121" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF121" t="inlineStr">
@@ -14445,7 +14445,7 @@
       </c>
       <c r="AE122" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF122" t="inlineStr">
@@ -14565,7 +14565,7 @@
       </c>
       <c r="AE123" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="AF123" t="inlineStr">
@@ -14677,7 +14677,7 @@
       </c>
       <c r="AE124" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF124" t="inlineStr">
@@ -14797,7 +14797,7 @@
       </c>
       <c r="AE125" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF125" t="inlineStr">
@@ -14907,7 +14907,7 @@
       </c>
       <c r="AE126" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF126" t="inlineStr">
@@ -15017,7 +15017,7 @@
       </c>
       <c r="AE127" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF127" t="inlineStr">
@@ -15137,7 +15137,7 @@
       </c>
       <c r="AE128" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="AF128" t="inlineStr">
@@ -15251,7 +15251,7 @@
       </c>
       <c r="AE129" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF129" t="inlineStr">
@@ -15365,7 +15365,7 @@
       </c>
       <c r="AE130" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF130" t="inlineStr">
@@ -15485,7 +15485,7 @@
       </c>
       <c r="AE131" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="AF131" t="inlineStr">
@@ -15595,7 +15595,7 @@
       </c>
       <c r="AE132" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF132" t="inlineStr">
@@ -15711,7 +15711,7 @@
       </c>
       <c r="AE133" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF133" t="inlineStr">
@@ -15823,7 +15823,7 @@
       </c>
       <c r="AE134" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:51</t>
+          <t>2026-09-18 13:07:02</t>
         </is>
       </c>
       <c r="AF134" t="inlineStr">
@@ -15935,7 +15935,7 @@
       </c>
       <c r="AE135" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF135" t="inlineStr">
@@ -16049,7 +16049,7 @@
       </c>
       <c r="AE136" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF136" t="inlineStr">
@@ -16163,7 +16163,7 @@
       </c>
       <c r="AE137" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF137" t="inlineStr">
@@ -16277,7 +16277,7 @@
       </c>
       <c r="AE138" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:49</t>
+          <t>2026-09-18 13:07:00</t>
         </is>
       </c>
       <c r="AF138" t="inlineStr">
@@ -16387,7 +16387,7 @@
       </c>
       <c r="AE139" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF139" t="inlineStr">
@@ -16497,7 +16497,7 @@
       </c>
       <c r="AE140" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF140" t="inlineStr">
@@ -16607,7 +16607,7 @@
       </c>
       <c r="AE141" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF141" t="inlineStr">
@@ -16721,7 +16721,7 @@
       </c>
       <c r="AE142" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF142" t="inlineStr">
@@ -16835,7 +16835,7 @@
       </c>
       <c r="AE143" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF143" t="inlineStr">
@@ -16963,7 +16963,7 @@
       </c>
       <c r="AE144" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="AF144" t="inlineStr">
@@ -17091,7 +17091,7 @@
       </c>
       <c r="AE145" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="AF145" t="inlineStr">
@@ -17201,7 +17201,7 @@
       </c>
       <c r="AE146" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF146" t="inlineStr">
@@ -17311,7 +17311,7 @@
       </c>
       <c r="AE147" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF147" t="inlineStr">
@@ -17431,7 +17431,7 @@
       </c>
       <c r="AE148" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="AF148" t="inlineStr">
@@ -17545,7 +17545,7 @@
       </c>
       <c r="AE149" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF149" t="inlineStr">
@@ -17655,7 +17655,7 @@
       </c>
       <c r="AE150" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF150" t="inlineStr">
@@ -17783,7 +17783,7 @@
       </c>
       <c r="AE151" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="AF151" t="inlineStr">
@@ -17905,7 +17905,7 @@
       <c r="AD152" t="inlineStr"/>
       <c r="AE152" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="AF152" t="inlineStr">
@@ -18033,7 +18033,7 @@
       </c>
       <c r="AE153" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="AF153" t="inlineStr">
@@ -18149,7 +18149,7 @@
       </c>
       <c r="AE154" t="inlineStr">
         <is>
-          <t>2026-09-18 09:23:05</t>
+          <t>2026-09-18 13:07:17</t>
         </is>
       </c>
       <c r="AF154" t="inlineStr">
@@ -18277,7 +18277,7 @@
       </c>
       <c r="AE155" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="AF155" t="inlineStr">
@@ -18409,7 +18409,7 @@
       </c>
       <c r="AE156" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="AF156" t="inlineStr">
@@ -18523,7 +18523,7 @@
       </c>
       <c r="AE157" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF157" t="inlineStr">
@@ -18645,7 +18645,7 @@
       <c r="AD158" t="inlineStr"/>
       <c r="AE158" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="AF158" t="inlineStr">
@@ -18757,7 +18757,7 @@
       </c>
       <c r="AE159" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF159" t="inlineStr">
@@ -18857,7 +18857,7 @@
       </c>
       <c r="AE160" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF160" t="inlineStr">
@@ -18967,7 +18967,7 @@
       </c>
       <c r="AE161" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF161" t="inlineStr">
@@ -19083,7 +19083,7 @@
       </c>
       <c r="AE162" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF162" t="inlineStr">
@@ -19199,7 +19199,7 @@
       </c>
       <c r="AE163" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF163" t="inlineStr">
@@ -19327,7 +19327,7 @@
       </c>
       <c r="AE164" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="AF164" t="inlineStr">
@@ -19437,7 +19437,7 @@
       </c>
       <c r="AE165" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF165" t="inlineStr">
@@ -19551,7 +19551,7 @@
       </c>
       <c r="AE166" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF166" t="inlineStr">
@@ -19665,7 +19665,7 @@
       </c>
       <c r="AE167" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF167" t="inlineStr">
@@ -19779,7 +19779,7 @@
       </c>
       <c r="AE168" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF168" t="inlineStr">
@@ -19889,7 +19889,7 @@
       </c>
       <c r="AE169" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF169" t="inlineStr">
@@ -20003,7 +20003,7 @@
       </c>
       <c r="AE170" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF170" t="inlineStr">
@@ -20113,7 +20113,7 @@
       </c>
       <c r="AE171" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF171" t="inlineStr">
@@ -20225,7 +20225,7 @@
       </c>
       <c r="AE172" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF172" t="inlineStr">
@@ -20341,7 +20341,7 @@
       </c>
       <c r="AE173" t="inlineStr">
         <is>
-          <t>2026-09-18 09:23:05</t>
+          <t>2026-09-18 13:07:17</t>
         </is>
       </c>
       <c r="AF173" t="inlineStr">
@@ -20457,7 +20457,7 @@
       </c>
       <c r="AE174" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF174" t="inlineStr">
@@ -20569,7 +20569,7 @@
       </c>
       <c r="AE175" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF175" t="inlineStr">
@@ -20681,7 +20681,7 @@
       </c>
       <c r="AE176" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF176" t="inlineStr">
@@ -20809,7 +20809,7 @@
       </c>
       <c r="AE177" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:51</t>
+          <t>2026-09-18 13:07:02</t>
         </is>
       </c>
       <c r="AF177" t="inlineStr">
@@ -20919,7 +20919,7 @@
       </c>
       <c r="AE178" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF178" t="inlineStr">
@@ -21039,7 +21039,7 @@
       </c>
       <c r="AE179" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="AF179" t="inlineStr">
@@ -21161,7 +21161,7 @@
       <c r="AD180" t="inlineStr"/>
       <c r="AE180" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="AF180" t="inlineStr">
@@ -21287,7 +21287,7 @@
       <c r="AD181" t="inlineStr"/>
       <c r="AE181" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="AF181" t="inlineStr">
@@ -21413,7 +21413,7 @@
       <c r="AD182" t="inlineStr"/>
       <c r="AE182" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="AF182" t="inlineStr">
@@ -21529,7 +21529,7 @@
       </c>
       <c r="AE183" t="inlineStr">
         <is>
-          <t>2026-09-18 09:23:05</t>
+          <t>2026-09-18 13:07:17</t>
         </is>
       </c>
       <c r="AF183" t="inlineStr">
@@ -21643,7 +21643,7 @@
       </c>
       <c r="AE184" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF184" t="inlineStr">
@@ -21757,7 +21757,7 @@
       </c>
       <c r="AE185" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF185" t="inlineStr">
@@ -21871,7 +21871,7 @@
       </c>
       <c r="AE186" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF186" t="inlineStr">
@@ -21991,7 +21991,7 @@
       </c>
       <c r="AE187" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="AF187" t="inlineStr">
@@ -22111,7 +22111,7 @@
       </c>
       <c r="AE188" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="AF188" t="inlineStr">
@@ -22221,7 +22221,7 @@
       </c>
       <c r="AE189" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF189" t="inlineStr">
@@ -22331,7 +22331,7 @@
       </c>
       <c r="AE190" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF190" t="inlineStr">
@@ -22441,7 +22441,7 @@
       </c>
       <c r="AE191" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF191" t="inlineStr">
@@ -22557,7 +22557,7 @@
       </c>
       <c r="AE192" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF192" t="inlineStr">
@@ -22685,7 +22685,7 @@
       </c>
       <c r="AE193" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="AF193" t="inlineStr">
@@ -22797,7 +22797,7 @@
       </c>
       <c r="AE194" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF194" t="inlineStr">
@@ -22909,7 +22909,7 @@
       </c>
       <c r="AE195" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF195" t="inlineStr">
@@ -23027,7 +23027,7 @@
       </c>
       <c r="AE196" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:49</t>
+          <t>2026-09-18 13:07:00</t>
         </is>
       </c>
       <c r="AF196" t="inlineStr">
@@ -23137,7 +23137,7 @@
       </c>
       <c r="AE197" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF197" t="inlineStr">
@@ -23247,7 +23247,7 @@
       </c>
       <c r="AE198" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF198" t="inlineStr">
@@ -23359,7 +23359,7 @@
       </c>
       <c r="AE199" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF199" t="inlineStr">
@@ -23469,7 +23469,7 @@
       </c>
       <c r="AE200" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF200" t="inlineStr">
@@ -23589,7 +23589,7 @@
       </c>
       <c r="AE201" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="AF201" t="inlineStr">
@@ -23705,7 +23705,7 @@
       </c>
       <c r="AE202" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF202" t="inlineStr">
@@ -23821,7 +23821,7 @@
       </c>
       <c r="AE203" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF203" t="inlineStr">
@@ -23949,7 +23949,7 @@
       </c>
       <c r="AE204" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="AF204" t="inlineStr">
@@ -24061,7 +24061,7 @@
       </c>
       <c r="AE205" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF205" t="inlineStr">
@@ -24173,7 +24173,7 @@
       </c>
       <c r="AE206" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF206" t="inlineStr">
@@ -24285,7 +24285,7 @@
       </c>
       <c r="AE207" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF207" t="inlineStr">
@@ -24401,7 +24401,7 @@
       </c>
       <c r="AE208" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF208" t="inlineStr">
@@ -24511,7 +24511,7 @@
       </c>
       <c r="AE209" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF209" t="inlineStr">
@@ -24631,7 +24631,7 @@
       </c>
       <c r="AE210" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="AF210" t="inlineStr">
@@ -24741,7 +24741,7 @@
       </c>
       <c r="AE211" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF211" t="inlineStr">
@@ -24861,7 +24861,7 @@
       </c>
       <c r="AE212" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="AF212" t="inlineStr">
@@ -24971,7 +24971,7 @@
       </c>
       <c r="AE213" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF213" t="inlineStr">
@@ -25085,7 +25085,7 @@
       </c>
       <c r="AE214" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:49</t>
+          <t>2026-09-18 13:07:00</t>
         </is>
       </c>
       <c r="AF214" t="inlineStr">
@@ -25195,7 +25195,7 @@
       </c>
       <c r="AE215" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF215" t="inlineStr">
@@ -25305,7 +25305,7 @@
       </c>
       <c r="AE216" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF216" t="inlineStr">
@@ -25419,7 +25419,7 @@
       </c>
       <c r="AE217" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF217" t="inlineStr">
@@ -25529,7 +25529,7 @@
       </c>
       <c r="AE218" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF218" t="inlineStr">
@@ -25641,7 +25641,7 @@
       </c>
       <c r="AE219" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF219" t="inlineStr">
@@ -25751,7 +25751,7 @@
       </c>
       <c r="AE220" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF220" t="inlineStr">
@@ -25871,7 +25871,7 @@
       </c>
       <c r="AE221" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="AF221" t="inlineStr">
@@ -25983,7 +25983,7 @@
       </c>
       <c r="AE222" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF222" t="inlineStr">
@@ -26093,7 +26093,7 @@
       </c>
       <c r="AE223" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF223" t="inlineStr">
@@ -26217,7 +26217,7 @@
       </c>
       <c r="AE224" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:51</t>
+          <t>2026-09-18 13:07:02</t>
         </is>
       </c>
       <c r="AF224" t="inlineStr">
@@ -26341,7 +26341,7 @@
       </c>
       <c r="AE225" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:51</t>
+          <t>2026-09-18 13:07:02</t>
         </is>
       </c>
       <c r="AF225" t="inlineStr">
@@ -26451,7 +26451,7 @@
       </c>
       <c r="AE226" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF226" t="inlineStr">
@@ -26561,7 +26561,7 @@
       </c>
       <c r="AE227" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF227" t="inlineStr">
@@ -26671,7 +26671,7 @@
       </c>
       <c r="AE228" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF228" t="inlineStr">
@@ -26783,7 +26783,7 @@
       </c>
       <c r="AE229" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF229" t="inlineStr">
@@ -26893,7 +26893,7 @@
       </c>
       <c r="AE230" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF230" t="inlineStr">
@@ -27003,7 +27003,7 @@
       </c>
       <c r="AE231" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF231" t="inlineStr">
@@ -27131,7 +27131,7 @@
       </c>
       <c r="AE232" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="AF232" t="inlineStr">
@@ -27237,7 +27237,7 @@
       </c>
       <c r="AE233" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF233" t="inlineStr">
@@ -27349,7 +27349,7 @@
       </c>
       <c r="AE234" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF234" t="inlineStr">
@@ -27465,7 +27465,7 @@
       </c>
       <c r="AE235" t="inlineStr">
         <is>
-          <t>2026-09-18 09:23:05</t>
+          <t>2026-09-18 13:07:17</t>
         </is>
       </c>
       <c r="AF235" t="inlineStr">
@@ -27581,7 +27581,7 @@
       </c>
       <c r="AE236" t="inlineStr">
         <is>
-          <t>2026-09-18 09:23:05</t>
+          <t>2026-09-18 13:07:17</t>
         </is>
       </c>
       <c r="AF236" t="inlineStr">
@@ -27691,7 +27691,7 @@
       </c>
       <c r="AE237" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF237" t="inlineStr">
@@ -27801,7 +27801,7 @@
       </c>
       <c r="AE238" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF238" t="inlineStr">
@@ -27917,7 +27917,7 @@
       </c>
       <c r="AE239" t="inlineStr">
         <is>
-          <t>2026-09-18 09:23:05</t>
+          <t>2026-09-18 13:07:17</t>
         </is>
       </c>
       <c r="AF239" t="inlineStr">
@@ -28033,7 +28033,7 @@
       </c>
       <c r="AE240" t="inlineStr">
         <is>
-          <t>2026-09-18 09:23:05</t>
+          <t>2026-09-18 13:07:17</t>
         </is>
       </c>
       <c r="AF240" t="inlineStr">
@@ -28143,7 +28143,7 @@
       </c>
       <c r="AE241" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF241" t="inlineStr">
@@ -28259,7 +28259,7 @@
       </c>
       <c r="AE242" t="inlineStr">
         <is>
-          <t>2026-09-18 09:23:05</t>
+          <t>2026-09-18 13:07:17</t>
         </is>
       </c>
       <c r="AF242" t="inlineStr">
@@ -28375,7 +28375,7 @@
       </c>
       <c r="AE243" t="inlineStr">
         <is>
-          <t>2026-09-18 09:23:05</t>
+          <t>2026-09-18 13:07:17</t>
         </is>
       </c>
       <c r="AF243" t="inlineStr">
@@ -28485,7 +28485,7 @@
       </c>
       <c r="AE244" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF244" t="inlineStr">
@@ -28595,7 +28595,7 @@
       </c>
       <c r="AE245" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF245" t="inlineStr">
@@ -28705,7 +28705,7 @@
       </c>
       <c r="AE246" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF246" t="inlineStr">
@@ -28805,7 +28805,7 @@
       </c>
       <c r="AE247" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF247" t="inlineStr">
@@ -28921,7 +28921,7 @@
       </c>
       <c r="AE248" t="inlineStr">
         <is>
-          <t>2026-09-18 09:23:05</t>
+          <t>2026-09-18 13:07:17</t>
         </is>
       </c>
       <c r="AF248" t="inlineStr">
@@ -29031,7 +29031,7 @@
       </c>
       <c r="AE249" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF249" t="inlineStr">
@@ -29143,7 +29143,7 @@
       </c>
       <c r="AE250" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF250" t="inlineStr">
@@ -29253,7 +29253,7 @@
       </c>
       <c r="AE251" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF251" t="inlineStr">
@@ -29373,7 +29373,7 @@
       </c>
       <c r="AE252" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="AF252" t="inlineStr">
@@ -29485,7 +29485,7 @@
       </c>
       <c r="AE253" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF253" t="inlineStr">
@@ -29595,7 +29595,7 @@
       </c>
       <c r="AE254" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF254" t="inlineStr">
@@ -29707,7 +29707,7 @@
       </c>
       <c r="AE255" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF255" t="inlineStr">
@@ -29823,7 +29823,7 @@
       </c>
       <c r="AE256" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF256" t="inlineStr">
@@ -29935,7 +29935,7 @@
       </c>
       <c r="AE257" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF257" t="inlineStr">
@@ -30045,7 +30045,7 @@
       </c>
       <c r="AE258" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF258" t="inlineStr">
@@ -30161,7 +30161,7 @@
       </c>
       <c r="AE259" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF259" t="inlineStr">
@@ -30271,7 +30271,7 @@
       </c>
       <c r="AE260" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF260" t="inlineStr">
@@ -30397,7 +30397,7 @@
       <c r="AD261" t="inlineStr"/>
       <c r="AE261" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="AF261" t="inlineStr">
@@ -30525,7 +30525,7 @@
       </c>
       <c r="AE262" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="AF262" t="inlineStr">
@@ -30637,7 +30637,7 @@
       </c>
       <c r="AE263" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF263" t="inlineStr">
@@ -30737,7 +30737,7 @@
       </c>
       <c r="AE264" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF264" t="inlineStr">
@@ -30837,7 +30837,7 @@
       </c>
       <c r="AE265" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF265" t="inlineStr">
@@ -30951,7 +30951,7 @@
       </c>
       <c r="AE266" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF266" t="inlineStr">
@@ -31065,7 +31065,7 @@
       </c>
       <c r="AE267" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF267" t="inlineStr">
@@ -31165,7 +31165,7 @@
       </c>
       <c r="AE268" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF268" t="inlineStr">
@@ -31285,7 +31285,7 @@
       </c>
       <c r="AE269" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="AF269" t="inlineStr">
@@ -31397,7 +31397,7 @@
       </c>
       <c r="AE270" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF270" t="inlineStr">
@@ -31509,7 +31509,7 @@
       </c>
       <c r="AE271" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF271" t="inlineStr">
@@ -31623,7 +31623,7 @@
       </c>
       <c r="AE272" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF272" t="inlineStr">
@@ -31737,7 +31737,7 @@
       </c>
       <c r="AE273" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:49</t>
+          <t>2026-09-18 13:07:00</t>
         </is>
       </c>
       <c r="AF273" t="inlineStr">
@@ -31851,7 +31851,7 @@
       </c>
       <c r="AE274" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:49</t>
+          <t>2026-09-18 13:07:00</t>
         </is>
       </c>
       <c r="AF274" t="inlineStr">
@@ -31983,7 +31983,7 @@
       </c>
       <c r="AE275" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="AF275" t="inlineStr">
@@ -32111,7 +32111,7 @@
       </c>
       <c r="AE276" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="AF276" t="inlineStr">
@@ -32239,7 +32239,7 @@
       </c>
       <c r="AE277" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="AF277" t="inlineStr">
@@ -32367,7 +32367,7 @@
       </c>
       <c r="AE278" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="AF278" t="inlineStr">
@@ -32479,7 +32479,7 @@
       </c>
       <c r="AE279" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF279" t="inlineStr">
@@ -32591,7 +32591,7 @@
       </c>
       <c r="AE280" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF280" t="inlineStr">
@@ -32701,7 +32701,7 @@
       </c>
       <c r="AE281" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF281" t="inlineStr">
@@ -32811,7 +32811,7 @@
       </c>
       <c r="AE282" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF282" t="inlineStr">
@@ -32939,7 +32939,7 @@
       </c>
       <c r="AE283" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="AF283" t="inlineStr">
@@ -33049,7 +33049,7 @@
       </c>
       <c r="AE284" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF284" t="inlineStr">
@@ -33177,7 +33177,7 @@
       </c>
       <c r="AE285" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="AF285" t="inlineStr">
@@ -33289,7 +33289,7 @@
       </c>
       <c r="AE286" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF286" t="inlineStr">
@@ -33401,7 +33401,7 @@
       </c>
       <c r="AE287" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF287" t="inlineStr">
@@ -33511,7 +33511,7 @@
       </c>
       <c r="AE288" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF288" t="inlineStr">
@@ -33631,7 +33631,7 @@
       </c>
       <c r="AE289" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="AF289" t="inlineStr">
@@ -33755,7 +33755,7 @@
       </c>
       <c r="AE290" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="AF290" t="inlineStr">
@@ -33879,7 +33879,7 @@
       </c>
       <c r="AE291" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="AF291" t="inlineStr">
@@ -34003,7 +34003,7 @@
       </c>
       <c r="AE292" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="AF292" t="inlineStr">
@@ -34115,7 +34115,7 @@
       </c>
       <c r="AE293" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF293" t="inlineStr">
@@ -34231,7 +34231,7 @@
       </c>
       <c r="AE294" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF294" t="inlineStr">
@@ -34343,7 +34343,7 @@
       </c>
       <c r="AE295" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:51</t>
+          <t>2026-09-18 13:07:02</t>
         </is>
       </c>
       <c r="AF295" t="inlineStr">
@@ -34471,7 +34471,7 @@
       </c>
       <c r="AE296" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:51</t>
+          <t>2026-09-18 13:07:02</t>
         </is>
       </c>
       <c r="AF296" t="inlineStr">
@@ -34599,7 +34599,7 @@
       </c>
       <c r="AE297" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="AF297" t="inlineStr">
@@ -34711,7 +34711,7 @@
       </c>
       <c r="AE298" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF298" t="inlineStr">
@@ -34823,7 +34823,7 @@
       </c>
       <c r="AE299" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF299" t="inlineStr">
@@ -34933,7 +34933,7 @@
       </c>
       <c r="AE300" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF300" t="inlineStr">
@@ -35043,7 +35043,7 @@
       </c>
       <c r="AE301" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF301" t="inlineStr">
@@ -35159,7 +35159,7 @@
       </c>
       <c r="AE302" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF302" t="inlineStr">
@@ -35271,7 +35271,7 @@
       </c>
       <c r="AE303" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF303" t="inlineStr">
@@ -35391,7 +35391,7 @@
       </c>
       <c r="AE304" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="AF304" t="inlineStr">
@@ -35519,7 +35519,7 @@
       </c>
       <c r="AE305" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="AF305" t="inlineStr">
@@ -35635,7 +35635,7 @@
       </c>
       <c r="AE306" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF306" t="inlineStr">
@@ -35735,7 +35735,7 @@
       </c>
       <c r="AE307" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF307" t="inlineStr">
@@ -35847,7 +35847,7 @@
       </c>
       <c r="AE308" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF308" t="inlineStr">
@@ -35975,7 +35975,7 @@
       </c>
       <c r="AE309" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="AF309" t="inlineStr">
@@ -36099,7 +36099,7 @@
       </c>
       <c r="AE310" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:51</t>
+          <t>2026-09-18 13:07:02</t>
         </is>
       </c>
       <c r="AF310" t="inlineStr">
@@ -36211,7 +36211,7 @@
       </c>
       <c r="AE311" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF311" t="inlineStr">
@@ -36321,7 +36321,7 @@
       </c>
       <c r="AE312" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF312" t="inlineStr">
@@ -36431,7 +36431,7 @@
       </c>
       <c r="AE313" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF313" t="inlineStr">
@@ -36541,7 +36541,7 @@
       </c>
       <c r="AE314" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF314" t="inlineStr">
@@ -36651,7 +36651,7 @@
       </c>
       <c r="AE315" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF315" t="inlineStr">
@@ -36771,7 +36771,7 @@
       </c>
       <c r="AE316" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="AF316" t="inlineStr">
@@ -36881,7 +36881,7 @@
       </c>
       <c r="AE317" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF317" t="inlineStr">
@@ -36991,7 +36991,7 @@
       </c>
       <c r="AE318" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF318" t="inlineStr">
@@ -37101,7 +37101,7 @@
       </c>
       <c r="AE319" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF319" t="inlineStr">
@@ -37221,7 +37221,7 @@
       </c>
       <c r="AE320" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="AF320" t="inlineStr">
@@ -37341,7 +37341,7 @@
       </c>
       <c r="AE321" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="AF321" t="inlineStr">
@@ -37461,7 +37461,7 @@
       </c>
       <c r="AE322" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="AF322" t="inlineStr">
@@ -37581,7 +37581,7 @@
       </c>
       <c r="AE323" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="AF323" t="inlineStr">
@@ -37697,7 +37697,7 @@
       </c>
       <c r="AE324" t="inlineStr">
         <is>
-          <t>2026-09-18 09:23:05</t>
+          <t>2026-09-18 13:07:17</t>
         </is>
       </c>
       <c r="AF324" t="inlineStr">
@@ -37813,7 +37813,7 @@
       </c>
       <c r="AE325" t="inlineStr">
         <is>
-          <t>2026-09-18 09:23:05</t>
+          <t>2026-09-18 13:07:17</t>
         </is>
       </c>
       <c r="AF325" t="inlineStr">
@@ -37929,7 +37929,7 @@
       </c>
       <c r="AE326" t="inlineStr">
         <is>
-          <t>2026-09-18 09:23:05</t>
+          <t>2026-09-18 13:07:17</t>
         </is>
       </c>
       <c r="AF326" t="inlineStr">
@@ -38041,7 +38041,7 @@
       </c>
       <c r="AE327" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF327" t="inlineStr">
@@ -38157,7 +38157,7 @@
       </c>
       <c r="AE328" t="inlineStr">
         <is>
-          <t>2026-09-18 09:23:05</t>
+          <t>2026-09-18 13:07:17</t>
         </is>
       </c>
       <c r="AF328" t="inlineStr">
@@ -38277,7 +38277,7 @@
       </c>
       <c r="AE329" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="AF329" t="inlineStr">
@@ -38389,7 +38389,7 @@
       </c>
       <c r="AE330" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF330" t="inlineStr">
@@ -38505,7 +38505,7 @@
       </c>
       <c r="AE331" t="inlineStr">
         <is>
-          <t>2026-09-18 09:23:05</t>
+          <t>2026-09-18 13:07:17</t>
         </is>
       </c>
       <c r="AF331" t="inlineStr">
@@ -38621,7 +38621,7 @@
       </c>
       <c r="AE332" t="inlineStr">
         <is>
-          <t>2026-09-18 09:23:05</t>
+          <t>2026-09-18 13:07:17</t>
         </is>
       </c>
       <c r="AF332" t="inlineStr">
@@ -38737,7 +38737,7 @@
       </c>
       <c r="AE333" t="inlineStr">
         <is>
-          <t>2026-09-18 09:23:05</t>
+          <t>2026-09-18 13:07:17</t>
         </is>
       </c>
       <c r="AF333" t="inlineStr">
@@ -38853,7 +38853,7 @@
       </c>
       <c r="AE334" t="inlineStr">
         <is>
-          <t>2026-09-18 09:23:05</t>
+          <t>2026-09-18 13:07:17</t>
         </is>
       </c>
       <c r="AF334" t="inlineStr">
@@ -38967,7 +38967,7 @@
       </c>
       <c r="AE335" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:49</t>
+          <t>2026-09-18 13:07:00</t>
         </is>
       </c>
       <c r="AF335" t="inlineStr">
@@ -39083,7 +39083,7 @@
       </c>
       <c r="AE336" t="inlineStr">
         <is>
-          <t>2026-09-18 09:23:05</t>
+          <t>2026-09-18 13:07:17</t>
         </is>
       </c>
       <c r="AF336" t="inlineStr">
@@ -39199,7 +39199,7 @@
       </c>
       <c r="AE337" t="inlineStr">
         <is>
-          <t>2026-09-18 09:23:05</t>
+          <t>2026-09-18 13:07:17</t>
         </is>
       </c>
       <c r="AF337" t="inlineStr">
@@ -39315,7 +39315,7 @@
       </c>
       <c r="AE338" t="inlineStr">
         <is>
-          <t>2026-09-18 09:23:05</t>
+          <t>2026-09-18 13:07:17</t>
         </is>
       </c>
       <c r="AF338" t="inlineStr">
@@ -39425,7 +39425,7 @@
       </c>
       <c r="AE339" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF339" t="inlineStr">
@@ -39541,7 +39541,7 @@
       </c>
       <c r="AE340" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF340" t="inlineStr">
@@ -39653,7 +39653,7 @@
       </c>
       <c r="AE341" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF341" t="inlineStr">
@@ -39763,7 +39763,7 @@
       </c>
       <c r="AE342" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF342" t="inlineStr">
@@ -39875,7 +39875,7 @@
       </c>
       <c r="AE343" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF343" t="inlineStr">
@@ -39987,7 +39987,7 @@
       </c>
       <c r="AE344" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF344" t="inlineStr">
@@ -40099,7 +40099,7 @@
       </c>
       <c r="AE345" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF345" t="inlineStr">
@@ -40219,7 +40219,7 @@
       </c>
       <c r="AE346" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="AF346" t="inlineStr">
@@ -40347,7 +40347,7 @@
       </c>
       <c r="AE347" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="AF347" t="inlineStr">
@@ -40467,7 +40467,7 @@
       </c>
       <c r="AE348" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="AF348" t="inlineStr">
@@ -40595,7 +40595,7 @@
       </c>
       <c r="AE349" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="AF349" t="inlineStr">
@@ -40707,7 +40707,7 @@
       </c>
       <c r="AE350" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF350" t="inlineStr">
@@ -40817,7 +40817,7 @@
       </c>
       <c r="AE351" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF351" t="inlineStr">
@@ -40927,7 +40927,7 @@
       </c>
       <c r="AE352" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF352" t="inlineStr">
@@ -41039,7 +41039,7 @@
       </c>
       <c r="AE353" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF353" t="inlineStr">
@@ -41151,7 +41151,7 @@
       </c>
       <c r="AE354" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF354" t="inlineStr">
@@ -41261,7 +41261,7 @@
       </c>
       <c r="AE355" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF355" t="inlineStr">
@@ -41377,7 +41377,7 @@
       </c>
       <c r="AE356" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF356" t="inlineStr">
@@ -41487,7 +41487,7 @@
       </c>
       <c r="AE357" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF357" t="inlineStr">
@@ -41599,7 +41599,7 @@
       </c>
       <c r="AE358" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF358" t="inlineStr">
@@ -41709,7 +41709,7 @@
       </c>
       <c r="AE359" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF359" t="inlineStr">
@@ -41819,7 +41819,7 @@
       </c>
       <c r="AE360" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF360" t="inlineStr">
@@ -41947,7 +41947,7 @@
       </c>
       <c r="AE361" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="AF361" t="inlineStr">
@@ -42059,7 +42059,7 @@
       </c>
       <c r="AE362" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF362" t="inlineStr">
@@ -42187,7 +42187,7 @@
       </c>
       <c r="AE363" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="AF363" t="inlineStr">
@@ -42299,7 +42299,7 @@
       </c>
       <c r="AE364" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF364" t="inlineStr">
@@ -42409,7 +42409,7 @@
       </c>
       <c r="AE365" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF365" t="inlineStr">
@@ -42519,7 +42519,7 @@
       </c>
       <c r="AE366" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF366" t="inlineStr">
@@ -42629,7 +42629,7 @@
       </c>
       <c r="AE367" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF367" t="inlineStr">
@@ -42741,7 +42741,7 @@
       </c>
       <c r="AE368" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF368" t="inlineStr">
@@ -42851,7 +42851,7 @@
       </c>
       <c r="AE369" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF369" t="inlineStr">
@@ -42979,7 +42979,7 @@
       </c>
       <c r="AE370" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="AF370" t="inlineStr">
@@ -43091,7 +43091,7 @@
       </c>
       <c r="AE371" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF371" t="inlineStr">
@@ -43201,7 +43201,7 @@
       </c>
       <c r="AE372" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF372" t="inlineStr">
@@ -43311,7 +43311,7 @@
       </c>
       <c r="AE373" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF373" t="inlineStr">
@@ -43421,7 +43421,7 @@
       </c>
       <c r="AE374" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF374" t="inlineStr">
@@ -43531,7 +43531,7 @@
       </c>
       <c r="AE375" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF375" t="inlineStr">
@@ -43641,7 +43641,7 @@
       </c>
       <c r="AE376" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF376" t="inlineStr">
@@ -43753,7 +43753,7 @@
       </c>
       <c r="AE377" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF377" t="inlineStr">
@@ -43881,7 +43881,7 @@
       </c>
       <c r="AE378" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="AF378" t="inlineStr">
@@ -43991,7 +43991,7 @@
       </c>
       <c r="AE379" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF379" t="inlineStr">
@@ -44101,7 +44101,7 @@
       </c>
       <c r="AE380" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF380" t="inlineStr">
@@ -44213,7 +44213,7 @@
       </c>
       <c r="AE381" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:51</t>
+          <t>2026-09-18 13:07:02</t>
         </is>
       </c>
       <c r="AF381" t="inlineStr">
@@ -44323,7 +44323,7 @@
       </c>
       <c r="AE382" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF382" t="inlineStr">
@@ -44435,7 +44435,7 @@
       </c>
       <c r="AE383" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF383" t="inlineStr">
@@ -44563,7 +44563,7 @@
       </c>
       <c r="AE384" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="AF384" t="inlineStr">
@@ -44673,7 +44673,7 @@
       </c>
       <c r="AE385" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF385" t="inlineStr">
@@ -44785,7 +44785,7 @@
       </c>
       <c r="AE386" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF386" t="inlineStr">
@@ -44895,7 +44895,7 @@
       </c>
       <c r="AE387" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF387" t="inlineStr">
@@ -45005,7 +45005,7 @@
       </c>
       <c r="AE388" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF388" t="inlineStr">
@@ -45115,7 +45115,7 @@
       </c>
       <c r="AE389" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF389" t="inlineStr">
@@ -45215,7 +45215,7 @@
       </c>
       <c r="AE390" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF390" t="inlineStr">
@@ -45325,7 +45325,7 @@
       </c>
       <c r="AE391" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF391" t="inlineStr">
@@ -45425,7 +45425,7 @@
       </c>
       <c r="AE392" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF392" t="inlineStr">
@@ -45535,7 +45535,7 @@
       </c>
       <c r="AE393" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF393" t="inlineStr">
@@ -45663,7 +45663,7 @@
       </c>
       <c r="AE394" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="AF394" t="inlineStr">
@@ -45773,7 +45773,7 @@
       </c>
       <c r="AE395" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF395" t="inlineStr">
@@ -45883,7 +45883,7 @@
       </c>
       <c r="AE396" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF396" t="inlineStr">
@@ -45993,7 +45993,7 @@
       </c>
       <c r="AE397" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF397" t="inlineStr">
@@ -46103,7 +46103,7 @@
       </c>
       <c r="AE398" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF398" t="inlineStr">
@@ -46213,7 +46213,7 @@
       </c>
       <c r="AE399" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF399" t="inlineStr">
@@ -46323,7 +46323,7 @@
       </c>
       <c r="AE400" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF400" t="inlineStr">
@@ -46433,7 +46433,7 @@
       </c>
       <c r="AE401" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF401" t="inlineStr">
@@ -46543,7 +46543,7 @@
       </c>
       <c r="AE402" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF402" t="inlineStr">
@@ -46671,7 +46671,7 @@
       </c>
       <c r="AE403" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="AF403" t="inlineStr">
@@ -46783,7 +46783,7 @@
       </c>
       <c r="AE404" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF404" t="inlineStr">
@@ -46883,7 +46883,7 @@
       </c>
       <c r="AE405" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF405" t="inlineStr">
@@ -46993,7 +46993,7 @@
       </c>
       <c r="AE406" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF406" t="inlineStr">
@@ -47107,7 +47107,7 @@
       </c>
       <c r="AE407" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF407" t="inlineStr">
@@ -47217,7 +47217,7 @@
       </c>
       <c r="AE408" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF408" t="inlineStr">
@@ -47317,7 +47317,7 @@
       </c>
       <c r="AE409" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF409" t="inlineStr">
@@ -47429,7 +47429,7 @@
       </c>
       <c r="AE410" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF410" t="inlineStr">
@@ -47541,7 +47541,7 @@
       </c>
       <c r="AE411" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF411" t="inlineStr">
@@ -47651,7 +47651,7 @@
       </c>
       <c r="AE412" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF412" t="inlineStr">
@@ -47763,7 +47763,7 @@
       </c>
       <c r="AE413" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF413" t="inlineStr">
@@ -47875,7 +47875,7 @@
       </c>
       <c r="AE414" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF414" t="inlineStr">
@@ -47985,7 +47985,7 @@
       </c>
       <c r="AE415" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF415" t="inlineStr">
@@ -48113,7 +48113,7 @@
       </c>
       <c r="AE416" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="AF416" t="inlineStr">
@@ -48245,7 +48245,7 @@
       </c>
       <c r="AE417" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="AF417" t="inlineStr">
@@ -48377,7 +48377,7 @@
       </c>
       <c r="AE418" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="AF418" t="inlineStr">
@@ -48509,7 +48509,7 @@
       </c>
       <c r="AE419" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="AF419" t="inlineStr">
@@ -48633,7 +48633,7 @@
       </c>
       <c r="AE420" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:51</t>
+          <t>2026-09-18 13:07:02</t>
         </is>
       </c>
       <c r="AF420" t="inlineStr">
@@ -48745,7 +48745,7 @@
       </c>
       <c r="AE421" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF421" t="inlineStr">
@@ -48845,7 +48845,7 @@
       </c>
       <c r="AE422" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF422" t="inlineStr">
@@ -48965,7 +48965,7 @@
       </c>
       <c r="AE423" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="AF423" t="inlineStr">
@@ -49081,7 +49081,7 @@
       </c>
       <c r="AE424" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF424" t="inlineStr">
@@ -49193,7 +49193,7 @@
       </c>
       <c r="AE425" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF425" t="inlineStr">
@@ -49315,7 +49315,7 @@
       <c r="AD426" t="inlineStr"/>
       <c r="AE426" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="AF426" t="inlineStr">
@@ -49427,7 +49427,7 @@
       </c>
       <c r="AE427" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF427" t="inlineStr">
@@ -49537,7 +49537,7 @@
       </c>
       <c r="AE428" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF428" t="inlineStr">
@@ -49647,7 +49647,7 @@
       </c>
       <c r="AE429" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF429" t="inlineStr">
@@ -49757,7 +49757,7 @@
       </c>
       <c r="AE430" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF430" t="inlineStr">
@@ -49867,7 +49867,7 @@
       </c>
       <c r="AE431" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF431" t="inlineStr">
@@ -49995,7 +49995,7 @@
       </c>
       <c r="AE432" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="AF432" t="inlineStr">
@@ -50111,7 +50111,7 @@
       </c>
       <c r="AE433" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF433" t="inlineStr">
@@ -50221,7 +50221,7 @@
       </c>
       <c r="AE434" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF434" t="inlineStr">
@@ -50349,7 +50349,7 @@
       </c>
       <c r="AE435" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="AF435" t="inlineStr">
@@ -50477,7 +50477,7 @@
       </c>
       <c r="AE436" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="AF436" t="inlineStr">
@@ -50605,7 +50605,7 @@
       </c>
       <c r="AE437" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="AF437" t="inlineStr">
@@ -50733,7 +50733,7 @@
       </c>
       <c r="AE438" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="AF438" t="inlineStr">
@@ -50845,7 +50845,7 @@
       </c>
       <c r="AE439" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF439" t="inlineStr">
@@ -50955,7 +50955,7 @@
       </c>
       <c r="AE440" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF440" t="inlineStr">
@@ -51083,7 +51083,7 @@
       </c>
       <c r="AE441" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="AF441" t="inlineStr">
@@ -51195,7 +51195,7 @@
       </c>
       <c r="AE442" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF442" t="inlineStr">
@@ -51307,7 +51307,7 @@
       </c>
       <c r="AE443" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF443" t="inlineStr">
@@ -51423,7 +51423,7 @@
       </c>
       <c r="AE444" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF444" t="inlineStr">
@@ -51535,7 +51535,7 @@
       </c>
       <c r="AE445" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF445" t="inlineStr">
@@ -51647,7 +51647,7 @@
       </c>
       <c r="AE446" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF446" t="inlineStr">
@@ -51759,7 +51759,7 @@
       </c>
       <c r="AE447" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF447" t="inlineStr">
@@ -51871,7 +51871,7 @@
       </c>
       <c r="AE448" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF448" t="inlineStr">
@@ -51991,7 +51991,7 @@
       </c>
       <c r="AE449" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="AF449" t="inlineStr">
@@ -52101,7 +52101,7 @@
       </c>
       <c r="AE450" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF450" t="inlineStr">
@@ -52229,7 +52229,7 @@
       </c>
       <c r="AE451" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="AF451" t="inlineStr">
@@ -52349,7 +52349,7 @@
       </c>
       <c r="AE452" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="AF452" t="inlineStr">
@@ -52461,7 +52461,7 @@
       </c>
       <c r="AE453" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF453" t="inlineStr">
@@ -52573,7 +52573,7 @@
       </c>
       <c r="AE454" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF454" t="inlineStr">
@@ -52673,7 +52673,7 @@
       </c>
       <c r="AE455" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF455" t="inlineStr">
@@ -52789,7 +52789,7 @@
       </c>
       <c r="AE456" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF456" t="inlineStr">
@@ -52899,7 +52899,7 @@
       </c>
       <c r="AE457" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF457" t="inlineStr">
@@ -53011,7 +53011,7 @@
       </c>
       <c r="AE458" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF458" t="inlineStr">
@@ -53121,7 +53121,7 @@
       </c>
       <c r="AE459" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF459" t="inlineStr">
@@ -53233,7 +53233,7 @@
       </c>
       <c r="AE460" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF460" t="inlineStr">
@@ -53345,7 +53345,7 @@
       </c>
       <c r="AE461" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF461" t="inlineStr">
@@ -53445,7 +53445,7 @@
       </c>
       <c r="AE462" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF462" t="inlineStr">
@@ -53555,7 +53555,7 @@
       </c>
       <c r="AE463" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF463" t="inlineStr">
@@ -53667,7 +53667,7 @@
       </c>
       <c r="AE464" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF464" t="inlineStr">
@@ -53777,7 +53777,7 @@
       </c>
       <c r="AE465" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF465" t="inlineStr">
@@ -53887,7 +53887,7 @@
       </c>
       <c r="AE466" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF466" t="inlineStr">
@@ -53999,7 +53999,7 @@
       </c>
       <c r="AE467" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF467" t="inlineStr">
@@ -54109,7 +54109,7 @@
       </c>
       <c r="AE468" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF468" t="inlineStr">
@@ -54219,7 +54219,7 @@
       </c>
       <c r="AE469" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF469" t="inlineStr">
@@ -54329,7 +54329,7 @@
       </c>
       <c r="AE470" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF470" t="inlineStr">
@@ -54449,7 +54449,7 @@
       </c>
       <c r="AE471" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="AF471" t="inlineStr">
@@ -54573,7 +54573,7 @@
       </c>
       <c r="AE472" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:51</t>
+          <t>2026-09-18 13:07:02</t>
         </is>
       </c>
       <c r="AF472" t="inlineStr">
@@ -54683,7 +54683,7 @@
       </c>
       <c r="AE473" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF473" t="inlineStr">
@@ -54795,7 +54795,7 @@
       </c>
       <c r="AE474" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF474" t="inlineStr">
@@ -54905,7 +54905,7 @@
       </c>
       <c r="AE475" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF475" t="inlineStr">
@@ -55017,7 +55017,7 @@
       </c>
       <c r="AE476" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF476" t="inlineStr">
@@ -55129,7 +55129,7 @@
       </c>
       <c r="AE477" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF477" t="inlineStr">
@@ -55239,7 +55239,7 @@
       </c>
       <c r="AE478" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF478" t="inlineStr">
@@ -55349,7 +55349,7 @@
       </c>
       <c r="AE479" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF479" t="inlineStr">
@@ -55459,7 +55459,7 @@
       </c>
       <c r="AE480" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF480" t="inlineStr">
@@ -55569,7 +55569,7 @@
       </c>
       <c r="AE481" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF481" t="inlineStr">
@@ -55679,7 +55679,7 @@
       </c>
       <c r="AE482" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF482" t="inlineStr">
@@ -55789,7 +55789,7 @@
       </c>
       <c r="AE483" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF483" t="inlineStr">
@@ -55901,7 +55901,7 @@
       </c>
       <c r="AE484" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF484" t="inlineStr">
@@ -56013,7 +56013,7 @@
       </c>
       <c r="AE485" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF485" t="inlineStr">
@@ -56125,7 +56125,7 @@
       </c>
       <c r="AE486" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF486" t="inlineStr">
@@ -56235,7 +56235,7 @@
       </c>
       <c r="AE487" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF487" t="inlineStr">
@@ -56347,7 +56347,7 @@
       </c>
       <c r="AE488" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF488" t="inlineStr">
@@ -56447,7 +56447,7 @@
       </c>
       <c r="AE489" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF489" t="inlineStr">
@@ -56557,7 +56557,7 @@
       </c>
       <c r="AE490" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF490" t="inlineStr">
@@ -56657,7 +56657,7 @@
       </c>
       <c r="AE491" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF491" t="inlineStr">
@@ -56757,7 +56757,7 @@
       </c>
       <c r="AE492" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF492" t="inlineStr">
@@ -56869,7 +56869,7 @@
       </c>
       <c r="AE493" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF493" t="inlineStr">
@@ -56981,7 +56981,7 @@
       </c>
       <c r="AE494" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF494" t="inlineStr">
@@ -57093,7 +57093,7 @@
       </c>
       <c r="AE495" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF495" t="inlineStr">
@@ -57203,7 +57203,7 @@
       </c>
       <c r="AE496" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF496" t="inlineStr">
@@ -57313,7 +57313,7 @@
       </c>
       <c r="AE497" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF497" t="inlineStr">
@@ -57423,7 +57423,7 @@
       </c>
       <c r="AE498" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF498" t="inlineStr">
@@ -57535,7 +57535,7 @@
       </c>
       <c r="AE499" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF499" t="inlineStr">
@@ -57645,7 +57645,7 @@
       </c>
       <c r="AE500" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF500" t="inlineStr">
@@ -57755,7 +57755,7 @@
       </c>
       <c r="AE501" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF501" t="inlineStr">
@@ -57865,7 +57865,7 @@
       </c>
       <c r="AE502" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF502" t="inlineStr">
@@ -57975,7 +57975,7 @@
       </c>
       <c r="AE503" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF503" t="inlineStr">
@@ -58087,7 +58087,7 @@
       </c>
       <c r="AE504" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF504" t="inlineStr">
@@ -58199,7 +58199,7 @@
       </c>
       <c r="AE505" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF505" t="inlineStr">
@@ -58315,7 +58315,7 @@
       </c>
       <c r="AE506" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF506" t="inlineStr">
@@ -58443,7 +58443,7 @@
       </c>
       <c r="AE507" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="AF507" t="inlineStr">
@@ -58555,7 +58555,7 @@
       </c>
       <c r="AE508" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF508" t="inlineStr">
@@ -58665,7 +58665,7 @@
       </c>
       <c r="AE509" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF509" t="inlineStr">
@@ -58785,7 +58785,7 @@
       </c>
       <c r="AE510" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="AF510" t="inlineStr">
@@ -58895,7 +58895,7 @@
       </c>
       <c r="AE511" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF511" t="inlineStr">
@@ -59005,7 +59005,7 @@
       </c>
       <c r="AE512" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF512" t="inlineStr">
@@ -59115,7 +59115,7 @@
       </c>
       <c r="AE513" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF513" t="inlineStr">
@@ -59235,7 +59235,7 @@
       </c>
       <c r="AE514" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="AF514" t="inlineStr">
@@ -59351,7 +59351,7 @@
       </c>
       <c r="AE515" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF515" t="inlineStr">
@@ -59463,7 +59463,7 @@
       </c>
       <c r="AE516" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF516" t="inlineStr">
@@ -59583,7 +59583,7 @@
       </c>
       <c r="AE517" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="AF517" t="inlineStr">
@@ -59695,7 +59695,7 @@
       </c>
       <c r="AE518" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF518" t="inlineStr">
@@ -59795,7 +59795,7 @@
       </c>
       <c r="AE519" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF519" t="inlineStr">
@@ -59915,7 +59915,7 @@
       </c>
       <c r="AE520" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="AF520" t="inlineStr">
@@ -60025,7 +60025,7 @@
       </c>
       <c r="AE521" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF521" t="inlineStr">
@@ -60137,7 +60137,7 @@
       </c>
       <c r="AE522" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF522" t="inlineStr">
@@ -60253,7 +60253,7 @@
       </c>
       <c r="AE523" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF523" t="inlineStr">
@@ -60365,7 +60365,7 @@
       </c>
       <c r="AE524" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF524" t="inlineStr">
@@ -60477,7 +60477,7 @@
       </c>
       <c r="AE525" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF525" t="inlineStr">
@@ -60605,7 +60605,7 @@
       </c>
       <c r="AE526" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="AF526" t="inlineStr">
@@ -60715,7 +60715,7 @@
       </c>
       <c r="AE527" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF527" t="inlineStr">
@@ -60825,7 +60825,7 @@
       </c>
       <c r="AE528" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF528" t="inlineStr">
@@ -60935,7 +60935,7 @@
       </c>
       <c r="AE529" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF529" t="inlineStr">
@@ -61047,7 +61047,7 @@
       </c>
       <c r="AE530" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF530" t="inlineStr">
@@ -61175,7 +61175,7 @@
       </c>
       <c r="AE531" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="AF531" t="inlineStr">
@@ -61287,7 +61287,7 @@
       </c>
       <c r="AE532" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF532" t="inlineStr">
@@ -61399,7 +61399,7 @@
       </c>
       <c r="AE533" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF533" t="inlineStr">
@@ -61511,7 +61511,7 @@
       </c>
       <c r="AE534" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF534" t="inlineStr">
@@ -61611,7 +61611,7 @@
       </c>
       <c r="AE535" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF535" t="inlineStr">
@@ -61721,7 +61721,7 @@
       </c>
       <c r="AE536" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF536" t="inlineStr">
@@ -61831,7 +61831,7 @@
       </c>
       <c r="AE537" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF537" t="inlineStr">
@@ -61931,7 +61931,7 @@
       </c>
       <c r="AE538" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF538" t="inlineStr">
@@ -62041,7 +62041,7 @@
       </c>
       <c r="AE539" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF539" t="inlineStr">
@@ -62169,7 +62169,7 @@
       </c>
       <c r="AE540" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="AF540" t="inlineStr">
@@ -62279,7 +62279,7 @@
       </c>
       <c r="AE541" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF541" t="inlineStr">
@@ -62391,7 +62391,7 @@
       </c>
       <c r="AE542" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF542" t="inlineStr">
@@ -62501,7 +62501,7 @@
       </c>
       <c r="AE543" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF543" t="inlineStr">
@@ -62613,7 +62613,7 @@
       </c>
       <c r="AE544" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF544" t="inlineStr">
@@ -62723,7 +62723,7 @@
       </c>
       <c r="AE545" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF545" t="inlineStr">
@@ -62833,7 +62833,7 @@
       </c>
       <c r="AE546" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF546" t="inlineStr">
@@ -62933,7 +62933,7 @@
       </c>
       <c r="AE547" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF547" t="inlineStr">
@@ -63043,7 +63043,7 @@
       </c>
       <c r="AE548" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF548" t="inlineStr">
@@ -63155,7 +63155,7 @@
       </c>
       <c r="AE549" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF549" t="inlineStr">
@@ -63265,7 +63265,7 @@
       </c>
       <c r="AE550" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF550" t="inlineStr">
@@ -63375,7 +63375,7 @@
       </c>
       <c r="AE551" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF551" t="inlineStr">
@@ -63485,7 +63485,7 @@
       </c>
       <c r="AE552" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF552" t="inlineStr">
@@ -63595,7 +63595,7 @@
       </c>
       <c r="AE553" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF553" t="inlineStr">
@@ -63705,7 +63705,7 @@
       </c>
       <c r="AE554" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF554" t="inlineStr">
@@ -63815,7 +63815,7 @@
       </c>
       <c r="AE555" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF555" t="inlineStr">
@@ -63915,7 +63915,7 @@
       </c>
       <c r="AE556" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF556" t="inlineStr">
@@ -64025,7 +64025,7 @@
       </c>
       <c r="AE557" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF557" t="inlineStr">
@@ -64135,7 +64135,7 @@
       </c>
       <c r="AE558" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF558" t="inlineStr">
@@ -64247,7 +64247,7 @@
       </c>
       <c r="AE559" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF559" t="inlineStr">
@@ -64357,7 +64357,7 @@
       </c>
       <c r="AE560" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF560" t="inlineStr">
@@ -64469,7 +64469,7 @@
       </c>
       <c r="AE561" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF561" t="inlineStr">
@@ -64579,7 +64579,7 @@
       </c>
       <c r="AE562" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF562" t="inlineStr">
@@ -64689,7 +64689,7 @@
       </c>
       <c r="AE563" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF563" t="inlineStr">
@@ -64799,7 +64799,7 @@
       </c>
       <c r="AE564" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF564" t="inlineStr">
@@ -64909,7 +64909,7 @@
       </c>
       <c r="AE565" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF565" t="inlineStr">
@@ -65019,7 +65019,7 @@
       </c>
       <c r="AE566" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF566" t="inlineStr">
@@ -65131,7 +65131,7 @@
       </c>
       <c r="AE567" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF567" t="inlineStr">
@@ -65241,7 +65241,7 @@
       </c>
       <c r="AE568" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF568" t="inlineStr">
@@ -65353,7 +65353,7 @@
       </c>
       <c r="AE569" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF569" t="inlineStr">
@@ -65465,7 +65465,7 @@
       </c>
       <c r="AE570" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF570" t="inlineStr">
@@ -65575,7 +65575,7 @@
       </c>
       <c r="AE571" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF571" t="inlineStr">
@@ -65687,7 +65687,7 @@
       </c>
       <c r="AE572" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF572" t="inlineStr">
@@ -65799,7 +65799,7 @@
       </c>
       <c r="AE573" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF573" t="inlineStr">
@@ -65909,7 +65909,7 @@
       </c>
       <c r="AE574" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF574" t="inlineStr">
@@ -66019,7 +66019,7 @@
       </c>
       <c r="AE575" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF575" t="inlineStr">
@@ -66129,7 +66129,7 @@
       </c>
       <c r="AE576" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF576" t="inlineStr">
@@ -66239,7 +66239,7 @@
       </c>
       <c r="AE577" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF577" t="inlineStr">
@@ -66339,7 +66339,7 @@
       </c>
       <c r="AE578" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF578" t="inlineStr">
@@ -66451,7 +66451,7 @@
       </c>
       <c r="AE579" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF579" t="inlineStr">
@@ -66561,7 +66561,7 @@
       </c>
       <c r="AE580" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF580" t="inlineStr">
@@ -66671,7 +66671,7 @@
       </c>
       <c r="AE581" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF581" t="inlineStr">
@@ -66799,7 +66799,7 @@
       </c>
       <c r="AE582" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="AF582" t="inlineStr">
@@ -66911,7 +66911,7 @@
       </c>
       <c r="AE583" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF583" t="inlineStr">
@@ -67023,7 +67023,7 @@
       </c>
       <c r="AE584" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF584" t="inlineStr">
@@ -67151,7 +67151,7 @@
       </c>
       <c r="AE585" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="AF585" t="inlineStr">
@@ -67263,7 +67263,7 @@
       </c>
       <c r="AE586" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF586" t="inlineStr">
@@ -67391,7 +67391,7 @@
       </c>
       <c r="AE587" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="AF587" t="inlineStr">
@@ -67519,7 +67519,7 @@
       </c>
       <c r="AE588" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="AF588" t="inlineStr">
@@ -67631,7 +67631,7 @@
       </c>
       <c r="AE589" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF589" t="inlineStr">
@@ -67743,7 +67743,7 @@
       </c>
       <c r="AE590" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF590" t="inlineStr">
@@ -67853,7 +67853,7 @@
       </c>
       <c r="AE591" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF591" t="inlineStr">
@@ -67965,7 +67965,7 @@
       </c>
       <c r="AE592" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF592" t="inlineStr">
@@ -68075,7 +68075,7 @@
       </c>
       <c r="AE593" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF593" t="inlineStr">
@@ -68185,7 +68185,7 @@
       </c>
       <c r="AE594" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF594" t="inlineStr">
@@ -68297,7 +68297,7 @@
       </c>
       <c r="AE595" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF595" t="inlineStr">
@@ -68409,7 +68409,7 @@
       </c>
       <c r="AE596" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF596" t="inlineStr">
@@ -68521,7 +68521,7 @@
       </c>
       <c r="AE597" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF597" t="inlineStr">
@@ -68631,7 +68631,7 @@
       </c>
       <c r="AE598" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF598" t="inlineStr">
@@ -68741,7 +68741,7 @@
       </c>
       <c r="AE599" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF599" t="inlineStr">
@@ -68853,7 +68853,7 @@
       </c>
       <c r="AE600" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF600" t="inlineStr">
@@ -68965,7 +68965,7 @@
       </c>
       <c r="AE601" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF601" t="inlineStr">
@@ -69075,7 +69075,7 @@
       </c>
       <c r="AE602" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF602" t="inlineStr">
@@ -69187,7 +69187,7 @@
       </c>
       <c r="AE603" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF603" t="inlineStr">
@@ -69297,7 +69297,7 @@
       </c>
       <c r="AE604" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF604" t="inlineStr">
@@ -69397,7 +69397,7 @@
       </c>
       <c r="AE605" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF605" t="inlineStr">
@@ -69507,7 +69507,7 @@
       </c>
       <c r="AE606" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF606" t="inlineStr">
@@ -69619,7 +69619,7 @@
       </c>
       <c r="AE607" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF607" t="inlineStr">
@@ -69729,7 +69729,7 @@
       </c>
       <c r="AE608" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF608" t="inlineStr">
@@ -69841,7 +69841,7 @@
       </c>
       <c r="AE609" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF609" t="inlineStr">
@@ -69951,7 +69951,7 @@
       </c>
       <c r="AE610" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF610" t="inlineStr">
@@ -70061,7 +70061,7 @@
       </c>
       <c r="AE611" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF611" t="inlineStr">
@@ -70171,7 +70171,7 @@
       </c>
       <c r="AE612" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF612" t="inlineStr">
@@ -70281,7 +70281,7 @@
       </c>
       <c r="AE613" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF613" t="inlineStr">
@@ -70391,7 +70391,7 @@
       </c>
       <c r="AE614" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF614" t="inlineStr">
@@ -70503,7 +70503,7 @@
       </c>
       <c r="AE615" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF615" t="inlineStr">
@@ -70613,7 +70613,7 @@
       </c>
       <c r="AE616" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF616" t="inlineStr">
@@ -70723,7 +70723,7 @@
       </c>
       <c r="AE617" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF617" t="inlineStr">
@@ -70833,7 +70833,7 @@
       </c>
       <c r="AE618" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF618" t="inlineStr">
@@ -70945,7 +70945,7 @@
       </c>
       <c r="AE619" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF619" t="inlineStr">
@@ -71055,7 +71055,7 @@
       </c>
       <c r="AE620" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF620" t="inlineStr">
@@ -71167,7 +71167,7 @@
       </c>
       <c r="AE621" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF621" t="inlineStr">
@@ -71279,7 +71279,7 @@
       </c>
       <c r="AE622" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF622" t="inlineStr">
@@ -71379,7 +71379,7 @@
       </c>
       <c r="AE623" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF623" t="inlineStr">
@@ -71489,7 +71489,7 @@
       </c>
       <c r="AE624" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF624" t="inlineStr">
@@ -71601,7 +71601,7 @@
       </c>
       <c r="AE625" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF625" t="inlineStr">
@@ -71713,7 +71713,7 @@
       </c>
       <c r="AE626" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF626" t="inlineStr">
@@ -71825,7 +71825,7 @@
       </c>
       <c r="AE627" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF627" t="inlineStr">
@@ -71937,7 +71937,7 @@
       </c>
       <c r="AE628" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF628" t="inlineStr">
@@ -72047,7 +72047,7 @@
       </c>
       <c r="AE629" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF629" t="inlineStr">
@@ -72157,7 +72157,7 @@
       </c>
       <c r="AE630" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF630" t="inlineStr">
@@ -72269,7 +72269,7 @@
       </c>
       <c r="AE631" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF631" t="inlineStr">
@@ -72379,7 +72379,7 @@
       </c>
       <c r="AE632" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF632" t="inlineStr">
@@ -72491,7 +72491,7 @@
       </c>
       <c r="AE633" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF633" t="inlineStr">
@@ -72591,7 +72591,7 @@
       </c>
       <c r="AE634" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF634" t="inlineStr">
@@ -72701,7 +72701,7 @@
       </c>
       <c r="AE635" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF635" t="inlineStr">
@@ -72813,7 +72813,7 @@
       </c>
       <c r="AE636" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF636" t="inlineStr">
@@ -72923,7 +72923,7 @@
       <c r="AD637" t="inlineStr"/>
       <c r="AE637" t="inlineStr">
         <is>
-          <t>2026-09-18 09:23:05</t>
+          <t>2026-09-18 13:07:17</t>
         </is>
       </c>
       <c r="AF637" t="inlineStr">
@@ -73035,7 +73035,7 @@
       </c>
       <c r="AE638" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF638" t="inlineStr">
@@ -73147,7 +73147,7 @@
       </c>
       <c r="AE639" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF639" t="inlineStr">
@@ -73257,7 +73257,7 @@
       </c>
       <c r="AE640" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF640" t="inlineStr">
@@ -73369,7 +73369,7 @@
       </c>
       <c r="AE641" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF641" t="inlineStr">
@@ -73469,7 +73469,7 @@
       </c>
       <c r="AE642" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF642" t="inlineStr">
@@ -73569,7 +73569,7 @@
       </c>
       <c r="AE643" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF643" t="inlineStr">
@@ -73669,7 +73669,7 @@
       </c>
       <c r="AE644" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF644" t="inlineStr">
@@ -73781,7 +73781,7 @@
       </c>
       <c r="AE645" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF645" t="inlineStr">
@@ -73881,7 +73881,7 @@
       </c>
       <c r="AE646" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF646" t="inlineStr">
@@ -73991,7 +73991,7 @@
       </c>
       <c r="AE647" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF647" t="inlineStr">
@@ -74091,7 +74091,7 @@
       </c>
       <c r="AE648" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF648" t="inlineStr">
@@ -74203,7 +74203,7 @@
       </c>
       <c r="AE649" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF649" t="inlineStr">
@@ -74315,7 +74315,7 @@
       </c>
       <c r="AE650" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF650" t="inlineStr">
@@ -74427,7 +74427,7 @@
       </c>
       <c r="AE651" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF651" t="inlineStr">
@@ -74539,7 +74539,7 @@
       </c>
       <c r="AE652" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF652" t="inlineStr">
@@ -74639,7 +74639,7 @@
       </c>
       <c r="AE653" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF653" t="inlineStr">
@@ -74751,7 +74751,7 @@
       </c>
       <c r="AE654" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF654" t="inlineStr">
@@ -74861,7 +74861,7 @@
       </c>
       <c r="AE655" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF655" t="inlineStr">
@@ -74973,7 +74973,7 @@
       </c>
       <c r="AE656" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF656" t="inlineStr">
@@ -75073,7 +75073,7 @@
       </c>
       <c r="AE657" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF657" t="inlineStr">
@@ -75173,7 +75173,7 @@
       </c>
       <c r="AE658" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF658" t="inlineStr">
@@ -75273,7 +75273,7 @@
       </c>
       <c r="AE659" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF659" t="inlineStr">
@@ -75373,7 +75373,7 @@
       </c>
       <c r="AE660" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF660" t="inlineStr">
@@ -75485,7 +75485,7 @@
       </c>
       <c r="AE661" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF661" t="inlineStr">
@@ -75597,7 +75597,7 @@
       </c>
       <c r="AE662" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF662" t="inlineStr">
@@ -75697,7 +75697,7 @@
       </c>
       <c r="AE663" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF663" t="inlineStr">
@@ -75807,7 +75807,7 @@
       </c>
       <c r="AE664" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF664" t="inlineStr">
@@ -75919,7 +75919,7 @@
       </c>
       <c r="AE665" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF665" t="inlineStr">
@@ -76031,7 +76031,7 @@
       </c>
       <c r="AE666" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF666" t="inlineStr">
@@ -76143,7 +76143,7 @@
       </c>
       <c r="AE667" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF667" t="inlineStr">
@@ -76255,7 +76255,7 @@
       </c>
       <c r="AE668" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF668" t="inlineStr">
@@ -76367,7 +76367,7 @@
       </c>
       <c r="AE669" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF669" t="inlineStr">
@@ -76479,7 +76479,7 @@
       </c>
       <c r="AE670" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF670" t="inlineStr">
@@ -76591,7 +76591,7 @@
       </c>
       <c r="AE671" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF671" t="inlineStr">
@@ -76691,7 +76691,7 @@
       </c>
       <c r="AE672" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF672" t="inlineStr">
@@ -76791,7 +76791,7 @@
       </c>
       <c r="AE673" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF673" t="inlineStr">
@@ -76903,7 +76903,7 @@
       </c>
       <c r="AE674" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:35</t>
+          <t>2026-09-18 13:06:42</t>
         </is>
       </c>
       <c r="AF674" t="inlineStr">
@@ -77003,7 +77003,7 @@
       </c>
       <c r="AE675" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF675" t="inlineStr">
@@ -77103,7 +77103,7 @@
       </c>
       <c r="AE676" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF676" t="inlineStr">
@@ -77203,7 +77203,7 @@
       </c>
       <c r="AE677" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF677" t="inlineStr">
@@ -77313,7 +77313,7 @@
       </c>
       <c r="AE678" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF678" t="inlineStr">
@@ -77413,7 +77413,7 @@
       </c>
       <c r="AE679" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF679" t="inlineStr">
@@ -77523,7 +77523,7 @@
       </c>
       <c r="AE680" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF680" t="inlineStr">
@@ -77605,7 +77605,7 @@
       <c r="AD681" t="inlineStr"/>
       <c r="AE681" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF681" t="inlineStr">
@@ -77687,7 +77687,7 @@
       <c r="AD682" t="inlineStr"/>
       <c r="AE682" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF682" t="inlineStr">
@@ -77769,7 +77769,7 @@
       <c r="AD683" t="inlineStr"/>
       <c r="AE683" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF683" t="inlineStr">
@@ -77851,7 +77851,7 @@
       <c r="AD684" t="inlineStr"/>
       <c r="AE684" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="AF684" t="inlineStr">
